--- a/Shortage.xlsx
+++ b/Shortage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\MR1\PPGS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A148FC52-1C8A-4B38-B008-6319899A66B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F5AA64E-EB66-461C-9B2A-A0C60F6F68C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1147" uniqueCount="75">
   <si>
     <t>sl.no.</t>
   </si>
@@ -755,7 +755,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="103">
+  <dxfs count="211">
     <dxf>
       <fill>
         <patternFill>
@@ -774,6 +774,1068 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -18236,134 +19298,134 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="K126">
-    <cfRule type="duplicateValues" dxfId="102" priority="748"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="748"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K6 K24">
-    <cfRule type="duplicateValues" dxfId="101" priority="749"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="749"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7:K23">
-    <cfRule type="duplicateValues" dxfId="100" priority="751"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="751"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K126 K6:K24">
-    <cfRule type="duplicateValues" dxfId="99" priority="752"/>
-    <cfRule type="duplicateValues" dxfId="98" priority="753"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="752"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="753"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25:K31 K54:K57">
-    <cfRule type="duplicateValues" dxfId="97" priority="756"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="756"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25:K31 K54:K57">
-    <cfRule type="duplicateValues" dxfId="96" priority="758"/>
-    <cfRule type="duplicateValues" dxfId="95" priority="759"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="758"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="759"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27:K53">
-    <cfRule type="duplicateValues" dxfId="94" priority="762"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="762"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27:K53">
-    <cfRule type="duplicateValues" dxfId="93" priority="763"/>
-    <cfRule type="duplicateValues" dxfId="92" priority="764"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="763"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="764"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K126 K6:K57">
-    <cfRule type="duplicateValues" dxfId="91" priority="765"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="765"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K58:K62 K72:K75">
-    <cfRule type="duplicateValues" dxfId="90" priority="767"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="767"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K58:K62 K72:K75">
-    <cfRule type="duplicateValues" dxfId="89" priority="769"/>
-    <cfRule type="duplicateValues" dxfId="88" priority="770"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="769"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="770"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K58:K62">
-    <cfRule type="duplicateValues" dxfId="87" priority="773"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="773"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K126 K5:K62 K72:K75">
-    <cfRule type="duplicateValues" dxfId="86" priority="774"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="774"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K63:K71">
-    <cfRule type="duplicateValues" dxfId="85" priority="777"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="777"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K63:K71">
-    <cfRule type="duplicateValues" dxfId="84" priority="778"/>
-    <cfRule type="duplicateValues" dxfId="83" priority="779"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="778"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="779"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K126 K5:K75">
-    <cfRule type="duplicateValues" dxfId="82" priority="780"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="780"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K76:K79 K90:K92 K116">
-    <cfRule type="duplicateValues" dxfId="81" priority="782"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="782"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K76:K79 K90:K92 K116">
-    <cfRule type="duplicateValues" dxfId="80" priority="785"/>
-    <cfRule type="duplicateValues" dxfId="79" priority="786"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="785"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="786"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K76:K79">
-    <cfRule type="duplicateValues" dxfId="78" priority="791"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="791"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K80:K89">
-    <cfRule type="duplicateValues" dxfId="77" priority="792"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="792"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K80:K89">
-    <cfRule type="duplicateValues" dxfId="76" priority="793"/>
-    <cfRule type="duplicateValues" dxfId="75" priority="794"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="793"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="794"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K126:K127 K5:K92 K116">
-    <cfRule type="duplicateValues" dxfId="74" priority="795"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="795"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K99:K113 K115">
-    <cfRule type="duplicateValues" dxfId="73" priority="798"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="798"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K99:K113 K115">
-    <cfRule type="duplicateValues" dxfId="72" priority="800"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="801"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="800"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="801"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K93:K98">
-    <cfRule type="duplicateValues" dxfId="70" priority="804"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="804"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K93:K98">
-    <cfRule type="duplicateValues" dxfId="69" priority="805"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="806"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="805"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="806"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K126:K127 K5:K113 K115:K116">
-    <cfRule type="duplicateValues" dxfId="67" priority="807"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="807"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K114">
-    <cfRule type="duplicateValues" dxfId="66" priority="810"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="810"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K114">
-    <cfRule type="duplicateValues" dxfId="65" priority="811"/>
-    <cfRule type="duplicateValues" dxfId="64" priority="812"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="811"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="812"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K126:K127 K5:K116">
-    <cfRule type="duplicateValues" dxfId="63" priority="813"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="813"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K117:K123 K125">
-    <cfRule type="duplicateValues" dxfId="62" priority="844"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="844"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K117:K123 K125">
-    <cfRule type="duplicateValues" dxfId="61" priority="846"/>
-    <cfRule type="duplicateValues" dxfId="60" priority="847"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="846"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="847"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5:K123 K125:K127">
-    <cfRule type="duplicateValues" dxfId="59" priority="850"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="850"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K124">
-    <cfRule type="duplicateValues" dxfId="58" priority="852"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="852"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K124">
-    <cfRule type="duplicateValues" dxfId="57" priority="853"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="854"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="853"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="854"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5:K127">
-    <cfRule type="duplicateValues" dxfId="55" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="855"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="855"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB6:BB126">
-    <cfRule type="expression" dxfId="53" priority="1019">
+    <cfRule type="expression" dxfId="56" priority="1019">
       <formula>$AC6&lt;&gt;""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="52" priority="1020">
+    <cfRule type="expression" dxfId="55" priority="1020">
       <formula>$AB6&lt;&gt;""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="51" priority="1021">
+    <cfRule type="expression" dxfId="54" priority="1021">
       <formula>$T6&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24228,16 +25290,16 @@
       <c r="V49" s="46"/>
       <c r="W49" s="46"/>
       <c r="X49" s="46">
-        <v>3817.2</v>
+        <v>3735.4</v>
       </c>
       <c r="Y49" s="46"/>
       <c r="Z49" s="46">
         <f>+T49-X49</f>
-        <v>0</v>
+        <v>81.799999999999727</v>
       </c>
       <c r="AA49" s="39">
         <f>Z49/T49</f>
-        <v>0</v>
+        <v>2.1429319920360405E-2</v>
       </c>
       <c r="AB49" s="73">
         <v>3817.2</v>
@@ -24284,16 +25346,16 @@
       </c>
       <c r="BC49" s="45">
         <f>+X49</f>
-        <v>3817.2</v>
+        <v>3735.4</v>
       </c>
       <c r="BD49" s="45"/>
       <c r="BE49" s="45">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>81.799999999999727</v>
       </c>
       <c r="BF49" s="39">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2.1429319920360405E-2</v>
       </c>
     </row>
     <row r="50" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -24486,16 +25548,16 @@
       <c r="V51" s="46"/>
       <c r="W51" s="46"/>
       <c r="X51" s="46">
-        <v>3909.2</v>
+        <v>3955.2</v>
       </c>
       <c r="Y51" s="46"/>
       <c r="Z51" s="46">
         <f>+T51-X51</f>
-        <v>0</v>
+        <v>-46</v>
       </c>
       <c r="AA51" s="39">
         <f>Z51/T51</f>
-        <v>0</v>
+        <v>-1.1767113475902998E-2</v>
       </c>
       <c r="AB51" s="73">
         <v>3909.2</v>
@@ -24542,16 +25604,16 @@
       </c>
       <c r="BC51" s="45">
         <f>+X51</f>
-        <v>3909.2</v>
+        <v>3955.2</v>
       </c>
       <c r="BD51" s="45"/>
       <c r="BE51" s="45">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-46</v>
       </c>
       <c r="BF51" s="39">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-1.1767113475902998E-2</v>
       </c>
     </row>
     <row r="52" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -24744,16 +25806,16 @@
       <c r="V53" s="46"/>
       <c r="W53" s="46"/>
       <c r="X53" s="46">
-        <v>3496.1</v>
+        <v>3541.8</v>
       </c>
       <c r="Y53" s="46"/>
       <c r="Z53" s="46">
         <f>+T53-X53</f>
-        <v>0</v>
+        <v>-45.700000000000273</v>
       </c>
       <c r="AA53" s="39">
         <f>Z53/T53</f>
-        <v>0</v>
+        <v>-1.3071708475158112E-2</v>
       </c>
       <c r="AB53" s="73">
         <v>3516.31</v>
@@ -24800,16 +25862,16 @@
       </c>
       <c r="BC53" s="45">
         <f>+X53</f>
-        <v>3496.1</v>
+        <v>3541.8</v>
       </c>
       <c r="BD53" s="45"/>
       <c r="BE53" s="45">
         <f t="shared" si="5"/>
-        <v>20.210000000000036</v>
+        <v>-25.490000000000236</v>
       </c>
       <c r="BF53" s="39">
         <f t="shared" si="6"/>
-        <v>5.7475023533192574E-3</v>
+        <v>-7.2490764466159804E-3</v>
       </c>
     </row>
     <row r="54" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -27648,51 +28710,51 @@
         <v>8.8856445238753821E-3</v>
       </c>
     </row>
-    <row r="76" spans="1:58" s="91" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="76">
+    <row r="76" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A76" s="21">
         <f>IF(ISBLANK(F76),"",COUNTA($F$6:F76))</f>
         <v>71</v>
       </c>
-      <c r="B76" s="77" t="s">
+      <c r="B76" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="C76" s="77" t="s">
+      <c r="C76" s="37" t="s">
         <v>61</v>
       </c>
-      <c r="D76" s="78"/>
-      <c r="E76" s="79" t="s">
+      <c r="D76" s="22"/>
+      <c r="E76" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="F76" s="80">
+      <c r="F76" s="36">
         <v>46248</v>
       </c>
-      <c r="G76" s="81" t="s">
+      <c r="G76" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="H76" s="81">
+      <c r="H76" s="24">
         <v>58</v>
       </c>
-      <c r="I76" s="81">
+      <c r="I76" s="24">
         <v>4</v>
       </c>
-      <c r="J76" s="81" t="s">
+      <c r="J76" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="K76" s="82">
+      <c r="K76" s="25">
         <v>162011713</v>
       </c>
-      <c r="L76" s="83">
+      <c r="L76" s="26">
         <v>46249</v>
       </c>
-      <c r="M76" s="84">
+      <c r="M76" s="38">
         <v>46251</v>
       </c>
-      <c r="N76" s="85">
+      <c r="N76" s="52">
         <v>16582</v>
       </c>
-      <c r="O76" s="86"/>
-      <c r="P76" s="86"/>
-      <c r="Q76" s="86"/>
+      <c r="O76" s="27"/>
+      <c r="P76" s="27"/>
+      <c r="Q76" s="27"/>
       <c r="R76" s="46">
         <v>4861.51</v>
       </c>
@@ -27709,16 +28771,16 @@
       <c r="V76" s="46"/>
       <c r="W76" s="46"/>
       <c r="X76" s="46">
-        <v>3728.9</v>
+        <v>3521.4</v>
       </c>
       <c r="Y76" s="46"/>
       <c r="Z76" s="46">
         <f>+T76-X76</f>
-        <v>0</v>
+        <v>207.5</v>
       </c>
       <c r="AA76" s="39">
         <f>Z76/T76</f>
-        <v>0</v>
+        <v>5.5646437287135614E-2</v>
       </c>
       <c r="AB76" s="73">
         <v>3872.5</v>
@@ -27733,48 +28795,48 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AJ76" s="87"/>
-      <c r="AK76" s="87"/>
-      <c r="AL76" s="87"/>
-      <c r="AM76" s="88"/>
-      <c r="AN76" s="88"/>
-      <c r="AO76" s="88"/>
-      <c r="AP76" s="89">
+      <c r="AJ76" s="32"/>
+      <c r="AK76" s="32"/>
+      <c r="AL76" s="32"/>
+      <c r="AM76" s="33"/>
+      <c r="AN76" s="33"/>
+      <c r="AO76" s="33"/>
+      <c r="AP76" s="34">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AQ76" s="87">
+      <c r="AQ76" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR76" s="87">
+      <c r="AR76" s="32">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AS76" s="87"/>
-      <c r="AT76" s="87"/>
-      <c r="AU76" s="87"/>
-      <c r="AV76" s="87"/>
-      <c r="AW76" s="87"/>
-      <c r="AX76" s="87"/>
-      <c r="AY76" s="87"/>
-      <c r="AZ76" s="90"/>
-      <c r="BB76" s="92">
+      <c r="AS76" s="32"/>
+      <c r="AT76" s="32"/>
+      <c r="AU76" s="32"/>
+      <c r="AV76" s="32"/>
+      <c r="AW76" s="32"/>
+      <c r="AX76" s="32"/>
+      <c r="AY76" s="32"/>
+      <c r="AZ76" s="35"/>
+      <c r="BB76" s="45">
         <f>IF(AND(AB76="",AC76=""),T76,IF(AC76="",AB76,AC76))</f>
         <v>3872.5</v>
       </c>
-      <c r="BC76" s="92">
+      <c r="BC76" s="45">
         <f>+X76</f>
-        <v>3728.9</v>
-      </c>
-      <c r="BD76" s="92"/>
-      <c r="BE76" s="92">
+        <v>3521.4</v>
+      </c>
+      <c r="BD76" s="45"/>
+      <c r="BE76" s="45">
         <f t="shared" si="5"/>
-        <v>143.59999999999991</v>
+        <v>351.09999999999991</v>
       </c>
       <c r="BF76" s="39">
         <f t="shared" si="6"/>
-        <v>3.7081988379599716E-2</v>
+        <v>9.0664945125887644E-2</v>
       </c>
     </row>
     <row r="77" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -27906,51 +28968,51 @@
         <v>5.9604443240314281E-3</v>
       </c>
     </row>
-    <row r="78" spans="1:58" s="91" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A78" s="76">
+    <row r="78" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A78" s="21">
         <f>IF(ISBLANK(F78),"",COUNTA($F$6:F78))</f>
         <v>73</v>
       </c>
-      <c r="B78" s="77" t="s">
+      <c r="B78" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="C78" s="77" t="s">
+      <c r="C78" s="37" t="s">
         <v>61</v>
       </c>
-      <c r="D78" s="78"/>
-      <c r="E78" s="79" t="s">
+      <c r="D78" s="22"/>
+      <c r="E78" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="F78" s="80">
+      <c r="F78" s="36">
         <v>46249</v>
       </c>
-      <c r="G78" s="81" t="s">
+      <c r="G78" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="H78" s="81">
+      <c r="H78" s="24">
         <v>58</v>
       </c>
-      <c r="I78" s="81">
+      <c r="I78" s="24">
         <v>1</v>
       </c>
-      <c r="J78" s="81" t="s">
+      <c r="J78" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="K78" s="82">
+      <c r="K78" s="25">
         <v>162006441</v>
       </c>
-      <c r="L78" s="83">
+      <c r="L78" s="26">
         <v>46249</v>
       </c>
-      <c r="M78" s="84">
+      <c r="M78" s="38">
         <v>46251</v>
       </c>
-      <c r="N78" s="85">
+      <c r="N78" s="52">
         <v>16578</v>
       </c>
-      <c r="O78" s="86"/>
-      <c r="P78" s="86"/>
-      <c r="Q78" s="86"/>
+      <c r="O78" s="27"/>
+      <c r="P78" s="27"/>
+      <c r="Q78" s="27"/>
       <c r="R78" s="46">
         <v>5113.3100000000004</v>
       </c>
@@ -27967,16 +29029,16 @@
       <c r="V78" s="46"/>
       <c r="W78" s="46"/>
       <c r="X78" s="46">
-        <v>3915.7</v>
+        <v>3803.6</v>
       </c>
       <c r="Y78" s="46"/>
       <c r="Z78" s="46">
         <f>+T78-X78</f>
-        <v>0</v>
+        <v>112.09999999999991</v>
       </c>
       <c r="AA78" s="39">
         <f>Z78/T78</f>
-        <v>0</v>
+        <v>2.8628342314273289E-2</v>
       </c>
       <c r="AB78" s="73">
         <v>3915.7</v>
@@ -27991,95 +29053,95 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AJ78" s="87"/>
-      <c r="AK78" s="87"/>
-      <c r="AL78" s="87"/>
-      <c r="AM78" s="88"/>
-      <c r="AN78" s="88"/>
-      <c r="AO78" s="88"/>
-      <c r="AP78" s="89">
+      <c r="AJ78" s="32"/>
+      <c r="AK78" s="32"/>
+      <c r="AL78" s="32"/>
+      <c r="AM78" s="33"/>
+      <c r="AN78" s="33"/>
+      <c r="AO78" s="33"/>
+      <c r="AP78" s="34">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AQ78" s="87">
+      <c r="AQ78" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR78" s="87">
+      <c r="AR78" s="32">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AS78" s="87"/>
-      <c r="AT78" s="87"/>
-      <c r="AU78" s="87"/>
-      <c r="AV78" s="87"/>
-      <c r="AW78" s="87"/>
-      <c r="AX78" s="87"/>
-      <c r="AY78" s="87"/>
-      <c r="AZ78" s="90"/>
-      <c r="BB78" s="92">
+      <c r="AS78" s="32"/>
+      <c r="AT78" s="32"/>
+      <c r="AU78" s="32"/>
+      <c r="AV78" s="32"/>
+      <c r="AW78" s="32"/>
+      <c r="AX78" s="32"/>
+      <c r="AY78" s="32"/>
+      <c r="AZ78" s="35"/>
+      <c r="BB78" s="45">
         <f>IF(AND(AB78="",AC78=""),T78,IF(AC78="",AB78,AC78))</f>
         <v>3915.7</v>
       </c>
-      <c r="BC78" s="92">
+      <c r="BC78" s="45">
         <f>+X78</f>
-        <v>3915.7</v>
-      </c>
-      <c r="BD78" s="92"/>
-      <c r="BE78" s="92">
+        <v>3803.6</v>
+      </c>
+      <c r="BD78" s="45"/>
+      <c r="BE78" s="45">
         <f t="shared" ref="BE78:BE87" si="47">+BB78-BC78</f>
-        <v>0</v>
+        <v>112.09999999999991</v>
       </c>
       <c r="BF78" s="39">
         <f t="shared" ref="BF78:BF87" si="48">+BE78/BB78</f>
-        <v>0</v>
+        <v>2.8628342314273289E-2</v>
       </c>
     </row>
-    <row r="79" spans="1:58" s="91" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="76">
+    <row r="79" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A79" s="21">
         <f>IF(ISBLANK(F79),"",COUNTA($F$6:F79))</f>
         <v>74</v>
       </c>
-      <c r="B79" s="77" t="s">
+      <c r="B79" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="C79" s="77" t="s">
+      <c r="C79" s="37" t="s">
         <v>61</v>
       </c>
-      <c r="D79" s="78"/>
-      <c r="E79" s="79" t="s">
+      <c r="D79" s="22"/>
+      <c r="E79" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="F79" s="80">
+      <c r="F79" s="36">
         <v>46249</v>
       </c>
-      <c r="G79" s="81" t="s">
+      <c r="G79" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="H79" s="81">
+      <c r="H79" s="24">
         <v>58</v>
       </c>
-      <c r="I79" s="81">
+      <c r="I79" s="24">
         <v>2</v>
       </c>
-      <c r="J79" s="81" t="s">
+      <c r="J79" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="K79" s="82">
+      <c r="K79" s="25">
         <v>162011715</v>
       </c>
-      <c r="L79" s="83">
+      <c r="L79" s="26">
         <v>46249</v>
       </c>
-      <c r="M79" s="84">
+      <c r="M79" s="38">
         <v>46251</v>
       </c>
-      <c r="N79" s="85">
+      <c r="N79" s="52">
         <v>16580</v>
       </c>
-      <c r="O79" s="86"/>
-      <c r="P79" s="86"/>
-      <c r="Q79" s="86"/>
+      <c r="O79" s="27"/>
+      <c r="P79" s="27"/>
+      <c r="Q79" s="27"/>
       <c r="R79" s="46">
         <v>4967.6000000000004</v>
       </c>
@@ -28096,16 +29158,16 @@
       <c r="V79" s="46"/>
       <c r="W79" s="46"/>
       <c r="X79" s="46">
-        <v>3795</v>
+        <v>3901</v>
       </c>
       <c r="Y79" s="46"/>
       <c r="Z79" s="46">
         <f>+T79-X79</f>
-        <v>0</v>
+        <v>-106</v>
       </c>
       <c r="AA79" s="39">
         <f>Z79/T79</f>
-        <v>0</v>
+        <v>-2.7931488801054019E-2</v>
       </c>
       <c r="AB79" s="73">
         <v>3803.66</v>
@@ -28120,95 +29182,95 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AJ79" s="87"/>
-      <c r="AK79" s="87"/>
-      <c r="AL79" s="87"/>
-      <c r="AM79" s="88"/>
-      <c r="AN79" s="88"/>
-      <c r="AO79" s="88"/>
-      <c r="AP79" s="89">
+      <c r="AJ79" s="32"/>
+      <c r="AK79" s="32"/>
+      <c r="AL79" s="32"/>
+      <c r="AM79" s="33"/>
+      <c r="AN79" s="33"/>
+      <c r="AO79" s="33"/>
+      <c r="AP79" s="34">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AQ79" s="87">
+      <c r="AQ79" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR79" s="87">
+      <c r="AR79" s="32">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AS79" s="87"/>
-      <c r="AT79" s="87"/>
-      <c r="AU79" s="87"/>
-      <c r="AV79" s="87"/>
-      <c r="AW79" s="87"/>
-      <c r="AX79" s="87"/>
-      <c r="AY79" s="87"/>
-      <c r="AZ79" s="90"/>
-      <c r="BB79" s="92">
+      <c r="AS79" s="32"/>
+      <c r="AT79" s="32"/>
+      <c r="AU79" s="32"/>
+      <c r="AV79" s="32"/>
+      <c r="AW79" s="32"/>
+      <c r="AX79" s="32"/>
+      <c r="AY79" s="32"/>
+      <c r="AZ79" s="35"/>
+      <c r="BB79" s="45">
         <f>IF(AND(AB79="",AC79=""),T79,IF(AC79="",AB79,AC79))</f>
         <v>3803.66</v>
       </c>
-      <c r="BC79" s="92">
+      <c r="BC79" s="45">
         <f>+X79</f>
-        <v>3795</v>
-      </c>
-      <c r="BD79" s="92"/>
-      <c r="BE79" s="92">
+        <v>3901</v>
+      </c>
+      <c r="BD79" s="45"/>
+      <c r="BE79" s="45">
         <f t="shared" si="47"/>
-        <v>8.6599999999998545</v>
+        <v>-97.340000000000146</v>
       </c>
       <c r="BF79" s="39">
         <f t="shared" si="48"/>
-        <v>2.2767544943553984E-3</v>
+        <v>-2.5591141164036782E-2</v>
       </c>
     </row>
-    <row r="80" spans="1:58" s="91" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="76">
+    <row r="80" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A80" s="21">
         <f>IF(ISBLANK(F80),"",COUNTA($F$6:F80))</f>
         <v>75</v>
       </c>
-      <c r="B80" s="77" t="s">
+      <c r="B80" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="C80" s="77" t="s">
+      <c r="C80" s="37" t="s">
         <v>61</v>
       </c>
-      <c r="D80" s="78"/>
-      <c r="E80" s="79" t="s">
+      <c r="D80" s="22"/>
+      <c r="E80" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="F80" s="80">
+      <c r="F80" s="36">
         <v>46249</v>
       </c>
-      <c r="G80" s="81" t="s">
+      <c r="G80" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="H80" s="81">
+      <c r="H80" s="24">
         <v>58</v>
       </c>
-      <c r="I80" s="81">
+      <c r="I80" s="24">
         <v>1</v>
       </c>
-      <c r="J80" s="81" t="s">
+      <c r="J80" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="K80" s="82">
+      <c r="K80" s="25">
         <v>162004402</v>
       </c>
-      <c r="L80" s="83">
+      <c r="L80" s="26">
         <v>46249</v>
       </c>
-      <c r="M80" s="84">
+      <c r="M80" s="38">
         <v>46251</v>
       </c>
-      <c r="N80" s="85">
+      <c r="N80" s="52">
         <v>16581</v>
       </c>
-      <c r="O80" s="86"/>
-      <c r="P80" s="86"/>
-      <c r="Q80" s="86"/>
+      <c r="O80" s="27"/>
+      <c r="P80" s="27"/>
+      <c r="Q80" s="27"/>
       <c r="R80" s="46">
         <v>5097.8</v>
       </c>
@@ -28225,16 +29287,16 @@
       <c r="V80" s="46"/>
       <c r="W80" s="46"/>
       <c r="X80" s="46">
-        <v>3906</v>
+        <v>4083.6</v>
       </c>
       <c r="Y80" s="46"/>
       <c r="Z80" s="46">
         <f>+T80-X80</f>
-        <v>0</v>
+        <v>-177.59999999999991</v>
       </c>
       <c r="AA80" s="39">
         <f>Z80/T80</f>
-        <v>0</v>
+        <v>-4.5468509984638993E-2</v>
       </c>
       <c r="AB80" s="73">
         <v>3905.95</v>
@@ -28249,591 +29311,663 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AJ80" s="87"/>
-      <c r="AK80" s="87"/>
-      <c r="AL80" s="87"/>
-      <c r="AM80" s="88"/>
-      <c r="AN80" s="88"/>
-      <c r="AO80" s="88"/>
-      <c r="AP80" s="89">
+      <c r="AJ80" s="32"/>
+      <c r="AK80" s="32"/>
+      <c r="AL80" s="32"/>
+      <c r="AM80" s="33"/>
+      <c r="AN80" s="33"/>
+      <c r="AO80" s="33"/>
+      <c r="AP80" s="34">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AQ80" s="87">
+      <c r="AQ80" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR80" s="87">
+      <c r="AR80" s="32">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AS80" s="87"/>
-      <c r="AT80" s="87"/>
-      <c r="AU80" s="87"/>
-      <c r="AV80" s="87"/>
-      <c r="AW80" s="87"/>
-      <c r="AX80" s="87"/>
-      <c r="AY80" s="87"/>
-      <c r="AZ80" s="90"/>
-      <c r="BB80" s="92">
+      <c r="AS80" s="32"/>
+      <c r="AT80" s="32"/>
+      <c r="AU80" s="32"/>
+      <c r="AV80" s="32"/>
+      <c r="AW80" s="32"/>
+      <c r="AX80" s="32"/>
+      <c r="AY80" s="32"/>
+      <c r="AZ80" s="35"/>
+      <c r="BB80" s="45">
         <f>IF(AND(AB80="",AC80=""),T80,IF(AC80="",AB80,AC80))</f>
         <v>3905.95</v>
       </c>
-      <c r="BC80" s="92">
+      <c r="BC80" s="45">
         <f>+X80</f>
-        <v>3906</v>
-      </c>
-      <c r="BD80" s="92"/>
-      <c r="BE80" s="92">
+        <v>4083.6</v>
+      </c>
+      <c r="BD80" s="45"/>
+      <c r="BE80" s="45">
         <f t="shared" si="47"/>
-        <v>-5.0000000000181899E-2</v>
+        <v>-177.65000000000009</v>
       </c>
       <c r="BF80" s="39">
         <f t="shared" si="48"/>
-        <v>-1.2800983115549841E-5</v>
+        <v>-4.5481893009383149E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A81" s="53">
+    <row r="81" spans="1:58" s="91" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A81" s="76">
         <f>IF(ISBLANK(F81),"",COUNTA($F$6:F81))</f>
         <v>76</v>
       </c>
-      <c r="B81" s="54" t="s">
+      <c r="B81" s="77" t="s">
         <v>60</v>
       </c>
-      <c r="C81" s="54" t="s">
+      <c r="C81" s="77" t="s">
         <v>61</v>
       </c>
-      <c r="D81" s="55"/>
-      <c r="E81" s="56" t="s">
+      <c r="D81" s="78"/>
+      <c r="E81" s="79" t="s">
         <v>64</v>
       </c>
-      <c r="F81" s="57">
+      <c r="F81" s="80">
         <v>46250</v>
       </c>
-      <c r="G81" s="58" t="s">
+      <c r="G81" s="81" t="s">
         <v>59</v>
       </c>
-      <c r="H81" s="58">
+      <c r="H81" s="81">
         <v>59</v>
       </c>
-      <c r="I81" s="58">
+      <c r="I81" s="81">
         <v>3</v>
       </c>
-      <c r="J81" s="58" t="s">
+      <c r="J81" s="81" t="s">
         <v>64</v>
       </c>
-      <c r="K81" s="59">
+      <c r="K81" s="82">
         <v>162004403</v>
       </c>
-      <c r="L81" s="60">
+      <c r="L81" s="83">
         <v>46250</v>
       </c>
-      <c r="M81" s="61"/>
-      <c r="N81" s="62"/>
-      <c r="O81" s="63"/>
-      <c r="P81" s="63"/>
-      <c r="Q81" s="63"/>
-      <c r="R81" s="64"/>
-      <c r="S81" s="64"/>
-      <c r="T81" s="64">
+      <c r="M81" s="84">
+        <v>46252</v>
+      </c>
+      <c r="N81" s="85">
+        <v>16583</v>
+      </c>
+      <c r="O81" s="86"/>
+      <c r="P81" s="86"/>
+      <c r="Q81" s="86"/>
+      <c r="R81" s="46">
+        <v>5055.07</v>
+      </c>
+      <c r="S81" s="46">
+        <v>1175.7699999999995</v>
+      </c>
+      <c r="T81" s="46">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="U81" s="64"/>
-      <c r="V81" s="64"/>
-      <c r="W81" s="64"/>
-      <c r="X81" s="64"/>
-      <c r="Y81" s="64"/>
-      <c r="Z81" s="64">
+        <v>3879.3</v>
+      </c>
+      <c r="U81" s="46">
+        <v>3899.8</v>
+      </c>
+      <c r="V81" s="46"/>
+      <c r="W81" s="46"/>
+      <c r="X81" s="46">
+        <v>3891</v>
+      </c>
+      <c r="Y81" s="46"/>
+      <c r="Z81" s="46">
         <f>+T81-X81</f>
-        <v>0</v>
-      </c>
-      <c r="AA81" s="65" t="e">
+        <v>-11.699999999999818</v>
+      </c>
+      <c r="AA81" s="39">
         <f>Z81/T81</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB81" s="66"/>
-      <c r="AC81" s="66"/>
-      <c r="AD81" s="66"/>
-      <c r="AE81" s="65"/>
-      <c r="AF81" s="67"/>
-      <c r="AG81" s="67"/>
-      <c r="AH81" s="68"/>
-      <c r="AI81" s="68">
+        <v>-3.0160080426880668E-3</v>
+      </c>
+      <c r="AB81" s="73">
+        <v>3879.3</v>
+      </c>
+      <c r="AC81" s="73"/>
+      <c r="AD81" s="73"/>
+      <c r="AE81" s="39"/>
+      <c r="AF81" s="74"/>
+      <c r="AG81" s="74"/>
+      <c r="AH81" s="75"/>
+      <c r="AI81" s="75">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AJ81" s="69"/>
-      <c r="AK81" s="69"/>
-      <c r="AL81" s="69"/>
-      <c r="AM81" s="70"/>
-      <c r="AN81" s="70"/>
-      <c r="AO81" s="70"/>
-      <c r="AP81" s="71">
+      <c r="AJ81" s="87"/>
+      <c r="AK81" s="87"/>
+      <c r="AL81" s="87"/>
+      <c r="AM81" s="88"/>
+      <c r="AN81" s="88"/>
+      <c r="AO81" s="88"/>
+      <c r="AP81" s="89">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AQ81" s="69">
+      <c r="AQ81" s="87">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR81" s="69">
+      <c r="AR81" s="87">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AS81" s="69"/>
-      <c r="AT81" s="69"/>
-      <c r="AU81" s="69"/>
-      <c r="AV81" s="69"/>
-      <c r="AW81" s="69"/>
-      <c r="AX81" s="69"/>
-      <c r="AY81" s="69"/>
-      <c r="AZ81" s="72"/>
-      <c r="BB81" s="45">
+      <c r="AS81" s="87"/>
+      <c r="AT81" s="87"/>
+      <c r="AU81" s="87"/>
+      <c r="AV81" s="87"/>
+      <c r="AW81" s="87"/>
+      <c r="AX81" s="87"/>
+      <c r="AY81" s="87"/>
+      <c r="AZ81" s="90"/>
+      <c r="BB81" s="92">
         <f>IF(AND(AB81="",AC81=""),T81,IF(AC81="",AB81,AC81))</f>
-        <v>0</v>
-      </c>
-      <c r="BC81" s="45">
+        <v>3879.3</v>
+      </c>
+      <c r="BC81" s="92">
         <f>+X81</f>
-        <v>0</v>
-      </c>
-      <c r="BD81" s="45"/>
-      <c r="BE81" s="45">
+        <v>3891</v>
+      </c>
+      <c r="BD81" s="92"/>
+      <c r="BE81" s="92">
         <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="BF81" s="39" t="e">
+        <v>-11.699999999999818</v>
+      </c>
+      <c r="BF81" s="39">
         <f t="shared" si="48"/>
-        <v>#DIV/0!</v>
+        <v>-3.0160080426880668E-3</v>
       </c>
     </row>
-    <row r="82" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A82" s="53">
+    <row r="82" spans="1:58" s="91" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A82" s="76">
         <f>IF(ISBLANK(F82),"",COUNTA($F$6:F82))</f>
         <v>77</v>
       </c>
-      <c r="B82" s="54" t="s">
+      <c r="B82" s="77" t="s">
         <v>60</v>
       </c>
-      <c r="C82" s="54" t="s">
+      <c r="C82" s="77" t="s">
         <v>61</v>
       </c>
-      <c r="D82" s="55"/>
-      <c r="E82" s="56" t="s">
+      <c r="D82" s="78"/>
+      <c r="E82" s="79" t="s">
         <v>65</v>
       </c>
-      <c r="F82" s="57">
+      <c r="F82" s="80">
         <v>46250</v>
       </c>
-      <c r="G82" s="58" t="s">
+      <c r="G82" s="81" t="s">
         <v>59</v>
       </c>
-      <c r="H82" s="58">
+      <c r="H82" s="81">
         <v>58</v>
       </c>
-      <c r="I82" s="58">
+      <c r="I82" s="81">
         <v>12</v>
       </c>
-      <c r="J82" s="58" t="s">
+      <c r="J82" s="81" t="s">
         <v>67</v>
       </c>
-      <c r="K82" s="59">
+      <c r="K82" s="82">
         <v>162011717</v>
       </c>
-      <c r="L82" s="60">
+      <c r="L82" s="83">
         <v>46251</v>
       </c>
-      <c r="M82" s="61"/>
-      <c r="N82" s="62"/>
-      <c r="O82" s="63"/>
-      <c r="P82" s="63"/>
-      <c r="Q82" s="63"/>
-      <c r="R82" s="64"/>
-      <c r="S82" s="64"/>
-      <c r="T82" s="64">
+      <c r="M82" s="84">
+        <v>46252</v>
+      </c>
+      <c r="N82" s="85">
+        <v>16585</v>
+      </c>
+      <c r="O82" s="86"/>
+      <c r="P82" s="86"/>
+      <c r="Q82" s="86"/>
+      <c r="R82" s="46">
+        <v>4123.6000000000004</v>
+      </c>
+      <c r="S82" s="46">
+        <v>961.00000000000045</v>
+      </c>
+      <c r="T82" s="46">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="U82" s="64"/>
-      <c r="V82" s="64"/>
-      <c r="W82" s="64"/>
-      <c r="X82" s="64"/>
-      <c r="Y82" s="64"/>
-      <c r="Z82" s="64">
+        <v>3162.6</v>
+      </c>
+      <c r="U82" s="46">
+        <v>3226.4</v>
+      </c>
+      <c r="V82" s="46"/>
+      <c r="W82" s="46"/>
+      <c r="X82" s="46">
+        <v>3199</v>
+      </c>
+      <c r="Y82" s="46"/>
+      <c r="Z82" s="46">
         <f>+T82-X82</f>
-        <v>0</v>
-      </c>
-      <c r="AA82" s="65" t="e">
+        <v>-36.400000000000091</v>
+      </c>
+      <c r="AA82" s="39">
         <f>Z82/T82</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB82" s="66"/>
-      <c r="AC82" s="66"/>
-      <c r="AD82" s="66"/>
-      <c r="AE82" s="65"/>
-      <c r="AF82" s="67"/>
-      <c r="AG82" s="67"/>
-      <c r="AH82" s="68"/>
-      <c r="AI82" s="68">
+        <v>-1.1509517485613132E-2</v>
+      </c>
+      <c r="AB82" s="73">
+        <v>3461.9999999999995</v>
+      </c>
+      <c r="AC82" s="73"/>
+      <c r="AD82" s="73"/>
+      <c r="AE82" s="39"/>
+      <c r="AF82" s="74"/>
+      <c r="AG82" s="74"/>
+      <c r="AH82" s="75"/>
+      <c r="AI82" s="75">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AJ82" s="69"/>
-      <c r="AK82" s="69"/>
-      <c r="AL82" s="69"/>
-      <c r="AM82" s="70"/>
-      <c r="AN82" s="70"/>
-      <c r="AO82" s="70"/>
-      <c r="AP82" s="71">
+      <c r="AJ82" s="87"/>
+      <c r="AK82" s="87"/>
+      <c r="AL82" s="87"/>
+      <c r="AM82" s="88"/>
+      <c r="AN82" s="88"/>
+      <c r="AO82" s="88"/>
+      <c r="AP82" s="89">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AQ82" s="69">
+      <c r="AQ82" s="87">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR82" s="69">
+      <c r="AR82" s="87">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AS82" s="69"/>
-      <c r="AT82" s="69"/>
-      <c r="AU82" s="69"/>
-      <c r="AV82" s="69"/>
-      <c r="AW82" s="69"/>
-      <c r="AX82" s="69"/>
-      <c r="AY82" s="69"/>
-      <c r="AZ82" s="72"/>
-      <c r="BB82" s="45">
+      <c r="AS82" s="87"/>
+      <c r="AT82" s="87"/>
+      <c r="AU82" s="87"/>
+      <c r="AV82" s="87"/>
+      <c r="AW82" s="87"/>
+      <c r="AX82" s="87"/>
+      <c r="AY82" s="87"/>
+      <c r="AZ82" s="90"/>
+      <c r="BB82" s="92">
         <f>IF(AND(AB82="",AC82=""),T82,IF(AC82="",AB82,AC82))</f>
-        <v>0</v>
-      </c>
-      <c r="BC82" s="45">
+        <v>3461.9999999999995</v>
+      </c>
+      <c r="BC82" s="92">
         <f>+X82</f>
-        <v>0</v>
-      </c>
-      <c r="BD82" s="45"/>
-      <c r="BE82" s="45">
+        <v>3199</v>
+      </c>
+      <c r="BD82" s="92"/>
+      <c r="BE82" s="92">
         <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="BF82" s="39" t="e">
+        <v>262.99999999999955</v>
+      </c>
+      <c r="BF82" s="39">
         <f t="shared" si="48"/>
-        <v>#DIV/0!</v>
+        <v>7.5967648757943262E-2</v>
       </c>
     </row>
-    <row r="83" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A83" s="53">
+    <row r="83" spans="1:58" s="91" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A83" s="76">
         <f>IF(ISBLANK(F83),"",COUNTA($F$6:F83))</f>
         <v>78</v>
       </c>
-      <c r="B83" s="54" t="s">
+      <c r="B83" s="77" t="s">
         <v>60</v>
       </c>
-      <c r="C83" s="54" t="s">
+      <c r="C83" s="77" t="s">
         <v>61</v>
       </c>
-      <c r="D83" s="55"/>
-      <c r="E83" s="56" t="s">
+      <c r="D83" s="78"/>
+      <c r="E83" s="79" t="s">
         <v>64</v>
       </c>
-      <c r="F83" s="57">
+      <c r="F83" s="80">
         <v>46250</v>
       </c>
-      <c r="G83" s="58" t="s">
+      <c r="G83" s="81" t="s">
         <v>59</v>
       </c>
-      <c r="H83" s="58">
+      <c r="H83" s="81">
         <v>59</v>
       </c>
-      <c r="I83" s="58">
-        <v>0</v>
-      </c>
-      <c r="J83" s="58" t="s">
+      <c r="I83" s="81">
+        <v>0</v>
+      </c>
+      <c r="J83" s="81" t="s">
         <v>64</v>
       </c>
-      <c r="K83" s="59">
+      <c r="K83" s="82">
         <v>162004404</v>
       </c>
-      <c r="L83" s="60">
+      <c r="L83" s="83">
         <v>46251</v>
       </c>
-      <c r="M83" s="61"/>
-      <c r="N83" s="62"/>
-      <c r="O83" s="63"/>
-      <c r="P83" s="63"/>
-      <c r="Q83" s="63"/>
-      <c r="R83" s="64"/>
-      <c r="S83" s="64"/>
-      <c r="T83" s="64">
+      <c r="M83" s="84">
+        <v>46252</v>
+      </c>
+      <c r="N83" s="85">
+        <v>16586</v>
+      </c>
+      <c r="O83" s="86"/>
+      <c r="P83" s="86"/>
+      <c r="Q83" s="86"/>
+      <c r="R83" s="46">
+        <v>5338.96</v>
+      </c>
+      <c r="S83" s="46">
+        <v>1233.6599999999999</v>
+      </c>
+      <c r="T83" s="46">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="U83" s="64"/>
-      <c r="V83" s="64"/>
-      <c r="W83" s="64"/>
-      <c r="X83" s="64"/>
-      <c r="Y83" s="64"/>
-      <c r="Z83" s="64">
+        <v>4105.3</v>
+      </c>
+      <c r="U83" s="46">
+        <v>4118.8</v>
+      </c>
+      <c r="V83" s="46"/>
+      <c r="W83" s="46"/>
+      <c r="X83" s="46">
+        <v>3974.2</v>
+      </c>
+      <c r="Y83" s="46"/>
+      <c r="Z83" s="46">
         <f>+T83-X83</f>
-        <v>0</v>
-      </c>
-      <c r="AA83" s="65" t="e">
+        <v>131.10000000000036</v>
+      </c>
+      <c r="AA83" s="39">
         <f>Z83/T83</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB83" s="66"/>
-      <c r="AC83" s="66"/>
-      <c r="AD83" s="66"/>
-      <c r="AE83" s="65"/>
-      <c r="AF83" s="67"/>
-      <c r="AG83" s="67"/>
-      <c r="AH83" s="68"/>
-      <c r="AI83" s="68">
+        <v>3.1934328794485267E-2</v>
+      </c>
+      <c r="AB83" s="73">
+        <v>4105.25</v>
+      </c>
+      <c r="AC83" s="73"/>
+      <c r="AD83" s="73"/>
+      <c r="AE83" s="39"/>
+      <c r="AF83" s="74"/>
+      <c r="AG83" s="74"/>
+      <c r="AH83" s="75"/>
+      <c r="AI83" s="75">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AJ83" s="69"/>
-      <c r="AK83" s="69"/>
-      <c r="AL83" s="69"/>
-      <c r="AM83" s="70"/>
-      <c r="AN83" s="70"/>
-      <c r="AO83" s="70"/>
-      <c r="AP83" s="71">
+      <c r="AJ83" s="87"/>
+      <c r="AK83" s="87"/>
+      <c r="AL83" s="87"/>
+      <c r="AM83" s="88"/>
+      <c r="AN83" s="88"/>
+      <c r="AO83" s="88"/>
+      <c r="AP83" s="89">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AQ83" s="69">
+      <c r="AQ83" s="87">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR83" s="69">
+      <c r="AR83" s="87">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AS83" s="69"/>
-      <c r="AT83" s="69"/>
-      <c r="AU83" s="69"/>
-      <c r="AV83" s="69"/>
-      <c r="AW83" s="69"/>
-      <c r="AX83" s="69"/>
-      <c r="AY83" s="69"/>
-      <c r="AZ83" s="72"/>
-      <c r="BB83" s="45">
+      <c r="AS83" s="87"/>
+      <c r="AT83" s="87"/>
+      <c r="AU83" s="87"/>
+      <c r="AV83" s="87"/>
+      <c r="AW83" s="87"/>
+      <c r="AX83" s="87"/>
+      <c r="AY83" s="87"/>
+      <c r="AZ83" s="90"/>
+      <c r="BB83" s="92">
         <f>IF(AND(AB83="",AC83=""),T83,IF(AC83="",AB83,AC83))</f>
-        <v>0</v>
-      </c>
-      <c r="BC83" s="45">
+        <v>4105.25</v>
+      </c>
+      <c r="BC83" s="92">
         <f>+X83</f>
-        <v>0</v>
-      </c>
-      <c r="BD83" s="45"/>
-      <c r="BE83" s="45">
+        <v>3974.2</v>
+      </c>
+      <c r="BD83" s="92"/>
+      <c r="BE83" s="92">
         <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="BF83" s="39" t="e">
+        <v>131.05000000000018</v>
+      </c>
+      <c r="BF83" s="39">
         <f t="shared" si="48"/>
-        <v>#DIV/0!</v>
+        <v>3.1922538213263546E-2</v>
       </c>
     </row>
-    <row r="84" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A84" s="53">
+    <row r="84" spans="1:58" s="91" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A84" s="76">
         <f>IF(ISBLANK(F84),"",COUNTA($F$6:F84))</f>
         <v>79</v>
       </c>
-      <c r="B84" s="54" t="s">
+      <c r="B84" s="77" t="s">
         <v>60</v>
       </c>
-      <c r="C84" s="54" t="s">
+      <c r="C84" s="77" t="s">
         <v>61</v>
       </c>
-      <c r="D84" s="55"/>
-      <c r="E84" s="56" t="s">
+      <c r="D84" s="78"/>
+      <c r="E84" s="79" t="s">
         <v>65</v>
       </c>
-      <c r="F84" s="57">
+      <c r="F84" s="80">
         <v>46251</v>
       </c>
-      <c r="G84" s="58" t="s">
+      <c r="G84" s="81" t="s">
         <v>59</v>
       </c>
-      <c r="H84" s="58">
+      <c r="H84" s="81">
         <v>59</v>
       </c>
-      <c r="I84" s="58">
-        <v>0</v>
-      </c>
-      <c r="J84" s="58" t="s">
+      <c r="I84" s="81">
+        <v>0</v>
+      </c>
+      <c r="J84" s="81" t="s">
         <v>67</v>
       </c>
-      <c r="K84" s="59">
+      <c r="K84" s="82">
         <v>162011719</v>
       </c>
-      <c r="L84" s="60">
+      <c r="L84" s="83">
         <v>46252</v>
       </c>
-      <c r="M84" s="61"/>
-      <c r="N84" s="62"/>
-      <c r="O84" s="63"/>
-      <c r="P84" s="63"/>
-      <c r="Q84" s="63"/>
-      <c r="R84" s="64"/>
-      <c r="S84" s="64"/>
-      <c r="T84" s="64">
+      <c r="M84" s="84">
+        <v>46253</v>
+      </c>
+      <c r="N84" s="85">
+        <v>16589</v>
+      </c>
+      <c r="O84" s="86"/>
+      <c r="P84" s="86"/>
+      <c r="Q84" s="86"/>
+      <c r="R84" s="46">
+        <v>5367.81</v>
+      </c>
+      <c r="S84" s="46">
+        <v>1236.5100000000002</v>
+      </c>
+      <c r="T84" s="46">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="U84" s="64"/>
-      <c r="V84" s="64"/>
-      <c r="W84" s="64"/>
-      <c r="X84" s="64"/>
-      <c r="Y84" s="64"/>
-      <c r="Z84" s="64">
+        <v>4131.3</v>
+      </c>
+      <c r="U84" s="46">
+        <v>4155.8</v>
+      </c>
+      <c r="V84" s="46"/>
+      <c r="W84" s="46"/>
+      <c r="X84" s="46">
+        <v>4199.6000000000004</v>
+      </c>
+      <c r="Y84" s="46"/>
+      <c r="Z84" s="46">
         <f>+T84-X84</f>
-        <v>0</v>
-      </c>
-      <c r="AA84" s="65" t="e">
+        <v>-68.300000000000182</v>
+      </c>
+      <c r="AA84" s="39">
         <f>Z84/T84</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB84" s="66"/>
-      <c r="AC84" s="66"/>
-      <c r="AD84" s="66"/>
-      <c r="AE84" s="65"/>
-      <c r="AF84" s="67"/>
-      <c r="AG84" s="67"/>
-      <c r="AH84" s="68"/>
-      <c r="AI84" s="68">
+        <v>-1.6532326386367532E-2</v>
+      </c>
+      <c r="AB84" s="73">
+        <v>4152.76</v>
+      </c>
+      <c r="AC84" s="73"/>
+      <c r="AD84" s="73"/>
+      <c r="AE84" s="39"/>
+      <c r="AF84" s="74"/>
+      <c r="AG84" s="74"/>
+      <c r="AH84" s="75"/>
+      <c r="AI84" s="75">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AJ84" s="69"/>
-      <c r="AK84" s="69"/>
-      <c r="AL84" s="69"/>
-      <c r="AM84" s="70"/>
-      <c r="AN84" s="70"/>
-      <c r="AO84" s="70"/>
-      <c r="AP84" s="71">
+      <c r="AJ84" s="87"/>
+      <c r="AK84" s="87"/>
+      <c r="AL84" s="87"/>
+      <c r="AM84" s="88"/>
+      <c r="AN84" s="88"/>
+      <c r="AO84" s="88"/>
+      <c r="AP84" s="89">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AQ84" s="69">
+      <c r="AQ84" s="87">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR84" s="69">
+      <c r="AR84" s="87">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AS84" s="69"/>
-      <c r="AT84" s="69"/>
-      <c r="AU84" s="69"/>
-      <c r="AV84" s="69"/>
-      <c r="AW84" s="69"/>
-      <c r="AX84" s="69"/>
-      <c r="AY84" s="69"/>
-      <c r="AZ84" s="72"/>
-      <c r="BB84" s="45">
+      <c r="AS84" s="87"/>
+      <c r="AT84" s="87"/>
+      <c r="AU84" s="87"/>
+      <c r="AV84" s="87"/>
+      <c r="AW84" s="87"/>
+      <c r="AX84" s="87"/>
+      <c r="AY84" s="87"/>
+      <c r="AZ84" s="90"/>
+      <c r="BB84" s="92">
         <f>IF(AND(AB84="",AC84=""),T84,IF(AC84="",AB84,AC84))</f>
-        <v>0</v>
-      </c>
-      <c r="BC84" s="45">
+        <v>4152.76</v>
+      </c>
+      <c r="BC84" s="92">
         <f>+X84</f>
-        <v>0</v>
-      </c>
-      <c r="BD84" s="45"/>
-      <c r="BE84" s="45">
+        <v>4199.6000000000004</v>
+      </c>
+      <c r="BD84" s="92"/>
+      <c r="BE84" s="92">
         <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="BF84" s="39" t="e">
+        <v>-46.840000000000146</v>
+      </c>
+      <c r="BF84" s="39">
         <f t="shared" si="48"/>
-        <v>#DIV/0!</v>
+        <v>-1.1279245610148467E-2</v>
       </c>
     </row>
     <row r="85" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A85" s="21" t="str">
+      <c r="A85" s="53">
         <f>IF(ISBLANK(F85),"",COUNTA($F$6:F85))</f>
-        <v/>
-      </c>
-      <c r="B85" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="B85" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="C85" s="37" t="s">
+      <c r="C85" s="54" t="s">
         <v>61</v>
       </c>
-      <c r="D85" s="22"/>
-      <c r="E85" s="23"/>
-      <c r="F85" s="36"/>
-      <c r="G85" s="24"/>
-      <c r="H85" s="24"/>
-      <c r="I85" s="24"/>
-      <c r="J85" s="24"/>
-      <c r="K85" s="25"/>
-      <c r="L85" s="26"/>
-      <c r="M85" s="38"/>
-      <c r="N85" s="52"/>
-      <c r="O85" s="27"/>
-      <c r="P85" s="27"/>
-      <c r="Q85" s="27"/>
-      <c r="R85" s="28"/>
-      <c r="S85" s="28"/>
-      <c r="T85" s="46">
+      <c r="D85" s="55"/>
+      <c r="E85" s="56" t="s">
+        <v>64</v>
+      </c>
+      <c r="F85" s="57">
+        <v>46252</v>
+      </c>
+      <c r="G85" s="58" t="s">
+        <v>59</v>
+      </c>
+      <c r="H85" s="58">
+        <v>57</v>
+      </c>
+      <c r="I85" s="58">
+        <v>1</v>
+      </c>
+      <c r="J85" s="58" t="s">
+        <v>64</v>
+      </c>
+      <c r="K85" s="59">
+        <v>162004407</v>
+      </c>
+      <c r="L85" s="60">
+        <v>46253</v>
+      </c>
+      <c r="M85" s="61"/>
+      <c r="N85" s="62"/>
+      <c r="O85" s="63"/>
+      <c r="P85" s="63"/>
+      <c r="Q85" s="63"/>
+      <c r="R85" s="64"/>
+      <c r="S85" s="64"/>
+      <c r="T85" s="64">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U85" s="28"/>
-      <c r="V85" s="28"/>
-      <c r="W85" s="28"/>
-      <c r="X85" s="28"/>
-      <c r="Y85" s="28"/>
-      <c r="Z85" s="28">
+      <c r="U85" s="64"/>
+      <c r="V85" s="64"/>
+      <c r="W85" s="64"/>
+      <c r="X85" s="64"/>
+      <c r="Y85" s="64"/>
+      <c r="Z85" s="64">
         <f>+T85-X85</f>
         <v>0</v>
       </c>
-      <c r="AA85" s="29" t="e">
+      <c r="AA85" s="65" t="e">
         <f>Z85/T85</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB85" s="40"/>
-      <c r="AC85" s="40"/>
-      <c r="AD85" s="40"/>
-      <c r="AE85" s="29"/>
-      <c r="AF85" s="30"/>
-      <c r="AG85" s="30"/>
-      <c r="AH85" s="31"/>
-      <c r="AI85" s="31">
+      <c r="AB85" s="66"/>
+      <c r="AC85" s="66"/>
+      <c r="AD85" s="66"/>
+      <c r="AE85" s="65"/>
+      <c r="AF85" s="67"/>
+      <c r="AG85" s="67"/>
+      <c r="AH85" s="68"/>
+      <c r="AI85" s="68">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AJ85" s="32"/>
-      <c r="AK85" s="32"/>
-      <c r="AL85" s="32"/>
-      <c r="AM85" s="33"/>
-      <c r="AN85" s="33"/>
-      <c r="AO85" s="33"/>
-      <c r="AP85" s="34">
+      <c r="AJ85" s="69"/>
+      <c r="AK85" s="69"/>
+      <c r="AL85" s="69"/>
+      <c r="AM85" s="70"/>
+      <c r="AN85" s="70"/>
+      <c r="AO85" s="70"/>
+      <c r="AP85" s="71">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AQ85" s="32">
+      <c r="AQ85" s="69">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR85" s="32">
+      <c r="AR85" s="69">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AS85" s="32"/>
-      <c r="AT85" s="32"/>
-      <c r="AU85" s="32"/>
-      <c r="AV85" s="32"/>
-      <c r="AW85" s="32"/>
-      <c r="AX85" s="32"/>
-      <c r="AY85" s="32"/>
-      <c r="AZ85" s="35"/>
+      <c r="AS85" s="69"/>
+      <c r="AT85" s="69"/>
+      <c r="AU85" s="69"/>
+      <c r="AV85" s="69"/>
+      <c r="AW85" s="69"/>
+      <c r="AX85" s="69"/>
+      <c r="AY85" s="69"/>
+      <c r="AZ85" s="72"/>
       <c r="BB85" s="45">
         <f>IF(AND(AB85="",AC85=""),T85,IF(AC85="",AB85,AC85))</f>
         <v>0</v>
@@ -28853,86 +29987,102 @@
       </c>
     </row>
     <row r="86" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A86" s="21" t="str">
+      <c r="A86" s="53">
         <f>IF(ISBLANK(F86),"",COUNTA($F$6:F86))</f>
-        <v/>
-      </c>
-      <c r="B86" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="B86" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="C86" s="37" t="s">
+      <c r="C86" s="54" t="s">
         <v>61</v>
       </c>
-      <c r="D86" s="22"/>
-      <c r="E86" s="23"/>
-      <c r="F86" s="36"/>
-      <c r="G86" s="24"/>
-      <c r="H86" s="24"/>
-      <c r="I86" s="24"/>
-      <c r="J86" s="24"/>
-      <c r="K86" s="25"/>
-      <c r="L86" s="26"/>
-      <c r="M86" s="38"/>
-      <c r="N86" s="52"/>
-      <c r="O86" s="27"/>
-      <c r="P86" s="27"/>
-      <c r="Q86" s="27"/>
-      <c r="R86" s="28"/>
-      <c r="S86" s="28"/>
-      <c r="T86" s="46">
+      <c r="D86" s="55"/>
+      <c r="E86" s="56" t="s">
+        <v>63</v>
+      </c>
+      <c r="F86" s="57">
+        <v>46253</v>
+      </c>
+      <c r="G86" s="58" t="s">
+        <v>59</v>
+      </c>
+      <c r="H86" s="58">
+        <v>59</v>
+      </c>
+      <c r="I86" s="58">
+        <v>6</v>
+      </c>
+      <c r="J86" s="58" t="s">
+        <v>63</v>
+      </c>
+      <c r="K86" s="59">
+        <v>162006452</v>
+      </c>
+      <c r="L86" s="60">
+        <v>46253</v>
+      </c>
+      <c r="M86" s="61"/>
+      <c r="N86" s="62"/>
+      <c r="O86" s="63"/>
+      <c r="P86" s="63"/>
+      <c r="Q86" s="63"/>
+      <c r="R86" s="64"/>
+      <c r="S86" s="64"/>
+      <c r="T86" s="64">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U86" s="28"/>
-      <c r="V86" s="28"/>
-      <c r="W86" s="28"/>
-      <c r="X86" s="28"/>
-      <c r="Y86" s="28"/>
-      <c r="Z86" s="28">
+      <c r="U86" s="64"/>
+      <c r="V86" s="64"/>
+      <c r="W86" s="64"/>
+      <c r="X86" s="64"/>
+      <c r="Y86" s="64"/>
+      <c r="Z86" s="64">
         <f>+T86-X86</f>
         <v>0</v>
       </c>
-      <c r="AA86" s="29" t="e">
+      <c r="AA86" s="65" t="e">
         <f>Z86/T86</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB86" s="40"/>
-      <c r="AC86" s="40"/>
-      <c r="AD86" s="40"/>
-      <c r="AE86" s="29"/>
-      <c r="AF86" s="30"/>
-      <c r="AG86" s="30"/>
-      <c r="AH86" s="31"/>
-      <c r="AI86" s="31">
+      <c r="AB86" s="66"/>
+      <c r="AC86" s="66"/>
+      <c r="AD86" s="66"/>
+      <c r="AE86" s="65"/>
+      <c r="AF86" s="67"/>
+      <c r="AG86" s="67"/>
+      <c r="AH86" s="68"/>
+      <c r="AI86" s="68">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AJ86" s="32"/>
-      <c r="AK86" s="32"/>
-      <c r="AL86" s="32"/>
-      <c r="AM86" s="33"/>
-      <c r="AN86" s="33"/>
-      <c r="AO86" s="33"/>
-      <c r="AP86" s="34">
+      <c r="AJ86" s="69"/>
+      <c r="AK86" s="69"/>
+      <c r="AL86" s="69"/>
+      <c r="AM86" s="70"/>
+      <c r="AN86" s="70"/>
+      <c r="AO86" s="70"/>
+      <c r="AP86" s="71">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AQ86" s="32">
+      <c r="AQ86" s="69">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR86" s="32">
+      <c r="AR86" s="69">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AS86" s="32"/>
-      <c r="AT86" s="32"/>
-      <c r="AU86" s="32"/>
-      <c r="AV86" s="32"/>
-      <c r="AW86" s="32"/>
-      <c r="AX86" s="32"/>
-      <c r="AY86" s="32"/>
-      <c r="AZ86" s="35"/>
+      <c r="AS86" s="69"/>
+      <c r="AT86" s="69"/>
+      <c r="AU86" s="69"/>
+      <c r="AV86" s="69"/>
+      <c r="AW86" s="69"/>
+      <c r="AX86" s="69"/>
+      <c r="AY86" s="69"/>
+      <c r="AZ86" s="72"/>
       <c r="BB86" s="45">
         <f>IF(AND(AB86="",AC86=""),T86,IF(AC86="",AB86,AC86))</f>
         <v>0</v>
@@ -28952,86 +30102,102 @@
       </c>
     </row>
     <row r="87" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="21" t="str">
+      <c r="A87" s="53">
         <f>IF(ISBLANK(F87),"",COUNTA($F$6:F87))</f>
-        <v/>
-      </c>
-      <c r="B87" s="37" t="s">
+        <v>82</v>
+      </c>
+      <c r="B87" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="C87" s="37" t="s">
+      <c r="C87" s="54" t="s">
         <v>61</v>
       </c>
-      <c r="D87" s="22"/>
-      <c r="E87" s="23"/>
-      <c r="F87" s="36"/>
-      <c r="G87" s="24"/>
-      <c r="H87" s="24"/>
-      <c r="I87" s="24"/>
-      <c r="J87" s="24"/>
-      <c r="K87" s="25"/>
-      <c r="L87" s="26"/>
-      <c r="M87" s="38"/>
-      <c r="N87" s="52"/>
-      <c r="O87" s="27"/>
-      <c r="P87" s="27"/>
-      <c r="Q87" s="27"/>
-      <c r="R87" s="28"/>
-      <c r="S87" s="28"/>
-      <c r="T87" s="46">
+      <c r="D87" s="55"/>
+      <c r="E87" s="56" t="s">
+        <v>63</v>
+      </c>
+      <c r="F87" s="57">
+        <v>46253</v>
+      </c>
+      <c r="G87" s="58" t="s">
+        <v>59</v>
+      </c>
+      <c r="H87" s="58">
+        <v>58</v>
+      </c>
+      <c r="I87" s="58">
+        <v>2</v>
+      </c>
+      <c r="J87" s="58" t="s">
+        <v>63</v>
+      </c>
+      <c r="K87" s="59">
+        <v>162006453</v>
+      </c>
+      <c r="L87" s="60">
+        <v>46254</v>
+      </c>
+      <c r="M87" s="61"/>
+      <c r="N87" s="62"/>
+      <c r="O87" s="63"/>
+      <c r="P87" s="63"/>
+      <c r="Q87" s="63"/>
+      <c r="R87" s="64"/>
+      <c r="S87" s="64"/>
+      <c r="T87" s="64">
         <f t="shared" ref="T87" si="49">+R87-S87</f>
         <v>0</v>
       </c>
-      <c r="U87" s="28"/>
-      <c r="V87" s="28"/>
-      <c r="W87" s="28"/>
-      <c r="X87" s="28"/>
-      <c r="Y87" s="28"/>
-      <c r="Z87" s="28">
+      <c r="U87" s="64"/>
+      <c r="V87" s="64"/>
+      <c r="W87" s="64"/>
+      <c r="X87" s="64"/>
+      <c r="Y87" s="64"/>
+      <c r="Z87" s="64">
         <f>+T87-X87</f>
         <v>0</v>
       </c>
-      <c r="AA87" s="29" t="e">
+      <c r="AA87" s="65" t="e">
         <f>Z87/T87</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB87" s="40"/>
-      <c r="AC87" s="40"/>
-      <c r="AD87" s="40"/>
-      <c r="AE87" s="29"/>
-      <c r="AF87" s="30"/>
-      <c r="AG87" s="30"/>
-      <c r="AH87" s="31"/>
-      <c r="AI87" s="31">
+      <c r="AB87" s="66"/>
+      <c r="AC87" s="66"/>
+      <c r="AD87" s="66"/>
+      <c r="AE87" s="65"/>
+      <c r="AF87" s="67"/>
+      <c r="AG87" s="67"/>
+      <c r="AH87" s="68"/>
+      <c r="AI87" s="68">
         <f t="shared" ref="AI87" si="50">+AG87+AH87</f>
         <v>0</v>
       </c>
-      <c r="AJ87" s="32"/>
-      <c r="AK87" s="32"/>
-      <c r="AL87" s="32"/>
-      <c r="AM87" s="33"/>
-      <c r="AN87" s="33"/>
-      <c r="AO87" s="33"/>
-      <c r="AP87" s="34">
+      <c r="AJ87" s="69"/>
+      <c r="AK87" s="69"/>
+      <c r="AL87" s="69"/>
+      <c r="AM87" s="70"/>
+      <c r="AN87" s="70"/>
+      <c r="AO87" s="70"/>
+      <c r="AP87" s="71">
         <f t="shared" ref="AP87" si="51">ROUNDUP((AO87-AM87+(AO87&lt;AM87))*24,0)</f>
         <v>0</v>
       </c>
-      <c r="AQ87" s="32">
+      <c r="AQ87" s="69">
         <f t="shared" ref="AQ87" si="52">IF(AP87&gt;5,(AP87-5),0)</f>
         <v>0</v>
       </c>
-      <c r="AR87" s="32">
+      <c r="AR87" s="69">
         <f t="shared" ref="AR87" si="53">+AQ87*8850</f>
         <v>0</v>
       </c>
-      <c r="AS87" s="32"/>
-      <c r="AT87" s="32"/>
-      <c r="AU87" s="32"/>
-      <c r="AV87" s="32"/>
-      <c r="AW87" s="32"/>
-      <c r="AX87" s="32"/>
-      <c r="AY87" s="32"/>
-      <c r="AZ87" s="35"/>
+      <c r="AS87" s="69"/>
+      <c r="AT87" s="69"/>
+      <c r="AU87" s="69"/>
+      <c r="AV87" s="69"/>
+      <c r="AW87" s="69"/>
+      <c r="AX87" s="69"/>
+      <c r="AY87" s="69"/>
+      <c r="AZ87" s="72"/>
       <c r="BB87" s="45">
         <f>IF(AND(AB87="",AC87=""),T87,IF(AC87="",AB87,AC87))</f>
         <v>0</v>
@@ -29051,86 +30217,102 @@
       </c>
     </row>
     <row r="88" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="21" t="str">
+      <c r="A88" s="53">
         <f>IF(ISBLANK(F88),"",COUNTA($F$6:F88))</f>
-        <v/>
-      </c>
-      <c r="B88" s="37" t="s">
+        <v>83</v>
+      </c>
+      <c r="B88" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="C88" s="37" t="s">
+      <c r="C88" s="54" t="s">
         <v>61</v>
       </c>
-      <c r="D88" s="22"/>
-      <c r="E88" s="23"/>
-      <c r="F88" s="36"/>
-      <c r="G88" s="24"/>
-      <c r="H88" s="24"/>
-      <c r="I88" s="24"/>
-      <c r="J88" s="24"/>
-      <c r="K88" s="25"/>
-      <c r="L88" s="26"/>
-      <c r="M88" s="38"/>
-      <c r="N88" s="52"/>
-      <c r="O88" s="27"/>
-      <c r="P88" s="27"/>
-      <c r="Q88" s="27"/>
-      <c r="R88" s="28"/>
-      <c r="S88" s="28"/>
-      <c r="T88" s="46">
+      <c r="D88" s="55"/>
+      <c r="E88" s="56" t="s">
+        <v>65</v>
+      </c>
+      <c r="F88" s="57">
+        <v>46254</v>
+      </c>
+      <c r="G88" s="58" t="s">
+        <v>59</v>
+      </c>
+      <c r="H88" s="58">
+        <v>59</v>
+      </c>
+      <c r="I88" s="58">
+        <v>0</v>
+      </c>
+      <c r="J88" s="58" t="s">
+        <v>67</v>
+      </c>
+      <c r="K88" s="59">
+        <v>162011721</v>
+      </c>
+      <c r="L88" s="60">
+        <v>46254</v>
+      </c>
+      <c r="M88" s="61"/>
+      <c r="N88" s="62"/>
+      <c r="O88" s="63"/>
+      <c r="P88" s="63"/>
+      <c r="Q88" s="63"/>
+      <c r="R88" s="64"/>
+      <c r="S88" s="64"/>
+      <c r="T88" s="64">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U88" s="28"/>
-      <c r="V88" s="28"/>
-      <c r="W88" s="28"/>
-      <c r="X88" s="28"/>
-      <c r="Y88" s="28"/>
-      <c r="Z88" s="28">
+      <c r="U88" s="64"/>
+      <c r="V88" s="64"/>
+      <c r="W88" s="64"/>
+      <c r="X88" s="64"/>
+      <c r="Y88" s="64"/>
+      <c r="Z88" s="64">
         <f>+T88-X88</f>
         <v>0</v>
       </c>
-      <c r="AA88" s="29" t="e">
+      <c r="AA88" s="65" t="e">
         <f>Z88/T88</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB88" s="40"/>
-      <c r="AC88" s="40"/>
-      <c r="AD88" s="40"/>
-      <c r="AE88" s="29"/>
-      <c r="AF88" s="30"/>
-      <c r="AG88" s="30"/>
-      <c r="AH88" s="31"/>
-      <c r="AI88" s="31">
+      <c r="AB88" s="66"/>
+      <c r="AC88" s="66"/>
+      <c r="AD88" s="66"/>
+      <c r="AE88" s="65"/>
+      <c r="AF88" s="67"/>
+      <c r="AG88" s="67"/>
+      <c r="AH88" s="68"/>
+      <c r="AI88" s="68">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AJ88" s="32"/>
-      <c r="AK88" s="32"/>
-      <c r="AL88" s="32"/>
-      <c r="AM88" s="33"/>
-      <c r="AN88" s="33"/>
-      <c r="AO88" s="33"/>
-      <c r="AP88" s="34">
+      <c r="AJ88" s="69"/>
+      <c r="AK88" s="69"/>
+      <c r="AL88" s="69"/>
+      <c r="AM88" s="70"/>
+      <c r="AN88" s="70"/>
+      <c r="AO88" s="70"/>
+      <c r="AP88" s="71">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AQ88" s="32">
+      <c r="AQ88" s="69">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AR88" s="32">
+      <c r="AR88" s="69">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AS88" s="32"/>
-      <c r="AT88" s="32"/>
-      <c r="AU88" s="32"/>
-      <c r="AV88" s="32"/>
-      <c r="AW88" s="32"/>
-      <c r="AX88" s="32"/>
-      <c r="AY88" s="32"/>
-      <c r="AZ88" s="35"/>
+      <c r="AS88" s="69"/>
+      <c r="AT88" s="69"/>
+      <c r="AU88" s="69"/>
+      <c r="AV88" s="69"/>
+      <c r="AW88" s="69"/>
+      <c r="AX88" s="69"/>
+      <c r="AY88" s="69"/>
+      <c r="AZ88" s="72"/>
       <c r="BB88" s="45">
         <f>IF(AND(AB88="",AC88=""),T88,IF(AC88="",AB88,AC88))</f>
         <v>0</v>
@@ -29251,11 +30433,11 @@
     <row r="90" spans="1:58" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="9">
         <f>+COUNT(A6:A89)</f>
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B90" s="10">
         <f>+COUNTIF(X6:X89,"&gt;0")</f>
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C90" s="10"/>
       <c r="D90" s="10"/>
@@ -29274,19 +30456,19 @@
       <c r="Q90" s="10"/>
       <c r="R90" s="12">
         <f t="shared" ref="R90:Y90" si="56">SUM(R6:R89)</f>
-        <v>376353.77999999991</v>
+        <v>396239.21999999991</v>
       </c>
       <c r="S90" s="12">
         <f t="shared" si="56"/>
-        <v>87936.479999999981</v>
+        <v>92543.419999999984</v>
       </c>
       <c r="T90" s="12">
         <f t="shared" si="56"/>
-        <v>288417.30000000005</v>
+        <v>303695.8</v>
       </c>
       <c r="U90" s="12">
         <f t="shared" si="56"/>
-        <v>289922.90000000002</v>
+        <v>305323.7</v>
       </c>
       <c r="V90" s="12">
         <f t="shared" si="56"/>
@@ -29298,7 +30480,7 @@
       </c>
       <c r="X90" s="12">
         <f t="shared" si="56"/>
-        <v>286764.00000000006</v>
+        <v>302001.69999999995</v>
       </c>
       <c r="Y90" s="12">
         <f t="shared" si="56"/>
@@ -29306,11 +30488,11 @@
       </c>
       <c r="Z90" s="12">
         <f>T90-X90</f>
-        <v>1653.2999999999884</v>
+        <v>1694.1000000000349</v>
       </c>
       <c r="AA90" s="13">
         <f>Z90/T90</f>
-        <v>5.7323191084584319E-3</v>
+        <v>5.5782793176594311E-3</v>
       </c>
       <c r="AB90" s="41"/>
       <c r="AC90" s="41"/>
@@ -29378,11 +30560,11 @@
       <c r="AZ90" s="19"/>
       <c r="BB90" s="42">
         <f>SUM(BB6:BB89)</f>
-        <v>289598.51</v>
+        <v>305197.82</v>
       </c>
       <c r="BC90" s="42">
         <f>SUM(BC6:BC89)</f>
-        <v>286764.00000000006</v>
+        <v>302001.69999999995</v>
       </c>
       <c r="BD90" s="42">
         <f>SUM(BD6:BD89)</f>
@@ -29390,148 +30572,153 @@
       </c>
       <c r="BE90" s="42">
         <f>SUM(BE6:BE89)</f>
-        <v>2834.5099999999975</v>
+        <v>3196.1199999999967</v>
       </c>
       <c r="BF90" s="43">
         <f t="shared" si="55"/>
-        <v>9.7877230100389592E-3</v>
+        <v>1.0472289743091863E-2</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="K6:K12">
-    <cfRule type="duplicateValues" dxfId="50" priority="1008"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="1011"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K6:K12">
-    <cfRule type="duplicateValues" dxfId="49" priority="1009"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="1010"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="1012"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="1013"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K89">
-    <cfRule type="duplicateValues" dxfId="47" priority="1011"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="1014"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K89">
-    <cfRule type="duplicateValues" dxfId="46" priority="1012"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="1013"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="1015"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="1016"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K89 K5">
-    <cfRule type="duplicateValues" dxfId="44" priority="1014"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="1017"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K89:K90 K5">
-    <cfRule type="duplicateValues" dxfId="43" priority="1016"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="1019"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K89:K90">
-    <cfRule type="duplicateValues" dxfId="42" priority="1018"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="1021"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13:K14 K88">
-    <cfRule type="duplicateValues" dxfId="41" priority="1019"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="1022"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13:K14 K88">
-    <cfRule type="duplicateValues" dxfId="40" priority="1021"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="1022"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="1024"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="1025"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13:K14 K5 K88:K90">
-    <cfRule type="duplicateValues" dxfId="38" priority="1025"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="1028"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K88:K90 K5:K14">
-    <cfRule type="duplicateValues" dxfId="37" priority="1028"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="1031"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K36 K15:K26">
-    <cfRule type="duplicateValues" dxfId="36" priority="1030"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="1033"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K36 K15:K26">
-    <cfRule type="duplicateValues" dxfId="35" priority="1032"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="1033"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="1035"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="1036"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K15:K26">
-    <cfRule type="duplicateValues" dxfId="33" priority="1036"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="1039"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27:K35">
-    <cfRule type="duplicateValues" dxfId="32" priority="1037"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="1040"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27:K35">
-    <cfRule type="duplicateValues" dxfId="31" priority="1038"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="1039"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="1041"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="1042"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5:K36 K88:K90">
-    <cfRule type="duplicateValues" dxfId="29" priority="1040"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="1043"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K37:K54 K61:K64">
-    <cfRule type="duplicateValues" dxfId="28" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K37:K54 K61:K64">
-    <cfRule type="duplicateValues" dxfId="27" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K37:K54">
-    <cfRule type="duplicateValues" dxfId="25" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K37:K54">
-    <cfRule type="duplicateValues" dxfId="24" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K37:K54">
-    <cfRule type="duplicateValues" dxfId="23" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K6:K54 K61:K64 K88:K90">
-    <cfRule type="duplicateValues" dxfId="22" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K55:K60">
-    <cfRule type="duplicateValues" dxfId="21" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K55:K60">
-    <cfRule type="duplicateValues" dxfId="20" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K55:K60">
-    <cfRule type="duplicateValues" dxfId="18" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K55:K60">
-    <cfRule type="duplicateValues" dxfId="17" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K55:K60">
-    <cfRule type="duplicateValues" dxfId="16" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K55:K60">
-    <cfRule type="duplicateValues" dxfId="15" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K6:K64 K88:K90">
-    <cfRule type="duplicateValues" dxfId="14" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K65:K87">
-    <cfRule type="duplicateValues" dxfId="13" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K65:K87">
-    <cfRule type="duplicateValues" dxfId="12" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K65:K87">
-    <cfRule type="duplicateValues" dxfId="10" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K65:K87">
-    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K65:K87">
-    <cfRule type="duplicateValues" dxfId="8" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K65:K87">
-    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K65:K87">
-    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K6:K90">
-    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5:K90">
-    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K5:K88">
     <cfRule type="duplicateValues" dxfId="3" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB6:BB89">
-    <cfRule type="expression" dxfId="2" priority="1079">
+    <cfRule type="expression" dxfId="2" priority="1094">
       <formula>$AC6&lt;&gt;""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="1080">
+    <cfRule type="expression" dxfId="1" priority="1095">
       <formula>$AB6&lt;&gt;""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="1081">
+    <cfRule type="expression" dxfId="0" priority="1096">
       <formula>$T6&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Shortage.xlsx
+++ b/Shortage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\MR1\PPGS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F5AA64E-EB66-461C-9B2A-A0C60F6F68C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23E5A793-A92E-490A-81BA-E02D4C3B55E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Aug-26" sheetId="5" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Aug-26'!$A$5:$BF$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Aug-26'!$A$5:$BF$97</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jul-26'!$A$5:$BG$127</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1147" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="75">
   <si>
     <t>sl.no.</t>
   </si>
@@ -755,7 +755,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="211">
+  <dxfs count="196">
     <dxf>
       <fill>
         <patternFill>
@@ -954,357 +954,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2501,6 +2150,207 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
@@ -19298,134 +19148,134 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="K126">
-    <cfRule type="duplicateValues" dxfId="105" priority="748"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="748"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K6 K24">
-    <cfRule type="duplicateValues" dxfId="104" priority="749"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="749"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7:K23">
-    <cfRule type="duplicateValues" dxfId="103" priority="751"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="751"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K126 K6:K24">
-    <cfRule type="duplicateValues" dxfId="102" priority="752"/>
-    <cfRule type="duplicateValues" dxfId="101" priority="753"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="752"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="753"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25:K31 K54:K57">
-    <cfRule type="duplicateValues" dxfId="100" priority="756"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="756"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25:K31 K54:K57">
-    <cfRule type="duplicateValues" dxfId="99" priority="758"/>
-    <cfRule type="duplicateValues" dxfId="98" priority="759"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="758"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="759"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27:K53">
-    <cfRule type="duplicateValues" dxfId="97" priority="762"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="762"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27:K53">
-    <cfRule type="duplicateValues" dxfId="96" priority="763"/>
-    <cfRule type="duplicateValues" dxfId="95" priority="764"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="763"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="764"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K126 K6:K57">
-    <cfRule type="duplicateValues" dxfId="94" priority="765"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="765"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K58:K62 K72:K75">
-    <cfRule type="duplicateValues" dxfId="93" priority="767"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="767"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K58:K62 K72:K75">
-    <cfRule type="duplicateValues" dxfId="92" priority="769"/>
-    <cfRule type="duplicateValues" dxfId="91" priority="770"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="769"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="770"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K58:K62">
-    <cfRule type="duplicateValues" dxfId="90" priority="773"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="773"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K126 K5:K62 K72:K75">
-    <cfRule type="duplicateValues" dxfId="89" priority="774"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="774"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K63:K71">
-    <cfRule type="duplicateValues" dxfId="88" priority="777"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="777"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K63:K71">
-    <cfRule type="duplicateValues" dxfId="87" priority="778"/>
-    <cfRule type="duplicateValues" dxfId="86" priority="779"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="778"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="779"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K126 K5:K75">
-    <cfRule type="duplicateValues" dxfId="85" priority="780"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="780"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K76:K79 K90:K92 K116">
-    <cfRule type="duplicateValues" dxfId="84" priority="782"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="782"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K76:K79 K90:K92 K116">
-    <cfRule type="duplicateValues" dxfId="83" priority="785"/>
-    <cfRule type="duplicateValues" dxfId="82" priority="786"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="785"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="786"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K76:K79">
-    <cfRule type="duplicateValues" dxfId="81" priority="791"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="791"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K80:K89">
-    <cfRule type="duplicateValues" dxfId="80" priority="792"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="792"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K80:K89">
-    <cfRule type="duplicateValues" dxfId="79" priority="793"/>
-    <cfRule type="duplicateValues" dxfId="78" priority="794"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="793"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="794"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K126:K127 K5:K92 K116">
-    <cfRule type="duplicateValues" dxfId="77" priority="795"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="795"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K99:K113 K115">
-    <cfRule type="duplicateValues" dxfId="76" priority="798"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="798"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K99:K113 K115">
-    <cfRule type="duplicateValues" dxfId="75" priority="800"/>
-    <cfRule type="duplicateValues" dxfId="74" priority="801"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="800"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="801"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K93:K98">
-    <cfRule type="duplicateValues" dxfId="73" priority="804"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="804"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K93:K98">
-    <cfRule type="duplicateValues" dxfId="72" priority="805"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="806"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="805"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="806"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K126:K127 K5:K113 K115:K116">
-    <cfRule type="duplicateValues" dxfId="70" priority="807"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="807"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K114">
-    <cfRule type="duplicateValues" dxfId="69" priority="810"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="810"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K114">
-    <cfRule type="duplicateValues" dxfId="68" priority="811"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="812"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="811"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="812"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K126:K127 K5:K116">
-    <cfRule type="duplicateValues" dxfId="66" priority="813"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="813"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K117:K123 K125">
-    <cfRule type="duplicateValues" dxfId="65" priority="844"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="844"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K117:K123 K125">
-    <cfRule type="duplicateValues" dxfId="64" priority="846"/>
-    <cfRule type="duplicateValues" dxfId="63" priority="847"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="846"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="847"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5:K123 K125:K127">
-    <cfRule type="duplicateValues" dxfId="62" priority="850"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="850"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K124">
-    <cfRule type="duplicateValues" dxfId="61" priority="852"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="852"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K124">
-    <cfRule type="duplicateValues" dxfId="60" priority="853"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="854"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="853"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="854"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5:K127">
-    <cfRule type="duplicateValues" dxfId="58" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="855"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="855"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB6:BB126">
-    <cfRule type="expression" dxfId="56" priority="1019">
+    <cfRule type="expression" dxfId="73" priority="1019">
       <formula>$AC6&lt;&gt;""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="55" priority="1020">
+    <cfRule type="expression" dxfId="72" priority="1020">
       <formula>$AB6&lt;&gt;""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="54" priority="1021">
+    <cfRule type="expression" dxfId="71" priority="1021">
       <formula>$T6&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19436,7 +19286,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{499C2CF5-E587-4B95-9659-4BA38F5371D8}">
-  <dimension ref="A1:BF90"/>
+  <dimension ref="A1:BF97"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.42578125" bestFit="1" customWidth="1"/>
@@ -19734,7 +19584,7 @@
         <v>1195.7700000000004</v>
       </c>
       <c r="T6" s="46">
-        <f t="shared" ref="T6:T89" si="0">+R6-S6</f>
+        <f t="shared" ref="T6:T96" si="0">+R6-S6</f>
         <v>3897.2</v>
       </c>
       <c r="U6" s="46">
@@ -19764,7 +19614,7 @@
       <c r="AG6" s="74"/>
       <c r="AH6" s="75"/>
       <c r="AI6" s="75">
-        <f t="shared" ref="AI6:AI89" si="1">+AG6+AH6</f>
+        <f t="shared" ref="AI6:AI96" si="1">+AG6+AH6</f>
         <v>0</v>
       </c>
       <c r="AJ6" s="32"/>
@@ -19774,15 +19624,15 @@
       <c r="AN6" s="33"/>
       <c r="AO6" s="33"/>
       <c r="AP6" s="34">
-        <f t="shared" ref="AP6:AP89" si="2">ROUNDUP((AO6-AM6+(AO6&lt;AM6))*24,0)</f>
+        <f t="shared" ref="AP6:AP96" si="2">ROUNDUP((AO6-AM6+(AO6&lt;AM6))*24,0)</f>
         <v>0</v>
       </c>
       <c r="AQ6" s="32">
-        <f t="shared" ref="AQ6:AQ89" si="3">IF(AP6&gt;5,(AP6-5),0)</f>
+        <f t="shared" ref="AQ6:AQ96" si="3">IF(AP6&gt;5,(AP6-5),0)</f>
         <v>0</v>
       </c>
       <c r="AR6" s="32">
-        <f t="shared" ref="AR6:AR89" si="4">+AQ6*8850</f>
+        <f t="shared" ref="AR6:AR96" si="4">+AQ6*8850</f>
         <v>0</v>
       </c>
       <c r="AS6" s="32"/>
@@ -19798,16 +19648,16 @@
         <v>3897.2</v>
       </c>
       <c r="BC6" s="45">
-        <f>+X6</f>
+        <f t="shared" ref="BC6:BC37" si="5">+X6</f>
         <v>3787</v>
       </c>
       <c r="BD6" s="45"/>
       <c r="BE6" s="45">
-        <f t="shared" ref="BE6:BE77" si="5">+BB6-BC6</f>
+        <f t="shared" ref="BE6:BE77" si="6">+BB6-BC6</f>
         <v>110.19999999999982</v>
       </c>
       <c r="BF6" s="39">
-        <f t="shared" ref="BF6:BF77" si="6">+BE6/BB6</f>
+        <f t="shared" ref="BF6:BF77" si="7">+BE6/BB6</f>
         <v>2.8276711485168794E-2</v>
       </c>
     </row>
@@ -19927,16 +19777,16 @@
         <v>3906.7</v>
       </c>
       <c r="BC7" s="45">
-        <f>+X7</f>
+        <f t="shared" si="5"/>
         <v>3844</v>
       </c>
       <c r="BD7" s="45"/>
       <c r="BE7" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>62.699999999999818</v>
       </c>
       <c r="BF7" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1.6049351114751535E-2</v>
       </c>
     </row>
@@ -20056,16 +19906,16 @@
         <v>3568.7</v>
       </c>
       <c r="BC8" s="45">
-        <f>+X8</f>
+        <f t="shared" si="5"/>
         <v>3476.8</v>
       </c>
       <c r="BD8" s="45"/>
       <c r="BE8" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>91.899999999999636</v>
       </c>
       <c r="BF8" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2.5751674279149168E-2</v>
       </c>
     </row>
@@ -20185,16 +20035,16 @@
         <v>4135.0600000000004</v>
       </c>
       <c r="BC9" s="45">
-        <f>+X9</f>
+        <f t="shared" si="5"/>
         <v>4148.2</v>
       </c>
       <c r="BD9" s="45"/>
       <c r="BE9" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-13.139999999999418</v>
       </c>
       <c r="BF9" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-3.177704797511866E-3</v>
       </c>
     </row>
@@ -20314,16 +20164,16 @@
         <v>3969.81</v>
       </c>
       <c r="BC10" s="45">
-        <f>+X10</f>
+        <f t="shared" si="5"/>
         <v>4026.2</v>
       </c>
       <c r="BD10" s="45"/>
       <c r="BE10" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-56.389999999999873</v>
       </c>
       <c r="BF10" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-1.4204710049095516E-2</v>
       </c>
     </row>
@@ -20443,16 +20293,16 @@
         <v>3830.4</v>
       </c>
       <c r="BC11" s="45">
-        <f>+X11</f>
+        <f t="shared" si="5"/>
         <v>3723.4</v>
       </c>
       <c r="BD11" s="45"/>
       <c r="BE11" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>107</v>
       </c>
       <c r="BF11" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2.7934419381787801E-2</v>
       </c>
     </row>
@@ -20572,16 +20422,16 @@
         <v>3426.75</v>
       </c>
       <c r="BC12" s="45">
-        <f>+X12</f>
+        <f t="shared" si="5"/>
         <v>3368.8</v>
       </c>
       <c r="BD12" s="45"/>
       <c r="BE12" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>57.949999999999818</v>
       </c>
       <c r="BF12" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1.6911067337856515E-2</v>
       </c>
     </row>
@@ -20701,16 +20551,16 @@
         <v>3937.35</v>
       </c>
       <c r="BC13" s="45">
-        <f>+X13</f>
+        <f t="shared" si="5"/>
         <v>3823.2</v>
       </c>
       <c r="BD13" s="45"/>
       <c r="BE13" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>114.15000000000009</v>
       </c>
       <c r="BF13" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2.8991580631643133E-2</v>
       </c>
     </row>
@@ -20830,16 +20680,16 @@
         <v>3761.06</v>
       </c>
       <c r="BC14" s="45">
-        <f>+X14</f>
+        <f t="shared" si="5"/>
         <v>3802.8</v>
       </c>
       <c r="BD14" s="45"/>
       <c r="BE14" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-41.740000000000236</v>
       </c>
       <c r="BF14" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-1.1097935156578262E-2</v>
       </c>
     </row>
@@ -20895,7 +20745,7 @@
         <v>1196.9900000000002</v>
       </c>
       <c r="T15" s="46">
-        <f t="shared" ref="T15:T86" si="7">+R15-S15</f>
+        <f t="shared" ref="T15:T86" si="8">+R15-S15</f>
         <v>3915.1</v>
       </c>
       <c r="U15" s="46">
@@ -20925,7 +20775,7 @@
       <c r="AG15" s="74"/>
       <c r="AH15" s="75"/>
       <c r="AI15" s="75">
-        <f t="shared" ref="AI15:AI86" si="8">+AG15+AH15</f>
+        <f t="shared" ref="AI15:AI86" si="9">+AG15+AH15</f>
         <v>0</v>
       </c>
       <c r="AJ15" s="32"/>
@@ -20935,15 +20785,15 @@
       <c r="AN15" s="33"/>
       <c r="AO15" s="33"/>
       <c r="AP15" s="34">
-        <f t="shared" ref="AP15:AP86" si="9">ROUNDUP((AO15-AM15+(AO15&lt;AM15))*24,0)</f>
+        <f t="shared" ref="AP15:AP86" si="10">ROUNDUP((AO15-AM15+(AO15&lt;AM15))*24,0)</f>
         <v>0</v>
       </c>
       <c r="AQ15" s="32">
-        <f t="shared" ref="AQ15:AQ86" si="10">IF(AP15&gt;5,(AP15-5),0)</f>
+        <f t="shared" ref="AQ15:AQ86" si="11">IF(AP15&gt;5,(AP15-5),0)</f>
         <v>0</v>
       </c>
       <c r="AR15" s="32">
-        <f t="shared" ref="AR15:AR86" si="11">+AQ15*8850</f>
+        <f t="shared" ref="AR15:AR86" si="12">+AQ15*8850</f>
         <v>0</v>
       </c>
       <c r="AS15" s="32"/>
@@ -20959,16 +20809,16 @@
         <v>3915.1</v>
       </c>
       <c r="BC15" s="45">
-        <f>+X15</f>
+        <f t="shared" si="5"/>
         <v>3799.8</v>
       </c>
       <c r="BD15" s="45"/>
       <c r="BE15" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>115.29999999999973</v>
       </c>
       <c r="BF15" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2.9450077903501758E-2</v>
       </c>
     </row>
@@ -21024,7 +20874,7 @@
         <v>1175.29</v>
       </c>
       <c r="T16" s="46">
-        <f t="shared" ref="T16:T17" si="12">+R16-S16</f>
+        <f t="shared" ref="T16:T17" si="13">+R16-S16</f>
         <v>3826.8</v>
       </c>
       <c r="U16" s="46">
@@ -21054,7 +20904,7 @@
       <c r="AG16" s="74"/>
       <c r="AH16" s="75"/>
       <c r="AI16" s="75">
-        <f t="shared" ref="AI16:AI17" si="13">+AG16+AH16</f>
+        <f t="shared" ref="AI16:AI17" si="14">+AG16+AH16</f>
         <v>0</v>
       </c>
       <c r="AJ16" s="32"/>
@@ -21064,15 +20914,15 @@
       <c r="AN16" s="33"/>
       <c r="AO16" s="33"/>
       <c r="AP16" s="34">
-        <f t="shared" ref="AP16:AP17" si="14">ROUNDUP((AO16-AM16+(AO16&lt;AM16))*24,0)</f>
+        <f t="shared" ref="AP16:AP17" si="15">ROUNDUP((AO16-AM16+(AO16&lt;AM16))*24,0)</f>
         <v>0</v>
       </c>
       <c r="AQ16" s="32">
-        <f t="shared" ref="AQ16:AQ17" si="15">IF(AP16&gt;5,(AP16-5),0)</f>
+        <f t="shared" ref="AQ16:AQ17" si="16">IF(AP16&gt;5,(AP16-5),0)</f>
         <v>0</v>
       </c>
       <c r="AR16" s="32">
-        <f t="shared" ref="AR16:AR17" si="16">+AQ16*8850</f>
+        <f t="shared" ref="AR16:AR17" si="17">+AQ16*8850</f>
         <v>0</v>
       </c>
       <c r="AS16" s="32"/>
@@ -21088,16 +20938,16 @@
         <v>3826.75</v>
       </c>
       <c r="BC16" s="45">
-        <f>+X16</f>
+        <f t="shared" si="5"/>
         <v>3709.2</v>
       </c>
       <c r="BD16" s="45"/>
       <c r="BE16" s="45">
-        <f t="shared" ref="BE16:BE17" si="17">+BB16-BC16</f>
+        <f t="shared" ref="BE16:BE17" si="18">+BB16-BC16</f>
         <v>117.55000000000018</v>
       </c>
       <c r="BF16" s="39">
-        <f t="shared" ref="BF16:BF17" si="18">+BE16/BB16</f>
+        <f t="shared" ref="BF16:BF17" si="19">+BE16/BB16</f>
         <v>3.0717972169595657E-2</v>
       </c>
     </row>
@@ -21153,7 +21003,7 @@
         <v>1149.48</v>
       </c>
       <c r="T17" s="46">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>3769.4</v>
       </c>
       <c r="U17" s="46">
@@ -21183,7 +21033,7 @@
       <c r="AG17" s="74"/>
       <c r="AH17" s="75"/>
       <c r="AI17" s="75">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AJ17" s="32"/>
@@ -21193,15 +21043,15 @@
       <c r="AN17" s="33"/>
       <c r="AO17" s="33"/>
       <c r="AP17" s="34">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AQ17" s="32">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AR17" s="32">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AS17" s="32"/>
@@ -21217,16 +21067,16 @@
         <v>3769.4</v>
       </c>
       <c r="BC17" s="45">
-        <f>+X17</f>
+        <f t="shared" si="5"/>
         <v>3682.6</v>
       </c>
       <c r="BD17" s="45"/>
       <c r="BE17" s="45">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>86.800000000000182</v>
       </c>
       <c r="BF17" s="39">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>2.3027537539130945E-2</v>
       </c>
     </row>
@@ -21282,7 +21132,7 @@
         <v>1150.6500000000005</v>
       </c>
       <c r="T18" s="46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3799.7</v>
       </c>
       <c r="U18" s="46">
@@ -21312,7 +21162,7 @@
       <c r="AG18" s="74"/>
       <c r="AH18" s="75"/>
       <c r="AI18" s="75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ18" s="32"/>
@@ -21322,15 +21172,15 @@
       <c r="AN18" s="33"/>
       <c r="AO18" s="33"/>
       <c r="AP18" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ18" s="32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR18" s="32">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS18" s="32"/>
@@ -21346,16 +21196,16 @@
         <v>3841.65</v>
       </c>
       <c r="BC18" s="45">
-        <f>+X18</f>
+        <f t="shared" si="5"/>
         <v>3936.8</v>
       </c>
       <c r="BD18" s="45"/>
       <c r="BE18" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-95.150000000000091</v>
       </c>
       <c r="BF18" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-2.476800333190168E-2</v>
       </c>
     </row>
@@ -21411,7 +21261,7 @@
         <v>1179.6700000000005</v>
       </c>
       <c r="T19" s="46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3935.6</v>
       </c>
       <c r="U19" s="46">
@@ -21441,7 +21291,7 @@
       <c r="AG19" s="74"/>
       <c r="AH19" s="75"/>
       <c r="AI19" s="75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ19" s="32"/>
@@ -21451,15 +21301,15 @@
       <c r="AN19" s="33"/>
       <c r="AO19" s="33"/>
       <c r="AP19" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ19" s="32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR19" s="32">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS19" s="32"/>
@@ -21475,16 +21325,16 @@
         <v>3935.6</v>
       </c>
       <c r="BC19" s="45">
-        <f>+X19</f>
+        <f t="shared" si="5"/>
         <v>3869.6</v>
       </c>
       <c r="BD19" s="45"/>
       <c r="BE19" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>66</v>
       </c>
       <c r="BF19" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1.6769996950909645E-2</v>
       </c>
     </row>
@@ -21540,7 +21390,7 @@
         <v>1187.3400000000001</v>
       </c>
       <c r="T20" s="46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3919.2</v>
       </c>
       <c r="U20" s="46">
@@ -21570,7 +21420,7 @@
       <c r="AG20" s="74"/>
       <c r="AH20" s="75"/>
       <c r="AI20" s="75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ20" s="32"/>
@@ -21580,15 +21430,15 @@
       <c r="AN20" s="33"/>
       <c r="AO20" s="33"/>
       <c r="AP20" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ20" s="32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR20" s="32">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS20" s="32"/>
@@ -21604,16 +21454,16 @@
         <v>3919.15</v>
       </c>
       <c r="BC20" s="45">
-        <f>+X20</f>
+        <f t="shared" si="5"/>
         <v>3997.8</v>
       </c>
       <c r="BD20" s="45"/>
       <c r="BE20" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-78.650000000000091</v>
       </c>
       <c r="BF20" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-2.0068127017337966E-2</v>
       </c>
     </row>
@@ -21669,7 +21519,7 @@
         <v>1162.4000000000005</v>
       </c>
       <c r="T21" s="46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3754.2</v>
       </c>
       <c r="U21" s="46">
@@ -21699,7 +21549,7 @@
       <c r="AG21" s="74"/>
       <c r="AH21" s="75"/>
       <c r="AI21" s="75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ21" s="32"/>
@@ -21709,15 +21559,15 @@
       <c r="AN21" s="33"/>
       <c r="AO21" s="33"/>
       <c r="AP21" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ21" s="32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR21" s="32">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS21" s="32"/>
@@ -21733,16 +21583,16 @@
         <v>3766.35</v>
       </c>
       <c r="BC21" s="45">
-        <f>+X21</f>
+        <f t="shared" si="5"/>
         <v>3729.4</v>
       </c>
       <c r="BD21" s="45"/>
       <c r="BE21" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>36.949999999999818</v>
       </c>
       <c r="BF21" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>9.8105592948079228E-3</v>
       </c>
     </row>
@@ -21798,7 +21648,7 @@
         <v>1231.8599999999997</v>
       </c>
       <c r="T22" s="46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4049.8</v>
       </c>
       <c r="U22" s="46">
@@ -21828,7 +21678,7 @@
       <c r="AG22" s="74"/>
       <c r="AH22" s="75"/>
       <c r="AI22" s="75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ22" s="32"/>
@@ -21838,15 +21688,15 @@
       <c r="AN22" s="33"/>
       <c r="AO22" s="33"/>
       <c r="AP22" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ22" s="32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR22" s="32">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS22" s="32"/>
@@ -21862,16 +21712,16 @@
         <v>4049.75</v>
       </c>
       <c r="BC22" s="45">
-        <f>+X22</f>
+        <f t="shared" si="5"/>
         <v>3931.6</v>
       </c>
       <c r="BD22" s="45"/>
       <c r="BE22" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>118.15000000000009</v>
       </c>
       <c r="BF22" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2.9174640409901868E-2</v>
       </c>
     </row>
@@ -21927,7 +21777,7 @@
         <v>1232.04</v>
       </c>
       <c r="T23" s="46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4044.5</v>
       </c>
       <c r="U23" s="46">
@@ -21957,7 +21807,7 @@
       <c r="AG23" s="74"/>
       <c r="AH23" s="75"/>
       <c r="AI23" s="75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ23" s="32"/>
@@ -21967,15 +21817,15 @@
       <c r="AN23" s="33"/>
       <c r="AO23" s="33"/>
       <c r="AP23" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ23" s="32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR23" s="32">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS23" s="32"/>
@@ -21991,16 +21841,16 @@
         <v>4044.5</v>
       </c>
       <c r="BC23" s="45">
-        <f>+X23</f>
+        <f t="shared" si="5"/>
         <v>4171.8</v>
       </c>
       <c r="BD23" s="45"/>
       <c r="BE23" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-127.30000000000018</v>
       </c>
       <c r="BF23" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-3.14748423785388E-2</v>
       </c>
     </row>
@@ -22056,7 +21906,7 @@
         <v>1128.7800000000002</v>
       </c>
       <c r="T24" s="46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3714.4</v>
       </c>
       <c r="U24" s="46">
@@ -22086,7 +21936,7 @@
       <c r="AG24" s="74"/>
       <c r="AH24" s="75"/>
       <c r="AI24" s="75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ24" s="32"/>
@@ -22096,15 +21946,15 @@
       <c r="AN24" s="33"/>
       <c r="AO24" s="33"/>
       <c r="AP24" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ24" s="32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR24" s="32">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS24" s="32"/>
@@ -22120,16 +21970,16 @@
         <v>3714.4</v>
       </c>
       <c r="BC24" s="45">
-        <f>+X24</f>
+        <f t="shared" si="5"/>
         <v>3789.4</v>
       </c>
       <c r="BD24" s="45"/>
       <c r="BE24" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-75</v>
       </c>
       <c r="BF24" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-2.0191686409648933E-2</v>
       </c>
     </row>
@@ -22185,7 +22035,7 @@
         <v>1131.3999999999996</v>
       </c>
       <c r="T25" s="46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3885</v>
       </c>
       <c r="U25" s="46">
@@ -22215,7 +22065,7 @@
       <c r="AG25" s="74"/>
       <c r="AH25" s="75"/>
       <c r="AI25" s="75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ25" s="32"/>
@@ -22225,15 +22075,15 @@
       <c r="AN25" s="33"/>
       <c r="AO25" s="33"/>
       <c r="AP25" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ25" s="32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR25" s="32">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS25" s="32"/>
@@ -22249,16 +22099,16 @@
         <v>3905.1</v>
       </c>
       <c r="BC25" s="45">
-        <f>+X25</f>
+        <f t="shared" si="5"/>
         <v>3785.2</v>
       </c>
       <c r="BD25" s="45"/>
       <c r="BE25" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>119.90000000000009</v>
       </c>
       <c r="BF25" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3.0703439092468848E-2</v>
       </c>
     </row>
@@ -22314,7 +22164,7 @@
         <v>1135.2999999999997</v>
       </c>
       <c r="T26" s="46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3684.6</v>
       </c>
       <c r="U26" s="46">
@@ -22344,7 +22194,7 @@
       <c r="AG26" s="74"/>
       <c r="AH26" s="75"/>
       <c r="AI26" s="75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ26" s="32"/>
@@ -22354,15 +22204,15 @@
       <c r="AN26" s="33"/>
       <c r="AO26" s="33"/>
       <c r="AP26" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ26" s="32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR26" s="32">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS26" s="32"/>
@@ -22378,16 +22228,16 @@
         <v>3684.6</v>
       </c>
       <c r="BC26" s="45">
-        <f>+X26</f>
+        <f t="shared" si="5"/>
         <v>3665.8</v>
       </c>
       <c r="BD26" s="45"/>
       <c r="BE26" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>18.799999999999727</v>
       </c>
       <c r="BF26" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>5.1023177549801135E-3</v>
       </c>
     </row>
@@ -22443,7 +22293,7 @@
         <v>1202.0099999999998</v>
       </c>
       <c r="T27" s="46">
-        <f t="shared" ref="T27:T35" si="19">+R27-S27</f>
+        <f t="shared" ref="T27:T35" si="20">+R27-S27</f>
         <v>3910.1</v>
       </c>
       <c r="U27" s="46">
@@ -22473,7 +22323,7 @@
       <c r="AG27" s="74"/>
       <c r="AH27" s="75"/>
       <c r="AI27" s="75">
-        <f t="shared" ref="AI27:AI35" si="20">+AG27+AH27</f>
+        <f t="shared" ref="AI27:AI35" si="21">+AG27+AH27</f>
         <v>0</v>
       </c>
       <c r="AJ27" s="32"/>
@@ -22483,15 +22333,15 @@
       <c r="AN27" s="33"/>
       <c r="AO27" s="33"/>
       <c r="AP27" s="34">
-        <f t="shared" ref="AP27:AP35" si="21">ROUNDUP((AO27-AM27+(AO27&lt;AM27))*24,0)</f>
+        <f t="shared" ref="AP27:AP35" si="22">ROUNDUP((AO27-AM27+(AO27&lt;AM27))*24,0)</f>
         <v>0</v>
       </c>
       <c r="AQ27" s="32">
-        <f t="shared" ref="AQ27:AQ35" si="22">IF(AP27&gt;5,(AP27-5),0)</f>
+        <f t="shared" ref="AQ27:AQ35" si="23">IF(AP27&gt;5,(AP27-5),0)</f>
         <v>0</v>
       </c>
       <c r="AR27" s="32">
-        <f t="shared" ref="AR27:AR35" si="23">+AQ27*8850</f>
+        <f t="shared" ref="AR27:AR35" si="24">+AQ27*8850</f>
         <v>0</v>
       </c>
       <c r="AS27" s="32"/>
@@ -22507,16 +22357,16 @@
         <v>3910.1</v>
       </c>
       <c r="BC27" s="45">
-        <f>+X27</f>
+        <f t="shared" si="5"/>
         <v>3988.4</v>
       </c>
       <c r="BD27" s="45"/>
       <c r="BE27" s="45">
-        <f t="shared" ref="BE27:BE35" si="24">+BB27-BC27</f>
+        <f t="shared" ref="BE27:BE35" si="25">+BB27-BC27</f>
         <v>-78.300000000000182</v>
       </c>
       <c r="BF27" s="39">
-        <f t="shared" ref="BF27:BF35" si="25">+BE27/BB27</f>
+        <f t="shared" ref="BF27:BF35" si="26">+BE27/BB27</f>
         <v>-2.0025063297613919E-2</v>
       </c>
     </row>
@@ -22572,7 +22422,7 @@
         <v>1238.7600000000002</v>
       </c>
       <c r="T28" s="46">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4031</v>
       </c>
       <c r="U28" s="46">
@@ -22602,7 +22452,7 @@
       <c r="AG28" s="74"/>
       <c r="AH28" s="75"/>
       <c r="AI28" s="75">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AJ28" s="32"/>
@@ -22612,15 +22462,15 @@
       <c r="AN28" s="33"/>
       <c r="AO28" s="33"/>
       <c r="AP28" s="34">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AQ28" s="32">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AR28" s="32">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AS28" s="32"/>
@@ -22636,16 +22486,16 @@
         <v>4030.95</v>
       </c>
       <c r="BC28" s="45">
-        <f>+X28</f>
+        <f t="shared" si="5"/>
         <v>3923.8</v>
       </c>
       <c r="BD28" s="45"/>
       <c r="BE28" s="45">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>107.14999999999964</v>
       </c>
       <c r="BF28" s="39">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>2.6581823143427639E-2</v>
       </c>
     </row>
@@ -22701,7 +22551,7 @@
         <v>1043.8000000000002</v>
       </c>
       <c r="T29" s="46">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>3429.5</v>
       </c>
       <c r="U29" s="46">
@@ -22731,7 +22581,7 @@
       <c r="AG29" s="74"/>
       <c r="AH29" s="75"/>
       <c r="AI29" s="75">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AJ29" s="32"/>
@@ -22741,15 +22591,15 @@
       <c r="AN29" s="33"/>
       <c r="AO29" s="33"/>
       <c r="AP29" s="34">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AQ29" s="32">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AR29" s="32">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AS29" s="32"/>
@@ -22765,16 +22615,16 @@
         <v>3429.45</v>
       </c>
       <c r="BC29" s="45">
-        <f>+X29</f>
+        <f t="shared" si="5"/>
         <v>3362</v>
       </c>
       <c r="BD29" s="45"/>
       <c r="BE29" s="45">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>67.449999999999818</v>
       </c>
       <c r="BF29" s="39">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>1.966787677324347E-2</v>
       </c>
     </row>
@@ -22830,7 +22680,7 @@
         <v>1222.7600000000002</v>
       </c>
       <c r="T30" s="46">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4078</v>
       </c>
       <c r="U30" s="46">
@@ -22860,7 +22710,7 @@
       <c r="AG30" s="74"/>
       <c r="AH30" s="75"/>
       <c r="AI30" s="75">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AJ30" s="32"/>
@@ -22870,15 +22720,15 @@
       <c r="AN30" s="33"/>
       <c r="AO30" s="33"/>
       <c r="AP30" s="34">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AQ30" s="32">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AR30" s="32">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AS30" s="32"/>
@@ -22894,16 +22744,16 @@
         <v>4077.95</v>
       </c>
       <c r="BC30" s="45">
-        <f>+X30</f>
+        <f t="shared" si="5"/>
         <v>4099.8</v>
       </c>
       <c r="BD30" s="45"/>
       <c r="BE30" s="45">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-21.850000000000364</v>
       </c>
       <c r="BF30" s="39">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>-5.3580843315882646E-3</v>
       </c>
     </row>
@@ -22959,7 +22809,7 @@
         <v>1187.5900000000001</v>
       </c>
       <c r="T31" s="46">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>3907.2</v>
       </c>
       <c r="U31" s="46">
@@ -22989,7 +22839,7 @@
       <c r="AG31" s="74"/>
       <c r="AH31" s="75"/>
       <c r="AI31" s="75">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AJ31" s="32"/>
@@ -22999,15 +22849,15 @@
       <c r="AN31" s="33"/>
       <c r="AO31" s="33"/>
       <c r="AP31" s="34">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AQ31" s="32">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AR31" s="32">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AS31" s="32"/>
@@ -23023,16 +22873,16 @@
         <v>3907.2</v>
       </c>
       <c r="BC31" s="45">
-        <f>+X31</f>
+        <f t="shared" si="5"/>
         <v>3884.2</v>
       </c>
       <c r="BD31" s="45"/>
       <c r="BE31" s="45">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>23</v>
       </c>
       <c r="BF31" s="39">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>5.8865683865683867E-3</v>
       </c>
     </row>
@@ -23088,7 +22938,7 @@
         <v>1215.58</v>
       </c>
       <c r="T32" s="46">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>3982.3</v>
       </c>
       <c r="U32" s="46">
@@ -23118,7 +22968,7 @@
       <c r="AG32" s="74"/>
       <c r="AH32" s="75"/>
       <c r="AI32" s="75">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AJ32" s="32"/>
@@ -23128,15 +22978,15 @@
       <c r="AN32" s="33"/>
       <c r="AO32" s="33"/>
       <c r="AP32" s="34">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AQ32" s="32">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AR32" s="32">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AS32" s="32"/>
@@ -23152,16 +23002,16 @@
         <v>3982.3</v>
       </c>
       <c r="BC32" s="45">
-        <f>+X32</f>
+        <f t="shared" si="5"/>
         <v>3944.4</v>
       </c>
       <c r="BD32" s="45"/>
       <c r="BE32" s="45">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>37.900000000000091</v>
       </c>
       <c r="BF32" s="39">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>9.5171132260251836E-3</v>
       </c>
     </row>
@@ -23217,7 +23067,7 @@
         <v>1208.6799999999998</v>
       </c>
       <c r="T33" s="46">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>3995.9</v>
       </c>
       <c r="U33" s="46">
@@ -23247,7 +23097,7 @@
       <c r="AG33" s="74"/>
       <c r="AH33" s="75"/>
       <c r="AI33" s="75">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AJ33" s="32"/>
@@ -23257,15 +23107,15 @@
       <c r="AN33" s="33"/>
       <c r="AO33" s="33"/>
       <c r="AP33" s="34">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AQ33" s="32">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AR33" s="32">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AS33" s="32"/>
@@ -23281,16 +23131,16 @@
         <v>4188.25</v>
       </c>
       <c r="BC33" s="45">
-        <f>+X33</f>
+        <f t="shared" si="5"/>
         <v>4022.2</v>
       </c>
       <c r="BD33" s="45"/>
       <c r="BE33" s="45">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>166.05000000000018</v>
       </c>
       <c r="BF33" s="39">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>3.9646630454247045E-2</v>
       </c>
     </row>
@@ -23346,7 +23196,7 @@
         <v>1092.1600000000003</v>
       </c>
       <c r="T34" s="46">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>3551.4</v>
       </c>
       <c r="U34" s="46">
@@ -23376,7 +23226,7 @@
       <c r="AG34" s="74"/>
       <c r="AH34" s="75"/>
       <c r="AI34" s="75">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AJ34" s="32"/>
@@ -23386,15 +23236,15 @@
       <c r="AN34" s="33"/>
       <c r="AO34" s="33"/>
       <c r="AP34" s="34">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AQ34" s="32">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AR34" s="32">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AS34" s="32"/>
@@ -23410,16 +23260,16 @@
         <v>3551.35</v>
       </c>
       <c r="BC34" s="45">
-        <f>+X34</f>
+        <f t="shared" si="5"/>
         <v>3585.4</v>
       </c>
       <c r="BD34" s="45"/>
       <c r="BE34" s="45">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-34.050000000000182</v>
       </c>
       <c r="BF34" s="39">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>-9.5879031917440356E-3</v>
       </c>
     </row>
@@ -23475,7 +23325,7 @@
         <v>1162.42</v>
       </c>
       <c r="T35" s="46">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>3855.5</v>
       </c>
       <c r="U35" s="46">
@@ -23505,7 +23355,7 @@
       <c r="AG35" s="74"/>
       <c r="AH35" s="75"/>
       <c r="AI35" s="75">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AJ35" s="32"/>
@@ -23515,15 +23365,15 @@
       <c r="AN35" s="33"/>
       <c r="AO35" s="33"/>
       <c r="AP35" s="34">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AQ35" s="32">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AR35" s="32">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AS35" s="32"/>
@@ -23539,16 +23389,16 @@
         <v>3855.45</v>
       </c>
       <c r="BC35" s="45">
-        <f>+X35</f>
+        <f t="shared" si="5"/>
         <v>3969</v>
       </c>
       <c r="BD35" s="45"/>
       <c r="BE35" s="45">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-113.55000000000018</v>
       </c>
       <c r="BF35" s="39">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>-2.9451814963233913E-2</v>
       </c>
     </row>
@@ -23604,7 +23454,7 @@
         <v>1202.5800000000004</v>
       </c>
       <c r="T36" s="46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3903.1</v>
       </c>
       <c r="U36" s="46">
@@ -23634,7 +23484,7 @@
       <c r="AG36" s="74"/>
       <c r="AH36" s="75"/>
       <c r="AI36" s="75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ36" s="32"/>
@@ -23644,15 +23494,15 @@
       <c r="AN36" s="33"/>
       <c r="AO36" s="33"/>
       <c r="AP36" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ36" s="32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR36" s="32">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS36" s="32"/>
@@ -23668,16 +23518,16 @@
         <v>3903.05</v>
       </c>
       <c r="BC36" s="45">
-        <f>+X36</f>
+        <f t="shared" si="5"/>
         <v>3800.4</v>
       </c>
       <c r="BD36" s="45"/>
       <c r="BE36" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>102.65000000000009</v>
       </c>
       <c r="BF36" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2.6299944914874286E-2</v>
       </c>
     </row>
@@ -23733,7 +23583,7 @@
         <v>1169.4599999999996</v>
       </c>
       <c r="T37" s="46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3841.9</v>
       </c>
       <c r="U37" s="46">
@@ -23763,7 +23613,7 @@
       <c r="AG37" s="74"/>
       <c r="AH37" s="75"/>
       <c r="AI37" s="75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ37" s="32"/>
@@ -23773,15 +23623,15 @@
       <c r="AN37" s="33"/>
       <c r="AO37" s="33"/>
       <c r="AP37" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ37" s="32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR37" s="32">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS37" s="32"/>
@@ -23797,16 +23647,16 @@
         <v>3841.85</v>
       </c>
       <c r="BC37" s="45">
-        <f>+X37</f>
+        <f t="shared" si="5"/>
         <v>3788.6</v>
       </c>
       <c r="BD37" s="45"/>
       <c r="BE37" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>53.25</v>
       </c>
       <c r="BF37" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1.3860509910589951E-2</v>
       </c>
     </row>
@@ -23862,7 +23712,7 @@
         <v>1193.0200000000004</v>
       </c>
       <c r="T38" s="46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3934</v>
       </c>
       <c r="U38" s="46">
@@ -23892,7 +23742,7 @@
       <c r="AG38" s="74"/>
       <c r="AH38" s="75"/>
       <c r="AI38" s="75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ38" s="32"/>
@@ -23902,15 +23752,15 @@
       <c r="AN38" s="33"/>
       <c r="AO38" s="33"/>
       <c r="AP38" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ38" s="32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR38" s="32">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS38" s="32"/>
@@ -23926,16 +23776,16 @@
         <v>4057.01</v>
       </c>
       <c r="BC38" s="45">
-        <f>+X38</f>
+        <f t="shared" ref="BC38:BC69" si="27">+X38</f>
         <v>4142</v>
       </c>
       <c r="BD38" s="45"/>
       <c r="BE38" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-84.989999999999782</v>
       </c>
       <c r="BF38" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-2.0948925440164006E-2</v>
       </c>
     </row>
@@ -23991,7 +23841,7 @@
         <v>1210.5999999999995</v>
       </c>
       <c r="T39" s="46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3973.8</v>
       </c>
       <c r="U39" s="46">
@@ -24021,7 +23871,7 @@
       <c r="AG39" s="74"/>
       <c r="AH39" s="75"/>
       <c r="AI39" s="75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ39" s="32"/>
@@ -24031,15 +23881,15 @@
       <c r="AN39" s="33"/>
       <c r="AO39" s="33"/>
       <c r="AP39" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ39" s="32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR39" s="32">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS39" s="32"/>
@@ -24055,16 +23905,16 @@
         <v>3973.75</v>
       </c>
       <c r="BC39" s="45">
-        <f>+X39</f>
+        <f t="shared" si="27"/>
         <v>3862.8</v>
       </c>
       <c r="BD39" s="45"/>
       <c r="BE39" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>110.94999999999982</v>
       </c>
       <c r="BF39" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2.7920729789241854E-2</v>
       </c>
     </row>
@@ -24120,7 +23970,7 @@
         <v>1121.9000000000005</v>
       </c>
       <c r="T40" s="46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3737.7</v>
       </c>
       <c r="U40" s="46">
@@ -24150,7 +24000,7 @@
       <c r="AG40" s="74"/>
       <c r="AH40" s="75"/>
       <c r="AI40" s="75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ40" s="32"/>
@@ -24160,15 +24010,15 @@
       <c r="AN40" s="33"/>
       <c r="AO40" s="33"/>
       <c r="AP40" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ40" s="32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR40" s="32">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS40" s="32"/>
@@ -24184,16 +24034,16 @@
         <v>3765.15</v>
       </c>
       <c r="BC40" s="45">
-        <f>+X40</f>
+        <f t="shared" si="27"/>
         <v>3936</v>
       </c>
       <c r="BD40" s="45"/>
       <c r="BE40" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-170.84999999999991</v>
       </c>
       <c r="BF40" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-4.5376678219991209E-2</v>
       </c>
     </row>
@@ -24249,7 +24099,7 @@
         <v>1149.9299999999994</v>
       </c>
       <c r="T41" s="46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3785.3</v>
       </c>
       <c r="U41" s="46">
@@ -24279,7 +24129,7 @@
       <c r="AG41" s="74"/>
       <c r="AH41" s="75"/>
       <c r="AI41" s="75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ41" s="32"/>
@@ -24289,15 +24139,15 @@
       <c r="AN41" s="33"/>
       <c r="AO41" s="33"/>
       <c r="AP41" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ41" s="32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR41" s="32">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS41" s="32"/>
@@ -24313,16 +24163,16 @@
         <v>3785.25</v>
       </c>
       <c r="BC41" s="45">
-        <f>+X41</f>
+        <f t="shared" si="27"/>
         <v>3668.8</v>
       </c>
       <c r="BD41" s="45"/>
       <c r="BE41" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>116.44999999999982</v>
       </c>
       <c r="BF41" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3.0764150320322255E-2</v>
       </c>
     </row>
@@ -24378,7 +24228,7 @@
         <v>1131.5699999999997</v>
       </c>
       <c r="T42" s="46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3692.5</v>
       </c>
       <c r="U42" s="46">
@@ -24408,7 +24258,7 @@
       <c r="AG42" s="74"/>
       <c r="AH42" s="75"/>
       <c r="AI42" s="75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ42" s="32"/>
@@ -24418,15 +24268,15 @@
       <c r="AN42" s="33"/>
       <c r="AO42" s="33"/>
       <c r="AP42" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ42" s="32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR42" s="32">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS42" s="32"/>
@@ -24442,16 +24292,16 @@
         <v>3692.5</v>
       </c>
       <c r="BC42" s="45">
-        <f>+X42</f>
+        <f t="shared" si="27"/>
         <v>3548.4</v>
       </c>
       <c r="BD42" s="45"/>
       <c r="BE42" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>144.09999999999991</v>
       </c>
       <c r="BF42" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3.9025050778605255E-2</v>
       </c>
     </row>
@@ -24507,7 +24357,7 @@
         <v>1166.0999999999999</v>
       </c>
       <c r="T43" s="46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3738.9</v>
       </c>
       <c r="U43" s="46">
@@ -24537,7 +24387,7 @@
       <c r="AG43" s="74"/>
       <c r="AH43" s="75"/>
       <c r="AI43" s="75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ43" s="32"/>
@@ -24547,15 +24397,15 @@
       <c r="AN43" s="33"/>
       <c r="AO43" s="33"/>
       <c r="AP43" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ43" s="32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR43" s="32">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS43" s="32"/>
@@ -24571,16 +24421,16 @@
         <v>3770.26</v>
       </c>
       <c r="BC43" s="45">
-        <f>+X43</f>
+        <f t="shared" si="27"/>
         <v>3763</v>
       </c>
       <c r="BD43" s="45"/>
       <c r="BE43" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>7.2600000000002183</v>
       </c>
       <c r="BF43" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1.9255966432023834E-3</v>
       </c>
     </row>
@@ -24636,7 +24486,7 @@
         <v>1204.9500000000003</v>
       </c>
       <c r="T44" s="46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3874.6</v>
       </c>
       <c r="U44" s="46">
@@ -24666,7 +24516,7 @@
       <c r="AG44" s="74"/>
       <c r="AH44" s="75"/>
       <c r="AI44" s="75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ44" s="32"/>
@@ -24676,15 +24526,15 @@
       <c r="AN44" s="33"/>
       <c r="AO44" s="33"/>
       <c r="AP44" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ44" s="32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR44" s="32">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS44" s="32"/>
@@ -24700,16 +24550,16 @@
         <v>3874.6</v>
       </c>
       <c r="BC44" s="45">
-        <f>+X44</f>
+        <f t="shared" si="27"/>
         <v>3772</v>
       </c>
       <c r="BD44" s="45"/>
       <c r="BE44" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>102.59999999999991</v>
       </c>
       <c r="BF44" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2.6480152789965392E-2</v>
       </c>
     </row>
@@ -24765,7 +24615,7 @@
         <v>1184.3199999999997</v>
       </c>
       <c r="T45" s="46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3929.5</v>
       </c>
       <c r="U45" s="46">
@@ -24795,7 +24645,7 @@
       <c r="AG45" s="74"/>
       <c r="AH45" s="75"/>
       <c r="AI45" s="75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ45" s="32"/>
@@ -24805,15 +24655,15 @@
       <c r="AN45" s="33"/>
       <c r="AO45" s="33"/>
       <c r="AP45" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ45" s="32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR45" s="32">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS45" s="32"/>
@@ -24829,16 +24679,16 @@
         <v>3929.5</v>
       </c>
       <c r="BC45" s="45">
-        <f>+X45</f>
+        <f t="shared" si="27"/>
         <v>3857.6</v>
       </c>
       <c r="BD45" s="45"/>
       <c r="BE45" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>71.900000000000091</v>
       </c>
       <c r="BF45" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1.8297493319760806E-2</v>
       </c>
     </row>
@@ -24894,7 +24744,7 @@
         <v>1182.5</v>
       </c>
       <c r="T46" s="46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3818.8</v>
       </c>
       <c r="U46" s="46">
@@ -24924,7 +24774,7 @@
       <c r="AG46" s="74"/>
       <c r="AH46" s="75"/>
       <c r="AI46" s="75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ46" s="32"/>
@@ -24934,15 +24784,15 @@
       <c r="AN46" s="33"/>
       <c r="AO46" s="33"/>
       <c r="AP46" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ46" s="32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR46" s="32">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS46" s="32"/>
@@ -24958,16 +24808,16 @@
         <v>3818.8</v>
       </c>
       <c r="BC46" s="45">
-        <f>+X46</f>
+        <f t="shared" si="27"/>
         <v>3734.4</v>
       </c>
       <c r="BD46" s="45"/>
       <c r="BE46" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>84.400000000000091</v>
       </c>
       <c r="BF46" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2.2101183617890461E-2</v>
       </c>
     </row>
@@ -25023,7 +24873,7 @@
         <v>1207.3999999999996</v>
       </c>
       <c r="T47" s="46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3992.3</v>
       </c>
       <c r="U47" s="46">
@@ -25053,7 +24903,7 @@
       <c r="AG47" s="74"/>
       <c r="AH47" s="75"/>
       <c r="AI47" s="75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ47" s="32"/>
@@ -25063,15 +24913,15 @@
       <c r="AN47" s="33"/>
       <c r="AO47" s="33"/>
       <c r="AP47" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ47" s="32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR47" s="32">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS47" s="32"/>
@@ -25087,16 +24937,16 @@
         <v>3992.25</v>
       </c>
       <c r="BC47" s="45">
-        <f>+X47</f>
+        <f t="shared" si="27"/>
         <v>3907.2</v>
       </c>
       <c r="BD47" s="45"/>
       <c r="BE47" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>85.050000000000182</v>
       </c>
       <c r="BF47" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2.1303776066128169E-2</v>
       </c>
     </row>
@@ -25152,7 +25002,7 @@
         <v>1197.3000000000002</v>
       </c>
       <c r="T48" s="46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3959.3</v>
       </c>
       <c r="U48" s="46">
@@ -25182,7 +25032,7 @@
       <c r="AG48" s="74"/>
       <c r="AH48" s="75"/>
       <c r="AI48" s="75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ48" s="32"/>
@@ -25192,15 +25042,15 @@
       <c r="AN48" s="33"/>
       <c r="AO48" s="33"/>
       <c r="AP48" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ48" s="32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR48" s="32">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS48" s="32"/>
@@ -25216,16 +25066,16 @@
         <v>3964.47</v>
       </c>
       <c r="BC48" s="45">
-        <f>+X48</f>
+        <f t="shared" si="27"/>
         <v>3892</v>
       </c>
       <c r="BD48" s="45"/>
       <c r="BE48" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>72.4699999999998</v>
       </c>
       <c r="BF48" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1.8279870953746606E-2</v>
       </c>
     </row>
@@ -25281,7 +25131,7 @@
         <v>1178.3200000000006</v>
       </c>
       <c r="T49" s="46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3817.2</v>
       </c>
       <c r="U49" s="46">
@@ -25311,7 +25161,7 @@
       <c r="AG49" s="74"/>
       <c r="AH49" s="75"/>
       <c r="AI49" s="75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ49" s="32"/>
@@ -25321,15 +25171,15 @@
       <c r="AN49" s="33"/>
       <c r="AO49" s="33"/>
       <c r="AP49" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ49" s="32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR49" s="32">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS49" s="32"/>
@@ -25345,16 +25195,16 @@
         <v>3817.2</v>
       </c>
       <c r="BC49" s="45">
-        <f>+X49</f>
+        <f t="shared" si="27"/>
         <v>3735.4</v>
       </c>
       <c r="BD49" s="45"/>
       <c r="BE49" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>81.799999999999727</v>
       </c>
       <c r="BF49" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2.1429319920360405E-2</v>
       </c>
     </row>
@@ -25410,7 +25260,7 @@
         <v>1224.56</v>
       </c>
       <c r="T50" s="46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3953.4</v>
       </c>
       <c r="U50" s="46">
@@ -25440,7 +25290,7 @@
       <c r="AG50" s="74"/>
       <c r="AH50" s="75"/>
       <c r="AI50" s="75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ50" s="32"/>
@@ -25450,15 +25300,15 @@
       <c r="AN50" s="33"/>
       <c r="AO50" s="33"/>
       <c r="AP50" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ50" s="32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR50" s="32">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS50" s="32"/>
@@ -25474,16 +25324,16 @@
         <v>3953.4</v>
       </c>
       <c r="BC50" s="45">
-        <f>+X50</f>
+        <f t="shared" si="27"/>
         <v>3823.6</v>
       </c>
       <c r="BD50" s="45"/>
       <c r="BE50" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>129.80000000000018</v>
       </c>
       <c r="BF50" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3.2832498608792476E-2</v>
       </c>
     </row>
@@ -25539,7 +25389,7 @@
         <v>1197.7799999999997</v>
       </c>
       <c r="T51" s="46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3909.2</v>
       </c>
       <c r="U51" s="46">
@@ -25569,7 +25419,7 @@
       <c r="AG51" s="74"/>
       <c r="AH51" s="75"/>
       <c r="AI51" s="75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ51" s="32"/>
@@ -25579,15 +25429,15 @@
       <c r="AN51" s="33"/>
       <c r="AO51" s="33"/>
       <c r="AP51" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ51" s="32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR51" s="32">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS51" s="32"/>
@@ -25603,16 +25453,16 @@
         <v>3909.2</v>
       </c>
       <c r="BC51" s="45">
-        <f>+X51</f>
+        <f t="shared" si="27"/>
         <v>3955.2</v>
       </c>
       <c r="BD51" s="45"/>
       <c r="BE51" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-46</v>
       </c>
       <c r="BF51" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-1.1767113475902998E-2</v>
       </c>
     </row>
@@ -25668,7 +25518,7 @@
         <v>1188.1699999999996</v>
       </c>
       <c r="T52" s="46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3912.4</v>
       </c>
       <c r="U52" s="46">
@@ -25698,7 +25548,7 @@
       <c r="AG52" s="74"/>
       <c r="AH52" s="75"/>
       <c r="AI52" s="75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ52" s="32"/>
@@ -25708,15 +25558,15 @@
       <c r="AN52" s="33"/>
       <c r="AO52" s="33"/>
       <c r="AP52" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ52" s="32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR52" s="32">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS52" s="32"/>
@@ -25732,16 +25582,16 @@
         <v>3912.35</v>
       </c>
       <c r="BC52" s="45">
-        <f>+X52</f>
+        <f t="shared" si="27"/>
         <v>3769.4</v>
       </c>
       <c r="BD52" s="45"/>
       <c r="BE52" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>142.94999999999982</v>
       </c>
       <c r="BF52" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3.6538142037394361E-2</v>
       </c>
     </row>
@@ -25797,7 +25647,7 @@
         <v>1080.5000000000005</v>
       </c>
       <c r="T53" s="46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3496.1</v>
       </c>
       <c r="U53" s="46">
@@ -25827,7 +25677,7 @@
       <c r="AG53" s="74"/>
       <c r="AH53" s="75"/>
       <c r="AI53" s="75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ53" s="32"/>
@@ -25837,15 +25687,15 @@
       <c r="AN53" s="33"/>
       <c r="AO53" s="33"/>
       <c r="AP53" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ53" s="32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR53" s="32">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS53" s="32"/>
@@ -25861,16 +25711,16 @@
         <v>3516.31</v>
       </c>
       <c r="BC53" s="45">
-        <f>+X53</f>
+        <f t="shared" si="27"/>
         <v>3541.8</v>
       </c>
       <c r="BD53" s="45"/>
       <c r="BE53" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-25.490000000000236</v>
       </c>
       <c r="BF53" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-7.2490764466159804E-3</v>
       </c>
     </row>
@@ -25926,7 +25776,7 @@
         <v>1155.42</v>
       </c>
       <c r="T54" s="46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3777.3</v>
       </c>
       <c r="U54" s="46">
@@ -25956,7 +25806,7 @@
       <c r="AG54" s="74"/>
       <c r="AH54" s="75"/>
       <c r="AI54" s="75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ54" s="32"/>
@@ -25966,15 +25816,15 @@
       <c r="AN54" s="33"/>
       <c r="AO54" s="33"/>
       <c r="AP54" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ54" s="32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR54" s="32">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS54" s="32"/>
@@ -25990,16 +25840,16 @@
         <v>3777.25</v>
       </c>
       <c r="BC54" s="45">
-        <f>+X54</f>
+        <f t="shared" si="27"/>
         <v>3840.6</v>
       </c>
       <c r="BD54" s="45"/>
       <c r="BE54" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-63.349999999999909</v>
       </c>
       <c r="BF54" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-1.6771460718776863E-2</v>
       </c>
     </row>
@@ -26055,7 +25905,7 @@
         <v>1207.3499999999999</v>
       </c>
       <c r="T55" s="46">
-        <f t="shared" ref="T55:T60" si="26">+R55-S55</f>
+        <f t="shared" ref="T55:T60" si="28">+R55-S55</f>
         <v>3870.4</v>
       </c>
       <c r="U55" s="46">
@@ -26085,7 +25935,7 @@
       <c r="AG55" s="74"/>
       <c r="AH55" s="75"/>
       <c r="AI55" s="75">
-        <f t="shared" ref="AI55:AI60" si="27">+AG55+AH55</f>
+        <f t="shared" ref="AI55:AI60" si="29">+AG55+AH55</f>
         <v>0</v>
       </c>
       <c r="AJ55" s="32"/>
@@ -26095,15 +25945,15 @@
       <c r="AN55" s="33"/>
       <c r="AO55" s="33"/>
       <c r="AP55" s="34">
-        <f t="shared" ref="AP55:AP60" si="28">ROUNDUP((AO55-AM55+(AO55&lt;AM55))*24,0)</f>
+        <f t="shared" ref="AP55:AP60" si="30">ROUNDUP((AO55-AM55+(AO55&lt;AM55))*24,0)</f>
         <v>0</v>
       </c>
       <c r="AQ55" s="32">
-        <f t="shared" ref="AQ55:AQ60" si="29">IF(AP55&gt;5,(AP55-5),0)</f>
+        <f t="shared" ref="AQ55:AQ60" si="31">IF(AP55&gt;5,(AP55-5),0)</f>
         <v>0</v>
       </c>
       <c r="AR55" s="32">
-        <f t="shared" ref="AR55:AR60" si="30">+AQ55*8850</f>
+        <f t="shared" ref="AR55:AR60" si="32">+AQ55*8850</f>
         <v>0</v>
       </c>
       <c r="AS55" s="32"/>
@@ -26119,16 +25969,16 @@
         <v>3870.4</v>
       </c>
       <c r="BC55" s="45">
-        <f>+X55</f>
+        <f t="shared" si="27"/>
         <v>3777.2</v>
       </c>
       <c r="BD55" s="45"/>
       <c r="BE55" s="45">
-        <f t="shared" ref="BE55:BE60" si="31">+BB55-BC55</f>
+        <f t="shared" ref="BE55:BE60" si="33">+BB55-BC55</f>
         <v>93.200000000000273</v>
       </c>
       <c r="BF55" s="39">
-        <f t="shared" ref="BF55:BF60" si="32">+BE55/BB55</f>
+        <f t="shared" ref="BF55:BF60" si="34">+BE55/BB55</f>
         <v>2.4080198429103004E-2</v>
       </c>
     </row>
@@ -26184,7 +26034,7 @@
         <v>1151.3000000000002</v>
       </c>
       <c r="T56" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>4021.7</v>
       </c>
       <c r="U56" s="46">
@@ -26214,7 +26064,7 @@
       <c r="AG56" s="74"/>
       <c r="AH56" s="75"/>
       <c r="AI56" s="75">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AJ56" s="32"/>
@@ -26224,15 +26074,15 @@
       <c r="AN56" s="33"/>
       <c r="AO56" s="33"/>
       <c r="AP56" s="34">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AQ56" s="32">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AR56" s="32">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AS56" s="32"/>
@@ -26248,16 +26098,16 @@
         <v>4021.7</v>
       </c>
       <c r="BC56" s="45">
-        <f>+X56</f>
+        <f t="shared" si="27"/>
         <v>4039.3</v>
       </c>
       <c r="BD56" s="45"/>
       <c r="BE56" s="45">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>-17.600000000000364</v>
       </c>
       <c r="BF56" s="39">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-4.37625879603162E-3</v>
       </c>
     </row>
@@ -26313,7 +26163,7 @@
         <v>1192.46</v>
       </c>
       <c r="T57" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>3902.7</v>
       </c>
       <c r="U57" s="46">
@@ -26343,7 +26193,7 @@
       <c r="AG57" s="74"/>
       <c r="AH57" s="75"/>
       <c r="AI57" s="75">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AJ57" s="32"/>
@@ -26353,15 +26203,15 @@
       <c r="AN57" s="33"/>
       <c r="AO57" s="33"/>
       <c r="AP57" s="34">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AQ57" s="32">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AR57" s="32">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AS57" s="32"/>
@@ -26377,16 +26227,16 @@
         <v>3902.65</v>
       </c>
       <c r="BC57" s="45">
-        <f>+X57</f>
+        <f t="shared" si="27"/>
         <v>3836.2</v>
       </c>
       <c r="BD57" s="45"/>
       <c r="BE57" s="45">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>66.450000000000273</v>
       </c>
       <c r="BF57" s="39">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>1.7026891983652204E-2</v>
       </c>
     </row>
@@ -26442,7 +26292,7 @@
         <v>1242.2000000000003</v>
       </c>
       <c r="T58" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>4008.6</v>
       </c>
       <c r="U58" s="46">
@@ -26472,7 +26322,7 @@
       <c r="AG58" s="74"/>
       <c r="AH58" s="75"/>
       <c r="AI58" s="75">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AJ58" s="32"/>
@@ -26482,15 +26332,15 @@
       <c r="AN58" s="33"/>
       <c r="AO58" s="33"/>
       <c r="AP58" s="34">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AQ58" s="32">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AR58" s="32">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AS58" s="32"/>
@@ -26506,16 +26356,16 @@
         <v>4010.54</v>
       </c>
       <c r="BC58" s="45">
-        <f>+X58</f>
+        <f t="shared" si="27"/>
         <v>3991.6</v>
       </c>
       <c r="BD58" s="45"/>
       <c r="BE58" s="45">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>18.940000000000055</v>
       </c>
       <c r="BF58" s="39">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>4.7225560647693463E-3</v>
       </c>
     </row>
@@ -26571,7 +26421,7 @@
         <v>1171.0999999999995</v>
       </c>
       <c r="T59" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>4096.6000000000004</v>
       </c>
       <c r="U59" s="46">
@@ -26601,7 +26451,7 @@
       <c r="AG59" s="74"/>
       <c r="AH59" s="75"/>
       <c r="AI59" s="75">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AJ59" s="32"/>
@@ -26611,15 +26461,15 @@
       <c r="AN59" s="33"/>
       <c r="AO59" s="33"/>
       <c r="AP59" s="34">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AQ59" s="32">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AR59" s="32">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AS59" s="32"/>
@@ -26635,16 +26485,16 @@
         <v>4096.55</v>
       </c>
       <c r="BC59" s="45">
-        <f>+X59</f>
+        <f t="shared" si="27"/>
         <v>4103.6000000000004</v>
       </c>
       <c r="BD59" s="45"/>
       <c r="BE59" s="45">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>-7.0500000000001819</v>
       </c>
       <c r="BF59" s="39">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-1.7209603202695393E-3</v>
       </c>
     </row>
@@ -26700,7 +26550,7 @@
         <v>1171.0999999999995</v>
       </c>
       <c r="T60" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>4117.8</v>
       </c>
       <c r="U60" s="46">
@@ -26730,7 +26580,7 @@
       <c r="AG60" s="74"/>
       <c r="AH60" s="75"/>
       <c r="AI60" s="75">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AJ60" s="32"/>
@@ -26740,15 +26590,15 @@
       <c r="AN60" s="33"/>
       <c r="AO60" s="33"/>
       <c r="AP60" s="34">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AQ60" s="32">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AR60" s="32">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AS60" s="32"/>
@@ -26764,16 +26614,16 @@
         <v>4117.75</v>
       </c>
       <c r="BC60" s="45">
-        <f>+X60</f>
+        <f t="shared" si="27"/>
         <v>4096</v>
       </c>
       <c r="BD60" s="45"/>
       <c r="BE60" s="45">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>21.75</v>
       </c>
       <c r="BF60" s="39">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>5.2820108068726852E-3</v>
       </c>
     </row>
@@ -26829,7 +26679,7 @@
         <v>1198.0999999999999</v>
       </c>
       <c r="T61" s="46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3667.1</v>
       </c>
       <c r="U61" s="46">
@@ -26859,7 +26709,7 @@
       <c r="AG61" s="74"/>
       <c r="AH61" s="75"/>
       <c r="AI61" s="75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ61" s="32"/>
@@ -26869,15 +26719,15 @@
       <c r="AN61" s="33"/>
       <c r="AO61" s="33"/>
       <c r="AP61" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ61" s="32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR61" s="32">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS61" s="32"/>
@@ -26893,16 +26743,16 @@
         <v>3679.26</v>
       </c>
       <c r="BC61" s="45">
-        <f>+X61</f>
+        <f t="shared" si="27"/>
         <v>3673.6</v>
       </c>
       <c r="BD61" s="45"/>
       <c r="BE61" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>5.6600000000003092</v>
       </c>
       <c r="BF61" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1.5383528209477746E-3</v>
       </c>
     </row>
@@ -26958,7 +26808,7 @@
         <v>1140.5900000000001</v>
       </c>
       <c r="T62" s="46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3785.7</v>
       </c>
       <c r="U62" s="46">
@@ -26988,7 +26838,7 @@
       <c r="AG62" s="74"/>
       <c r="AH62" s="75"/>
       <c r="AI62" s="75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ62" s="32"/>
@@ -26998,15 +26848,15 @@
       <c r="AN62" s="33"/>
       <c r="AO62" s="33"/>
       <c r="AP62" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ62" s="32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR62" s="32">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS62" s="32"/>
@@ -27022,16 +26872,16 @@
         <v>3785.7</v>
       </c>
       <c r="BC62" s="45">
-        <f>+X62</f>
+        <f t="shared" si="27"/>
         <v>3729.6</v>
       </c>
       <c r="BD62" s="45"/>
       <c r="BE62" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>56.099999999999909</v>
       </c>
       <c r="BF62" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1.4818923844995618E-2</v>
       </c>
     </row>
@@ -27087,7 +26937,7 @@
         <v>1195.6999999999998</v>
       </c>
       <c r="T63" s="46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3896.8</v>
       </c>
       <c r="U63" s="46">
@@ -27117,7 +26967,7 @@
       <c r="AG63" s="74"/>
       <c r="AH63" s="75"/>
       <c r="AI63" s="75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ63" s="32"/>
@@ -27127,15 +26977,15 @@
       <c r="AN63" s="33"/>
       <c r="AO63" s="33"/>
       <c r="AP63" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ63" s="32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR63" s="32">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS63" s="32"/>
@@ -27151,16 +27001,16 @@
         <v>3896.75</v>
       </c>
       <c r="BC63" s="45">
-        <f>+X63</f>
+        <f t="shared" si="27"/>
         <v>3856.8</v>
       </c>
       <c r="BD63" s="45"/>
       <c r="BE63" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>39.949999999999818</v>
       </c>
       <c r="BF63" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1.0252133187912958E-2</v>
       </c>
     </row>
@@ -27216,7 +27066,7 @@
         <v>1190.6000000000004</v>
       </c>
       <c r="T64" s="46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3916</v>
       </c>
       <c r="U64" s="46">
@@ -27246,7 +27096,7 @@
       <c r="AG64" s="74"/>
       <c r="AH64" s="75"/>
       <c r="AI64" s="75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ64" s="32"/>
@@ -27256,15 +27106,15 @@
       <c r="AN64" s="33"/>
       <c r="AO64" s="33"/>
       <c r="AP64" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ64" s="32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR64" s="32">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS64" s="32"/>
@@ -27280,16 +27130,16 @@
         <v>3921.68</v>
       </c>
       <c r="BC64" s="45">
-        <f>+X64</f>
+        <f t="shared" si="27"/>
         <v>4016</v>
       </c>
       <c r="BD64" s="45"/>
       <c r="BE64" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-94.320000000000164</v>
       </c>
       <c r="BF64" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-2.405091695395855E-2</v>
       </c>
     </row>
@@ -27345,7 +27195,7 @@
         <v>1253.33</v>
       </c>
       <c r="T65" s="46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4057</v>
       </c>
       <c r="U65" s="46">
@@ -27375,7 +27225,7 @@
       <c r="AG65" s="74"/>
       <c r="AH65" s="75"/>
       <c r="AI65" s="75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ65" s="32"/>
@@ -27385,15 +27235,15 @@
       <c r="AN65" s="33"/>
       <c r="AO65" s="33"/>
       <c r="AP65" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ65" s="32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR65" s="32">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS65" s="32"/>
@@ -27409,16 +27259,16 @@
         <v>4194.05</v>
       </c>
       <c r="BC65" s="45">
-        <f>+X65</f>
+        <f t="shared" si="27"/>
         <v>4194.6000000000004</v>
       </c>
       <c r="BD65" s="45"/>
       <c r="BE65" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-0.5500000000001819</v>
       </c>
       <c r="BF65" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-1.3113816001244187E-4</v>
       </c>
     </row>
@@ -27474,7 +27324,7 @@
         <v>1083.29</v>
       </c>
       <c r="T66" s="46">
-        <f t="shared" ref="T66:T73" si="33">+R66-S66</f>
+        <f t="shared" ref="T66:T73" si="35">+R66-S66</f>
         <v>3590</v>
       </c>
       <c r="U66" s="46">
@@ -27504,7 +27354,7 @@
       <c r="AG66" s="74"/>
       <c r="AH66" s="75"/>
       <c r="AI66" s="75">
-        <f t="shared" ref="AI66:AI73" si="34">+AG66+AH66</f>
+        <f t="shared" ref="AI66:AI73" si="36">+AG66+AH66</f>
         <v>0</v>
       </c>
       <c r="AJ66" s="32"/>
@@ -27514,15 +27364,15 @@
       <c r="AN66" s="33"/>
       <c r="AO66" s="33"/>
       <c r="AP66" s="34">
-        <f t="shared" ref="AP66:AP73" si="35">ROUNDUP((AO66-AM66+(AO66&lt;AM66))*24,0)</f>
+        <f t="shared" ref="AP66:AP73" si="37">ROUNDUP((AO66-AM66+(AO66&lt;AM66))*24,0)</f>
         <v>0</v>
       </c>
       <c r="AQ66" s="32">
-        <f t="shared" ref="AQ66:AQ73" si="36">IF(AP66&gt;5,(AP66-5),0)</f>
+        <f t="shared" ref="AQ66:AQ73" si="38">IF(AP66&gt;5,(AP66-5),0)</f>
         <v>0</v>
       </c>
       <c r="AR66" s="32">
-        <f t="shared" ref="AR66:AR73" si="37">+AQ66*8850</f>
+        <f t="shared" ref="AR66:AR73" si="39">+AQ66*8850</f>
         <v>0</v>
       </c>
       <c r="AS66" s="32"/>
@@ -27538,16 +27388,16 @@
         <v>3590</v>
       </c>
       <c r="BC66" s="45">
-        <f>+X66</f>
+        <f t="shared" si="27"/>
         <v>3522.6</v>
       </c>
       <c r="BD66" s="45"/>
       <c r="BE66" s="45">
-        <f t="shared" ref="BE66:BE73" si="38">+BB66-BC66</f>
+        <f t="shared" ref="BE66:BE73" si="40">+BB66-BC66</f>
         <v>67.400000000000091</v>
       </c>
       <c r="BF66" s="39">
-        <f t="shared" ref="BF66:BF73" si="39">+BE66/BB66</f>
+        <f t="shared" ref="BF66:BF73" si="41">+BE66/BB66</f>
         <v>1.877437325905295E-2</v>
       </c>
     </row>
@@ -27603,7 +27453,7 @@
         <v>1206.1700000000005</v>
       </c>
       <c r="T67" s="46">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>3985.6</v>
       </c>
       <c r="U67" s="46">
@@ -27633,7 +27483,7 @@
       <c r="AG67" s="74"/>
       <c r="AH67" s="75"/>
       <c r="AI67" s="75">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AJ67" s="32"/>
@@ -27643,15 +27493,15 @@
       <c r="AN67" s="33"/>
       <c r="AO67" s="33"/>
       <c r="AP67" s="34">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AQ67" s="32">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="AR67" s="32">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AS67" s="32"/>
@@ -27667,16 +27517,16 @@
         <v>3985.55</v>
       </c>
       <c r="BC67" s="45">
-        <f>+X67</f>
+        <f t="shared" si="27"/>
         <v>3933</v>
       </c>
       <c r="BD67" s="45"/>
       <c r="BE67" s="45">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>52.550000000000182</v>
       </c>
       <c r="BF67" s="39">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>1.3185131286773514E-2</v>
       </c>
     </row>
@@ -27732,7 +27582,7 @@
         <v>1206.7599999999998</v>
       </c>
       <c r="T68" s="46">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>3927.6</v>
       </c>
       <c r="U68" s="46">
@@ -27762,7 +27612,7 @@
       <c r="AG68" s="74"/>
       <c r="AH68" s="75"/>
       <c r="AI68" s="75">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AJ68" s="32"/>
@@ -27772,15 +27622,15 @@
       <c r="AN68" s="33"/>
       <c r="AO68" s="33"/>
       <c r="AP68" s="34">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AQ68" s="32">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="AR68" s="32">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AS68" s="32"/>
@@ -27796,16 +27646,16 @@
         <v>3965.72</v>
       </c>
       <c r="BC68" s="45">
-        <f>+X68</f>
+        <f t="shared" si="27"/>
         <v>4092.6</v>
       </c>
       <c r="BD68" s="45"/>
       <c r="BE68" s="45">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>-126.88000000000011</v>
       </c>
       <c r="BF68" s="39">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>-3.1994190210100588E-2</v>
       </c>
     </row>
@@ -27861,7 +27711,7 @@
         <v>1170.6200000000003</v>
       </c>
       <c r="T69" s="46">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>3866.9</v>
       </c>
       <c r="U69" s="46">
@@ -27891,7 +27741,7 @@
       <c r="AG69" s="74"/>
       <c r="AH69" s="75"/>
       <c r="AI69" s="75">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AJ69" s="32"/>
@@ -27901,15 +27751,15 @@
       <c r="AN69" s="33"/>
       <c r="AO69" s="33"/>
       <c r="AP69" s="34">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AQ69" s="32">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="AR69" s="32">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AS69" s="32"/>
@@ -27925,16 +27775,16 @@
         <v>3894.02</v>
       </c>
       <c r="BC69" s="45">
-        <f>+X69</f>
+        <f t="shared" si="27"/>
         <v>4001.6</v>
       </c>
       <c r="BD69" s="45"/>
       <c r="BE69" s="45">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>-107.57999999999993</v>
       </c>
       <c r="BF69" s="39">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>-2.7626976748963777E-2</v>
       </c>
     </row>
@@ -27990,7 +27840,7 @@
         <v>1143.3699999999999</v>
       </c>
       <c r="T70" s="46">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>3667.5</v>
       </c>
       <c r="U70" s="46">
@@ -28020,7 +27870,7 @@
       <c r="AG70" s="74"/>
       <c r="AH70" s="75"/>
       <c r="AI70" s="75">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AJ70" s="32"/>
@@ -28030,15 +27880,15 @@
       <c r="AN70" s="33"/>
       <c r="AO70" s="33"/>
       <c r="AP70" s="34">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AQ70" s="32">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="AR70" s="32">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AS70" s="32"/>
@@ -28054,16 +27904,16 @@
         <v>3667.5</v>
       </c>
       <c r="BC70" s="45">
-        <f>+X70</f>
+        <f t="shared" ref="BC70:BC96" si="42">+X70</f>
         <v>3335.4</v>
       </c>
       <c r="BD70" s="45"/>
       <c r="BE70" s="45">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>332.09999999999991</v>
       </c>
       <c r="BF70" s="39">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>9.0552147239263775E-2</v>
       </c>
     </row>
@@ -28119,7 +27969,7 @@
         <v>1081.3200000000002</v>
       </c>
       <c r="T71" s="46">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>3576.4</v>
       </c>
       <c r="U71" s="46">
@@ -28149,7 +27999,7 @@
       <c r="AG71" s="74"/>
       <c r="AH71" s="75"/>
       <c r="AI71" s="75">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AJ71" s="32"/>
@@ -28159,15 +28009,15 @@
       <c r="AN71" s="33"/>
       <c r="AO71" s="33"/>
       <c r="AP71" s="34">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AQ71" s="32">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="AR71" s="32">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AS71" s="32"/>
@@ -28183,16 +28033,16 @@
         <v>3576.4</v>
       </c>
       <c r="BC71" s="45">
-        <f>+X71</f>
+        <f t="shared" si="42"/>
         <v>3253.4</v>
       </c>
       <c r="BD71" s="45"/>
       <c r="BE71" s="45">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>323</v>
       </c>
       <c r="BF71" s="39">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>9.0314282518733927E-2</v>
       </c>
     </row>
@@ -28248,7 +28098,7 @@
         <v>1150.2099999999996</v>
       </c>
       <c r="T72" s="46">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>3804.9</v>
       </c>
       <c r="U72" s="46">
@@ -28278,7 +28128,7 @@
       <c r="AG72" s="74"/>
       <c r="AH72" s="75"/>
       <c r="AI72" s="75">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AJ72" s="32"/>
@@ -28288,15 +28138,15 @@
       <c r="AN72" s="33"/>
       <c r="AO72" s="33"/>
       <c r="AP72" s="34">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AQ72" s="32">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="AR72" s="32">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AS72" s="32"/>
@@ -28312,16 +28162,16 @@
         <v>4000.9</v>
       </c>
       <c r="BC72" s="45">
-        <f>+X72</f>
+        <f t="shared" si="42"/>
         <v>4004.8</v>
       </c>
       <c r="BD72" s="45"/>
       <c r="BE72" s="45">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>-3.9000000000000909</v>
       </c>
       <c r="BF72" s="39">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>-9.747806743482944E-4</v>
       </c>
     </row>
@@ -28377,7 +28227,7 @@
         <v>1150.9300000000003</v>
       </c>
       <c r="T73" s="46">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>3765.2</v>
       </c>
       <c r="U73" s="46">
@@ -28397,7 +28247,9 @@
         <f>Z73/T73</f>
         <v>-2.3371932433868541E-3</v>
       </c>
-      <c r="AB73" s="73"/>
+      <c r="AB73" s="73">
+        <v>3765.2</v>
+      </c>
       <c r="AC73" s="73"/>
       <c r="AD73" s="73"/>
       <c r="AE73" s="39"/>
@@ -28405,7 +28257,7 @@
       <c r="AG73" s="74"/>
       <c r="AH73" s="75"/>
       <c r="AI73" s="75">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AJ73" s="32"/>
@@ -28415,15 +28267,15 @@
       <c r="AN73" s="33"/>
       <c r="AO73" s="33"/>
       <c r="AP73" s="34">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AQ73" s="32">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="AR73" s="32">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AS73" s="32"/>
@@ -28439,16 +28291,16 @@
         <v>3765.2</v>
       </c>
       <c r="BC73" s="45">
-        <f>+X73</f>
+        <f t="shared" si="42"/>
         <v>3774</v>
       </c>
       <c r="BD73" s="45"/>
       <c r="BE73" s="45">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>-8.8000000000001819</v>
       </c>
       <c r="BF73" s="39">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>-2.3371932433868541E-3</v>
       </c>
     </row>
@@ -28504,7 +28356,7 @@
         <v>1062</v>
       </c>
       <c r="T74" s="46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3502.2</v>
       </c>
       <c r="U74" s="46">
@@ -28534,7 +28386,7 @@
       <c r="AG74" s="74"/>
       <c r="AH74" s="75"/>
       <c r="AI74" s="75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ74" s="32"/>
@@ -28544,15 +28396,15 @@
       <c r="AN74" s="33"/>
       <c r="AO74" s="33"/>
       <c r="AP74" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ74" s="32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR74" s="32">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS74" s="32"/>
@@ -28568,16 +28420,16 @@
         <v>3502.15</v>
       </c>
       <c r="BC74" s="45">
-        <f>+X74</f>
+        <f t="shared" si="42"/>
         <v>3402.2</v>
       </c>
       <c r="BD74" s="45"/>
       <c r="BE74" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>99.950000000000273</v>
       </c>
       <c r="BF74" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2.8539611381579965E-2</v>
       </c>
     </row>
@@ -28633,7 +28485,7 @@
         <v>1223.3100000000004</v>
       </c>
       <c r="T75" s="46">
-        <f t="shared" ref="T75" si="40">+R75-S75</f>
+        <f t="shared" ref="T75" si="43">+R75-S75</f>
         <v>3972.7</v>
       </c>
       <c r="U75" s="46">
@@ -28663,7 +28515,7 @@
       <c r="AG75" s="74"/>
       <c r="AH75" s="75"/>
       <c r="AI75" s="75">
-        <f t="shared" ref="AI75" si="41">+AG75+AH75</f>
+        <f t="shared" ref="AI75" si="44">+AG75+AH75</f>
         <v>0</v>
       </c>
       <c r="AJ75" s="32"/>
@@ -28673,15 +28525,15 @@
       <c r="AN75" s="33"/>
       <c r="AO75" s="33"/>
       <c r="AP75" s="34">
-        <f t="shared" ref="AP75" si="42">ROUNDUP((AO75-AM75+(AO75&lt;AM75))*24,0)</f>
+        <f t="shared" ref="AP75" si="45">ROUNDUP((AO75-AM75+(AO75&lt;AM75))*24,0)</f>
         <v>0</v>
       </c>
       <c r="AQ75" s="32">
-        <f t="shared" ref="AQ75" si="43">IF(AP75&gt;5,(AP75-5),0)</f>
+        <f t="shared" ref="AQ75" si="46">IF(AP75&gt;5,(AP75-5),0)</f>
         <v>0</v>
       </c>
       <c r="AR75" s="32">
-        <f t="shared" ref="AR75" si="44">+AQ75*8850</f>
+        <f t="shared" ref="AR75" si="47">+AQ75*8850</f>
         <v>0</v>
       </c>
       <c r="AS75" s="32"/>
@@ -28697,16 +28549,16 @@
         <v>3972.7</v>
       </c>
       <c r="BC75" s="45">
-        <f>+X75</f>
+        <f t="shared" si="42"/>
         <v>3937.4</v>
       </c>
       <c r="BD75" s="45"/>
       <c r="BE75" s="45">
-        <f t="shared" ref="BE75" si="45">+BB75-BC75</f>
+        <f t="shared" ref="BE75" si="48">+BB75-BC75</f>
         <v>35.299999999999727</v>
       </c>
       <c r="BF75" s="39">
-        <f t="shared" ref="BF75" si="46">+BE75/BB75</f>
+        <f t="shared" ref="BF75" si="49">+BE75/BB75</f>
         <v>8.8856445238753821E-3</v>
       </c>
     </row>
@@ -28762,7 +28614,7 @@
         <v>1132.6100000000001</v>
       </c>
       <c r="T76" s="46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3728.9</v>
       </c>
       <c r="U76" s="46">
@@ -28792,7 +28644,7 @@
       <c r="AG76" s="74"/>
       <c r="AH76" s="75"/>
       <c r="AI76" s="75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ76" s="32"/>
@@ -28802,15 +28654,15 @@
       <c r="AN76" s="33"/>
       <c r="AO76" s="33"/>
       <c r="AP76" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ76" s="32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR76" s="32">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS76" s="32"/>
@@ -28826,16 +28678,16 @@
         <v>3872.5</v>
       </c>
       <c r="BC76" s="45">
-        <f>+X76</f>
+        <f t="shared" si="42"/>
         <v>3521.4</v>
       </c>
       <c r="BD76" s="45"/>
       <c r="BE76" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>351.09999999999991</v>
       </c>
       <c r="BF76" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>9.0664945125887644E-2</v>
       </c>
     </row>
@@ -28891,7 +28743,7 @@
         <v>1134.4799999999996</v>
       </c>
       <c r="T77" s="46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3691</v>
       </c>
       <c r="U77" s="46">
@@ -28921,7 +28773,7 @@
       <c r="AG77" s="74"/>
       <c r="AH77" s="75"/>
       <c r="AI77" s="75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ77" s="32"/>
@@ -28931,15 +28783,15 @@
       <c r="AN77" s="33"/>
       <c r="AO77" s="33"/>
       <c r="AP77" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ77" s="32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR77" s="32">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS77" s="32"/>
@@ -28955,16 +28807,16 @@
         <v>3691</v>
       </c>
       <c r="BC77" s="45">
-        <f>+X77</f>
+        <f t="shared" si="42"/>
         <v>3669</v>
       </c>
       <c r="BD77" s="45"/>
       <c r="BE77" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>22</v>
       </c>
       <c r="BF77" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>5.9604443240314281E-3</v>
       </c>
     </row>
@@ -29020,7 +28872,7 @@
         <v>1197.6100000000006</v>
       </c>
       <c r="T78" s="46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3915.7</v>
       </c>
       <c r="U78" s="46">
@@ -29050,7 +28902,7 @@
       <c r="AG78" s="74"/>
       <c r="AH78" s="75"/>
       <c r="AI78" s="75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ78" s="32"/>
@@ -29060,15 +28912,15 @@
       <c r="AN78" s="33"/>
       <c r="AO78" s="33"/>
       <c r="AP78" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ78" s="32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR78" s="32">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS78" s="32"/>
@@ -29084,16 +28936,16 @@
         <v>3915.7</v>
       </c>
       <c r="BC78" s="45">
-        <f>+X78</f>
+        <f t="shared" si="42"/>
         <v>3803.6</v>
       </c>
       <c r="BD78" s="45"/>
       <c r="BE78" s="45">
-        <f t="shared" ref="BE78:BE87" si="47">+BB78-BC78</f>
+        <f t="shared" ref="BE78:BE87" si="50">+BB78-BC78</f>
         <v>112.09999999999991</v>
       </c>
       <c r="BF78" s="39">
-        <f t="shared" ref="BF78:BF87" si="48">+BE78/BB78</f>
+        <f t="shared" ref="BF78:BF87" si="51">+BE78/BB78</f>
         <v>2.8628342314273289E-2</v>
       </c>
     </row>
@@ -29149,7 +29001,7 @@
         <v>1172.6000000000004</v>
       </c>
       <c r="T79" s="46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3795</v>
       </c>
       <c r="U79" s="46">
@@ -29179,7 +29031,7 @@
       <c r="AG79" s="74"/>
       <c r="AH79" s="75"/>
       <c r="AI79" s="75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ79" s="32"/>
@@ -29189,15 +29041,15 @@
       <c r="AN79" s="33"/>
       <c r="AO79" s="33"/>
       <c r="AP79" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ79" s="32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR79" s="32">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS79" s="32"/>
@@ -29213,16 +29065,16 @@
         <v>3803.66</v>
       </c>
       <c r="BC79" s="45">
-        <f>+X79</f>
+        <f t="shared" si="42"/>
         <v>3901</v>
       </c>
       <c r="BD79" s="45"/>
       <c r="BE79" s="45">
-        <f t="shared" si="47"/>
+        <f t="shared" si="50"/>
         <v>-97.340000000000146</v>
       </c>
       <c r="BF79" s="39">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>-2.5591141164036782E-2</v>
       </c>
     </row>
@@ -29278,7 +29130,7 @@
         <v>1191.8000000000002</v>
       </c>
       <c r="T80" s="46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3906</v>
       </c>
       <c r="U80" s="46">
@@ -29308,7 +29160,7 @@
       <c r="AG80" s="74"/>
       <c r="AH80" s="75"/>
       <c r="AI80" s="75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ80" s="32"/>
@@ -29318,15 +29170,15 @@
       <c r="AN80" s="33"/>
       <c r="AO80" s="33"/>
       <c r="AP80" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ80" s="32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR80" s="32">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS80" s="32"/>
@@ -29342,64 +29194,64 @@
         <v>3905.95</v>
       </c>
       <c r="BC80" s="45">
-        <f>+X80</f>
+        <f t="shared" si="42"/>
         <v>4083.6</v>
       </c>
       <c r="BD80" s="45"/>
       <c r="BE80" s="45">
-        <f t="shared" si="47"/>
+        <f t="shared" si="50"/>
         <v>-177.65000000000009</v>
       </c>
       <c r="BF80" s="39">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>-4.5481893009383149E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:58" s="91" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A81" s="76">
+    <row r="81" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A81" s="21">
         <f>IF(ISBLANK(F81),"",COUNTA($F$6:F81))</f>
         <v>76</v>
       </c>
-      <c r="B81" s="77" t="s">
+      <c r="B81" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="C81" s="77" t="s">
+      <c r="C81" s="37" t="s">
         <v>61</v>
       </c>
-      <c r="D81" s="78"/>
-      <c r="E81" s="79" t="s">
+      <c r="D81" s="22"/>
+      <c r="E81" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="F81" s="80">
+      <c r="F81" s="36">
         <v>46250</v>
       </c>
-      <c r="G81" s="81" t="s">
+      <c r="G81" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="H81" s="81">
+      <c r="H81" s="24">
         <v>59</v>
       </c>
-      <c r="I81" s="81">
+      <c r="I81" s="24">
         <v>3</v>
       </c>
-      <c r="J81" s="81" t="s">
+      <c r="J81" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="K81" s="82">
+      <c r="K81" s="25">
         <v>162004403</v>
       </c>
-      <c r="L81" s="83">
+      <c r="L81" s="26">
         <v>46250</v>
       </c>
-      <c r="M81" s="84">
+      <c r="M81" s="38">
         <v>46252</v>
       </c>
-      <c r="N81" s="85">
+      <c r="N81" s="52">
         <v>16583</v>
       </c>
-      <c r="O81" s="86"/>
-      <c r="P81" s="86"/>
-      <c r="Q81" s="86"/>
+      <c r="O81" s="27"/>
+      <c r="P81" s="27"/>
+      <c r="Q81" s="27"/>
       <c r="R81" s="46">
         <v>5055.07</v>
       </c>
@@ -29407,7 +29259,7 @@
         <v>1175.7699999999995</v>
       </c>
       <c r="T81" s="46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3879.3</v>
       </c>
       <c r="U81" s="46">
@@ -29437,98 +29289,98 @@
       <c r="AG81" s="74"/>
       <c r="AH81" s="75"/>
       <c r="AI81" s="75">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AJ81" s="87"/>
-      <c r="AK81" s="87"/>
-      <c r="AL81" s="87"/>
-      <c r="AM81" s="88"/>
-      <c r="AN81" s="88"/>
-      <c r="AO81" s="88"/>
-      <c r="AP81" s="89">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AQ81" s="87">
+      <c r="AJ81" s="32"/>
+      <c r="AK81" s="32"/>
+      <c r="AL81" s="32"/>
+      <c r="AM81" s="33"/>
+      <c r="AN81" s="33"/>
+      <c r="AO81" s="33"/>
+      <c r="AP81" s="34">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR81" s="87">
+      <c r="AQ81" s="32">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AS81" s="87"/>
-      <c r="AT81" s="87"/>
-      <c r="AU81" s="87"/>
-      <c r="AV81" s="87"/>
-      <c r="AW81" s="87"/>
-      <c r="AX81" s="87"/>
-      <c r="AY81" s="87"/>
-      <c r="AZ81" s="90"/>
-      <c r="BB81" s="92">
+      <c r="AR81" s="32">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AS81" s="32"/>
+      <c r="AT81" s="32"/>
+      <c r="AU81" s="32"/>
+      <c r="AV81" s="32"/>
+      <c r="AW81" s="32"/>
+      <c r="AX81" s="32"/>
+      <c r="AY81" s="32"/>
+      <c r="AZ81" s="35"/>
+      <c r="BB81" s="45">
         <f>IF(AND(AB81="",AC81=""),T81,IF(AC81="",AB81,AC81))</f>
         <v>3879.3</v>
       </c>
-      <c r="BC81" s="92">
-        <f>+X81</f>
+      <c r="BC81" s="45">
+        <f t="shared" si="42"/>
         <v>3891</v>
       </c>
-      <c r="BD81" s="92"/>
-      <c r="BE81" s="92">
-        <f t="shared" si="47"/>
+      <c r="BD81" s="45"/>
+      <c r="BE81" s="45">
+        <f t="shared" si="50"/>
         <v>-11.699999999999818</v>
       </c>
       <c r="BF81" s="39">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>-3.0160080426880668E-3</v>
       </c>
     </row>
-    <row r="82" spans="1:58" s="91" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A82" s="76">
+    <row r="82" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A82" s="21">
         <f>IF(ISBLANK(F82),"",COUNTA($F$6:F82))</f>
         <v>77</v>
       </c>
-      <c r="B82" s="77" t="s">
+      <c r="B82" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="C82" s="77" t="s">
+      <c r="C82" s="37" t="s">
         <v>61</v>
       </c>
-      <c r="D82" s="78"/>
-      <c r="E82" s="79" t="s">
+      <c r="D82" s="22"/>
+      <c r="E82" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="F82" s="80">
+      <c r="F82" s="36">
         <v>46250</v>
       </c>
-      <c r="G82" s="81" t="s">
+      <c r="G82" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="H82" s="81">
+      <c r="H82" s="24">
         <v>58</v>
       </c>
-      <c r="I82" s="81">
+      <c r="I82" s="24">
         <v>12</v>
       </c>
-      <c r="J82" s="81" t="s">
+      <c r="J82" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="K82" s="82">
+      <c r="K82" s="25">
         <v>162011717</v>
       </c>
-      <c r="L82" s="83">
+      <c r="L82" s="26">
         <v>46251</v>
       </c>
-      <c r="M82" s="84">
+      <c r="M82" s="38">
         <v>46252</v>
       </c>
-      <c r="N82" s="85">
+      <c r="N82" s="52">
         <v>16585</v>
       </c>
-      <c r="O82" s="86"/>
-      <c r="P82" s="86"/>
-      <c r="Q82" s="86"/>
+      <c r="O82" s="27"/>
+      <c r="P82" s="27"/>
+      <c r="Q82" s="27"/>
       <c r="R82" s="46">
         <v>4123.6000000000004</v>
       </c>
@@ -29536,7 +29388,7 @@
         <v>961.00000000000045</v>
       </c>
       <c r="T82" s="46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3162.6</v>
       </c>
       <c r="U82" s="46">
@@ -29566,98 +29418,98 @@
       <c r="AG82" s="74"/>
       <c r="AH82" s="75"/>
       <c r="AI82" s="75">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AJ82" s="87"/>
-      <c r="AK82" s="87"/>
-      <c r="AL82" s="87"/>
-      <c r="AM82" s="88"/>
-      <c r="AN82" s="88"/>
-      <c r="AO82" s="88"/>
-      <c r="AP82" s="89">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AQ82" s="87">
+      <c r="AJ82" s="32"/>
+      <c r="AK82" s="32"/>
+      <c r="AL82" s="32"/>
+      <c r="AM82" s="33"/>
+      <c r="AN82" s="33"/>
+      <c r="AO82" s="33"/>
+      <c r="AP82" s="34">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR82" s="87">
+      <c r="AQ82" s="32">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AS82" s="87"/>
-      <c r="AT82" s="87"/>
-      <c r="AU82" s="87"/>
-      <c r="AV82" s="87"/>
-      <c r="AW82" s="87"/>
-      <c r="AX82" s="87"/>
-      <c r="AY82" s="87"/>
-      <c r="AZ82" s="90"/>
-      <c r="BB82" s="92">
+      <c r="AR82" s="32">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AS82" s="32"/>
+      <c r="AT82" s="32"/>
+      <c r="AU82" s="32"/>
+      <c r="AV82" s="32"/>
+      <c r="AW82" s="32"/>
+      <c r="AX82" s="32"/>
+      <c r="AY82" s="32"/>
+      <c r="AZ82" s="35"/>
+      <c r="BB82" s="45">
         <f>IF(AND(AB82="",AC82=""),T82,IF(AC82="",AB82,AC82))</f>
         <v>3461.9999999999995</v>
       </c>
-      <c r="BC82" s="92">
-        <f>+X82</f>
+      <c r="BC82" s="45">
+        <f t="shared" si="42"/>
         <v>3199</v>
       </c>
-      <c r="BD82" s="92"/>
-      <c r="BE82" s="92">
-        <f t="shared" si="47"/>
+      <c r="BD82" s="45"/>
+      <c r="BE82" s="45">
+        <f t="shared" si="50"/>
         <v>262.99999999999955</v>
       </c>
       <c r="BF82" s="39">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>7.5967648757943262E-2</v>
       </c>
     </row>
-    <row r="83" spans="1:58" s="91" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A83" s="76">
+    <row r="83" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A83" s="21">
         <f>IF(ISBLANK(F83),"",COUNTA($F$6:F83))</f>
         <v>78</v>
       </c>
-      <c r="B83" s="77" t="s">
+      <c r="B83" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="C83" s="77" t="s">
+      <c r="C83" s="37" t="s">
         <v>61</v>
       </c>
-      <c r="D83" s="78"/>
-      <c r="E83" s="79" t="s">
+      <c r="D83" s="22"/>
+      <c r="E83" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="F83" s="80">
+      <c r="F83" s="36">
         <v>46250</v>
       </c>
-      <c r="G83" s="81" t="s">
+      <c r="G83" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="H83" s="81">
+      <c r="H83" s="24">
         <v>59</v>
       </c>
-      <c r="I83" s="81">
-        <v>0</v>
-      </c>
-      <c r="J83" s="81" t="s">
+      <c r="I83" s="24">
+        <v>0</v>
+      </c>
+      <c r="J83" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="K83" s="82">
+      <c r="K83" s="25">
         <v>162004404</v>
       </c>
-      <c r="L83" s="83">
+      <c r="L83" s="26">
         <v>46251</v>
       </c>
-      <c r="M83" s="84">
+      <c r="M83" s="38">
         <v>46252</v>
       </c>
-      <c r="N83" s="85">
+      <c r="N83" s="52">
         <v>16586</v>
       </c>
-      <c r="O83" s="86"/>
-      <c r="P83" s="86"/>
-      <c r="Q83" s="86"/>
+      <c r="O83" s="27"/>
+      <c r="P83" s="27"/>
+      <c r="Q83" s="27"/>
       <c r="R83" s="46">
         <v>5338.96</v>
       </c>
@@ -29665,7 +29517,7 @@
         <v>1233.6599999999999</v>
       </c>
       <c r="T83" s="46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4105.3</v>
       </c>
       <c r="U83" s="46">
@@ -29695,98 +29547,98 @@
       <c r="AG83" s="74"/>
       <c r="AH83" s="75"/>
       <c r="AI83" s="75">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AJ83" s="87"/>
-      <c r="AK83" s="87"/>
-      <c r="AL83" s="87"/>
-      <c r="AM83" s="88"/>
-      <c r="AN83" s="88"/>
-      <c r="AO83" s="88"/>
-      <c r="AP83" s="89">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AQ83" s="87">
+      <c r="AJ83" s="32"/>
+      <c r="AK83" s="32"/>
+      <c r="AL83" s="32"/>
+      <c r="AM83" s="33"/>
+      <c r="AN83" s="33"/>
+      <c r="AO83" s="33"/>
+      <c r="AP83" s="34">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR83" s="87">
+      <c r="AQ83" s="32">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AS83" s="87"/>
-      <c r="AT83" s="87"/>
-      <c r="AU83" s="87"/>
-      <c r="AV83" s="87"/>
-      <c r="AW83" s="87"/>
-      <c r="AX83" s="87"/>
-      <c r="AY83" s="87"/>
-      <c r="AZ83" s="90"/>
-      <c r="BB83" s="92">
+      <c r="AR83" s="32">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AS83" s="32"/>
+      <c r="AT83" s="32"/>
+      <c r="AU83" s="32"/>
+      <c r="AV83" s="32"/>
+      <c r="AW83" s="32"/>
+      <c r="AX83" s="32"/>
+      <c r="AY83" s="32"/>
+      <c r="AZ83" s="35"/>
+      <c r="BB83" s="45">
         <f>IF(AND(AB83="",AC83=""),T83,IF(AC83="",AB83,AC83))</f>
         <v>4105.25</v>
       </c>
-      <c r="BC83" s="92">
-        <f>+X83</f>
+      <c r="BC83" s="45">
+        <f t="shared" si="42"/>
         <v>3974.2</v>
       </c>
-      <c r="BD83" s="92"/>
-      <c r="BE83" s="92">
-        <f t="shared" si="47"/>
+      <c r="BD83" s="45"/>
+      <c r="BE83" s="45">
+        <f t="shared" si="50"/>
         <v>131.05000000000018</v>
       </c>
       <c r="BF83" s="39">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>3.1922538213263546E-2</v>
       </c>
     </row>
-    <row r="84" spans="1:58" s="91" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A84" s="76">
+    <row r="84" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A84" s="21">
         <f>IF(ISBLANK(F84),"",COUNTA($F$6:F84))</f>
         <v>79</v>
       </c>
-      <c r="B84" s="77" t="s">
+      <c r="B84" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="C84" s="77" t="s">
+      <c r="C84" s="37" t="s">
         <v>61</v>
       </c>
-      <c r="D84" s="78"/>
-      <c r="E84" s="79" t="s">
+      <c r="D84" s="22"/>
+      <c r="E84" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="F84" s="80">
+      <c r="F84" s="36">
         <v>46251</v>
       </c>
-      <c r="G84" s="81" t="s">
+      <c r="G84" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="H84" s="81">
+      <c r="H84" s="24">
         <v>59</v>
       </c>
-      <c r="I84" s="81">
-        <v>0</v>
-      </c>
-      <c r="J84" s="81" t="s">
+      <c r="I84" s="24">
+        <v>0</v>
+      </c>
+      <c r="J84" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="K84" s="82">
+      <c r="K84" s="25">
         <v>162011719</v>
       </c>
-      <c r="L84" s="83">
+      <c r="L84" s="26">
         <v>46252</v>
       </c>
-      <c r="M84" s="84">
+      <c r="M84" s="38">
         <v>46253</v>
       </c>
-      <c r="N84" s="85">
+      <c r="N84" s="52">
         <v>16589</v>
       </c>
-      <c r="O84" s="86"/>
-      <c r="P84" s="86"/>
-      <c r="Q84" s="86"/>
+      <c r="O84" s="27"/>
+      <c r="P84" s="27"/>
+      <c r="Q84" s="27"/>
       <c r="R84" s="46">
         <v>5367.81</v>
       </c>
@@ -29794,7 +29646,7 @@
         <v>1236.5100000000002</v>
       </c>
       <c r="T84" s="46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4131.3</v>
       </c>
       <c r="U84" s="46">
@@ -29824,396 +29676,438 @@
       <c r="AG84" s="74"/>
       <c r="AH84" s="75"/>
       <c r="AI84" s="75">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AJ84" s="87"/>
-      <c r="AK84" s="87"/>
-      <c r="AL84" s="87"/>
-      <c r="AM84" s="88"/>
-      <c r="AN84" s="88"/>
-      <c r="AO84" s="88"/>
-      <c r="AP84" s="89">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AQ84" s="87">
+      <c r="AJ84" s="32"/>
+      <c r="AK84" s="32"/>
+      <c r="AL84" s="32"/>
+      <c r="AM84" s="33"/>
+      <c r="AN84" s="33"/>
+      <c r="AO84" s="33"/>
+      <c r="AP84" s="34">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR84" s="87">
+      <c r="AQ84" s="32">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AS84" s="87"/>
-      <c r="AT84" s="87"/>
-      <c r="AU84" s="87"/>
-      <c r="AV84" s="87"/>
-      <c r="AW84" s="87"/>
-      <c r="AX84" s="87"/>
-      <c r="AY84" s="87"/>
-      <c r="AZ84" s="90"/>
-      <c r="BB84" s="92">
+      <c r="AR84" s="32">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AS84" s="32"/>
+      <c r="AT84" s="32"/>
+      <c r="AU84" s="32"/>
+      <c r="AV84" s="32"/>
+      <c r="AW84" s="32"/>
+      <c r="AX84" s="32"/>
+      <c r="AY84" s="32"/>
+      <c r="AZ84" s="35"/>
+      <c r="BB84" s="45">
         <f>IF(AND(AB84="",AC84=""),T84,IF(AC84="",AB84,AC84))</f>
         <v>4152.76</v>
       </c>
-      <c r="BC84" s="92">
-        <f>+X84</f>
+      <c r="BC84" s="45">
+        <f t="shared" si="42"/>
         <v>4199.6000000000004</v>
       </c>
-      <c r="BD84" s="92"/>
-      <c r="BE84" s="92">
-        <f t="shared" si="47"/>
+      <c r="BD84" s="45"/>
+      <c r="BE84" s="45">
+        <f t="shared" si="50"/>
         <v>-46.840000000000146</v>
       </c>
       <c r="BF84" s="39">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>-1.1279245610148467E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A85" s="53">
+    <row r="85" spans="1:58" s="91" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A85" s="76">
         <f>IF(ISBLANK(F85),"",COUNTA($F$6:F85))</f>
         <v>80</v>
       </c>
-      <c r="B85" s="54" t="s">
+      <c r="B85" s="77" t="s">
         <v>60</v>
       </c>
-      <c r="C85" s="54" t="s">
+      <c r="C85" s="77" t="s">
         <v>61</v>
       </c>
-      <c r="D85" s="55"/>
-      <c r="E85" s="56" t="s">
+      <c r="D85" s="78"/>
+      <c r="E85" s="79" t="s">
         <v>64</v>
       </c>
-      <c r="F85" s="57">
+      <c r="F85" s="80">
         <v>46252</v>
       </c>
-      <c r="G85" s="58" t="s">
+      <c r="G85" s="81" t="s">
         <v>59</v>
       </c>
-      <c r="H85" s="58">
+      <c r="H85" s="81">
         <v>57</v>
       </c>
-      <c r="I85" s="58">
+      <c r="I85" s="81">
         <v>1</v>
       </c>
-      <c r="J85" s="58" t="s">
+      <c r="J85" s="81" t="s">
         <v>64</v>
       </c>
-      <c r="K85" s="59">
+      <c r="K85" s="82">
         <v>162004407</v>
       </c>
-      <c r="L85" s="60">
+      <c r="L85" s="83">
         <v>46253</v>
       </c>
-      <c r="M85" s="61"/>
-      <c r="N85" s="62"/>
-      <c r="O85" s="63"/>
-      <c r="P85" s="63"/>
-      <c r="Q85" s="63"/>
-      <c r="R85" s="64"/>
-      <c r="S85" s="64"/>
-      <c r="T85" s="64">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="U85" s="64"/>
-      <c r="V85" s="64"/>
-      <c r="W85" s="64"/>
-      <c r="X85" s="64"/>
-      <c r="Y85" s="64"/>
-      <c r="Z85" s="64">
+      <c r="M85" s="84">
+        <v>46254</v>
+      </c>
+      <c r="N85" s="85">
+        <v>16592</v>
+      </c>
+      <c r="O85" s="86"/>
+      <c r="P85" s="86"/>
+      <c r="Q85" s="86"/>
+      <c r="R85" s="46">
+        <v>5066.26</v>
+      </c>
+      <c r="S85" s="46">
+        <v>1171.8600000000001</v>
+      </c>
+      <c r="T85" s="46">
+        <f t="shared" si="8"/>
+        <v>3894.4</v>
+      </c>
+      <c r="U85" s="46">
+        <v>3908.8</v>
+      </c>
+      <c r="V85" s="46"/>
+      <c r="W85" s="46"/>
+      <c r="X85" s="46">
+        <v>3755.4</v>
+      </c>
+      <c r="Y85" s="46"/>
+      <c r="Z85" s="46">
         <f>+T85-X85</f>
-        <v>0</v>
-      </c>
-      <c r="AA85" s="65" t="e">
+        <v>139</v>
+      </c>
+      <c r="AA85" s="39">
         <f>Z85/T85</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB85" s="66"/>
-      <c r="AC85" s="66"/>
-      <c r="AD85" s="66"/>
-      <c r="AE85" s="65"/>
-      <c r="AF85" s="67"/>
-      <c r="AG85" s="67"/>
-      <c r="AH85" s="68"/>
-      <c r="AI85" s="68">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AJ85" s="69"/>
-      <c r="AK85" s="69"/>
-      <c r="AL85" s="69"/>
-      <c r="AM85" s="70"/>
-      <c r="AN85" s="70"/>
-      <c r="AO85" s="70"/>
-      <c r="AP85" s="71">
+        <v>3.5692276088742807E-2</v>
+      </c>
+      <c r="AB85" s="73">
+        <v>3894.35</v>
+      </c>
+      <c r="AC85" s="73"/>
+      <c r="AD85" s="73"/>
+      <c r="AE85" s="39"/>
+      <c r="AF85" s="74"/>
+      <c r="AG85" s="74"/>
+      <c r="AH85" s="75"/>
+      <c r="AI85" s="75">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AQ85" s="69">
+      <c r="AJ85" s="87"/>
+      <c r="AK85" s="87"/>
+      <c r="AL85" s="87"/>
+      <c r="AM85" s="88"/>
+      <c r="AN85" s="88"/>
+      <c r="AO85" s="88"/>
+      <c r="AP85" s="89">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR85" s="69">
+      <c r="AQ85" s="87">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AS85" s="69"/>
-      <c r="AT85" s="69"/>
-      <c r="AU85" s="69"/>
-      <c r="AV85" s="69"/>
-      <c r="AW85" s="69"/>
-      <c r="AX85" s="69"/>
-      <c r="AY85" s="69"/>
-      <c r="AZ85" s="72"/>
-      <c r="BB85" s="45">
+      <c r="AR85" s="87">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AS85" s="87"/>
+      <c r="AT85" s="87"/>
+      <c r="AU85" s="87"/>
+      <c r="AV85" s="87"/>
+      <c r="AW85" s="87"/>
+      <c r="AX85" s="87"/>
+      <c r="AY85" s="87"/>
+      <c r="AZ85" s="90"/>
+      <c r="BB85" s="92">
         <f>IF(AND(AB85="",AC85=""),T85,IF(AC85="",AB85,AC85))</f>
-        <v>0</v>
-      </c>
-      <c r="BC85" s="45">
-        <f>+X85</f>
-        <v>0</v>
-      </c>
-      <c r="BD85" s="45"/>
-      <c r="BE85" s="45">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="BF85" s="39" t="e">
-        <f t="shared" si="48"/>
-        <v>#DIV/0!</v>
+        <v>3894.35</v>
+      </c>
+      <c r="BC85" s="92">
+        <f t="shared" si="42"/>
+        <v>3755.4</v>
+      </c>
+      <c r="BD85" s="92"/>
+      <c r="BE85" s="92">
+        <f t="shared" si="50"/>
+        <v>138.94999999999982</v>
+      </c>
+      <c r="BF85" s="39">
+        <f t="shared" si="51"/>
+        <v>3.5679895232837266E-2</v>
       </c>
     </row>
-    <row r="86" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A86" s="53">
+    <row r="86" spans="1:58" s="91" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A86" s="76">
         <f>IF(ISBLANK(F86),"",COUNTA($F$6:F86))</f>
         <v>81</v>
       </c>
-      <c r="B86" s="54" t="s">
+      <c r="B86" s="77" t="s">
         <v>60</v>
       </c>
-      <c r="C86" s="54" t="s">
+      <c r="C86" s="77" t="s">
         <v>61</v>
       </c>
-      <c r="D86" s="55"/>
-      <c r="E86" s="56" t="s">
+      <c r="D86" s="78"/>
+      <c r="E86" s="79" t="s">
         <v>63</v>
       </c>
-      <c r="F86" s="57">
+      <c r="F86" s="80">
         <v>46253</v>
       </c>
-      <c r="G86" s="58" t="s">
+      <c r="G86" s="81" t="s">
         <v>59</v>
       </c>
-      <c r="H86" s="58">
+      <c r="H86" s="81">
         <v>59</v>
       </c>
-      <c r="I86" s="58">
+      <c r="I86" s="81">
         <v>6</v>
       </c>
-      <c r="J86" s="58" t="s">
+      <c r="J86" s="81" t="s">
         <v>63</v>
       </c>
-      <c r="K86" s="59">
+      <c r="K86" s="82">
         <v>162006452</v>
       </c>
-      <c r="L86" s="60">
+      <c r="L86" s="83">
         <v>46253</v>
       </c>
-      <c r="M86" s="61"/>
-      <c r="N86" s="62"/>
-      <c r="O86" s="63"/>
-      <c r="P86" s="63"/>
-      <c r="Q86" s="63"/>
-      <c r="R86" s="64"/>
-      <c r="S86" s="64"/>
-      <c r="T86" s="64">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="U86" s="64"/>
-      <c r="V86" s="64"/>
-      <c r="W86" s="64"/>
-      <c r="X86" s="64"/>
-      <c r="Y86" s="64"/>
-      <c r="Z86" s="64">
+      <c r="M86" s="84">
+        <v>46254</v>
+      </c>
+      <c r="N86" s="85">
+        <v>16593</v>
+      </c>
+      <c r="O86" s="86"/>
+      <c r="P86" s="86"/>
+      <c r="Q86" s="86"/>
+      <c r="R86" s="46">
+        <v>4811.58</v>
+      </c>
+      <c r="S86" s="46">
+        <v>1109.98</v>
+      </c>
+      <c r="T86" s="46">
+        <f t="shared" si="8"/>
+        <v>3701.6</v>
+      </c>
+      <c r="U86" s="46">
+        <v>3703.4</v>
+      </c>
+      <c r="V86" s="46"/>
+      <c r="W86" s="46"/>
+      <c r="X86" s="46">
+        <v>3701.6</v>
+      </c>
+      <c r="Y86" s="46"/>
+      <c r="Z86" s="46">
         <f>+T86-X86</f>
         <v>0</v>
       </c>
-      <c r="AA86" s="65" t="e">
+      <c r="AA86" s="39">
         <f>Z86/T86</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB86" s="66"/>
-      <c r="AC86" s="66"/>
-      <c r="AD86" s="66"/>
-      <c r="AE86" s="65"/>
-      <c r="AF86" s="67"/>
-      <c r="AG86" s="67"/>
-      <c r="AH86" s="68"/>
-      <c r="AI86" s="68">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AJ86" s="69"/>
-      <c r="AK86" s="69"/>
-      <c r="AL86" s="69"/>
-      <c r="AM86" s="70"/>
-      <c r="AN86" s="70"/>
-      <c r="AO86" s="70"/>
-      <c r="AP86" s="71">
+        <v>0</v>
+      </c>
+      <c r="AB86" s="73">
+        <v>3701.55</v>
+      </c>
+      <c r="AC86" s="73"/>
+      <c r="AD86" s="73"/>
+      <c r="AE86" s="39"/>
+      <c r="AF86" s="74"/>
+      <c r="AG86" s="74"/>
+      <c r="AH86" s="75"/>
+      <c r="AI86" s="75">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AQ86" s="69">
+      <c r="AJ86" s="87"/>
+      <c r="AK86" s="87"/>
+      <c r="AL86" s="87"/>
+      <c r="AM86" s="88"/>
+      <c r="AN86" s="88"/>
+      <c r="AO86" s="88"/>
+      <c r="AP86" s="89">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR86" s="69">
+      <c r="AQ86" s="87">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AS86" s="69"/>
-      <c r="AT86" s="69"/>
-      <c r="AU86" s="69"/>
-      <c r="AV86" s="69"/>
-      <c r="AW86" s="69"/>
-      <c r="AX86" s="69"/>
-      <c r="AY86" s="69"/>
-      <c r="AZ86" s="72"/>
-      <c r="BB86" s="45">
+      <c r="AR86" s="87">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AS86" s="87"/>
+      <c r="AT86" s="87"/>
+      <c r="AU86" s="87"/>
+      <c r="AV86" s="87"/>
+      <c r="AW86" s="87"/>
+      <c r="AX86" s="87"/>
+      <c r="AY86" s="87"/>
+      <c r="AZ86" s="90"/>
+      <c r="BB86" s="92">
         <f>IF(AND(AB86="",AC86=""),T86,IF(AC86="",AB86,AC86))</f>
-        <v>0</v>
-      </c>
-      <c r="BC86" s="45">
-        <f>+X86</f>
-        <v>0</v>
-      </c>
-      <c r="BD86" s="45"/>
-      <c r="BE86" s="45">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="BF86" s="39" t="e">
-        <f t="shared" si="48"/>
-        <v>#DIV/0!</v>
+        <v>3701.55</v>
+      </c>
+      <c r="BC86" s="92">
+        <f t="shared" si="42"/>
+        <v>3701.6</v>
+      </c>
+      <c r="BD86" s="92"/>
+      <c r="BE86" s="92">
+        <f t="shared" si="50"/>
+        <v>-4.9999999999727152E-2</v>
+      </c>
+      <c r="BF86" s="39">
+        <f t="shared" si="51"/>
+        <v>-1.3507854817502708E-5</v>
       </c>
     </row>
-    <row r="87" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="53">
+    <row r="87" spans="1:58" s="91" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A87" s="76">
         <f>IF(ISBLANK(F87),"",COUNTA($F$6:F87))</f>
         <v>82</v>
       </c>
-      <c r="B87" s="54" t="s">
+      <c r="B87" s="77" t="s">
         <v>60</v>
       </c>
-      <c r="C87" s="54" t="s">
+      <c r="C87" s="77" t="s">
         <v>61</v>
       </c>
-      <c r="D87" s="55"/>
-      <c r="E87" s="56" t="s">
+      <c r="D87" s="78"/>
+      <c r="E87" s="79" t="s">
         <v>63</v>
       </c>
-      <c r="F87" s="57">
+      <c r="F87" s="80">
         <v>46253</v>
       </c>
-      <c r="G87" s="58" t="s">
+      <c r="G87" s="81" t="s">
         <v>59</v>
       </c>
-      <c r="H87" s="58">
+      <c r="H87" s="81">
         <v>58</v>
       </c>
-      <c r="I87" s="58">
+      <c r="I87" s="81">
         <v>2</v>
       </c>
-      <c r="J87" s="58" t="s">
+      <c r="J87" s="81" t="s">
         <v>63</v>
       </c>
-      <c r="K87" s="59">
+      <c r="K87" s="82">
         <v>162006453</v>
       </c>
-      <c r="L87" s="60">
+      <c r="L87" s="83">
         <v>46254</v>
       </c>
-      <c r="M87" s="61"/>
-      <c r="N87" s="62"/>
-      <c r="O87" s="63"/>
-      <c r="P87" s="63"/>
-      <c r="Q87" s="63"/>
-      <c r="R87" s="64"/>
-      <c r="S87" s="64"/>
-      <c r="T87" s="64">
-        <f t="shared" ref="T87" si="49">+R87-S87</f>
-        <v>0</v>
-      </c>
-      <c r="U87" s="64"/>
-      <c r="V87" s="64"/>
-      <c r="W87" s="64"/>
-      <c r="X87" s="64"/>
-      <c r="Y87" s="64"/>
-      <c r="Z87" s="64">
+      <c r="M87" s="84">
+        <v>46254</v>
+      </c>
+      <c r="N87" s="85">
+        <v>16594</v>
+      </c>
+      <c r="O87" s="86"/>
+      <c r="P87" s="86"/>
+      <c r="Q87" s="86"/>
+      <c r="R87" s="46">
+        <v>5082.71</v>
+      </c>
+      <c r="S87" s="46">
+        <v>1171.9099999999999</v>
+      </c>
+      <c r="T87" s="46">
+        <f t="shared" ref="T87" si="52">+R87-S87</f>
+        <v>3910.8</v>
+      </c>
+      <c r="U87" s="46">
+        <v>3912.2</v>
+      </c>
+      <c r="V87" s="46"/>
+      <c r="W87" s="46"/>
+      <c r="X87" s="46">
+        <v>3805.2</v>
+      </c>
+      <c r="Y87" s="46"/>
+      <c r="Z87" s="46">
         <f>+T87-X87</f>
-        <v>0</v>
-      </c>
-      <c r="AA87" s="65" t="e">
+        <v>105.60000000000036</v>
+      </c>
+      <c r="AA87" s="39">
         <f>Z87/T87</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB87" s="66"/>
-      <c r="AC87" s="66"/>
-      <c r="AD87" s="66"/>
-      <c r="AE87" s="65"/>
-      <c r="AF87" s="67"/>
-      <c r="AG87" s="67"/>
-      <c r="AH87" s="68"/>
-      <c r="AI87" s="68">
-        <f t="shared" ref="AI87" si="50">+AG87+AH87</f>
-        <v>0</v>
-      </c>
-      <c r="AJ87" s="69"/>
-      <c r="AK87" s="69"/>
-      <c r="AL87" s="69"/>
-      <c r="AM87" s="70"/>
-      <c r="AN87" s="70"/>
-      <c r="AO87" s="70"/>
-      <c r="AP87" s="71">
-        <f t="shared" ref="AP87" si="51">ROUNDUP((AO87-AM87+(AO87&lt;AM87))*24,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AQ87" s="69">
-        <f t="shared" ref="AQ87" si="52">IF(AP87&gt;5,(AP87-5),0)</f>
-        <v>0</v>
-      </c>
-      <c r="AR87" s="69">
-        <f t="shared" ref="AR87" si="53">+AQ87*8850</f>
-        <v>0</v>
-      </c>
-      <c r="AS87" s="69"/>
-      <c r="AT87" s="69"/>
-      <c r="AU87" s="69"/>
-      <c r="AV87" s="69"/>
-      <c r="AW87" s="69"/>
-      <c r="AX87" s="69"/>
-      <c r="AY87" s="69"/>
-      <c r="AZ87" s="72"/>
-      <c r="BB87" s="45">
+        <v>2.7002147898128354E-2</v>
+      </c>
+      <c r="AB87" s="73">
+        <v>3910.8</v>
+      </c>
+      <c r="AC87" s="73"/>
+      <c r="AD87" s="73"/>
+      <c r="AE87" s="39"/>
+      <c r="AF87" s="74"/>
+      <c r="AG87" s="74"/>
+      <c r="AH87" s="75"/>
+      <c r="AI87" s="75">
+        <f t="shared" ref="AI87" si="53">+AG87+AH87</f>
+        <v>0</v>
+      </c>
+      <c r="AJ87" s="87"/>
+      <c r="AK87" s="87"/>
+      <c r="AL87" s="87"/>
+      <c r="AM87" s="88"/>
+      <c r="AN87" s="88"/>
+      <c r="AO87" s="88"/>
+      <c r="AP87" s="89">
+        <f t="shared" ref="AP87" si="54">ROUNDUP((AO87-AM87+(AO87&lt;AM87))*24,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ87" s="87">
+        <f t="shared" ref="AQ87" si="55">IF(AP87&gt;5,(AP87-5),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AR87" s="87">
+        <f t="shared" ref="AR87" si="56">+AQ87*8850</f>
+        <v>0</v>
+      </c>
+      <c r="AS87" s="87"/>
+      <c r="AT87" s="87"/>
+      <c r="AU87" s="87"/>
+      <c r="AV87" s="87"/>
+      <c r="AW87" s="87"/>
+      <c r="AX87" s="87"/>
+      <c r="AY87" s="87"/>
+      <c r="AZ87" s="90"/>
+      <c r="BB87" s="92">
         <f>IF(AND(AB87="",AC87=""),T87,IF(AC87="",AB87,AC87))</f>
-        <v>0</v>
-      </c>
-      <c r="BC87" s="45">
-        <f>+X87</f>
-        <v>0</v>
-      </c>
-      <c r="BD87" s="45"/>
-      <c r="BE87" s="45">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="BF87" s="39" t="e">
-        <f t="shared" si="48"/>
-        <v>#DIV/0!</v>
+        <v>3910.8</v>
+      </c>
+      <c r="BC87" s="92">
+        <f t="shared" si="42"/>
+        <v>3805.2</v>
+      </c>
+      <c r="BD87" s="92"/>
+      <c r="BE87" s="92">
+        <f t="shared" si="50"/>
+        <v>105.60000000000036</v>
+      </c>
+      <c r="BF87" s="39">
+        <f t="shared" si="51"/>
+        <v>2.7002147898128354E-2</v>
       </c>
     </row>
     <row r="88" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -30318,407 +30212,1223 @@
         <v>0</v>
       </c>
       <c r="BC88" s="45">
-        <f>+X88</f>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="BD88" s="45"/>
       <c r="BE88" s="45">
-        <f t="shared" ref="BE88:BE89" si="54">+BB88-BC88</f>
+        <f t="shared" ref="BE88:BE96" si="57">+BB88-BC88</f>
         <v>0</v>
       </c>
       <c r="BF88" s="39" t="e">
-        <f t="shared" ref="BF88:BF90" si="55">+BE88/BB88</f>
+        <f t="shared" ref="BF88:BF97" si="58">+BE88/BB88</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="89" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A89" s="21" t="str">
+      <c r="A89" s="53">
         <f>IF(ISBLANK(F89),"",COUNTA($F$6:F89))</f>
-        <v/>
-      </c>
-      <c r="B89" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="B89" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="C89" s="37" t="s">
+      <c r="C89" s="54" t="s">
         <v>61</v>
       </c>
-      <c r="D89" s="22"/>
-      <c r="E89" s="23"/>
-      <c r="F89" s="36"/>
-      <c r="G89" s="24"/>
-      <c r="H89" s="24"/>
-      <c r="I89" s="24"/>
-      <c r="J89" s="24"/>
-      <c r="K89" s="25"/>
-      <c r="L89" s="26"/>
-      <c r="M89" s="38"/>
-      <c r="N89" s="52"/>
-      <c r="O89" s="27"/>
-      <c r="P89" s="27"/>
-      <c r="Q89" s="27"/>
-      <c r="R89" s="28"/>
-      <c r="S89" s="28"/>
-      <c r="T89" s="46">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U89" s="28"/>
-      <c r="V89" s="28"/>
-      <c r="W89" s="28"/>
-      <c r="X89" s="28"/>
-      <c r="Y89" s="28"/>
-      <c r="Z89" s="28">
+      <c r="D89" s="55"/>
+      <c r="E89" s="56" t="s">
+        <v>65</v>
+      </c>
+      <c r="F89" s="57">
+        <v>46255</v>
+      </c>
+      <c r="G89" s="58" t="s">
+        <v>59</v>
+      </c>
+      <c r="H89" s="58">
+        <v>58</v>
+      </c>
+      <c r="I89" s="58">
+        <v>1</v>
+      </c>
+      <c r="J89" s="58" t="s">
+        <v>67</v>
+      </c>
+      <c r="K89" s="59">
+        <v>162011724</v>
+      </c>
+      <c r="L89" s="60">
+        <v>46256</v>
+      </c>
+      <c r="M89" s="61"/>
+      <c r="N89" s="62"/>
+      <c r="O89" s="63"/>
+      <c r="P89" s="63"/>
+      <c r="Q89" s="63"/>
+      <c r="R89" s="64"/>
+      <c r="S89" s="64"/>
+      <c r="T89" s="64">
+        <f t="shared" ref="T89:T95" si="59">+R89-S89</f>
+        <v>0</v>
+      </c>
+      <c r="U89" s="64"/>
+      <c r="V89" s="64"/>
+      <c r="W89" s="64"/>
+      <c r="X89" s="64"/>
+      <c r="Y89" s="64"/>
+      <c r="Z89" s="64">
         <f>+T89-X89</f>
         <v>0</v>
       </c>
-      <c r="AA89" s="29" t="e">
+      <c r="AA89" s="65" t="e">
         <f>Z89/T89</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB89" s="40"/>
-      <c r="AC89" s="40"/>
-      <c r="AD89" s="40"/>
-      <c r="AE89" s="29"/>
-      <c r="AF89" s="30"/>
-      <c r="AG89" s="30"/>
-      <c r="AH89" s="31"/>
-      <c r="AI89" s="31">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AJ89" s="32"/>
-      <c r="AK89" s="32"/>
-      <c r="AL89" s="32"/>
-      <c r="AM89" s="33"/>
-      <c r="AN89" s="33"/>
-      <c r="AO89" s="33"/>
-      <c r="AP89" s="34">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AQ89" s="32">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AR89" s="32">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AS89" s="32"/>
-      <c r="AT89" s="32"/>
-      <c r="AU89" s="32"/>
-      <c r="AV89" s="32"/>
-      <c r="AW89" s="32"/>
-      <c r="AX89" s="32"/>
-      <c r="AY89" s="32"/>
-      <c r="AZ89" s="35"/>
+      <c r="AB89" s="66"/>
+      <c r="AC89" s="66"/>
+      <c r="AD89" s="66"/>
+      <c r="AE89" s="65"/>
+      <c r="AF89" s="67"/>
+      <c r="AG89" s="67"/>
+      <c r="AH89" s="68"/>
+      <c r="AI89" s="68">
+        <f t="shared" ref="AI89:AI95" si="60">+AG89+AH89</f>
+        <v>0</v>
+      </c>
+      <c r="AJ89" s="69"/>
+      <c r="AK89" s="69"/>
+      <c r="AL89" s="69"/>
+      <c r="AM89" s="70"/>
+      <c r="AN89" s="70"/>
+      <c r="AO89" s="70"/>
+      <c r="AP89" s="71">
+        <f t="shared" ref="AP89:AP95" si="61">ROUNDUP((AO89-AM89+(AO89&lt;AM89))*24,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ89" s="69">
+        <f t="shared" ref="AQ89:AQ95" si="62">IF(AP89&gt;5,(AP89-5),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AR89" s="69">
+        <f t="shared" ref="AR89:AR95" si="63">+AQ89*8850</f>
+        <v>0</v>
+      </c>
+      <c r="AS89" s="69"/>
+      <c r="AT89" s="69"/>
+      <c r="AU89" s="69"/>
+      <c r="AV89" s="69"/>
+      <c r="AW89" s="69"/>
+      <c r="AX89" s="69"/>
+      <c r="AY89" s="69"/>
+      <c r="AZ89" s="72"/>
       <c r="BB89" s="45">
         <f>IF(AND(AB89="",AC89=""),T89,IF(AC89="",AB89,AC89))</f>
         <v>0</v>
       </c>
       <c r="BC89" s="45">
-        <f>+X89</f>
+        <f t="shared" ref="BC89:BC95" si="64">+X89</f>
         <v>0</v>
       </c>
       <c r="BD89" s="45"/>
       <c r="BE89" s="45">
-        <f t="shared" si="54"/>
+        <f t="shared" ref="BE89:BE95" si="65">+BB89-BC89</f>
         <v>0</v>
       </c>
       <c r="BF89" s="39" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" ref="BF89:BF95" si="66">+BE89/BB89</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="90" spans="1:58" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="9">
-        <f>+COUNT(A6:A89)</f>
-        <v>83</v>
-      </c>
-      <c r="B90" s="10">
-        <f>+COUNTIF(X6:X89,"&gt;0")</f>
-        <v>79</v>
-      </c>
-      <c r="C90" s="10"/>
-      <c r="D90" s="10"/>
-      <c r="E90" s="10"/>
-      <c r="F90" s="10"/>
-      <c r="G90" s="10"/>
-      <c r="H90" s="10"/>
-      <c r="I90" s="10"/>
-      <c r="J90" s="10"/>
-      <c r="K90" s="10"/>
-      <c r="L90" s="11"/>
-      <c r="M90" s="10"/>
-      <c r="N90" s="10"/>
-      <c r="O90" s="10"/>
-      <c r="P90" s="10"/>
-      <c r="Q90" s="10"/>
-      <c r="R90" s="12">
-        <f t="shared" ref="R90:Y90" si="56">SUM(R6:R89)</f>
-        <v>396239.21999999991</v>
-      </c>
-      <c r="S90" s="12">
-        <f t="shared" si="56"/>
-        <v>92543.419999999984</v>
-      </c>
-      <c r="T90" s="12">
-        <f t="shared" si="56"/>
-        <v>303695.8</v>
-      </c>
-      <c r="U90" s="12">
-        <f t="shared" si="56"/>
-        <v>305323.7</v>
-      </c>
-      <c r="V90" s="12">
-        <f t="shared" si="56"/>
-        <v>0</v>
-      </c>
-      <c r="W90" s="12">
-        <f t="shared" si="56"/>
-        <v>0</v>
-      </c>
-      <c r="X90" s="12">
-        <f t="shared" si="56"/>
-        <v>302001.69999999995</v>
-      </c>
-      <c r="Y90" s="12">
-        <f t="shared" si="56"/>
-        <v>0</v>
-      </c>
-      <c r="Z90" s="12">
-        <f>T90-X90</f>
-        <v>1694.1000000000349</v>
-      </c>
-      <c r="AA90" s="13">
+    <row r="90" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A90" s="53">
+        <f>IF(ISBLANK(F90),"",COUNTA($F$6:F90))</f>
+        <v>85</v>
+      </c>
+      <c r="B90" s="54" t="s">
+        <v>60</v>
+      </c>
+      <c r="C90" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="D90" s="55"/>
+      <c r="E90" s="56" t="s">
+        <v>64</v>
+      </c>
+      <c r="F90" s="57">
+        <v>46255</v>
+      </c>
+      <c r="G90" s="58" t="s">
+        <v>59</v>
+      </c>
+      <c r="H90" s="58">
+        <v>58</v>
+      </c>
+      <c r="I90" s="58">
+        <v>1</v>
+      </c>
+      <c r="J90" s="58" t="s">
+        <v>64</v>
+      </c>
+      <c r="K90" s="59">
+        <v>162004411</v>
+      </c>
+      <c r="L90" s="60">
+        <v>46255</v>
+      </c>
+      <c r="M90" s="61"/>
+      <c r="N90" s="62"/>
+      <c r="O90" s="63"/>
+      <c r="P90" s="63"/>
+      <c r="Q90" s="63"/>
+      <c r="R90" s="64"/>
+      <c r="S90" s="64"/>
+      <c r="T90" s="64">
+        <f t="shared" si="59"/>
+        <v>0</v>
+      </c>
+      <c r="U90" s="64"/>
+      <c r="V90" s="64"/>
+      <c r="W90" s="64"/>
+      <c r="X90" s="64"/>
+      <c r="Y90" s="64"/>
+      <c r="Z90" s="64">
+        <f>+T90-X90</f>
+        <v>0</v>
+      </c>
+      <c r="AA90" s="65" t="e">
         <f>Z90/T90</f>
-        <v>5.5782793176594311E-3</v>
-      </c>
-      <c r="AB90" s="41"/>
-      <c r="AC90" s="41"/>
-      <c r="AD90" s="41"/>
-      <c r="AE90" s="13"/>
-      <c r="AF90" s="12">
-        <f>SUM(AF6:AF89)</f>
-        <v>0</v>
-      </c>
-      <c r="AG90" s="12">
-        <f>SUM(AG6:AG89)</f>
-        <v>0</v>
-      </c>
-      <c r="AH90" s="12">
-        <f>SUM(AH6:AH89)</f>
-        <v>0</v>
-      </c>
-      <c r="AI90" s="12">
-        <f>SUM(AI6:AI89)</f>
-        <v>0</v>
-      </c>
-      <c r="AJ90" s="14"/>
-      <c r="AK90" s="14"/>
-      <c r="AL90" s="12"/>
-      <c r="AM90" s="15"/>
-      <c r="AN90" s="16"/>
-      <c r="AO90" s="16"/>
-      <c r="AP90" s="17"/>
-      <c r="AQ90" s="10">
-        <f>SUM(AQ6:AQ89)</f>
-        <v>0</v>
-      </c>
-      <c r="AR90" s="18">
-        <f>SUM(AR6:AR89)</f>
-        <v>0</v>
-      </c>
-      <c r="AS90" s="10">
-        <f>SUM(AS6:AS89)</f>
-        <v>0</v>
-      </c>
-      <c r="AT90" s="10">
-        <f>SUM(AT6:AT89)</f>
-        <v>0</v>
-      </c>
-      <c r="AU90" s="10">
-        <f>SUM(AU6:AU89)</f>
-        <v>0</v>
-      </c>
-      <c r="AV90" s="10">
-        <f>+SUM(AV6:AV89)</f>
-        <v>0</v>
-      </c>
-      <c r="AW90" s="10">
-        <f>SUM(AW6:AW89)</f>
-        <v>0</v>
-      </c>
-      <c r="AX90" s="10">
-        <f>SUM(AX6:AX89)</f>
-        <v>0</v>
-      </c>
-      <c r="AY90" s="10">
-        <f>SUM(AY6:AY89)</f>
-        <v>0</v>
-      </c>
-      <c r="AZ90" s="19"/>
-      <c r="BB90" s="42">
-        <f>SUM(BB6:BB89)</f>
-        <v>305197.82</v>
-      </c>
-      <c r="BC90" s="42">
-        <f>SUM(BC6:BC89)</f>
-        <v>302001.69999999995</v>
-      </c>
-      <c r="BD90" s="42">
-        <f>SUM(BD6:BD89)</f>
-        <v>0</v>
-      </c>
-      <c r="BE90" s="42">
-        <f>SUM(BE6:BE89)</f>
-        <v>3196.1199999999967</v>
-      </c>
-      <c r="BF90" s="43">
-        <f t="shared" si="55"/>
-        <v>1.0472289743091863E-2</v>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB90" s="66"/>
+      <c r="AC90" s="66"/>
+      <c r="AD90" s="66"/>
+      <c r="AE90" s="65"/>
+      <c r="AF90" s="67"/>
+      <c r="AG90" s="67"/>
+      <c r="AH90" s="68"/>
+      <c r="AI90" s="68">
+        <f t="shared" si="60"/>
+        <v>0</v>
+      </c>
+      <c r="AJ90" s="69"/>
+      <c r="AK90" s="69"/>
+      <c r="AL90" s="69"/>
+      <c r="AM90" s="70"/>
+      <c r="AN90" s="70"/>
+      <c r="AO90" s="70"/>
+      <c r="AP90" s="71">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+      <c r="AQ90" s="69">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="AR90" s="69">
+        <f t="shared" si="63"/>
+        <v>0</v>
+      </c>
+      <c r="AS90" s="69"/>
+      <c r="AT90" s="69"/>
+      <c r="AU90" s="69"/>
+      <c r="AV90" s="69"/>
+      <c r="AW90" s="69"/>
+      <c r="AX90" s="69"/>
+      <c r="AY90" s="69"/>
+      <c r="AZ90" s="72"/>
+      <c r="BB90" s="45">
+        <f>IF(AND(AB90="",AC90=""),T90,IF(AC90="",AB90,AC90))</f>
+        <v>0</v>
+      </c>
+      <c r="BC90" s="45">
+        <f t="shared" si="64"/>
+        <v>0</v>
+      </c>
+      <c r="BD90" s="45"/>
+      <c r="BE90" s="45">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="BF90" s="39" t="e">
+        <f t="shared" si="66"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="91" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A91" s="53">
+        <f>IF(ISBLANK(F91),"",COUNTA($F$6:F91))</f>
+        <v>86</v>
+      </c>
+      <c r="B91" s="54" t="s">
+        <v>60</v>
+      </c>
+      <c r="C91" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="D91" s="55"/>
+      <c r="E91" s="56" t="s">
+        <v>63</v>
+      </c>
+      <c r="F91" s="57">
+        <v>46256</v>
+      </c>
+      <c r="G91" s="58" t="s">
+        <v>59</v>
+      </c>
+      <c r="H91" s="58">
+        <v>58</v>
+      </c>
+      <c r="I91" s="58">
+        <v>0</v>
+      </c>
+      <c r="J91" s="58" t="s">
+        <v>63</v>
+      </c>
+      <c r="K91" s="59">
+        <v>162006457</v>
+      </c>
+      <c r="L91" s="60">
+        <v>46256</v>
+      </c>
+      <c r="M91" s="61"/>
+      <c r="N91" s="62"/>
+      <c r="O91" s="63"/>
+      <c r="P91" s="63"/>
+      <c r="Q91" s="63"/>
+      <c r="R91" s="64"/>
+      <c r="S91" s="64"/>
+      <c r="T91" s="64">
+        <f t="shared" si="59"/>
+        <v>0</v>
+      </c>
+      <c r="U91" s="64"/>
+      <c r="V91" s="64"/>
+      <c r="W91" s="64"/>
+      <c r="X91" s="64"/>
+      <c r="Y91" s="64"/>
+      <c r="Z91" s="64">
+        <f>+T91-X91</f>
+        <v>0</v>
+      </c>
+      <c r="AA91" s="65" t="e">
+        <f>Z91/T91</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB91" s="66"/>
+      <c r="AC91" s="66"/>
+      <c r="AD91" s="66"/>
+      <c r="AE91" s="65"/>
+      <c r="AF91" s="67"/>
+      <c r="AG91" s="67"/>
+      <c r="AH91" s="68"/>
+      <c r="AI91" s="68">
+        <f t="shared" si="60"/>
+        <v>0</v>
+      </c>
+      <c r="AJ91" s="69"/>
+      <c r="AK91" s="69"/>
+      <c r="AL91" s="69"/>
+      <c r="AM91" s="70"/>
+      <c r="AN91" s="70"/>
+      <c r="AO91" s="70"/>
+      <c r="AP91" s="71">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+      <c r="AQ91" s="69">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="AR91" s="69">
+        <f t="shared" si="63"/>
+        <v>0</v>
+      </c>
+      <c r="AS91" s="69"/>
+      <c r="AT91" s="69"/>
+      <c r="AU91" s="69"/>
+      <c r="AV91" s="69"/>
+      <c r="AW91" s="69"/>
+      <c r="AX91" s="69"/>
+      <c r="AY91" s="69"/>
+      <c r="AZ91" s="72"/>
+      <c r="BB91" s="45">
+        <f>IF(AND(AB91="",AC91=""),T91,IF(AC91="",AB91,AC91))</f>
+        <v>0</v>
+      </c>
+      <c r="BC91" s="45">
+        <f t="shared" si="64"/>
+        <v>0</v>
+      </c>
+      <c r="BD91" s="45"/>
+      <c r="BE91" s="45">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="BF91" s="39" t="e">
+        <f t="shared" si="66"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="92" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A92" s="53">
+        <f>IF(ISBLANK(F92),"",COUNTA($F$6:F92))</f>
+        <v>87</v>
+      </c>
+      <c r="B92" s="54" t="s">
+        <v>60</v>
+      </c>
+      <c r="C92" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="D92" s="55"/>
+      <c r="E92" s="56" t="s">
+        <v>65</v>
+      </c>
+      <c r="F92" s="57">
+        <v>46256</v>
+      </c>
+      <c r="G92" s="58" t="s">
+        <v>59</v>
+      </c>
+      <c r="H92" s="58">
+        <v>58</v>
+      </c>
+      <c r="I92" s="58">
+        <v>0</v>
+      </c>
+      <c r="J92" s="58" t="s">
+        <v>67</v>
+      </c>
+      <c r="K92" s="59">
+        <v>162011726</v>
+      </c>
+      <c r="L92" s="60">
+        <v>46256</v>
+      </c>
+      <c r="M92" s="61"/>
+      <c r="N92" s="62"/>
+      <c r="O92" s="63"/>
+      <c r="P92" s="63"/>
+      <c r="Q92" s="63"/>
+      <c r="R92" s="64"/>
+      <c r="S92" s="64"/>
+      <c r="T92" s="64">
+        <f t="shared" si="59"/>
+        <v>0</v>
+      </c>
+      <c r="U92" s="64"/>
+      <c r="V92" s="64"/>
+      <c r="W92" s="64"/>
+      <c r="X92" s="64"/>
+      <c r="Y92" s="64"/>
+      <c r="Z92" s="64">
+        <f>+T92-X92</f>
+        <v>0</v>
+      </c>
+      <c r="AA92" s="65" t="e">
+        <f>Z92/T92</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB92" s="66"/>
+      <c r="AC92" s="66"/>
+      <c r="AD92" s="66"/>
+      <c r="AE92" s="65"/>
+      <c r="AF92" s="67"/>
+      <c r="AG92" s="67"/>
+      <c r="AH92" s="68"/>
+      <c r="AI92" s="68">
+        <f t="shared" si="60"/>
+        <v>0</v>
+      </c>
+      <c r="AJ92" s="69"/>
+      <c r="AK92" s="69"/>
+      <c r="AL92" s="69"/>
+      <c r="AM92" s="70"/>
+      <c r="AN92" s="70"/>
+      <c r="AO92" s="70"/>
+      <c r="AP92" s="71">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+      <c r="AQ92" s="69">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="AR92" s="69">
+        <f t="shared" si="63"/>
+        <v>0</v>
+      </c>
+      <c r="AS92" s="69"/>
+      <c r="AT92" s="69"/>
+      <c r="AU92" s="69"/>
+      <c r="AV92" s="69"/>
+      <c r="AW92" s="69"/>
+      <c r="AX92" s="69"/>
+      <c r="AY92" s="69"/>
+      <c r="AZ92" s="72"/>
+      <c r="BB92" s="45">
+        <f>IF(AND(AB92="",AC92=""),T92,IF(AC92="",AB92,AC92))</f>
+        <v>0</v>
+      </c>
+      <c r="BC92" s="45">
+        <f t="shared" si="64"/>
+        <v>0</v>
+      </c>
+      <c r="BD92" s="45"/>
+      <c r="BE92" s="45">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="BF92" s="39" t="e">
+        <f t="shared" si="66"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="93" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A93" s="53">
+        <f>IF(ISBLANK(F93),"",COUNTA($F$6:F93))</f>
+        <v>88</v>
+      </c>
+      <c r="B93" s="54" t="s">
+        <v>60</v>
+      </c>
+      <c r="C93" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="D93" s="55"/>
+      <c r="E93" s="56" t="s">
+        <v>66</v>
+      </c>
+      <c r="F93" s="57">
+        <v>46256</v>
+      </c>
+      <c r="G93" s="58" t="s">
+        <v>59</v>
+      </c>
+      <c r="H93" s="58">
+        <v>59</v>
+      </c>
+      <c r="I93" s="58">
+        <v>0</v>
+      </c>
+      <c r="J93" s="58" t="s">
+        <v>66</v>
+      </c>
+      <c r="K93" s="59">
+        <v>162003211</v>
+      </c>
+      <c r="L93" s="60">
+        <v>46257</v>
+      </c>
+      <c r="M93" s="61"/>
+      <c r="N93" s="62"/>
+      <c r="O93" s="63"/>
+      <c r="P93" s="63"/>
+      <c r="Q93" s="63"/>
+      <c r="R93" s="64"/>
+      <c r="S93" s="64"/>
+      <c r="T93" s="64">
+        <f t="shared" si="59"/>
+        <v>0</v>
+      </c>
+      <c r="U93" s="64"/>
+      <c r="V93" s="64"/>
+      <c r="W93" s="64"/>
+      <c r="X93" s="64"/>
+      <c r="Y93" s="64"/>
+      <c r="Z93" s="64">
+        <f>+T93-X93</f>
+        <v>0</v>
+      </c>
+      <c r="AA93" s="65" t="e">
+        <f>Z93/T93</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB93" s="66"/>
+      <c r="AC93" s="66"/>
+      <c r="AD93" s="66"/>
+      <c r="AE93" s="65"/>
+      <c r="AF93" s="67"/>
+      <c r="AG93" s="67"/>
+      <c r="AH93" s="68"/>
+      <c r="AI93" s="68">
+        <f t="shared" si="60"/>
+        <v>0</v>
+      </c>
+      <c r="AJ93" s="69"/>
+      <c r="AK93" s="69"/>
+      <c r="AL93" s="69"/>
+      <c r="AM93" s="70"/>
+      <c r="AN93" s="70"/>
+      <c r="AO93" s="70"/>
+      <c r="AP93" s="71">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+      <c r="AQ93" s="69">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="AR93" s="69">
+        <f t="shared" si="63"/>
+        <v>0</v>
+      </c>
+      <c r="AS93" s="69"/>
+      <c r="AT93" s="69"/>
+      <c r="AU93" s="69"/>
+      <c r="AV93" s="69"/>
+      <c r="AW93" s="69"/>
+      <c r="AX93" s="69"/>
+      <c r="AY93" s="69"/>
+      <c r="AZ93" s="72"/>
+      <c r="BB93" s="45">
+        <f>IF(AND(AB93="",AC93=""),T93,IF(AC93="",AB93,AC93))</f>
+        <v>0</v>
+      </c>
+      <c r="BC93" s="45">
+        <f t="shared" si="64"/>
+        <v>0</v>
+      </c>
+      <c r="BD93" s="45"/>
+      <c r="BE93" s="45">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="BF93" s="39" t="e">
+        <f t="shared" si="66"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="94" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A94" s="21" t="str">
+        <f>IF(ISBLANK(F94),"",COUNTA($F$6:F94))</f>
+        <v/>
+      </c>
+      <c r="B94" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="C94" s="37" t="s">
+        <v>61</v>
+      </c>
+      <c r="D94" s="22"/>
+      <c r="E94" s="23"/>
+      <c r="F94" s="36"/>
+      <c r="G94" s="24"/>
+      <c r="H94" s="24"/>
+      <c r="I94" s="24"/>
+      <c r="J94" s="24"/>
+      <c r="K94" s="25"/>
+      <c r="L94" s="26"/>
+      <c r="M94" s="38"/>
+      <c r="N94" s="52"/>
+      <c r="O94" s="27"/>
+      <c r="P94" s="27"/>
+      <c r="Q94" s="27"/>
+      <c r="R94" s="28"/>
+      <c r="S94" s="28"/>
+      <c r="T94" s="46">
+        <f t="shared" si="59"/>
+        <v>0</v>
+      </c>
+      <c r="U94" s="28"/>
+      <c r="V94" s="28"/>
+      <c r="W94" s="28"/>
+      <c r="X94" s="28"/>
+      <c r="Y94" s="28"/>
+      <c r="Z94" s="28">
+        <f>+T94-X94</f>
+        <v>0</v>
+      </c>
+      <c r="AA94" s="29" t="e">
+        <f>Z94/T94</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB94" s="40"/>
+      <c r="AC94" s="40"/>
+      <c r="AD94" s="40"/>
+      <c r="AE94" s="29"/>
+      <c r="AF94" s="30"/>
+      <c r="AG94" s="30"/>
+      <c r="AH94" s="31"/>
+      <c r="AI94" s="31">
+        <f t="shared" si="60"/>
+        <v>0</v>
+      </c>
+      <c r="AJ94" s="32"/>
+      <c r="AK94" s="32"/>
+      <c r="AL94" s="32"/>
+      <c r="AM94" s="33"/>
+      <c r="AN94" s="33"/>
+      <c r="AO94" s="33"/>
+      <c r="AP94" s="34">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+      <c r="AQ94" s="32">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="AR94" s="32">
+        <f t="shared" si="63"/>
+        <v>0</v>
+      </c>
+      <c r="AS94" s="32"/>
+      <c r="AT94" s="32"/>
+      <c r="AU94" s="32"/>
+      <c r="AV94" s="32"/>
+      <c r="AW94" s="32"/>
+      <c r="AX94" s="32"/>
+      <c r="AY94" s="32"/>
+      <c r="AZ94" s="35"/>
+      <c r="BB94" s="45">
+        <f>IF(AND(AB94="",AC94=""),T94,IF(AC94="",AB94,AC94))</f>
+        <v>0</v>
+      </c>
+      <c r="BC94" s="45">
+        <f t="shared" si="64"/>
+        <v>0</v>
+      </c>
+      <c r="BD94" s="45"/>
+      <c r="BE94" s="45">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="BF94" s="39" t="e">
+        <f t="shared" si="66"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="95" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A95" s="21" t="str">
+        <f>IF(ISBLANK(F95),"",COUNTA($F$6:F95))</f>
+        <v/>
+      </c>
+      <c r="B95" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="C95" s="37" t="s">
+        <v>61</v>
+      </c>
+      <c r="D95" s="22"/>
+      <c r="E95" s="23"/>
+      <c r="F95" s="36"/>
+      <c r="G95" s="24"/>
+      <c r="H95" s="24"/>
+      <c r="I95" s="24"/>
+      <c r="J95" s="24"/>
+      <c r="K95" s="25"/>
+      <c r="L95" s="26"/>
+      <c r="M95" s="38"/>
+      <c r="N95" s="52"/>
+      <c r="O95" s="27"/>
+      <c r="P95" s="27"/>
+      <c r="Q95" s="27"/>
+      <c r="R95" s="28"/>
+      <c r="S95" s="28"/>
+      <c r="T95" s="46">
+        <f t="shared" si="59"/>
+        <v>0</v>
+      </c>
+      <c r="U95" s="28"/>
+      <c r="V95" s="28"/>
+      <c r="W95" s="28"/>
+      <c r="X95" s="28"/>
+      <c r="Y95" s="28"/>
+      <c r="Z95" s="28">
+        <f>+T95-X95</f>
+        <v>0</v>
+      </c>
+      <c r="AA95" s="29" t="e">
+        <f>Z95/T95</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB95" s="40"/>
+      <c r="AC95" s="40"/>
+      <c r="AD95" s="40"/>
+      <c r="AE95" s="29"/>
+      <c r="AF95" s="30"/>
+      <c r="AG95" s="30"/>
+      <c r="AH95" s="31"/>
+      <c r="AI95" s="31">
+        <f t="shared" si="60"/>
+        <v>0</v>
+      </c>
+      <c r="AJ95" s="32"/>
+      <c r="AK95" s="32"/>
+      <c r="AL95" s="32"/>
+      <c r="AM95" s="33"/>
+      <c r="AN95" s="33"/>
+      <c r="AO95" s="33"/>
+      <c r="AP95" s="34">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+      <c r="AQ95" s="32">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="AR95" s="32">
+        <f t="shared" si="63"/>
+        <v>0</v>
+      </c>
+      <c r="AS95" s="32"/>
+      <c r="AT95" s="32"/>
+      <c r="AU95" s="32"/>
+      <c r="AV95" s="32"/>
+      <c r="AW95" s="32"/>
+      <c r="AX95" s="32"/>
+      <c r="AY95" s="32"/>
+      <c r="AZ95" s="35"/>
+      <c r="BB95" s="45">
+        <f>IF(AND(AB95="",AC95=""),T95,IF(AC95="",AB95,AC95))</f>
+        <v>0</v>
+      </c>
+      <c r="BC95" s="45">
+        <f t="shared" si="64"/>
+        <v>0</v>
+      </c>
+      <c r="BD95" s="45"/>
+      <c r="BE95" s="45">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="BF95" s="39" t="e">
+        <f t="shared" si="66"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="96" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A96" s="21" t="str">
+        <f>IF(ISBLANK(F96),"",COUNTA($F$6:F96))</f>
+        <v/>
+      </c>
+      <c r="B96" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="C96" s="37" t="s">
+        <v>61</v>
+      </c>
+      <c r="D96" s="22"/>
+      <c r="E96" s="23"/>
+      <c r="F96" s="36"/>
+      <c r="G96" s="24"/>
+      <c r="H96" s="24"/>
+      <c r="I96" s="24"/>
+      <c r="J96" s="24"/>
+      <c r="K96" s="25"/>
+      <c r="L96" s="26"/>
+      <c r="M96" s="38"/>
+      <c r="N96" s="52"/>
+      <c r="O96" s="27"/>
+      <c r="P96" s="27"/>
+      <c r="Q96" s="27"/>
+      <c r="R96" s="28"/>
+      <c r="S96" s="28"/>
+      <c r="T96" s="46">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U96" s="28"/>
+      <c r="V96" s="28"/>
+      <c r="W96" s="28"/>
+      <c r="X96" s="28"/>
+      <c r="Y96" s="28"/>
+      <c r="Z96" s="28">
+        <f>+T96-X96</f>
+        <v>0</v>
+      </c>
+      <c r="AA96" s="29" t="e">
+        <f>Z96/T96</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB96" s="40"/>
+      <c r="AC96" s="40"/>
+      <c r="AD96" s="40"/>
+      <c r="AE96" s="29"/>
+      <c r="AF96" s="30"/>
+      <c r="AG96" s="30"/>
+      <c r="AH96" s="31"/>
+      <c r="AI96" s="31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="32"/>
+      <c r="AK96" s="32"/>
+      <c r="AL96" s="32"/>
+      <c r="AM96" s="33"/>
+      <c r="AN96" s="33"/>
+      <c r="AO96" s="33"/>
+      <c r="AP96" s="34">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AQ96" s="32">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AR96" s="32">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AS96" s="32"/>
+      <c r="AT96" s="32"/>
+      <c r="AU96" s="32"/>
+      <c r="AV96" s="32"/>
+      <c r="AW96" s="32"/>
+      <c r="AX96" s="32"/>
+      <c r="AY96" s="32"/>
+      <c r="AZ96" s="35"/>
+      <c r="BB96" s="45">
+        <f>IF(AND(AB96="",AC96=""),T96,IF(AC96="",AB96,AC96))</f>
+        <v>0</v>
+      </c>
+      <c r="BC96" s="45">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="BD96" s="45"/>
+      <c r="BE96" s="45">
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
+      <c r="BF96" s="39" t="e">
+        <f t="shared" si="58"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="97" spans="1:58" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="9">
+        <f>+COUNT(A6:A96)</f>
+        <v>88</v>
+      </c>
+      <c r="B97" s="10">
+        <f>+COUNTIF(X6:X96,"&gt;0")</f>
+        <v>82</v>
+      </c>
+      <c r="C97" s="10"/>
+      <c r="D97" s="10"/>
+      <c r="E97" s="10"/>
+      <c r="F97" s="10"/>
+      <c r="G97" s="10"/>
+      <c r="H97" s="10"/>
+      <c r="I97" s="10"/>
+      <c r="J97" s="10"/>
+      <c r="K97" s="10"/>
+      <c r="L97" s="11"/>
+      <c r="M97" s="10"/>
+      <c r="N97" s="10"/>
+      <c r="O97" s="10"/>
+      <c r="P97" s="10"/>
+      <c r="Q97" s="10"/>
+      <c r="R97" s="12">
+        <f t="shared" ref="R97:Y97" si="67">SUM(R6:R96)</f>
+        <v>411199.76999999996</v>
+      </c>
+      <c r="S97" s="12">
+        <f t="shared" si="67"/>
+        <v>95997.169999999984</v>
+      </c>
+      <c r="T97" s="12">
+        <f t="shared" si="67"/>
+        <v>315202.59999999998</v>
+      </c>
+      <c r="U97" s="12">
+        <f t="shared" si="67"/>
+        <v>316848.10000000003</v>
+      </c>
+      <c r="V97" s="12">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="W97" s="12">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="X97" s="12">
+        <f t="shared" si="67"/>
+        <v>313263.89999999997</v>
+      </c>
+      <c r="Y97" s="12">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="Z97" s="12">
+        <f>T97-X97</f>
+        <v>1938.7000000000116</v>
+      </c>
+      <c r="AA97" s="13">
+        <f>Z97/T97</f>
+        <v>6.1506472345088901E-3</v>
+      </c>
+      <c r="AB97" s="41"/>
+      <c r="AC97" s="41"/>
+      <c r="AD97" s="41"/>
+      <c r="AE97" s="13"/>
+      <c r="AF97" s="12">
+        <f>SUM(AF6:AF96)</f>
+        <v>0</v>
+      </c>
+      <c r="AG97" s="12">
+        <f>SUM(AG6:AG96)</f>
+        <v>0</v>
+      </c>
+      <c r="AH97" s="12">
+        <f>SUM(AH6:AH96)</f>
+        <v>0</v>
+      </c>
+      <c r="AI97" s="12">
+        <f>SUM(AI6:AI96)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ97" s="14"/>
+      <c r="AK97" s="14"/>
+      <c r="AL97" s="12"/>
+      <c r="AM97" s="15"/>
+      <c r="AN97" s="16"/>
+      <c r="AO97" s="16"/>
+      <c r="AP97" s="17"/>
+      <c r="AQ97" s="10">
+        <f>SUM(AQ6:AQ96)</f>
+        <v>0</v>
+      </c>
+      <c r="AR97" s="18">
+        <f>SUM(AR6:AR96)</f>
+        <v>0</v>
+      </c>
+      <c r="AS97" s="10">
+        <f>SUM(AS6:AS96)</f>
+        <v>0</v>
+      </c>
+      <c r="AT97" s="10">
+        <f>SUM(AT6:AT96)</f>
+        <v>0</v>
+      </c>
+      <c r="AU97" s="10">
+        <f>SUM(AU6:AU96)</f>
+        <v>0</v>
+      </c>
+      <c r="AV97" s="10">
+        <f>+SUM(AV6:AV96)</f>
+        <v>0</v>
+      </c>
+      <c r="AW97" s="10">
+        <f>SUM(AW6:AW96)</f>
+        <v>0</v>
+      </c>
+      <c r="AX97" s="10">
+        <f>SUM(AX6:AX96)</f>
+        <v>0</v>
+      </c>
+      <c r="AY97" s="10">
+        <f>SUM(AY6:AY96)</f>
+        <v>0</v>
+      </c>
+      <c r="AZ97" s="19"/>
+      <c r="BB97" s="42">
+        <f>SUM(BB6:BB96)</f>
+        <v>316704.51999999996</v>
+      </c>
+      <c r="BC97" s="42">
+        <f>SUM(BC6:BC96)</f>
+        <v>313263.89999999997</v>
+      </c>
+      <c r="BD97" s="42">
+        <f>SUM(BD6:BD96)</f>
+        <v>0</v>
+      </c>
+      <c r="BE97" s="42">
+        <f>SUM(BE6:BE96)</f>
+        <v>3440.6199999999972</v>
+      </c>
+      <c r="BF97" s="43">
+        <f t="shared" si="58"/>
+        <v>1.0863817163076793E-2</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="K6:K12">
-    <cfRule type="duplicateValues" dxfId="53" priority="1011"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="1031"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K6:K12">
-    <cfRule type="duplicateValues" dxfId="52" priority="1012"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="1013"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="1032"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="1033"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K89">
-    <cfRule type="duplicateValues" dxfId="50" priority="1014"/>
+  <conditionalFormatting sqref="K96">
+    <cfRule type="duplicateValues" dxfId="67" priority="1034"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K89">
-    <cfRule type="duplicateValues" dxfId="49" priority="1015"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="1016"/>
+  <conditionalFormatting sqref="K96">
+    <cfRule type="duplicateValues" dxfId="66" priority="1035"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="1036"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K89 K5">
-    <cfRule type="duplicateValues" dxfId="47" priority="1017"/>
+  <conditionalFormatting sqref="K96 K5">
+    <cfRule type="duplicateValues" dxfId="64" priority="1037"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K89:K90 K5">
-    <cfRule type="duplicateValues" dxfId="46" priority="1019"/>
+  <conditionalFormatting sqref="K96:K97 K5">
+    <cfRule type="duplicateValues" dxfId="63" priority="1039"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K89:K90">
-    <cfRule type="duplicateValues" dxfId="45" priority="1021"/>
+  <conditionalFormatting sqref="K96:K97">
+    <cfRule type="duplicateValues" dxfId="62" priority="1041"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13:K14 K88">
-    <cfRule type="duplicateValues" dxfId="44" priority="1022"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="1042"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13:K14 K88">
-    <cfRule type="duplicateValues" dxfId="43" priority="1024"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="1025"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="1044"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="1045"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K13:K14 K5 K88:K90">
-    <cfRule type="duplicateValues" dxfId="41" priority="1028"/>
+  <conditionalFormatting sqref="K13:K14 K5 K88 K96:K97">
+    <cfRule type="duplicateValues" dxfId="58" priority="1048"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K88:K90 K5:K14">
-    <cfRule type="duplicateValues" dxfId="40" priority="1031"/>
+  <conditionalFormatting sqref="K88 K5:K14 K96:K97">
+    <cfRule type="duplicateValues" dxfId="57" priority="1051"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K36 K15:K26">
-    <cfRule type="duplicateValues" dxfId="39" priority="1033"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="1053"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K36 K15:K26">
-    <cfRule type="duplicateValues" dxfId="38" priority="1035"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="1036"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="1055"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="1056"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K15:K26">
-    <cfRule type="duplicateValues" dxfId="36" priority="1039"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="1059"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27:K35">
-    <cfRule type="duplicateValues" dxfId="35" priority="1040"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="1060"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27:K35">
-    <cfRule type="duplicateValues" dxfId="34" priority="1041"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="1042"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="1061"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="1062"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K5:K36 K88:K90">
-    <cfRule type="duplicateValues" dxfId="32" priority="1043"/>
+  <conditionalFormatting sqref="K5:K36 K88 K96:K97">
+    <cfRule type="duplicateValues" dxfId="49" priority="1063"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K37:K54 K61:K64">
-    <cfRule type="duplicateValues" dxfId="31" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K37:K54 K61:K64">
-    <cfRule type="duplicateValues" dxfId="30" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K37:K54">
-    <cfRule type="duplicateValues" dxfId="28" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K37:K54">
-    <cfRule type="duplicateValues" dxfId="27" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K37:K54">
-    <cfRule type="duplicateValues" dxfId="26" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="58"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6:K54 K61:K64 K88:K90">
-    <cfRule type="duplicateValues" dxfId="25" priority="29"/>
+  <conditionalFormatting sqref="K6:K54 K61:K64 K88 K96:K97">
+    <cfRule type="duplicateValues" dxfId="42" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K55:K60">
-    <cfRule type="duplicateValues" dxfId="24" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K55:K60">
-    <cfRule type="duplicateValues" dxfId="23" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K55:K60">
-    <cfRule type="duplicateValues" dxfId="21" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K55:K60">
-    <cfRule type="duplicateValues" dxfId="20" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K55:K60">
-    <cfRule type="duplicateValues" dxfId="19" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K55:K60">
-    <cfRule type="duplicateValues" dxfId="18" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="39"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6:K64 K88:K90">
-    <cfRule type="duplicateValues" dxfId="17" priority="18"/>
+  <conditionalFormatting sqref="K6:K64 K88 K96:K97">
+    <cfRule type="duplicateValues" dxfId="34" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K65:K87">
-    <cfRule type="duplicateValues" dxfId="16" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K65:K87">
-    <cfRule type="duplicateValues" dxfId="15" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K65:K87">
-    <cfRule type="duplicateValues" dxfId="13" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K65:K87">
-    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K65:K87">
-    <cfRule type="duplicateValues" dxfId="11" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K65:K87">
+    <cfRule type="duplicateValues" dxfId="27" priority="28"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K65:K87">
+    <cfRule type="duplicateValues" dxfId="26" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K6:K88 K96:K97">
+    <cfRule type="duplicateValues" dxfId="25" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K5:K88 K96:K97">
+    <cfRule type="duplicateValues" dxfId="24" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K5:K88">
+    <cfRule type="duplicateValues" dxfId="20" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K89:K95">
+    <cfRule type="duplicateValues" dxfId="19" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K89:K95">
+    <cfRule type="duplicateValues" dxfId="18" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K89:K95">
+    <cfRule type="duplicateValues" dxfId="16" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K89:K95">
+    <cfRule type="duplicateValues" dxfId="15" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K89:K95">
+    <cfRule type="duplicateValues" dxfId="14" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K89:K95">
+    <cfRule type="duplicateValues" dxfId="13" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K89:K95">
+    <cfRule type="duplicateValues" dxfId="12" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K89:K95">
+    <cfRule type="duplicateValues" dxfId="11" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K89:K95">
     <cfRule type="duplicateValues" dxfId="10" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K65:K87">
+  <conditionalFormatting sqref="K89:K95">
     <cfRule type="duplicateValues" dxfId="9" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6:K90">
+  <conditionalFormatting sqref="K89:K95">
     <cfRule type="duplicateValues" dxfId="8" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K5:K90">
-    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
+  <conditionalFormatting sqref="K89:K95">
+    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
     <cfRule type="duplicateValues" dxfId="6" priority="3"/>
     <cfRule type="duplicateValues" dxfId="5" priority="4"/>
     <cfRule type="duplicateValues" dxfId="4" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K5:K88">
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+  <conditionalFormatting sqref="K5:K97">
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BB6:BB89">
-    <cfRule type="expression" dxfId="2" priority="1094">
+  <conditionalFormatting sqref="BB6:BB96">
+    <cfRule type="expression" dxfId="2" priority="1120">
       <formula>$AC6&lt;&gt;""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="1095">
+    <cfRule type="expression" dxfId="1" priority="1121">
       <formula>$AB6&lt;&gt;""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="1096">
+    <cfRule type="expression" dxfId="0" priority="1122">
       <formula>$T6&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Shortage.xlsx
+++ b/Shortage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\MR1\PPGS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23E5A793-A92E-490A-81BA-E02D4C3B55E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{793559C1-1146-4580-A59E-409CECD92D55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Aug-26" sheetId="5" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Aug-26'!$A$5:$BF$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Aug-26'!$A$5:$BH$107</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jul-26'!$A$5:$BG$127</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1223" uniqueCount="75">
   <si>
     <t>sl.no.</t>
   </si>
@@ -755,7 +755,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="196">
+  <dxfs count="141">
     <dxf>
       <fill>
         <patternFill>
@@ -774,6 +774,186 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1968,718 +2148,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -19148,134 +18616,134 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="K126">
-    <cfRule type="duplicateValues" dxfId="122" priority="748"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="748"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K6 K24">
-    <cfRule type="duplicateValues" dxfId="121" priority="749"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="749"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7:K23">
-    <cfRule type="duplicateValues" dxfId="120" priority="751"/>
+    <cfRule type="duplicateValues" dxfId="138" priority="751"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K126 K6:K24">
-    <cfRule type="duplicateValues" dxfId="119" priority="752"/>
-    <cfRule type="duplicateValues" dxfId="118" priority="753"/>
+    <cfRule type="duplicateValues" dxfId="137" priority="752"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="753"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25:K31 K54:K57">
-    <cfRule type="duplicateValues" dxfId="117" priority="756"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="756"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25:K31 K54:K57">
-    <cfRule type="duplicateValues" dxfId="116" priority="758"/>
-    <cfRule type="duplicateValues" dxfId="115" priority="759"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="758"/>
+    <cfRule type="duplicateValues" dxfId="133" priority="759"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27:K53">
-    <cfRule type="duplicateValues" dxfId="114" priority="762"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="762"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27:K53">
-    <cfRule type="duplicateValues" dxfId="113" priority="763"/>
-    <cfRule type="duplicateValues" dxfId="112" priority="764"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="763"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="764"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K126 K6:K57">
-    <cfRule type="duplicateValues" dxfId="111" priority="765"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="765"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K58:K62 K72:K75">
-    <cfRule type="duplicateValues" dxfId="110" priority="767"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="767"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K58:K62 K72:K75">
-    <cfRule type="duplicateValues" dxfId="109" priority="769"/>
-    <cfRule type="duplicateValues" dxfId="108" priority="770"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="769"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="770"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K58:K62">
-    <cfRule type="duplicateValues" dxfId="107" priority="773"/>
+    <cfRule type="duplicateValues" dxfId="125" priority="773"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K126 K5:K62 K72:K75">
-    <cfRule type="duplicateValues" dxfId="106" priority="774"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="774"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K63:K71">
-    <cfRule type="duplicateValues" dxfId="105" priority="777"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="777"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K63:K71">
-    <cfRule type="duplicateValues" dxfId="104" priority="778"/>
-    <cfRule type="duplicateValues" dxfId="103" priority="779"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="778"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="779"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K126 K5:K75">
-    <cfRule type="duplicateValues" dxfId="102" priority="780"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="780"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K76:K79 K90:K92 K116">
-    <cfRule type="duplicateValues" dxfId="101" priority="782"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="782"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K76:K79 K90:K92 K116">
-    <cfRule type="duplicateValues" dxfId="100" priority="785"/>
-    <cfRule type="duplicateValues" dxfId="99" priority="786"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="785"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="786"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K76:K79">
-    <cfRule type="duplicateValues" dxfId="98" priority="791"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="791"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K80:K89">
-    <cfRule type="duplicateValues" dxfId="97" priority="792"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="792"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K80:K89">
-    <cfRule type="duplicateValues" dxfId="96" priority="793"/>
-    <cfRule type="duplicateValues" dxfId="95" priority="794"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="793"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="794"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K126:K127 K5:K92 K116">
-    <cfRule type="duplicateValues" dxfId="94" priority="795"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="795"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K99:K113 K115">
-    <cfRule type="duplicateValues" dxfId="93" priority="798"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="798"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K99:K113 K115">
-    <cfRule type="duplicateValues" dxfId="92" priority="800"/>
-    <cfRule type="duplicateValues" dxfId="91" priority="801"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="800"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="801"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K93:K98">
-    <cfRule type="duplicateValues" dxfId="90" priority="804"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="804"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K93:K98">
-    <cfRule type="duplicateValues" dxfId="89" priority="805"/>
-    <cfRule type="duplicateValues" dxfId="88" priority="806"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="805"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="806"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K126:K127 K5:K113 K115:K116">
-    <cfRule type="duplicateValues" dxfId="87" priority="807"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="807"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K114">
-    <cfRule type="duplicateValues" dxfId="86" priority="810"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="810"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K114">
-    <cfRule type="duplicateValues" dxfId="85" priority="811"/>
-    <cfRule type="duplicateValues" dxfId="84" priority="812"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="811"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="812"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K126:K127 K5:K116">
-    <cfRule type="duplicateValues" dxfId="83" priority="813"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="813"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K117:K123 K125">
-    <cfRule type="duplicateValues" dxfId="82" priority="844"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="844"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K117:K123 K125">
-    <cfRule type="duplicateValues" dxfId="81" priority="846"/>
-    <cfRule type="duplicateValues" dxfId="80" priority="847"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="846"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="847"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5:K123 K125:K127">
-    <cfRule type="duplicateValues" dxfId="79" priority="850"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="850"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K124">
-    <cfRule type="duplicateValues" dxfId="78" priority="852"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="852"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K124">
-    <cfRule type="duplicateValues" dxfId="77" priority="853"/>
-    <cfRule type="duplicateValues" dxfId="76" priority="854"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="853"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="854"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5:K127">
-    <cfRule type="duplicateValues" dxfId="75" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="74" priority="855"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="855"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB6:BB126">
-    <cfRule type="expression" dxfId="73" priority="1019">
+    <cfRule type="expression" dxfId="91" priority="1019">
       <formula>$AC6&lt;&gt;""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="72" priority="1020">
+    <cfRule type="expression" dxfId="90" priority="1020">
       <formula>$AB6&lt;&gt;""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="71" priority="1021">
+    <cfRule type="expression" dxfId="89" priority="1021">
       <formula>$T6&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19286,7 +18754,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{499C2CF5-E587-4B95-9659-4BA38F5371D8}">
-  <dimension ref="A1:BF97"/>
+  <dimension ref="A1:BF107"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.42578125" bestFit="1" customWidth="1"/>
@@ -19584,7 +19052,7 @@
         <v>1195.7700000000004</v>
       </c>
       <c r="T6" s="46">
-        <f t="shared" ref="T6:T96" si="0">+R6-S6</f>
+        <f t="shared" ref="T6:T106" si="0">+R6-S6</f>
         <v>3897.2</v>
       </c>
       <c r="U6" s="46">
@@ -19614,7 +19082,7 @@
       <c r="AG6" s="74"/>
       <c r="AH6" s="75"/>
       <c r="AI6" s="75">
-        <f t="shared" ref="AI6:AI96" si="1">+AG6+AH6</f>
+        <f t="shared" ref="AI6:AI106" si="1">+AG6+AH6</f>
         <v>0</v>
       </c>
       <c r="AJ6" s="32"/>
@@ -19624,15 +19092,15 @@
       <c r="AN6" s="33"/>
       <c r="AO6" s="33"/>
       <c r="AP6" s="34">
-        <f t="shared" ref="AP6:AP96" si="2">ROUNDUP((AO6-AM6+(AO6&lt;AM6))*24,0)</f>
+        <f t="shared" ref="AP6:AP106" si="2">ROUNDUP((AO6-AM6+(AO6&lt;AM6))*24,0)</f>
         <v>0</v>
       </c>
       <c r="AQ6" s="32">
-        <f t="shared" ref="AQ6:AQ96" si="3">IF(AP6&gt;5,(AP6-5),0)</f>
+        <f t="shared" ref="AQ6:AQ106" si="3">IF(AP6&gt;5,(AP6-5),0)</f>
         <v>0</v>
       </c>
       <c r="AR6" s="32">
-        <f t="shared" ref="AR6:AR96" si="4">+AQ6*8850</f>
+        <f t="shared" ref="AR6:AR106" si="4">+AQ6*8850</f>
         <v>0</v>
       </c>
       <c r="AS6" s="32"/>
@@ -19648,16 +19116,16 @@
         <v>3897.2</v>
       </c>
       <c r="BC6" s="45">
-        <f t="shared" ref="BC6:BC37" si="5">+X6</f>
+        <f>+X6</f>
         <v>3787</v>
       </c>
       <c r="BD6" s="45"/>
       <c r="BE6" s="45">
-        <f t="shared" ref="BE6:BE77" si="6">+BB6-BC6</f>
+        <f t="shared" ref="BE6:BE77" si="5">+BB6-BC6</f>
         <v>110.19999999999982</v>
       </c>
       <c r="BF6" s="39">
-        <f t="shared" ref="BF6:BF77" si="7">+BE6/BB6</f>
+        <f t="shared" ref="BF6:BF77" si="6">+BE6/BB6</f>
         <v>2.8276711485168794E-2</v>
       </c>
     </row>
@@ -19777,16 +19245,16 @@
         <v>3906.7</v>
       </c>
       <c r="BC7" s="45">
-        <f t="shared" si="5"/>
+        <f>+X7</f>
         <v>3844</v>
       </c>
       <c r="BD7" s="45"/>
       <c r="BE7" s="45">
+        <f t="shared" si="5"/>
+        <v>62.699999999999818</v>
+      </c>
+      <c r="BF7" s="39">
         <f t="shared" si="6"/>
-        <v>62.699999999999818</v>
-      </c>
-      <c r="BF7" s="39">
-        <f t="shared" si="7"/>
         <v>1.6049351114751535E-2</v>
       </c>
     </row>
@@ -19906,16 +19374,16 @@
         <v>3568.7</v>
       </c>
       <c r="BC8" s="45">
-        <f t="shared" si="5"/>
+        <f>+X8</f>
         <v>3476.8</v>
       </c>
       <c r="BD8" s="45"/>
       <c r="BE8" s="45">
+        <f t="shared" si="5"/>
+        <v>91.899999999999636</v>
+      </c>
+      <c r="BF8" s="39">
         <f t="shared" si="6"/>
-        <v>91.899999999999636</v>
-      </c>
-      <c r="BF8" s="39">
-        <f t="shared" si="7"/>
         <v>2.5751674279149168E-2</v>
       </c>
     </row>
@@ -20035,16 +19503,16 @@
         <v>4135.0600000000004</v>
       </c>
       <c r="BC9" s="45">
-        <f t="shared" si="5"/>
+        <f>+X9</f>
         <v>4148.2</v>
       </c>
       <c r="BD9" s="45"/>
       <c r="BE9" s="45">
+        <f t="shared" si="5"/>
+        <v>-13.139999999999418</v>
+      </c>
+      <c r="BF9" s="39">
         <f t="shared" si="6"/>
-        <v>-13.139999999999418</v>
-      </c>
-      <c r="BF9" s="39">
-        <f t="shared" si="7"/>
         <v>-3.177704797511866E-3</v>
       </c>
     </row>
@@ -20164,16 +19632,16 @@
         <v>3969.81</v>
       </c>
       <c r="BC10" s="45">
-        <f t="shared" si="5"/>
+        <f>+X10</f>
         <v>4026.2</v>
       </c>
       <c r="BD10" s="45"/>
       <c r="BE10" s="45">
+        <f t="shared" si="5"/>
+        <v>-56.389999999999873</v>
+      </c>
+      <c r="BF10" s="39">
         <f t="shared" si="6"/>
-        <v>-56.389999999999873</v>
-      </c>
-      <c r="BF10" s="39">
-        <f t="shared" si="7"/>
         <v>-1.4204710049095516E-2</v>
       </c>
     </row>
@@ -20293,16 +19761,16 @@
         <v>3830.4</v>
       </c>
       <c r="BC11" s="45">
-        <f t="shared" si="5"/>
+        <f>+X11</f>
         <v>3723.4</v>
       </c>
       <c r="BD11" s="45"/>
       <c r="BE11" s="45">
+        <f t="shared" si="5"/>
+        <v>107</v>
+      </c>
+      <c r="BF11" s="39">
         <f t="shared" si="6"/>
-        <v>107</v>
-      </c>
-      <c r="BF11" s="39">
-        <f t="shared" si="7"/>
         <v>2.7934419381787801E-2</v>
       </c>
     </row>
@@ -20422,16 +19890,16 @@
         <v>3426.75</v>
       </c>
       <c r="BC12" s="45">
-        <f t="shared" si="5"/>
+        <f>+X12</f>
         <v>3368.8</v>
       </c>
       <c r="BD12" s="45"/>
       <c r="BE12" s="45">
+        <f t="shared" si="5"/>
+        <v>57.949999999999818</v>
+      </c>
+      <c r="BF12" s="39">
         <f t="shared" si="6"/>
-        <v>57.949999999999818</v>
-      </c>
-      <c r="BF12" s="39">
-        <f t="shared" si="7"/>
         <v>1.6911067337856515E-2</v>
       </c>
     </row>
@@ -20551,16 +20019,16 @@
         <v>3937.35</v>
       </c>
       <c r="BC13" s="45">
-        <f t="shared" si="5"/>
+        <f>+X13</f>
         <v>3823.2</v>
       </c>
       <c r="BD13" s="45"/>
       <c r="BE13" s="45">
+        <f t="shared" si="5"/>
+        <v>114.15000000000009</v>
+      </c>
+      <c r="BF13" s="39">
         <f t="shared" si="6"/>
-        <v>114.15000000000009</v>
-      </c>
-      <c r="BF13" s="39">
-        <f t="shared" si="7"/>
         <v>2.8991580631643133E-2</v>
       </c>
     </row>
@@ -20680,16 +20148,16 @@
         <v>3761.06</v>
       </c>
       <c r="BC14" s="45">
-        <f t="shared" si="5"/>
+        <f>+X14</f>
         <v>3802.8</v>
       </c>
       <c r="BD14" s="45"/>
       <c r="BE14" s="45">
+        <f t="shared" si="5"/>
+        <v>-41.740000000000236</v>
+      </c>
+      <c r="BF14" s="39">
         <f t="shared" si="6"/>
-        <v>-41.740000000000236</v>
-      </c>
-      <c r="BF14" s="39">
-        <f t="shared" si="7"/>
         <v>-1.1097935156578262E-2</v>
       </c>
     </row>
@@ -20745,7 +20213,7 @@
         <v>1196.9900000000002</v>
       </c>
       <c r="T15" s="46">
-        <f t="shared" ref="T15:T86" si="8">+R15-S15</f>
+        <f t="shared" ref="T15:T86" si="7">+R15-S15</f>
         <v>3915.1</v>
       </c>
       <c r="U15" s="46">
@@ -20775,7 +20243,7 @@
       <c r="AG15" s="74"/>
       <c r="AH15" s="75"/>
       <c r="AI15" s="75">
-        <f t="shared" ref="AI15:AI86" si="9">+AG15+AH15</f>
+        <f t="shared" ref="AI15:AI86" si="8">+AG15+AH15</f>
         <v>0</v>
       </c>
       <c r="AJ15" s="32"/>
@@ -20785,15 +20253,15 @@
       <c r="AN15" s="33"/>
       <c r="AO15" s="33"/>
       <c r="AP15" s="34">
-        <f t="shared" ref="AP15:AP86" si="10">ROUNDUP((AO15-AM15+(AO15&lt;AM15))*24,0)</f>
+        <f t="shared" ref="AP15:AP86" si="9">ROUNDUP((AO15-AM15+(AO15&lt;AM15))*24,0)</f>
         <v>0</v>
       </c>
       <c r="AQ15" s="32">
-        <f t="shared" ref="AQ15:AQ86" si="11">IF(AP15&gt;5,(AP15-5),0)</f>
+        <f t="shared" ref="AQ15:AQ86" si="10">IF(AP15&gt;5,(AP15-5),0)</f>
         <v>0</v>
       </c>
       <c r="AR15" s="32">
-        <f t="shared" ref="AR15:AR86" si="12">+AQ15*8850</f>
+        <f t="shared" ref="AR15:AR86" si="11">+AQ15*8850</f>
         <v>0</v>
       </c>
       <c r="AS15" s="32"/>
@@ -20809,16 +20277,16 @@
         <v>3915.1</v>
       </c>
       <c r="BC15" s="45">
-        <f t="shared" si="5"/>
+        <f>+X15</f>
         <v>3799.8</v>
       </c>
       <c r="BD15" s="45"/>
       <c r="BE15" s="45">
+        <f t="shared" si="5"/>
+        <v>115.29999999999973</v>
+      </c>
+      <c r="BF15" s="39">
         <f t="shared" si="6"/>
-        <v>115.29999999999973</v>
-      </c>
-      <c r="BF15" s="39">
-        <f t="shared" si="7"/>
         <v>2.9450077903501758E-2</v>
       </c>
     </row>
@@ -20874,7 +20342,7 @@
         <v>1175.29</v>
       </c>
       <c r="T16" s="46">
-        <f t="shared" ref="T16:T17" si="13">+R16-S16</f>
+        <f t="shared" ref="T16:T17" si="12">+R16-S16</f>
         <v>3826.8</v>
       </c>
       <c r="U16" s="46">
@@ -20904,7 +20372,7 @@
       <c r="AG16" s="74"/>
       <c r="AH16" s="75"/>
       <c r="AI16" s="75">
-        <f t="shared" ref="AI16:AI17" si="14">+AG16+AH16</f>
+        <f t="shared" ref="AI16:AI17" si="13">+AG16+AH16</f>
         <v>0</v>
       </c>
       <c r="AJ16" s="32"/>
@@ -20914,15 +20382,15 @@
       <c r="AN16" s="33"/>
       <c r="AO16" s="33"/>
       <c r="AP16" s="34">
-        <f t="shared" ref="AP16:AP17" si="15">ROUNDUP((AO16-AM16+(AO16&lt;AM16))*24,0)</f>
+        <f t="shared" ref="AP16:AP17" si="14">ROUNDUP((AO16-AM16+(AO16&lt;AM16))*24,0)</f>
         <v>0</v>
       </c>
       <c r="AQ16" s="32">
-        <f t="shared" ref="AQ16:AQ17" si="16">IF(AP16&gt;5,(AP16-5),0)</f>
+        <f t="shared" ref="AQ16:AQ17" si="15">IF(AP16&gt;5,(AP16-5),0)</f>
         <v>0</v>
       </c>
       <c r="AR16" s="32">
-        <f t="shared" ref="AR16:AR17" si="17">+AQ16*8850</f>
+        <f t="shared" ref="AR16:AR17" si="16">+AQ16*8850</f>
         <v>0</v>
       </c>
       <c r="AS16" s="32"/>
@@ -20938,16 +20406,16 @@
         <v>3826.75</v>
       </c>
       <c r="BC16" s="45">
-        <f t="shared" si="5"/>
+        <f>+X16</f>
         <v>3709.2</v>
       </c>
       <c r="BD16" s="45"/>
       <c r="BE16" s="45">
-        <f t="shared" ref="BE16:BE17" si="18">+BB16-BC16</f>
+        <f t="shared" ref="BE16:BE17" si="17">+BB16-BC16</f>
         <v>117.55000000000018</v>
       </c>
       <c r="BF16" s="39">
-        <f t="shared" ref="BF16:BF17" si="19">+BE16/BB16</f>
+        <f t="shared" ref="BF16:BF17" si="18">+BE16/BB16</f>
         <v>3.0717972169595657E-2</v>
       </c>
     </row>
@@ -21003,7 +20471,7 @@
         <v>1149.48</v>
       </c>
       <c r="T17" s="46">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>3769.4</v>
       </c>
       <c r="U17" s="46">
@@ -21033,7 +20501,7 @@
       <c r="AG17" s="74"/>
       <c r="AH17" s="75"/>
       <c r="AI17" s="75">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AJ17" s="32"/>
@@ -21043,15 +20511,15 @@
       <c r="AN17" s="33"/>
       <c r="AO17" s="33"/>
       <c r="AP17" s="34">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ17" s="32">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AQ17" s="32">
+      <c r="AR17" s="32">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="AR17" s="32">
-        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AS17" s="32"/>
@@ -21067,16 +20535,16 @@
         <v>3769.4</v>
       </c>
       <c r="BC17" s="45">
-        <f t="shared" si="5"/>
+        <f>+X17</f>
         <v>3682.6</v>
       </c>
       <c r="BD17" s="45"/>
       <c r="BE17" s="45">
+        <f t="shared" si="17"/>
+        <v>86.800000000000182</v>
+      </c>
+      <c r="BF17" s="39">
         <f t="shared" si="18"/>
-        <v>86.800000000000182</v>
-      </c>
-      <c r="BF17" s="39">
-        <f t="shared" si="19"/>
         <v>2.3027537539130945E-2</v>
       </c>
     </row>
@@ -21132,7 +20600,7 @@
         <v>1150.6500000000005</v>
       </c>
       <c r="T18" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3799.7</v>
       </c>
       <c r="U18" s="46">
@@ -21162,7 +20630,7 @@
       <c r="AG18" s="74"/>
       <c r="AH18" s="75"/>
       <c r="AI18" s="75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AJ18" s="32"/>
@@ -21172,15 +20640,15 @@
       <c r="AN18" s="33"/>
       <c r="AO18" s="33"/>
       <c r="AP18" s="34">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ18" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AQ18" s="32">
+      <c r="AR18" s="32">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AR18" s="32">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS18" s="32"/>
@@ -21196,16 +20664,16 @@
         <v>3841.65</v>
       </c>
       <c r="BC18" s="45">
-        <f t="shared" si="5"/>
+        <f>+X18</f>
         <v>3936.8</v>
       </c>
       <c r="BD18" s="45"/>
       <c r="BE18" s="45">
+        <f t="shared" si="5"/>
+        <v>-95.150000000000091</v>
+      </c>
+      <c r="BF18" s="39">
         <f t="shared" si="6"/>
-        <v>-95.150000000000091</v>
-      </c>
-      <c r="BF18" s="39">
-        <f t="shared" si="7"/>
         <v>-2.476800333190168E-2</v>
       </c>
     </row>
@@ -21261,7 +20729,7 @@
         <v>1179.6700000000005</v>
       </c>
       <c r="T19" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3935.6</v>
       </c>
       <c r="U19" s="46">
@@ -21291,7 +20759,7 @@
       <c r="AG19" s="74"/>
       <c r="AH19" s="75"/>
       <c r="AI19" s="75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AJ19" s="32"/>
@@ -21301,15 +20769,15 @@
       <c r="AN19" s="33"/>
       <c r="AO19" s="33"/>
       <c r="AP19" s="34">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ19" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AQ19" s="32">
+      <c r="AR19" s="32">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AR19" s="32">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS19" s="32"/>
@@ -21325,16 +20793,16 @@
         <v>3935.6</v>
       </c>
       <c r="BC19" s="45">
-        <f t="shared" si="5"/>
+        <f>+X19</f>
         <v>3869.6</v>
       </c>
       <c r="BD19" s="45"/>
       <c r="BE19" s="45">
+        <f t="shared" si="5"/>
+        <v>66</v>
+      </c>
+      <c r="BF19" s="39">
         <f t="shared" si="6"/>
-        <v>66</v>
-      </c>
-      <c r="BF19" s="39">
-        <f t="shared" si="7"/>
         <v>1.6769996950909645E-2</v>
       </c>
     </row>
@@ -21390,7 +20858,7 @@
         <v>1187.3400000000001</v>
       </c>
       <c r="T20" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3919.2</v>
       </c>
       <c r="U20" s="46">
@@ -21420,7 +20888,7 @@
       <c r="AG20" s="74"/>
       <c r="AH20" s="75"/>
       <c r="AI20" s="75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AJ20" s="32"/>
@@ -21430,15 +20898,15 @@
       <c r="AN20" s="33"/>
       <c r="AO20" s="33"/>
       <c r="AP20" s="34">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ20" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AQ20" s="32">
+      <c r="AR20" s="32">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AR20" s="32">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS20" s="32"/>
@@ -21454,16 +20922,16 @@
         <v>3919.15</v>
       </c>
       <c r="BC20" s="45">
-        <f t="shared" si="5"/>
+        <f>+X20</f>
         <v>3997.8</v>
       </c>
       <c r="BD20" s="45"/>
       <c r="BE20" s="45">
+        <f t="shared" si="5"/>
+        <v>-78.650000000000091</v>
+      </c>
+      <c r="BF20" s="39">
         <f t="shared" si="6"/>
-        <v>-78.650000000000091</v>
-      </c>
-      <c r="BF20" s="39">
-        <f t="shared" si="7"/>
         <v>-2.0068127017337966E-2</v>
       </c>
     </row>
@@ -21519,7 +20987,7 @@
         <v>1162.4000000000005</v>
       </c>
       <c r="T21" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3754.2</v>
       </c>
       <c r="U21" s="46">
@@ -21549,7 +21017,7 @@
       <c r="AG21" s="74"/>
       <c r="AH21" s="75"/>
       <c r="AI21" s="75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AJ21" s="32"/>
@@ -21559,15 +21027,15 @@
       <c r="AN21" s="33"/>
       <c r="AO21" s="33"/>
       <c r="AP21" s="34">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ21" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AQ21" s="32">
+      <c r="AR21" s="32">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AR21" s="32">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS21" s="32"/>
@@ -21583,16 +21051,16 @@
         <v>3766.35</v>
       </c>
       <c r="BC21" s="45">
-        <f t="shared" si="5"/>
+        <f>+X21</f>
         <v>3729.4</v>
       </c>
       <c r="BD21" s="45"/>
       <c r="BE21" s="45">
+        <f t="shared" si="5"/>
+        <v>36.949999999999818</v>
+      </c>
+      <c r="BF21" s="39">
         <f t="shared" si="6"/>
-        <v>36.949999999999818</v>
-      </c>
-      <c r="BF21" s="39">
-        <f t="shared" si="7"/>
         <v>9.8105592948079228E-3</v>
       </c>
     </row>
@@ -21648,7 +21116,7 @@
         <v>1231.8599999999997</v>
       </c>
       <c r="T22" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>4049.8</v>
       </c>
       <c r="U22" s="46">
@@ -21678,7 +21146,7 @@
       <c r="AG22" s="74"/>
       <c r="AH22" s="75"/>
       <c r="AI22" s="75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AJ22" s="32"/>
@@ -21688,15 +21156,15 @@
       <c r="AN22" s="33"/>
       <c r="AO22" s="33"/>
       <c r="AP22" s="34">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ22" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AQ22" s="32">
+      <c r="AR22" s="32">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AR22" s="32">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS22" s="32"/>
@@ -21712,16 +21180,16 @@
         <v>4049.75</v>
       </c>
       <c r="BC22" s="45">
-        <f t="shared" si="5"/>
+        <f>+X22</f>
         <v>3931.6</v>
       </c>
       <c r="BD22" s="45"/>
       <c r="BE22" s="45">
+        <f t="shared" si="5"/>
+        <v>118.15000000000009</v>
+      </c>
+      <c r="BF22" s="39">
         <f t="shared" si="6"/>
-        <v>118.15000000000009</v>
-      </c>
-      <c r="BF22" s="39">
-        <f t="shared" si="7"/>
         <v>2.9174640409901868E-2</v>
       </c>
     </row>
@@ -21777,7 +21245,7 @@
         <v>1232.04</v>
       </c>
       <c r="T23" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>4044.5</v>
       </c>
       <c r="U23" s="46">
@@ -21807,7 +21275,7 @@
       <c r="AG23" s="74"/>
       <c r="AH23" s="75"/>
       <c r="AI23" s="75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AJ23" s="32"/>
@@ -21817,15 +21285,15 @@
       <c r="AN23" s="33"/>
       <c r="AO23" s="33"/>
       <c r="AP23" s="34">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ23" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AQ23" s="32">
+      <c r="AR23" s="32">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AR23" s="32">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS23" s="32"/>
@@ -21841,16 +21309,16 @@
         <v>4044.5</v>
       </c>
       <c r="BC23" s="45">
-        <f t="shared" si="5"/>
+        <f>+X23</f>
         <v>4171.8</v>
       </c>
       <c r="BD23" s="45"/>
       <c r="BE23" s="45">
+        <f t="shared" si="5"/>
+        <v>-127.30000000000018</v>
+      </c>
+      <c r="BF23" s="39">
         <f t="shared" si="6"/>
-        <v>-127.30000000000018</v>
-      </c>
-      <c r="BF23" s="39">
-        <f t="shared" si="7"/>
         <v>-3.14748423785388E-2</v>
       </c>
     </row>
@@ -21906,7 +21374,7 @@
         <v>1128.7800000000002</v>
       </c>
       <c r="T24" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3714.4</v>
       </c>
       <c r="U24" s="46">
@@ -21936,7 +21404,7 @@
       <c r="AG24" s="74"/>
       <c r="AH24" s="75"/>
       <c r="AI24" s="75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AJ24" s="32"/>
@@ -21946,15 +21414,15 @@
       <c r="AN24" s="33"/>
       <c r="AO24" s="33"/>
       <c r="AP24" s="34">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ24" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AQ24" s="32">
+      <c r="AR24" s="32">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AR24" s="32">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS24" s="32"/>
@@ -21970,16 +21438,16 @@
         <v>3714.4</v>
       </c>
       <c r="BC24" s="45">
-        <f t="shared" si="5"/>
+        <f>+X24</f>
         <v>3789.4</v>
       </c>
       <c r="BD24" s="45"/>
       <c r="BE24" s="45">
+        <f t="shared" si="5"/>
+        <v>-75</v>
+      </c>
+      <c r="BF24" s="39">
         <f t="shared" si="6"/>
-        <v>-75</v>
-      </c>
-      <c r="BF24" s="39">
-        <f t="shared" si="7"/>
         <v>-2.0191686409648933E-2</v>
       </c>
     </row>
@@ -22035,7 +21503,7 @@
         <v>1131.3999999999996</v>
       </c>
       <c r="T25" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3885</v>
       </c>
       <c r="U25" s="46">
@@ -22065,7 +21533,7 @@
       <c r="AG25" s="74"/>
       <c r="AH25" s="75"/>
       <c r="AI25" s="75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AJ25" s="32"/>
@@ -22075,15 +21543,15 @@
       <c r="AN25" s="33"/>
       <c r="AO25" s="33"/>
       <c r="AP25" s="34">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ25" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AQ25" s="32">
+      <c r="AR25" s="32">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AR25" s="32">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS25" s="32"/>
@@ -22099,16 +21567,16 @@
         <v>3905.1</v>
       </c>
       <c r="BC25" s="45">
-        <f t="shared" si="5"/>
+        <f>+X25</f>
         <v>3785.2</v>
       </c>
       <c r="BD25" s="45"/>
       <c r="BE25" s="45">
+        <f t="shared" si="5"/>
+        <v>119.90000000000009</v>
+      </c>
+      <c r="BF25" s="39">
         <f t="shared" si="6"/>
-        <v>119.90000000000009</v>
-      </c>
-      <c r="BF25" s="39">
-        <f t="shared" si="7"/>
         <v>3.0703439092468848E-2</v>
       </c>
     </row>
@@ -22164,7 +21632,7 @@
         <v>1135.2999999999997</v>
       </c>
       <c r="T26" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3684.6</v>
       </c>
       <c r="U26" s="46">
@@ -22194,7 +21662,7 @@
       <c r="AG26" s="74"/>
       <c r="AH26" s="75"/>
       <c r="AI26" s="75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AJ26" s="32"/>
@@ -22204,15 +21672,15 @@
       <c r="AN26" s="33"/>
       <c r="AO26" s="33"/>
       <c r="AP26" s="34">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ26" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AQ26" s="32">
+      <c r="AR26" s="32">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AR26" s="32">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS26" s="32"/>
@@ -22228,16 +21696,16 @@
         <v>3684.6</v>
       </c>
       <c r="BC26" s="45">
-        <f t="shared" si="5"/>
+        <f>+X26</f>
         <v>3665.8</v>
       </c>
       <c r="BD26" s="45"/>
       <c r="BE26" s="45">
+        <f t="shared" si="5"/>
+        <v>18.799999999999727</v>
+      </c>
+      <c r="BF26" s="39">
         <f t="shared" si="6"/>
-        <v>18.799999999999727</v>
-      </c>
-      <c r="BF26" s="39">
-        <f t="shared" si="7"/>
         <v>5.1023177549801135E-3</v>
       </c>
     </row>
@@ -22293,7 +21761,7 @@
         <v>1202.0099999999998</v>
       </c>
       <c r="T27" s="46">
-        <f t="shared" ref="T27:T35" si="20">+R27-S27</f>
+        <f t="shared" ref="T27:T35" si="19">+R27-S27</f>
         <v>3910.1</v>
       </c>
       <c r="U27" s="46">
@@ -22323,7 +21791,7 @@
       <c r="AG27" s="74"/>
       <c r="AH27" s="75"/>
       <c r="AI27" s="75">
-        <f t="shared" ref="AI27:AI35" si="21">+AG27+AH27</f>
+        <f t="shared" ref="AI27:AI35" si="20">+AG27+AH27</f>
         <v>0</v>
       </c>
       <c r="AJ27" s="32"/>
@@ -22333,15 +21801,15 @@
       <c r="AN27" s="33"/>
       <c r="AO27" s="33"/>
       <c r="AP27" s="34">
-        <f t="shared" ref="AP27:AP35" si="22">ROUNDUP((AO27-AM27+(AO27&lt;AM27))*24,0)</f>
+        <f t="shared" ref="AP27:AP35" si="21">ROUNDUP((AO27-AM27+(AO27&lt;AM27))*24,0)</f>
         <v>0</v>
       </c>
       <c r="AQ27" s="32">
-        <f t="shared" ref="AQ27:AQ35" si="23">IF(AP27&gt;5,(AP27-5),0)</f>
+        <f t="shared" ref="AQ27:AQ35" si="22">IF(AP27&gt;5,(AP27-5),0)</f>
         <v>0</v>
       </c>
       <c r="AR27" s="32">
-        <f t="shared" ref="AR27:AR35" si="24">+AQ27*8850</f>
+        <f t="shared" ref="AR27:AR35" si="23">+AQ27*8850</f>
         <v>0</v>
       </c>
       <c r="AS27" s="32"/>
@@ -22357,16 +21825,16 @@
         <v>3910.1</v>
       </c>
       <c r="BC27" s="45">
-        <f t="shared" si="5"/>
+        <f>+X27</f>
         <v>3988.4</v>
       </c>
       <c r="BD27" s="45"/>
       <c r="BE27" s="45">
-        <f t="shared" ref="BE27:BE35" si="25">+BB27-BC27</f>
+        <f t="shared" ref="BE27:BE35" si="24">+BB27-BC27</f>
         <v>-78.300000000000182</v>
       </c>
       <c r="BF27" s="39">
-        <f t="shared" ref="BF27:BF35" si="26">+BE27/BB27</f>
+        <f t="shared" ref="BF27:BF35" si="25">+BE27/BB27</f>
         <v>-2.0025063297613919E-2</v>
       </c>
     </row>
@@ -22422,7 +21890,7 @@
         <v>1238.7600000000002</v>
       </c>
       <c r="T28" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>4031</v>
       </c>
       <c r="U28" s="46">
@@ -22452,7 +21920,7 @@
       <c r="AG28" s="74"/>
       <c r="AH28" s="75"/>
       <c r="AI28" s="75">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AJ28" s="32"/>
@@ -22462,15 +21930,15 @@
       <c r="AN28" s="33"/>
       <c r="AO28" s="33"/>
       <c r="AP28" s="34">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AQ28" s="32">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AQ28" s="32">
+      <c r="AR28" s="32">
         <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AR28" s="32">
-        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AS28" s="32"/>
@@ -22486,16 +21954,16 @@
         <v>4030.95</v>
       </c>
       <c r="BC28" s="45">
-        <f t="shared" si="5"/>
+        <f>+X28</f>
         <v>3923.8</v>
       </c>
       <c r="BD28" s="45"/>
       <c r="BE28" s="45">
+        <f t="shared" si="24"/>
+        <v>107.14999999999964</v>
+      </c>
+      <c r="BF28" s="39">
         <f t="shared" si="25"/>
-        <v>107.14999999999964</v>
-      </c>
-      <c r="BF28" s="39">
-        <f t="shared" si="26"/>
         <v>2.6581823143427639E-2</v>
       </c>
     </row>
@@ -22551,7 +22019,7 @@
         <v>1043.8000000000002</v>
       </c>
       <c r="T29" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>3429.5</v>
       </c>
       <c r="U29" s="46">
@@ -22581,7 +22049,7 @@
       <c r="AG29" s="74"/>
       <c r="AH29" s="75"/>
       <c r="AI29" s="75">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AJ29" s="32"/>
@@ -22591,15 +22059,15 @@
       <c r="AN29" s="33"/>
       <c r="AO29" s="33"/>
       <c r="AP29" s="34">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AQ29" s="32">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AQ29" s="32">
+      <c r="AR29" s="32">
         <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AR29" s="32">
-        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AS29" s="32"/>
@@ -22615,16 +22083,16 @@
         <v>3429.45</v>
       </c>
       <c r="BC29" s="45">
-        <f t="shared" si="5"/>
+        <f>+X29</f>
         <v>3362</v>
       </c>
       <c r="BD29" s="45"/>
       <c r="BE29" s="45">
+        <f t="shared" si="24"/>
+        <v>67.449999999999818</v>
+      </c>
+      <c r="BF29" s="39">
         <f t="shared" si="25"/>
-        <v>67.449999999999818</v>
-      </c>
-      <c r="BF29" s="39">
-        <f t="shared" si="26"/>
         <v>1.966787677324347E-2</v>
       </c>
     </row>
@@ -22680,7 +22148,7 @@
         <v>1222.7600000000002</v>
       </c>
       <c r="T30" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>4078</v>
       </c>
       <c r="U30" s="46">
@@ -22710,7 +22178,7 @@
       <c r="AG30" s="74"/>
       <c r="AH30" s="75"/>
       <c r="AI30" s="75">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AJ30" s="32"/>
@@ -22720,15 +22188,15 @@
       <c r="AN30" s="33"/>
       <c r="AO30" s="33"/>
       <c r="AP30" s="34">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AQ30" s="32">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AQ30" s="32">
+      <c r="AR30" s="32">
         <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AR30" s="32">
-        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AS30" s="32"/>
@@ -22744,16 +22212,16 @@
         <v>4077.95</v>
       </c>
       <c r="BC30" s="45">
-        <f t="shared" si="5"/>
+        <f>+X30</f>
         <v>4099.8</v>
       </c>
       <c r="BD30" s="45"/>
       <c r="BE30" s="45">
+        <f t="shared" si="24"/>
+        <v>-21.850000000000364</v>
+      </c>
+      <c r="BF30" s="39">
         <f t="shared" si="25"/>
-        <v>-21.850000000000364</v>
-      </c>
-      <c r="BF30" s="39">
-        <f t="shared" si="26"/>
         <v>-5.3580843315882646E-3</v>
       </c>
     </row>
@@ -22809,7 +22277,7 @@
         <v>1187.5900000000001</v>
       </c>
       <c r="T31" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>3907.2</v>
       </c>
       <c r="U31" s="46">
@@ -22839,7 +22307,7 @@
       <c r="AG31" s="74"/>
       <c r="AH31" s="75"/>
       <c r="AI31" s="75">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AJ31" s="32"/>
@@ -22849,15 +22317,15 @@
       <c r="AN31" s="33"/>
       <c r="AO31" s="33"/>
       <c r="AP31" s="34">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AQ31" s="32">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AQ31" s="32">
+      <c r="AR31" s="32">
         <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AR31" s="32">
-        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AS31" s="32"/>
@@ -22873,16 +22341,16 @@
         <v>3907.2</v>
       </c>
       <c r="BC31" s="45">
-        <f t="shared" si="5"/>
+        <f>+X31</f>
         <v>3884.2</v>
       </c>
       <c r="BD31" s="45"/>
       <c r="BE31" s="45">
+        <f t="shared" si="24"/>
+        <v>23</v>
+      </c>
+      <c r="BF31" s="39">
         <f t="shared" si="25"/>
-        <v>23</v>
-      </c>
-      <c r="BF31" s="39">
-        <f t="shared" si="26"/>
         <v>5.8865683865683867E-3</v>
       </c>
     </row>
@@ -22938,7 +22406,7 @@
         <v>1215.58</v>
       </c>
       <c r="T32" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>3982.3</v>
       </c>
       <c r="U32" s="46">
@@ -22968,7 +22436,7 @@
       <c r="AG32" s="74"/>
       <c r="AH32" s="75"/>
       <c r="AI32" s="75">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AJ32" s="32"/>
@@ -22978,15 +22446,15 @@
       <c r="AN32" s="33"/>
       <c r="AO32" s="33"/>
       <c r="AP32" s="34">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AQ32" s="32">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AQ32" s="32">
+      <c r="AR32" s="32">
         <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AR32" s="32">
-        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AS32" s="32"/>
@@ -23002,16 +22470,16 @@
         <v>3982.3</v>
       </c>
       <c r="BC32" s="45">
-        <f t="shared" si="5"/>
+        <f>+X32</f>
         <v>3944.4</v>
       </c>
       <c r="BD32" s="45"/>
       <c r="BE32" s="45">
+        <f t="shared" si="24"/>
+        <v>37.900000000000091</v>
+      </c>
+      <c r="BF32" s="39">
         <f t="shared" si="25"/>
-        <v>37.900000000000091</v>
-      </c>
-      <c r="BF32" s="39">
-        <f t="shared" si="26"/>
         <v>9.5171132260251836E-3</v>
       </c>
     </row>
@@ -23067,7 +22535,7 @@
         <v>1208.6799999999998</v>
       </c>
       <c r="T33" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>3995.9</v>
       </c>
       <c r="U33" s="46">
@@ -23097,7 +22565,7 @@
       <c r="AG33" s="74"/>
       <c r="AH33" s="75"/>
       <c r="AI33" s="75">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AJ33" s="32"/>
@@ -23107,15 +22575,15 @@
       <c r="AN33" s="33"/>
       <c r="AO33" s="33"/>
       <c r="AP33" s="34">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AQ33" s="32">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AQ33" s="32">
+      <c r="AR33" s="32">
         <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AR33" s="32">
-        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AS33" s="32"/>
@@ -23131,16 +22599,16 @@
         <v>4188.25</v>
       </c>
       <c r="BC33" s="45">
-        <f t="shared" si="5"/>
+        <f>+X33</f>
         <v>4022.2</v>
       </c>
       <c r="BD33" s="45"/>
       <c r="BE33" s="45">
+        <f t="shared" si="24"/>
+        <v>166.05000000000018</v>
+      </c>
+      <c r="BF33" s="39">
         <f t="shared" si="25"/>
-        <v>166.05000000000018</v>
-      </c>
-      <c r="BF33" s="39">
-        <f t="shared" si="26"/>
         <v>3.9646630454247045E-2</v>
       </c>
     </row>
@@ -23196,7 +22664,7 @@
         <v>1092.1600000000003</v>
       </c>
       <c r="T34" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>3551.4</v>
       </c>
       <c r="U34" s="46">
@@ -23226,7 +22694,7 @@
       <c r="AG34" s="74"/>
       <c r="AH34" s="75"/>
       <c r="AI34" s="75">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AJ34" s="32"/>
@@ -23236,15 +22704,15 @@
       <c r="AN34" s="33"/>
       <c r="AO34" s="33"/>
       <c r="AP34" s="34">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AQ34" s="32">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AQ34" s="32">
+      <c r="AR34" s="32">
         <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AR34" s="32">
-        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AS34" s="32"/>
@@ -23260,16 +22728,16 @@
         <v>3551.35</v>
       </c>
       <c r="BC34" s="45">
-        <f t="shared" si="5"/>
+        <f>+X34</f>
         <v>3585.4</v>
       </c>
       <c r="BD34" s="45"/>
       <c r="BE34" s="45">
+        <f t="shared" si="24"/>
+        <v>-34.050000000000182</v>
+      </c>
+      <c r="BF34" s="39">
         <f t="shared" si="25"/>
-        <v>-34.050000000000182</v>
-      </c>
-      <c r="BF34" s="39">
-        <f t="shared" si="26"/>
         <v>-9.5879031917440356E-3</v>
       </c>
     </row>
@@ -23325,7 +22793,7 @@
         <v>1162.42</v>
       </c>
       <c r="T35" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>3855.5</v>
       </c>
       <c r="U35" s="46">
@@ -23355,7 +22823,7 @@
       <c r="AG35" s="74"/>
       <c r="AH35" s="75"/>
       <c r="AI35" s="75">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AJ35" s="32"/>
@@ -23365,15 +22833,15 @@
       <c r="AN35" s="33"/>
       <c r="AO35" s="33"/>
       <c r="AP35" s="34">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AQ35" s="32">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AQ35" s="32">
+      <c r="AR35" s="32">
         <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AR35" s="32">
-        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AS35" s="32"/>
@@ -23389,16 +22857,16 @@
         <v>3855.45</v>
       </c>
       <c r="BC35" s="45">
-        <f t="shared" si="5"/>
+        <f>+X35</f>
         <v>3969</v>
       </c>
       <c r="BD35" s="45"/>
       <c r="BE35" s="45">
+        <f t="shared" si="24"/>
+        <v>-113.55000000000018</v>
+      </c>
+      <c r="BF35" s="39">
         <f t="shared" si="25"/>
-        <v>-113.55000000000018</v>
-      </c>
-      <c r="BF35" s="39">
-        <f t="shared" si="26"/>
         <v>-2.9451814963233913E-2</v>
       </c>
     </row>
@@ -23454,7 +22922,7 @@
         <v>1202.5800000000004</v>
       </c>
       <c r="T36" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3903.1</v>
       </c>
       <c r="U36" s="46">
@@ -23484,7 +22952,7 @@
       <c r="AG36" s="74"/>
       <c r="AH36" s="75"/>
       <c r="AI36" s="75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AJ36" s="32"/>
@@ -23494,15 +22962,15 @@
       <c r="AN36" s="33"/>
       <c r="AO36" s="33"/>
       <c r="AP36" s="34">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ36" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AQ36" s="32">
+      <c r="AR36" s="32">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AR36" s="32">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS36" s="32"/>
@@ -23518,16 +22986,16 @@
         <v>3903.05</v>
       </c>
       <c r="BC36" s="45">
-        <f t="shared" si="5"/>
+        <f>+X36</f>
         <v>3800.4</v>
       </c>
       <c r="BD36" s="45"/>
       <c r="BE36" s="45">
+        <f t="shared" si="5"/>
+        <v>102.65000000000009</v>
+      </c>
+      <c r="BF36" s="39">
         <f t="shared" si="6"/>
-        <v>102.65000000000009</v>
-      </c>
-      <c r="BF36" s="39">
-        <f t="shared" si="7"/>
         <v>2.6299944914874286E-2</v>
       </c>
     </row>
@@ -23583,7 +23051,7 @@
         <v>1169.4599999999996</v>
       </c>
       <c r="T37" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3841.9</v>
       </c>
       <c r="U37" s="46">
@@ -23613,7 +23081,7 @@
       <c r="AG37" s="74"/>
       <c r="AH37" s="75"/>
       <c r="AI37" s="75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AJ37" s="32"/>
@@ -23623,15 +23091,15 @@
       <c r="AN37" s="33"/>
       <c r="AO37" s="33"/>
       <c r="AP37" s="34">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ37" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AQ37" s="32">
+      <c r="AR37" s="32">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AR37" s="32">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS37" s="32"/>
@@ -23647,16 +23115,16 @@
         <v>3841.85</v>
       </c>
       <c r="BC37" s="45">
-        <f t="shared" si="5"/>
+        <f>+X37</f>
         <v>3788.6</v>
       </c>
       <c r="BD37" s="45"/>
       <c r="BE37" s="45">
+        <f t="shared" si="5"/>
+        <v>53.25</v>
+      </c>
+      <c r="BF37" s="39">
         <f t="shared" si="6"/>
-        <v>53.25</v>
-      </c>
-      <c r="BF37" s="39">
-        <f t="shared" si="7"/>
         <v>1.3860509910589951E-2</v>
       </c>
     </row>
@@ -23712,7 +23180,7 @@
         <v>1193.0200000000004</v>
       </c>
       <c r="T38" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3934</v>
       </c>
       <c r="U38" s="46">
@@ -23742,7 +23210,7 @@
       <c r="AG38" s="74"/>
       <c r="AH38" s="75"/>
       <c r="AI38" s="75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AJ38" s="32"/>
@@ -23752,15 +23220,15 @@
       <c r="AN38" s="33"/>
       <c r="AO38" s="33"/>
       <c r="AP38" s="34">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ38" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AQ38" s="32">
+      <c r="AR38" s="32">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AR38" s="32">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS38" s="32"/>
@@ -23776,16 +23244,16 @@
         <v>4057.01</v>
       </c>
       <c r="BC38" s="45">
-        <f t="shared" ref="BC38:BC69" si="27">+X38</f>
+        <f>+X38</f>
         <v>4142</v>
       </c>
       <c r="BD38" s="45"/>
       <c r="BE38" s="45">
+        <f t="shared" si="5"/>
+        <v>-84.989999999999782</v>
+      </c>
+      <c r="BF38" s="39">
         <f t="shared" si="6"/>
-        <v>-84.989999999999782</v>
-      </c>
-      <c r="BF38" s="39">
-        <f t="shared" si="7"/>
         <v>-2.0948925440164006E-2</v>
       </c>
     </row>
@@ -23841,7 +23309,7 @@
         <v>1210.5999999999995</v>
       </c>
       <c r="T39" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3973.8</v>
       </c>
       <c r="U39" s="46">
@@ -23871,7 +23339,7 @@
       <c r="AG39" s="74"/>
       <c r="AH39" s="75"/>
       <c r="AI39" s="75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AJ39" s="32"/>
@@ -23881,15 +23349,15 @@
       <c r="AN39" s="33"/>
       <c r="AO39" s="33"/>
       <c r="AP39" s="34">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ39" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AQ39" s="32">
+      <c r="AR39" s="32">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AR39" s="32">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS39" s="32"/>
@@ -23905,16 +23373,16 @@
         <v>3973.75</v>
       </c>
       <c r="BC39" s="45">
-        <f t="shared" si="27"/>
+        <f>+X39</f>
         <v>3862.8</v>
       </c>
       <c r="BD39" s="45"/>
       <c r="BE39" s="45">
+        <f t="shared" si="5"/>
+        <v>110.94999999999982</v>
+      </c>
+      <c r="BF39" s="39">
         <f t="shared" si="6"/>
-        <v>110.94999999999982</v>
-      </c>
-      <c r="BF39" s="39">
-        <f t="shared" si="7"/>
         <v>2.7920729789241854E-2</v>
       </c>
     </row>
@@ -23970,7 +23438,7 @@
         <v>1121.9000000000005</v>
       </c>
       <c r="T40" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3737.7</v>
       </c>
       <c r="U40" s="46">
@@ -24000,7 +23468,7 @@
       <c r="AG40" s="74"/>
       <c r="AH40" s="75"/>
       <c r="AI40" s="75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AJ40" s="32"/>
@@ -24010,15 +23478,15 @@
       <c r="AN40" s="33"/>
       <c r="AO40" s="33"/>
       <c r="AP40" s="34">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ40" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AQ40" s="32">
+      <c r="AR40" s="32">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AR40" s="32">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS40" s="32"/>
@@ -24034,16 +23502,16 @@
         <v>3765.15</v>
       </c>
       <c r="BC40" s="45">
-        <f t="shared" si="27"/>
+        <f>+X40</f>
         <v>3936</v>
       </c>
       <c r="BD40" s="45"/>
       <c r="BE40" s="45">
+        <f t="shared" si="5"/>
+        <v>-170.84999999999991</v>
+      </c>
+      <c r="BF40" s="39">
         <f t="shared" si="6"/>
-        <v>-170.84999999999991</v>
-      </c>
-      <c r="BF40" s="39">
-        <f t="shared" si="7"/>
         <v>-4.5376678219991209E-2</v>
       </c>
     </row>
@@ -24099,7 +23567,7 @@
         <v>1149.9299999999994</v>
       </c>
       <c r="T41" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3785.3</v>
       </c>
       <c r="U41" s="46">
@@ -24129,7 +23597,7 @@
       <c r="AG41" s="74"/>
       <c r="AH41" s="75"/>
       <c r="AI41" s="75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AJ41" s="32"/>
@@ -24139,15 +23607,15 @@
       <c r="AN41" s="33"/>
       <c r="AO41" s="33"/>
       <c r="AP41" s="34">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ41" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AQ41" s="32">
+      <c r="AR41" s="32">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AR41" s="32">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS41" s="32"/>
@@ -24163,16 +23631,16 @@
         <v>3785.25</v>
       </c>
       <c r="BC41" s="45">
-        <f t="shared" si="27"/>
+        <f>+X41</f>
         <v>3668.8</v>
       </c>
       <c r="BD41" s="45"/>
       <c r="BE41" s="45">
+        <f t="shared" si="5"/>
+        <v>116.44999999999982</v>
+      </c>
+      <c r="BF41" s="39">
         <f t="shared" si="6"/>
-        <v>116.44999999999982</v>
-      </c>
-      <c r="BF41" s="39">
-        <f t="shared" si="7"/>
         <v>3.0764150320322255E-2</v>
       </c>
     </row>
@@ -24228,7 +23696,7 @@
         <v>1131.5699999999997</v>
       </c>
       <c r="T42" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3692.5</v>
       </c>
       <c r="U42" s="46">
@@ -24258,7 +23726,7 @@
       <c r="AG42" s="74"/>
       <c r="AH42" s="75"/>
       <c r="AI42" s="75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AJ42" s="32"/>
@@ -24268,15 +23736,15 @@
       <c r="AN42" s="33"/>
       <c r="AO42" s="33"/>
       <c r="AP42" s="34">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ42" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AQ42" s="32">
+      <c r="AR42" s="32">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AR42" s="32">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS42" s="32"/>
@@ -24292,16 +23760,16 @@
         <v>3692.5</v>
       </c>
       <c r="BC42" s="45">
-        <f t="shared" si="27"/>
+        <f>+X42</f>
         <v>3548.4</v>
       </c>
       <c r="BD42" s="45"/>
       <c r="BE42" s="45">
+        <f t="shared" si="5"/>
+        <v>144.09999999999991</v>
+      </c>
+      <c r="BF42" s="39">
         <f t="shared" si="6"/>
-        <v>144.09999999999991</v>
-      </c>
-      <c r="BF42" s="39">
-        <f t="shared" si="7"/>
         <v>3.9025050778605255E-2</v>
       </c>
     </row>
@@ -24357,7 +23825,7 @@
         <v>1166.0999999999999</v>
       </c>
       <c r="T43" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3738.9</v>
       </c>
       <c r="U43" s="46">
@@ -24387,7 +23855,7 @@
       <c r="AG43" s="74"/>
       <c r="AH43" s="75"/>
       <c r="AI43" s="75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AJ43" s="32"/>
@@ -24397,15 +23865,15 @@
       <c r="AN43" s="33"/>
       <c r="AO43" s="33"/>
       <c r="AP43" s="34">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ43" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AQ43" s="32">
+      <c r="AR43" s="32">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AR43" s="32">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS43" s="32"/>
@@ -24421,16 +23889,16 @@
         <v>3770.26</v>
       </c>
       <c r="BC43" s="45">
-        <f t="shared" si="27"/>
+        <f>+X43</f>
         <v>3763</v>
       </c>
       <c r="BD43" s="45"/>
       <c r="BE43" s="45">
+        <f t="shared" si="5"/>
+        <v>7.2600000000002183</v>
+      </c>
+      <c r="BF43" s="39">
         <f t="shared" si="6"/>
-        <v>7.2600000000002183</v>
-      </c>
-      <c r="BF43" s="39">
-        <f t="shared" si="7"/>
         <v>1.9255966432023834E-3</v>
       </c>
     </row>
@@ -24486,7 +23954,7 @@
         <v>1204.9500000000003</v>
       </c>
       <c r="T44" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3874.6</v>
       </c>
       <c r="U44" s="46">
@@ -24516,7 +23984,7 @@
       <c r="AG44" s="74"/>
       <c r="AH44" s="75"/>
       <c r="AI44" s="75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AJ44" s="32"/>
@@ -24526,15 +23994,15 @@
       <c r="AN44" s="33"/>
       <c r="AO44" s="33"/>
       <c r="AP44" s="34">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ44" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AQ44" s="32">
+      <c r="AR44" s="32">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AR44" s="32">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS44" s="32"/>
@@ -24550,16 +24018,16 @@
         <v>3874.6</v>
       </c>
       <c r="BC44" s="45">
-        <f t="shared" si="27"/>
+        <f>+X44</f>
         <v>3772</v>
       </c>
       <c r="BD44" s="45"/>
       <c r="BE44" s="45">
+        <f t="shared" si="5"/>
+        <v>102.59999999999991</v>
+      </c>
+      <c r="BF44" s="39">
         <f t="shared" si="6"/>
-        <v>102.59999999999991</v>
-      </c>
-      <c r="BF44" s="39">
-        <f t="shared" si="7"/>
         <v>2.6480152789965392E-2</v>
       </c>
     </row>
@@ -24615,7 +24083,7 @@
         <v>1184.3199999999997</v>
       </c>
       <c r="T45" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3929.5</v>
       </c>
       <c r="U45" s="46">
@@ -24645,7 +24113,7 @@
       <c r="AG45" s="74"/>
       <c r="AH45" s="75"/>
       <c r="AI45" s="75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AJ45" s="32"/>
@@ -24655,15 +24123,15 @@
       <c r="AN45" s="33"/>
       <c r="AO45" s="33"/>
       <c r="AP45" s="34">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ45" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AQ45" s="32">
+      <c r="AR45" s="32">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AR45" s="32">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS45" s="32"/>
@@ -24679,16 +24147,16 @@
         <v>3929.5</v>
       </c>
       <c r="BC45" s="45">
-        <f t="shared" si="27"/>
+        <f>+X45</f>
         <v>3857.6</v>
       </c>
       <c r="BD45" s="45"/>
       <c r="BE45" s="45">
+        <f t="shared" si="5"/>
+        <v>71.900000000000091</v>
+      </c>
+      <c r="BF45" s="39">
         <f t="shared" si="6"/>
-        <v>71.900000000000091</v>
-      </c>
-      <c r="BF45" s="39">
-        <f t="shared" si="7"/>
         <v>1.8297493319760806E-2</v>
       </c>
     </row>
@@ -24744,7 +24212,7 @@
         <v>1182.5</v>
       </c>
       <c r="T46" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3818.8</v>
       </c>
       <c r="U46" s="46">
@@ -24774,7 +24242,7 @@
       <c r="AG46" s="74"/>
       <c r="AH46" s="75"/>
       <c r="AI46" s="75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AJ46" s="32"/>
@@ -24784,15 +24252,15 @@
       <c r="AN46" s="33"/>
       <c r="AO46" s="33"/>
       <c r="AP46" s="34">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ46" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AQ46" s="32">
+      <c r="AR46" s="32">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AR46" s="32">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS46" s="32"/>
@@ -24808,16 +24276,16 @@
         <v>3818.8</v>
       </c>
       <c r="BC46" s="45">
-        <f t="shared" si="27"/>
+        <f>+X46</f>
         <v>3734.4</v>
       </c>
       <c r="BD46" s="45"/>
       <c r="BE46" s="45">
+        <f t="shared" si="5"/>
+        <v>84.400000000000091</v>
+      </c>
+      <c r="BF46" s="39">
         <f t="shared" si="6"/>
-        <v>84.400000000000091</v>
-      </c>
-      <c r="BF46" s="39">
-        <f t="shared" si="7"/>
         <v>2.2101183617890461E-2</v>
       </c>
     </row>
@@ -24873,7 +24341,7 @@
         <v>1207.3999999999996</v>
       </c>
       <c r="T47" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3992.3</v>
       </c>
       <c r="U47" s="46">
@@ -24903,7 +24371,7 @@
       <c r="AG47" s="74"/>
       <c r="AH47" s="75"/>
       <c r="AI47" s="75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AJ47" s="32"/>
@@ -24913,15 +24381,15 @@
       <c r="AN47" s="33"/>
       <c r="AO47" s="33"/>
       <c r="AP47" s="34">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ47" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AQ47" s="32">
+      <c r="AR47" s="32">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AR47" s="32">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS47" s="32"/>
@@ -24937,16 +24405,16 @@
         <v>3992.25</v>
       </c>
       <c r="BC47" s="45">
-        <f t="shared" si="27"/>
+        <f>+X47</f>
         <v>3907.2</v>
       </c>
       <c r="BD47" s="45"/>
       <c r="BE47" s="45">
+        <f t="shared" si="5"/>
+        <v>85.050000000000182</v>
+      </c>
+      <c r="BF47" s="39">
         <f t="shared" si="6"/>
-        <v>85.050000000000182</v>
-      </c>
-      <c r="BF47" s="39">
-        <f t="shared" si="7"/>
         <v>2.1303776066128169E-2</v>
       </c>
     </row>
@@ -25002,7 +24470,7 @@
         <v>1197.3000000000002</v>
       </c>
       <c r="T48" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3959.3</v>
       </c>
       <c r="U48" s="46">
@@ -25032,7 +24500,7 @@
       <c r="AG48" s="74"/>
       <c r="AH48" s="75"/>
       <c r="AI48" s="75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AJ48" s="32"/>
@@ -25042,15 +24510,15 @@
       <c r="AN48" s="33"/>
       <c r="AO48" s="33"/>
       <c r="AP48" s="34">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ48" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AQ48" s="32">
+      <c r="AR48" s="32">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AR48" s="32">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS48" s="32"/>
@@ -25066,16 +24534,16 @@
         <v>3964.47</v>
       </c>
       <c r="BC48" s="45">
-        <f t="shared" si="27"/>
+        <f>+X48</f>
         <v>3892</v>
       </c>
       <c r="BD48" s="45"/>
       <c r="BE48" s="45">
+        <f t="shared" si="5"/>
+        <v>72.4699999999998</v>
+      </c>
+      <c r="BF48" s="39">
         <f t="shared" si="6"/>
-        <v>72.4699999999998</v>
-      </c>
-      <c r="BF48" s="39">
-        <f t="shared" si="7"/>
         <v>1.8279870953746606E-2</v>
       </c>
     </row>
@@ -25131,7 +24599,7 @@
         <v>1178.3200000000006</v>
       </c>
       <c r="T49" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3817.2</v>
       </c>
       <c r="U49" s="46">
@@ -25161,7 +24629,7 @@
       <c r="AG49" s="74"/>
       <c r="AH49" s="75"/>
       <c r="AI49" s="75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AJ49" s="32"/>
@@ -25171,15 +24639,15 @@
       <c r="AN49" s="33"/>
       <c r="AO49" s="33"/>
       <c r="AP49" s="34">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ49" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AQ49" s="32">
+      <c r="AR49" s="32">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AR49" s="32">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS49" s="32"/>
@@ -25195,16 +24663,16 @@
         <v>3817.2</v>
       </c>
       <c r="BC49" s="45">
-        <f t="shared" si="27"/>
+        <f>+X49</f>
         <v>3735.4</v>
       </c>
       <c r="BD49" s="45"/>
       <c r="BE49" s="45">
+        <f t="shared" si="5"/>
+        <v>81.799999999999727</v>
+      </c>
+      <c r="BF49" s="39">
         <f t="shared" si="6"/>
-        <v>81.799999999999727</v>
-      </c>
-      <c r="BF49" s="39">
-        <f t="shared" si="7"/>
         <v>2.1429319920360405E-2</v>
       </c>
     </row>
@@ -25260,7 +24728,7 @@
         <v>1224.56</v>
       </c>
       <c r="T50" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3953.4</v>
       </c>
       <c r="U50" s="46">
@@ -25290,7 +24758,7 @@
       <c r="AG50" s="74"/>
       <c r="AH50" s="75"/>
       <c r="AI50" s="75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AJ50" s="32"/>
@@ -25300,15 +24768,15 @@
       <c r="AN50" s="33"/>
       <c r="AO50" s="33"/>
       <c r="AP50" s="34">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ50" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AQ50" s="32">
+      <c r="AR50" s="32">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AR50" s="32">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS50" s="32"/>
@@ -25324,16 +24792,16 @@
         <v>3953.4</v>
       </c>
       <c r="BC50" s="45">
-        <f t="shared" si="27"/>
+        <f>+X50</f>
         <v>3823.6</v>
       </c>
       <c r="BD50" s="45"/>
       <c r="BE50" s="45">
+        <f t="shared" si="5"/>
+        <v>129.80000000000018</v>
+      </c>
+      <c r="BF50" s="39">
         <f t="shared" si="6"/>
-        <v>129.80000000000018</v>
-      </c>
-      <c r="BF50" s="39">
-        <f t="shared" si="7"/>
         <v>3.2832498608792476E-2</v>
       </c>
     </row>
@@ -25389,7 +24857,7 @@
         <v>1197.7799999999997</v>
       </c>
       <c r="T51" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3909.2</v>
       </c>
       <c r="U51" s="46">
@@ -25419,7 +24887,7 @@
       <c r="AG51" s="74"/>
       <c r="AH51" s="75"/>
       <c r="AI51" s="75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AJ51" s="32"/>
@@ -25429,15 +24897,15 @@
       <c r="AN51" s="33"/>
       <c r="AO51" s="33"/>
       <c r="AP51" s="34">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ51" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AQ51" s="32">
+      <c r="AR51" s="32">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AR51" s="32">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS51" s="32"/>
@@ -25453,16 +24921,16 @@
         <v>3909.2</v>
       </c>
       <c r="BC51" s="45">
-        <f t="shared" si="27"/>
+        <f>+X51</f>
         <v>3955.2</v>
       </c>
       <c r="BD51" s="45"/>
       <c r="BE51" s="45">
+        <f t="shared" si="5"/>
+        <v>-46</v>
+      </c>
+      <c r="BF51" s="39">
         <f t="shared" si="6"/>
-        <v>-46</v>
-      </c>
-      <c r="BF51" s="39">
-        <f t="shared" si="7"/>
         <v>-1.1767113475902998E-2</v>
       </c>
     </row>
@@ -25518,7 +24986,7 @@
         <v>1188.1699999999996</v>
       </c>
       <c r="T52" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3912.4</v>
       </c>
       <c r="U52" s="46">
@@ -25548,7 +25016,7 @@
       <c r="AG52" s="74"/>
       <c r="AH52" s="75"/>
       <c r="AI52" s="75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AJ52" s="32"/>
@@ -25558,15 +25026,15 @@
       <c r="AN52" s="33"/>
       <c r="AO52" s="33"/>
       <c r="AP52" s="34">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ52" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AQ52" s="32">
+      <c r="AR52" s="32">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AR52" s="32">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS52" s="32"/>
@@ -25582,16 +25050,16 @@
         <v>3912.35</v>
       </c>
       <c r="BC52" s="45">
-        <f t="shared" si="27"/>
+        <f>+X52</f>
         <v>3769.4</v>
       </c>
       <c r="BD52" s="45"/>
       <c r="BE52" s="45">
+        <f t="shared" si="5"/>
+        <v>142.94999999999982</v>
+      </c>
+      <c r="BF52" s="39">
         <f t="shared" si="6"/>
-        <v>142.94999999999982</v>
-      </c>
-      <c r="BF52" s="39">
-        <f t="shared" si="7"/>
         <v>3.6538142037394361E-2</v>
       </c>
     </row>
@@ -25647,7 +25115,7 @@
         <v>1080.5000000000005</v>
       </c>
       <c r="T53" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3496.1</v>
       </c>
       <c r="U53" s="46">
@@ -25677,7 +25145,7 @@
       <c r="AG53" s="74"/>
       <c r="AH53" s="75"/>
       <c r="AI53" s="75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AJ53" s="32"/>
@@ -25687,15 +25155,15 @@
       <c r="AN53" s="33"/>
       <c r="AO53" s="33"/>
       <c r="AP53" s="34">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ53" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AQ53" s="32">
+      <c r="AR53" s="32">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AR53" s="32">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS53" s="32"/>
@@ -25711,16 +25179,16 @@
         <v>3516.31</v>
       </c>
       <c r="BC53" s="45">
-        <f t="shared" si="27"/>
+        <f>+X53</f>
         <v>3541.8</v>
       </c>
       <c r="BD53" s="45"/>
       <c r="BE53" s="45">
+        <f t="shared" si="5"/>
+        <v>-25.490000000000236</v>
+      </c>
+      <c r="BF53" s="39">
         <f t="shared" si="6"/>
-        <v>-25.490000000000236</v>
-      </c>
-      <c r="BF53" s="39">
-        <f t="shared" si="7"/>
         <v>-7.2490764466159804E-3</v>
       </c>
     </row>
@@ -25776,7 +25244,7 @@
         <v>1155.42</v>
       </c>
       <c r="T54" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3777.3</v>
       </c>
       <c r="U54" s="46">
@@ -25806,7 +25274,7 @@
       <c r="AG54" s="74"/>
       <c r="AH54" s="75"/>
       <c r="AI54" s="75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AJ54" s="32"/>
@@ -25816,15 +25284,15 @@
       <c r="AN54" s="33"/>
       <c r="AO54" s="33"/>
       <c r="AP54" s="34">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ54" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AQ54" s="32">
+      <c r="AR54" s="32">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AR54" s="32">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS54" s="32"/>
@@ -25840,16 +25308,16 @@
         <v>3777.25</v>
       </c>
       <c r="BC54" s="45">
-        <f t="shared" si="27"/>
+        <f>+X54</f>
         <v>3840.6</v>
       </c>
       <c r="BD54" s="45"/>
       <c r="BE54" s="45">
+        <f t="shared" si="5"/>
+        <v>-63.349999999999909</v>
+      </c>
+      <c r="BF54" s="39">
         <f t="shared" si="6"/>
-        <v>-63.349999999999909</v>
-      </c>
-      <c r="BF54" s="39">
-        <f t="shared" si="7"/>
         <v>-1.6771460718776863E-2</v>
       </c>
     </row>
@@ -25905,7 +25373,7 @@
         <v>1207.3499999999999</v>
       </c>
       <c r="T55" s="46">
-        <f t="shared" ref="T55:T60" si="28">+R55-S55</f>
+        <f t="shared" ref="T55:T60" si="26">+R55-S55</f>
         <v>3870.4</v>
       </c>
       <c r="U55" s="46">
@@ -25935,7 +25403,7 @@
       <c r="AG55" s="74"/>
       <c r="AH55" s="75"/>
       <c r="AI55" s="75">
-        <f t="shared" ref="AI55:AI60" si="29">+AG55+AH55</f>
+        <f t="shared" ref="AI55:AI60" si="27">+AG55+AH55</f>
         <v>0</v>
       </c>
       <c r="AJ55" s="32"/>
@@ -25945,15 +25413,15 @@
       <c r="AN55" s="33"/>
       <c r="AO55" s="33"/>
       <c r="AP55" s="34">
-        <f t="shared" ref="AP55:AP60" si="30">ROUNDUP((AO55-AM55+(AO55&lt;AM55))*24,0)</f>
+        <f t="shared" ref="AP55:AP60" si="28">ROUNDUP((AO55-AM55+(AO55&lt;AM55))*24,0)</f>
         <v>0</v>
       </c>
       <c r="AQ55" s="32">
-        <f t="shared" ref="AQ55:AQ60" si="31">IF(AP55&gt;5,(AP55-5),0)</f>
+        <f t="shared" ref="AQ55:AQ60" si="29">IF(AP55&gt;5,(AP55-5),0)</f>
         <v>0</v>
       </c>
       <c r="AR55" s="32">
-        <f t="shared" ref="AR55:AR60" si="32">+AQ55*8850</f>
+        <f t="shared" ref="AR55:AR60" si="30">+AQ55*8850</f>
         <v>0</v>
       </c>
       <c r="AS55" s="32"/>
@@ -25969,16 +25437,16 @@
         <v>3870.4</v>
       </c>
       <c r="BC55" s="45">
-        <f t="shared" si="27"/>
+        <f>+X55</f>
         <v>3777.2</v>
       </c>
       <c r="BD55" s="45"/>
       <c r="BE55" s="45">
-        <f t="shared" ref="BE55:BE60" si="33">+BB55-BC55</f>
+        <f t="shared" ref="BE55:BE60" si="31">+BB55-BC55</f>
         <v>93.200000000000273</v>
       </c>
       <c r="BF55" s="39">
-        <f t="shared" ref="BF55:BF60" si="34">+BE55/BB55</f>
+        <f t="shared" ref="BF55:BF60" si="32">+BE55/BB55</f>
         <v>2.4080198429103004E-2</v>
       </c>
     </row>
@@ -26034,7 +25502,7 @@
         <v>1151.3000000000002</v>
       </c>
       <c r="T56" s="46">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>4021.7</v>
       </c>
       <c r="U56" s="46">
@@ -26064,7 +25532,7 @@
       <c r="AG56" s="74"/>
       <c r="AH56" s="75"/>
       <c r="AI56" s="75">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AJ56" s="32"/>
@@ -26074,15 +25542,15 @@
       <c r="AN56" s="33"/>
       <c r="AO56" s="33"/>
       <c r="AP56" s="34">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AQ56" s="32">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AR56" s="32">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="AQ56" s="32">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="AR56" s="32">
-        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AS56" s="32"/>
@@ -26098,16 +25566,16 @@
         <v>4021.7</v>
       </c>
       <c r="BC56" s="45">
-        <f t="shared" si="27"/>
+        <f>+X56</f>
         <v>4039.3</v>
       </c>
       <c r="BD56" s="45"/>
       <c r="BE56" s="45">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>-17.600000000000364</v>
       </c>
       <c r="BF56" s="39">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>-4.37625879603162E-3</v>
       </c>
     </row>
@@ -26163,7 +25631,7 @@
         <v>1192.46</v>
       </c>
       <c r="T57" s="46">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>3902.7</v>
       </c>
       <c r="U57" s="46">
@@ -26193,7 +25661,7 @@
       <c r="AG57" s="74"/>
       <c r="AH57" s="75"/>
       <c r="AI57" s="75">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AJ57" s="32"/>
@@ -26203,15 +25671,15 @@
       <c r="AN57" s="33"/>
       <c r="AO57" s="33"/>
       <c r="AP57" s="34">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AQ57" s="32">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AR57" s="32">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="AQ57" s="32">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="AR57" s="32">
-        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AS57" s="32"/>
@@ -26227,16 +25695,16 @@
         <v>3902.65</v>
       </c>
       <c r="BC57" s="45">
-        <f t="shared" si="27"/>
+        <f>+X57</f>
         <v>3836.2</v>
       </c>
       <c r="BD57" s="45"/>
       <c r="BE57" s="45">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>66.450000000000273</v>
       </c>
       <c r="BF57" s="39">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>1.7026891983652204E-2</v>
       </c>
     </row>
@@ -26292,7 +25760,7 @@
         <v>1242.2000000000003</v>
       </c>
       <c r="T58" s="46">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>4008.6</v>
       </c>
       <c r="U58" s="46">
@@ -26322,7 +25790,7 @@
       <c r="AG58" s="74"/>
       <c r="AH58" s="75"/>
       <c r="AI58" s="75">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AJ58" s="32"/>
@@ -26332,15 +25800,15 @@
       <c r="AN58" s="33"/>
       <c r="AO58" s="33"/>
       <c r="AP58" s="34">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AQ58" s="32">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AR58" s="32">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="AQ58" s="32">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="AR58" s="32">
-        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AS58" s="32"/>
@@ -26356,16 +25824,16 @@
         <v>4010.54</v>
       </c>
       <c r="BC58" s="45">
-        <f t="shared" si="27"/>
+        <f>+X58</f>
         <v>3991.6</v>
       </c>
       <c r="BD58" s="45"/>
       <c r="BE58" s="45">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>18.940000000000055</v>
       </c>
       <c r="BF58" s="39">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>4.7225560647693463E-3</v>
       </c>
     </row>
@@ -26421,7 +25889,7 @@
         <v>1171.0999999999995</v>
       </c>
       <c r="T59" s="46">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>4096.6000000000004</v>
       </c>
       <c r="U59" s="46">
@@ -26451,7 +25919,7 @@
       <c r="AG59" s="74"/>
       <c r="AH59" s="75"/>
       <c r="AI59" s="75">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AJ59" s="32"/>
@@ -26461,15 +25929,15 @@
       <c r="AN59" s="33"/>
       <c r="AO59" s="33"/>
       <c r="AP59" s="34">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AQ59" s="32">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AR59" s="32">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="AQ59" s="32">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="AR59" s="32">
-        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AS59" s="32"/>
@@ -26485,16 +25953,16 @@
         <v>4096.55</v>
       </c>
       <c r="BC59" s="45">
-        <f t="shared" si="27"/>
+        <f>+X59</f>
         <v>4103.6000000000004</v>
       </c>
       <c r="BD59" s="45"/>
       <c r="BE59" s="45">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>-7.0500000000001819</v>
       </c>
       <c r="BF59" s="39">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>-1.7209603202695393E-3</v>
       </c>
     </row>
@@ -26550,7 +26018,7 @@
         <v>1171.0999999999995</v>
       </c>
       <c r="T60" s="46">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>4117.8</v>
       </c>
       <c r="U60" s="46">
@@ -26580,7 +26048,7 @@
       <c r="AG60" s="74"/>
       <c r="AH60" s="75"/>
       <c r="AI60" s="75">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AJ60" s="32"/>
@@ -26590,15 +26058,15 @@
       <c r="AN60" s="33"/>
       <c r="AO60" s="33"/>
       <c r="AP60" s="34">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AQ60" s="32">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AR60" s="32">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="AQ60" s="32">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="AR60" s="32">
-        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AS60" s="32"/>
@@ -26614,16 +26082,16 @@
         <v>4117.75</v>
       </c>
       <c r="BC60" s="45">
-        <f t="shared" si="27"/>
+        <f>+X60</f>
         <v>4096</v>
       </c>
       <c r="BD60" s="45"/>
       <c r="BE60" s="45">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>21.75</v>
       </c>
       <c r="BF60" s="39">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>5.2820108068726852E-3</v>
       </c>
     </row>
@@ -26679,7 +26147,7 @@
         <v>1198.0999999999999</v>
       </c>
       <c r="T61" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3667.1</v>
       </c>
       <c r="U61" s="46">
@@ -26709,7 +26177,7 @@
       <c r="AG61" s="74"/>
       <c r="AH61" s="75"/>
       <c r="AI61" s="75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AJ61" s="32"/>
@@ -26719,15 +26187,15 @@
       <c r="AN61" s="33"/>
       <c r="AO61" s="33"/>
       <c r="AP61" s="34">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ61" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AQ61" s="32">
+      <c r="AR61" s="32">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AR61" s="32">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS61" s="32"/>
@@ -26743,16 +26211,16 @@
         <v>3679.26</v>
       </c>
       <c r="BC61" s="45">
-        <f t="shared" si="27"/>
+        <f>+X61</f>
         <v>3673.6</v>
       </c>
       <c r="BD61" s="45"/>
       <c r="BE61" s="45">
+        <f t="shared" si="5"/>
+        <v>5.6600000000003092</v>
+      </c>
+      <c r="BF61" s="39">
         <f t="shared" si="6"/>
-        <v>5.6600000000003092</v>
-      </c>
-      <c r="BF61" s="39">
-        <f t="shared" si="7"/>
         <v>1.5383528209477746E-3</v>
       </c>
     </row>
@@ -26808,7 +26276,7 @@
         <v>1140.5900000000001</v>
       </c>
       <c r="T62" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3785.7</v>
       </c>
       <c r="U62" s="46">
@@ -26838,7 +26306,7 @@
       <c r="AG62" s="74"/>
       <c r="AH62" s="75"/>
       <c r="AI62" s="75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AJ62" s="32"/>
@@ -26848,15 +26316,15 @@
       <c r="AN62" s="33"/>
       <c r="AO62" s="33"/>
       <c r="AP62" s="34">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ62" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AQ62" s="32">
+      <c r="AR62" s="32">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AR62" s="32">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS62" s="32"/>
@@ -26872,16 +26340,16 @@
         <v>3785.7</v>
       </c>
       <c r="BC62" s="45">
-        <f t="shared" si="27"/>
+        <f>+X62</f>
         <v>3729.6</v>
       </c>
       <c r="BD62" s="45"/>
       <c r="BE62" s="45">
+        <f t="shared" si="5"/>
+        <v>56.099999999999909</v>
+      </c>
+      <c r="BF62" s="39">
         <f t="shared" si="6"/>
-        <v>56.099999999999909</v>
-      </c>
-      <c r="BF62" s="39">
-        <f t="shared" si="7"/>
         <v>1.4818923844995618E-2</v>
       </c>
     </row>
@@ -26937,7 +26405,7 @@
         <v>1195.6999999999998</v>
       </c>
       <c r="T63" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3896.8</v>
       </c>
       <c r="U63" s="46">
@@ -26967,7 +26435,7 @@
       <c r="AG63" s="74"/>
       <c r="AH63" s="75"/>
       <c r="AI63" s="75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AJ63" s="32"/>
@@ -26977,15 +26445,15 @@
       <c r="AN63" s="33"/>
       <c r="AO63" s="33"/>
       <c r="AP63" s="34">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ63" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AQ63" s="32">
+      <c r="AR63" s="32">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AR63" s="32">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS63" s="32"/>
@@ -27001,16 +26469,16 @@
         <v>3896.75</v>
       </c>
       <c r="BC63" s="45">
-        <f t="shared" si="27"/>
+        <f>+X63</f>
         <v>3856.8</v>
       </c>
       <c r="BD63" s="45"/>
       <c r="BE63" s="45">
+        <f t="shared" si="5"/>
+        <v>39.949999999999818</v>
+      </c>
+      <c r="BF63" s="39">
         <f t="shared" si="6"/>
-        <v>39.949999999999818</v>
-      </c>
-      <c r="BF63" s="39">
-        <f t="shared" si="7"/>
         <v>1.0252133187912958E-2</v>
       </c>
     </row>
@@ -27066,7 +26534,7 @@
         <v>1190.6000000000004</v>
       </c>
       <c r="T64" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3916</v>
       </c>
       <c r="U64" s="46">
@@ -27096,7 +26564,7 @@
       <c r="AG64" s="74"/>
       <c r="AH64" s="75"/>
       <c r="AI64" s="75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AJ64" s="32"/>
@@ -27106,15 +26574,15 @@
       <c r="AN64" s="33"/>
       <c r="AO64" s="33"/>
       <c r="AP64" s="34">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ64" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AQ64" s="32">
+      <c r="AR64" s="32">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AR64" s="32">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS64" s="32"/>
@@ -27130,16 +26598,16 @@
         <v>3921.68</v>
       </c>
       <c r="BC64" s="45">
-        <f t="shared" si="27"/>
+        <f>+X64</f>
         <v>4016</v>
       </c>
       <c r="BD64" s="45"/>
       <c r="BE64" s="45">
+        <f t="shared" si="5"/>
+        <v>-94.320000000000164</v>
+      </c>
+      <c r="BF64" s="39">
         <f t="shared" si="6"/>
-        <v>-94.320000000000164</v>
-      </c>
-      <c r="BF64" s="39">
-        <f t="shared" si="7"/>
         <v>-2.405091695395855E-2</v>
       </c>
     </row>
@@ -27195,7 +26663,7 @@
         <v>1253.33</v>
       </c>
       <c r="T65" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>4057</v>
       </c>
       <c r="U65" s="46">
@@ -27225,7 +26693,7 @@
       <c r="AG65" s="74"/>
       <c r="AH65" s="75"/>
       <c r="AI65" s="75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AJ65" s="32"/>
@@ -27235,15 +26703,15 @@
       <c r="AN65" s="33"/>
       <c r="AO65" s="33"/>
       <c r="AP65" s="34">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ65" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AQ65" s="32">
+      <c r="AR65" s="32">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AR65" s="32">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS65" s="32"/>
@@ -27259,16 +26727,16 @@
         <v>4194.05</v>
       </c>
       <c r="BC65" s="45">
-        <f t="shared" si="27"/>
+        <f>+X65</f>
         <v>4194.6000000000004</v>
       </c>
       <c r="BD65" s="45"/>
       <c r="BE65" s="45">
+        <f t="shared" si="5"/>
+        <v>-0.5500000000001819</v>
+      </c>
+      <c r="BF65" s="39">
         <f t="shared" si="6"/>
-        <v>-0.5500000000001819</v>
-      </c>
-      <c r="BF65" s="39">
-        <f t="shared" si="7"/>
         <v>-1.3113816001244187E-4</v>
       </c>
     </row>
@@ -27324,7 +26792,7 @@
         <v>1083.29</v>
       </c>
       <c r="T66" s="46">
-        <f t="shared" ref="T66:T73" si="35">+R66-S66</f>
+        <f t="shared" ref="T66:T73" si="33">+R66-S66</f>
         <v>3590</v>
       </c>
       <c r="U66" s="46">
@@ -27354,7 +26822,7 @@
       <c r="AG66" s="74"/>
       <c r="AH66" s="75"/>
       <c r="AI66" s="75">
-        <f t="shared" ref="AI66:AI73" si="36">+AG66+AH66</f>
+        <f t="shared" ref="AI66:AI73" si="34">+AG66+AH66</f>
         <v>0</v>
       </c>
       <c r="AJ66" s="32"/>
@@ -27364,15 +26832,15 @@
       <c r="AN66" s="33"/>
       <c r="AO66" s="33"/>
       <c r="AP66" s="34">
-        <f t="shared" ref="AP66:AP73" si="37">ROUNDUP((AO66-AM66+(AO66&lt;AM66))*24,0)</f>
+        <f t="shared" ref="AP66:AP73" si="35">ROUNDUP((AO66-AM66+(AO66&lt;AM66))*24,0)</f>
         <v>0</v>
       </c>
       <c r="AQ66" s="32">
-        <f t="shared" ref="AQ66:AQ73" si="38">IF(AP66&gt;5,(AP66-5),0)</f>
+        <f t="shared" ref="AQ66:AQ73" si="36">IF(AP66&gt;5,(AP66-5),0)</f>
         <v>0</v>
       </c>
       <c r="AR66" s="32">
-        <f t="shared" ref="AR66:AR73" si="39">+AQ66*8850</f>
+        <f t="shared" ref="AR66:AR73" si="37">+AQ66*8850</f>
         <v>0</v>
       </c>
       <c r="AS66" s="32"/>
@@ -27388,16 +26856,16 @@
         <v>3590</v>
       </c>
       <c r="BC66" s="45">
-        <f t="shared" si="27"/>
+        <f>+X66</f>
         <v>3522.6</v>
       </c>
       <c r="BD66" s="45"/>
       <c r="BE66" s="45">
-        <f t="shared" ref="BE66:BE73" si="40">+BB66-BC66</f>
+        <f t="shared" ref="BE66:BE73" si="38">+BB66-BC66</f>
         <v>67.400000000000091</v>
       </c>
       <c r="BF66" s="39">
-        <f t="shared" ref="BF66:BF73" si="41">+BE66/BB66</f>
+        <f t="shared" ref="BF66:BF73" si="39">+BE66/BB66</f>
         <v>1.877437325905295E-2</v>
       </c>
     </row>
@@ -27453,7 +26921,7 @@
         <v>1206.1700000000005</v>
       </c>
       <c r="T67" s="46">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>3985.6</v>
       </c>
       <c r="U67" s="46">
@@ -27483,7 +26951,7 @@
       <c r="AG67" s="74"/>
       <c r="AH67" s="75"/>
       <c r="AI67" s="75">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AJ67" s="32"/>
@@ -27493,15 +26961,15 @@
       <c r="AN67" s="33"/>
       <c r="AO67" s="33"/>
       <c r="AP67" s="34">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ67" s="32">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AR67" s="32">
         <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AQ67" s="32">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="AR67" s="32">
-        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AS67" s="32"/>
@@ -27517,16 +26985,16 @@
         <v>3985.55</v>
       </c>
       <c r="BC67" s="45">
-        <f t="shared" si="27"/>
+        <f>+X67</f>
         <v>3933</v>
       </c>
       <c r="BD67" s="45"/>
       <c r="BE67" s="45">
-        <f t="shared" si="40"/>
+        <f t="shared" si="38"/>
         <v>52.550000000000182</v>
       </c>
       <c r="BF67" s="39">
-        <f t="shared" si="41"/>
+        <f t="shared" si="39"/>
         <v>1.3185131286773514E-2</v>
       </c>
     </row>
@@ -27582,7 +27050,7 @@
         <v>1206.7599999999998</v>
       </c>
       <c r="T68" s="46">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>3927.6</v>
       </c>
       <c r="U68" s="46">
@@ -27612,7 +27080,7 @@
       <c r="AG68" s="74"/>
       <c r="AH68" s="75"/>
       <c r="AI68" s="75">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AJ68" s="32"/>
@@ -27622,15 +27090,15 @@
       <c r="AN68" s="33"/>
       <c r="AO68" s="33"/>
       <c r="AP68" s="34">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ68" s="32">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AR68" s="32">
         <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AQ68" s="32">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="AR68" s="32">
-        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AS68" s="32"/>
@@ -27646,16 +27114,16 @@
         <v>3965.72</v>
       </c>
       <c r="BC68" s="45">
-        <f t="shared" si="27"/>
+        <f>+X68</f>
         <v>4092.6</v>
       </c>
       <c r="BD68" s="45"/>
       <c r="BE68" s="45">
-        <f t="shared" si="40"/>
+        <f t="shared" si="38"/>
         <v>-126.88000000000011</v>
       </c>
       <c r="BF68" s="39">
-        <f t="shared" si="41"/>
+        <f t="shared" si="39"/>
         <v>-3.1994190210100588E-2</v>
       </c>
     </row>
@@ -27711,7 +27179,7 @@
         <v>1170.6200000000003</v>
       </c>
       <c r="T69" s="46">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>3866.9</v>
       </c>
       <c r="U69" s="46">
@@ -27741,7 +27209,7 @@
       <c r="AG69" s="74"/>
       <c r="AH69" s="75"/>
       <c r="AI69" s="75">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AJ69" s="32"/>
@@ -27751,15 +27219,15 @@
       <c r="AN69" s="33"/>
       <c r="AO69" s="33"/>
       <c r="AP69" s="34">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ69" s="32">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AR69" s="32">
         <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AQ69" s="32">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="AR69" s="32">
-        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AS69" s="32"/>
@@ -27775,16 +27243,16 @@
         <v>3894.02</v>
       </c>
       <c r="BC69" s="45">
-        <f t="shared" si="27"/>
+        <f>+X69</f>
         <v>4001.6</v>
       </c>
       <c r="BD69" s="45"/>
       <c r="BE69" s="45">
-        <f t="shared" si="40"/>
+        <f t="shared" si="38"/>
         <v>-107.57999999999993</v>
       </c>
       <c r="BF69" s="39">
-        <f t="shared" si="41"/>
+        <f t="shared" si="39"/>
         <v>-2.7626976748963777E-2</v>
       </c>
     </row>
@@ -27840,7 +27308,7 @@
         <v>1143.3699999999999</v>
       </c>
       <c r="T70" s="46">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>3667.5</v>
       </c>
       <c r="U70" s="46">
@@ -27870,7 +27338,7 @@
       <c r="AG70" s="74"/>
       <c r="AH70" s="75"/>
       <c r="AI70" s="75">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AJ70" s="32"/>
@@ -27880,15 +27348,15 @@
       <c r="AN70" s="33"/>
       <c r="AO70" s="33"/>
       <c r="AP70" s="34">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ70" s="32">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AR70" s="32">
         <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AQ70" s="32">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="AR70" s="32">
-        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AS70" s="32"/>
@@ -27904,16 +27372,16 @@
         <v>3667.5</v>
       </c>
       <c r="BC70" s="45">
-        <f t="shared" ref="BC70:BC96" si="42">+X70</f>
+        <f>+X70</f>
         <v>3335.4</v>
       </c>
       <c r="BD70" s="45"/>
       <c r="BE70" s="45">
-        <f t="shared" si="40"/>
+        <f t="shared" si="38"/>
         <v>332.09999999999991</v>
       </c>
       <c r="BF70" s="39">
-        <f t="shared" si="41"/>
+        <f t="shared" si="39"/>
         <v>9.0552147239263775E-2</v>
       </c>
     </row>
@@ -27969,7 +27437,7 @@
         <v>1081.3200000000002</v>
       </c>
       <c r="T71" s="46">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>3576.4</v>
       </c>
       <c r="U71" s="46">
@@ -27999,7 +27467,7 @@
       <c r="AG71" s="74"/>
       <c r="AH71" s="75"/>
       <c r="AI71" s="75">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AJ71" s="32"/>
@@ -28009,15 +27477,15 @@
       <c r="AN71" s="33"/>
       <c r="AO71" s="33"/>
       <c r="AP71" s="34">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ71" s="32">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AR71" s="32">
         <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AQ71" s="32">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="AR71" s="32">
-        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AS71" s="32"/>
@@ -28033,16 +27501,16 @@
         <v>3576.4</v>
       </c>
       <c r="BC71" s="45">
-        <f t="shared" si="42"/>
+        <f>+X71</f>
         <v>3253.4</v>
       </c>
       <c r="BD71" s="45"/>
       <c r="BE71" s="45">
-        <f t="shared" si="40"/>
+        <f t="shared" si="38"/>
         <v>323</v>
       </c>
       <c r="BF71" s="39">
-        <f t="shared" si="41"/>
+        <f t="shared" si="39"/>
         <v>9.0314282518733927E-2</v>
       </c>
     </row>
@@ -28098,7 +27566,7 @@
         <v>1150.2099999999996</v>
       </c>
       <c r="T72" s="46">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>3804.9</v>
       </c>
       <c r="U72" s="46">
@@ -28128,7 +27596,7 @@
       <c r="AG72" s="74"/>
       <c r="AH72" s="75"/>
       <c r="AI72" s="75">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AJ72" s="32"/>
@@ -28138,15 +27606,15 @@
       <c r="AN72" s="33"/>
       <c r="AO72" s="33"/>
       <c r="AP72" s="34">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ72" s="32">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AR72" s="32">
         <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AQ72" s="32">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="AR72" s="32">
-        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AS72" s="32"/>
@@ -28162,16 +27630,16 @@
         <v>4000.9</v>
       </c>
       <c r="BC72" s="45">
-        <f t="shared" si="42"/>
+        <f>+X72</f>
         <v>4004.8</v>
       </c>
       <c r="BD72" s="45"/>
       <c r="BE72" s="45">
-        <f t="shared" si="40"/>
+        <f t="shared" si="38"/>
         <v>-3.9000000000000909</v>
       </c>
       <c r="BF72" s="39">
-        <f t="shared" si="41"/>
+        <f t="shared" si="39"/>
         <v>-9.747806743482944E-4</v>
       </c>
     </row>
@@ -28227,7 +27695,7 @@
         <v>1150.9300000000003</v>
       </c>
       <c r="T73" s="46">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>3765.2</v>
       </c>
       <c r="U73" s="46">
@@ -28257,7 +27725,7 @@
       <c r="AG73" s="74"/>
       <c r="AH73" s="75"/>
       <c r="AI73" s="75">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AJ73" s="32"/>
@@ -28267,15 +27735,15 @@
       <c r="AN73" s="33"/>
       <c r="AO73" s="33"/>
       <c r="AP73" s="34">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ73" s="32">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AR73" s="32">
         <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AQ73" s="32">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="AR73" s="32">
-        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AS73" s="32"/>
@@ -28291,16 +27759,16 @@
         <v>3765.2</v>
       </c>
       <c r="BC73" s="45">
-        <f t="shared" si="42"/>
+        <f>+X73</f>
         <v>3774</v>
       </c>
       <c r="BD73" s="45"/>
       <c r="BE73" s="45">
-        <f t="shared" si="40"/>
+        <f t="shared" si="38"/>
         <v>-8.8000000000001819</v>
       </c>
       <c r="BF73" s="39">
-        <f t="shared" si="41"/>
+        <f t="shared" si="39"/>
         <v>-2.3371932433868541E-3</v>
       </c>
     </row>
@@ -28356,7 +27824,7 @@
         <v>1062</v>
       </c>
       <c r="T74" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3502.2</v>
       </c>
       <c r="U74" s="46">
@@ -28386,7 +27854,7 @@
       <c r="AG74" s="74"/>
       <c r="AH74" s="75"/>
       <c r="AI74" s="75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AJ74" s="32"/>
@@ -28396,15 +27864,15 @@
       <c r="AN74" s="33"/>
       <c r="AO74" s="33"/>
       <c r="AP74" s="34">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ74" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AQ74" s="32">
+      <c r="AR74" s="32">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AR74" s="32">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS74" s="32"/>
@@ -28420,16 +27888,16 @@
         <v>3502.15</v>
       </c>
       <c r="BC74" s="45">
-        <f t="shared" si="42"/>
+        <f>+X74</f>
         <v>3402.2</v>
       </c>
       <c r="BD74" s="45"/>
       <c r="BE74" s="45">
+        <f t="shared" si="5"/>
+        <v>99.950000000000273</v>
+      </c>
+      <c r="BF74" s="39">
         <f t="shared" si="6"/>
-        <v>99.950000000000273</v>
-      </c>
-      <c r="BF74" s="39">
-        <f t="shared" si="7"/>
         <v>2.8539611381579965E-2</v>
       </c>
     </row>
@@ -28485,7 +27953,7 @@
         <v>1223.3100000000004</v>
       </c>
       <c r="T75" s="46">
-        <f t="shared" ref="T75" si="43">+R75-S75</f>
+        <f t="shared" ref="T75" si="40">+R75-S75</f>
         <v>3972.7</v>
       </c>
       <c r="U75" s="46">
@@ -28515,7 +27983,7 @@
       <c r="AG75" s="74"/>
       <c r="AH75" s="75"/>
       <c r="AI75" s="75">
-        <f t="shared" ref="AI75" si="44">+AG75+AH75</f>
+        <f t="shared" ref="AI75" si="41">+AG75+AH75</f>
         <v>0</v>
       </c>
       <c r="AJ75" s="32"/>
@@ -28525,15 +27993,15 @@
       <c r="AN75" s="33"/>
       <c r="AO75" s="33"/>
       <c r="AP75" s="34">
-        <f t="shared" ref="AP75" si="45">ROUNDUP((AO75-AM75+(AO75&lt;AM75))*24,0)</f>
+        <f t="shared" ref="AP75" si="42">ROUNDUP((AO75-AM75+(AO75&lt;AM75))*24,0)</f>
         <v>0</v>
       </c>
       <c r="AQ75" s="32">
-        <f t="shared" ref="AQ75" si="46">IF(AP75&gt;5,(AP75-5),0)</f>
+        <f t="shared" ref="AQ75" si="43">IF(AP75&gt;5,(AP75-5),0)</f>
         <v>0</v>
       </c>
       <c r="AR75" s="32">
-        <f t="shared" ref="AR75" si="47">+AQ75*8850</f>
+        <f t="shared" ref="AR75" si="44">+AQ75*8850</f>
         <v>0</v>
       </c>
       <c r="AS75" s="32"/>
@@ -28549,16 +28017,16 @@
         <v>3972.7</v>
       </c>
       <c r="BC75" s="45">
-        <f t="shared" si="42"/>
+        <f>+X75</f>
         <v>3937.4</v>
       </c>
       <c r="BD75" s="45"/>
       <c r="BE75" s="45">
-        <f t="shared" ref="BE75" si="48">+BB75-BC75</f>
+        <f t="shared" ref="BE75" si="45">+BB75-BC75</f>
         <v>35.299999999999727</v>
       </c>
       <c r="BF75" s="39">
-        <f t="shared" ref="BF75" si="49">+BE75/BB75</f>
+        <f t="shared" ref="BF75" si="46">+BE75/BB75</f>
         <v>8.8856445238753821E-3</v>
       </c>
     </row>
@@ -28614,7 +28082,7 @@
         <v>1132.6100000000001</v>
       </c>
       <c r="T76" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3728.9</v>
       </c>
       <c r="U76" s="46">
@@ -28644,7 +28112,7 @@
       <c r="AG76" s="74"/>
       <c r="AH76" s="75"/>
       <c r="AI76" s="75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AJ76" s="32"/>
@@ -28654,15 +28122,15 @@
       <c r="AN76" s="33"/>
       <c r="AO76" s="33"/>
       <c r="AP76" s="34">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ76" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AQ76" s="32">
+      <c r="AR76" s="32">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AR76" s="32">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS76" s="32"/>
@@ -28678,16 +28146,16 @@
         <v>3872.5</v>
       </c>
       <c r="BC76" s="45">
-        <f t="shared" si="42"/>
+        <f>+X76</f>
         <v>3521.4</v>
       </c>
       <c r="BD76" s="45"/>
       <c r="BE76" s="45">
+        <f t="shared" si="5"/>
+        <v>351.09999999999991</v>
+      </c>
+      <c r="BF76" s="39">
         <f t="shared" si="6"/>
-        <v>351.09999999999991</v>
-      </c>
-      <c r="BF76" s="39">
-        <f t="shared" si="7"/>
         <v>9.0664945125887644E-2</v>
       </c>
     </row>
@@ -28743,7 +28211,7 @@
         <v>1134.4799999999996</v>
       </c>
       <c r="T77" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3691</v>
       </c>
       <c r="U77" s="46">
@@ -28773,7 +28241,7 @@
       <c r="AG77" s="74"/>
       <c r="AH77" s="75"/>
       <c r="AI77" s="75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AJ77" s="32"/>
@@ -28783,15 +28251,15 @@
       <c r="AN77" s="33"/>
       <c r="AO77" s="33"/>
       <c r="AP77" s="34">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ77" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AQ77" s="32">
+      <c r="AR77" s="32">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AR77" s="32">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS77" s="32"/>
@@ -28807,16 +28275,16 @@
         <v>3691</v>
       </c>
       <c r="BC77" s="45">
-        <f t="shared" si="42"/>
+        <f>+X77</f>
         <v>3669</v>
       </c>
       <c r="BD77" s="45"/>
       <c r="BE77" s="45">
+        <f t="shared" si="5"/>
+        <v>22</v>
+      </c>
+      <c r="BF77" s="39">
         <f t="shared" si="6"/>
-        <v>22</v>
-      </c>
-      <c r="BF77" s="39">
-        <f t="shared" si="7"/>
         <v>5.9604443240314281E-3</v>
       </c>
     </row>
@@ -28872,7 +28340,7 @@
         <v>1197.6100000000006</v>
       </c>
       <c r="T78" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3915.7</v>
       </c>
       <c r="U78" s="46">
@@ -28902,7 +28370,7 @@
       <c r="AG78" s="74"/>
       <c r="AH78" s="75"/>
       <c r="AI78" s="75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AJ78" s="32"/>
@@ -28912,15 +28380,15 @@
       <c r="AN78" s="33"/>
       <c r="AO78" s="33"/>
       <c r="AP78" s="34">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ78" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AQ78" s="32">
+      <c r="AR78" s="32">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AR78" s="32">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS78" s="32"/>
@@ -28936,16 +28404,16 @@
         <v>3915.7</v>
       </c>
       <c r="BC78" s="45">
-        <f t="shared" si="42"/>
+        <f>+X78</f>
         <v>3803.6</v>
       </c>
       <c r="BD78" s="45"/>
       <c r="BE78" s="45">
-        <f t="shared" ref="BE78:BE87" si="50">+BB78-BC78</f>
+        <f t="shared" ref="BE78:BE87" si="47">+BB78-BC78</f>
         <v>112.09999999999991</v>
       </c>
       <c r="BF78" s="39">
-        <f t="shared" ref="BF78:BF87" si="51">+BE78/BB78</f>
+        <f t="shared" ref="BF78:BF87" si="48">+BE78/BB78</f>
         <v>2.8628342314273289E-2</v>
       </c>
     </row>
@@ -29001,7 +28469,7 @@
         <v>1172.6000000000004</v>
       </c>
       <c r="T79" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3795</v>
       </c>
       <c r="U79" s="46">
@@ -29010,16 +28478,16 @@
       <c r="V79" s="46"/>
       <c r="W79" s="46"/>
       <c r="X79" s="46">
-        <v>3901</v>
+        <v>3915.16</v>
       </c>
       <c r="Y79" s="46"/>
       <c r="Z79" s="46">
         <f>+T79-X79</f>
-        <v>-106</v>
+        <v>-120.15999999999985</v>
       </c>
       <c r="AA79" s="39">
         <f>Z79/T79</f>
-        <v>-2.7931488801054019E-2</v>
+        <v>-3.1662714097496665E-2</v>
       </c>
       <c r="AB79" s="73">
         <v>3803.66</v>
@@ -29031,7 +28499,7 @@
       <c r="AG79" s="74"/>
       <c r="AH79" s="75"/>
       <c r="AI79" s="75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AJ79" s="32"/>
@@ -29041,15 +28509,15 @@
       <c r="AN79" s="33"/>
       <c r="AO79" s="33"/>
       <c r="AP79" s="34">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ79" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AQ79" s="32">
+      <c r="AR79" s="32">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AR79" s="32">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS79" s="32"/>
@@ -29065,17 +28533,17 @@
         <v>3803.66</v>
       </c>
       <c r="BC79" s="45">
-        <f t="shared" si="42"/>
-        <v>3901</v>
+        <f>+X79</f>
+        <v>3915.16</v>
       </c>
       <c r="BD79" s="45"/>
       <c r="BE79" s="45">
-        <f t="shared" si="50"/>
-        <v>-97.340000000000146</v>
+        <f t="shared" si="47"/>
+        <v>-111.5</v>
       </c>
       <c r="BF79" s="39">
-        <f t="shared" si="51"/>
-        <v>-2.5591141164036782E-2</v>
+        <f t="shared" si="48"/>
+        <v>-2.9313871376516303E-2</v>
       </c>
     </row>
     <row r="80" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -29130,7 +28598,7 @@
         <v>1191.8000000000002</v>
       </c>
       <c r="T80" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3906</v>
       </c>
       <c r="U80" s="46">
@@ -29160,7 +28628,7 @@
       <c r="AG80" s="74"/>
       <c r="AH80" s="75"/>
       <c r="AI80" s="75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AJ80" s="32"/>
@@ -29170,15 +28638,15 @@
       <c r="AN80" s="33"/>
       <c r="AO80" s="33"/>
       <c r="AP80" s="34">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ80" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AQ80" s="32">
+      <c r="AR80" s="32">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AR80" s="32">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS80" s="32"/>
@@ -29194,16 +28662,16 @@
         <v>3905.95</v>
       </c>
       <c r="BC80" s="45">
-        <f t="shared" si="42"/>
+        <f>+X80</f>
         <v>4083.6</v>
       </c>
       <c r="BD80" s="45"/>
       <c r="BE80" s="45">
-        <f t="shared" si="50"/>
+        <f t="shared" si="47"/>
         <v>-177.65000000000009</v>
       </c>
       <c r="BF80" s="39">
-        <f t="shared" si="51"/>
+        <f t="shared" si="48"/>
         <v>-4.5481893009383149E-2</v>
       </c>
     </row>
@@ -29259,7 +28727,7 @@
         <v>1175.7699999999995</v>
       </c>
       <c r="T81" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3879.3</v>
       </c>
       <c r="U81" s="46">
@@ -29289,7 +28757,7 @@
       <c r="AG81" s="74"/>
       <c r="AH81" s="75"/>
       <c r="AI81" s="75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AJ81" s="32"/>
@@ -29299,15 +28767,15 @@
       <c r="AN81" s="33"/>
       <c r="AO81" s="33"/>
       <c r="AP81" s="34">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ81" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AQ81" s="32">
+      <c r="AR81" s="32">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AR81" s="32">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS81" s="32"/>
@@ -29323,16 +28791,16 @@
         <v>3879.3</v>
       </c>
       <c r="BC81" s="45">
-        <f t="shared" si="42"/>
+        <f>+X81</f>
         <v>3891</v>
       </c>
       <c r="BD81" s="45"/>
       <c r="BE81" s="45">
-        <f t="shared" si="50"/>
+        <f t="shared" si="47"/>
         <v>-11.699999999999818</v>
       </c>
       <c r="BF81" s="39">
-        <f t="shared" si="51"/>
+        <f t="shared" si="48"/>
         <v>-3.0160080426880668E-3</v>
       </c>
     </row>
@@ -29388,7 +28856,7 @@
         <v>961.00000000000045</v>
       </c>
       <c r="T82" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3162.6</v>
       </c>
       <c r="U82" s="46">
@@ -29418,7 +28886,7 @@
       <c r="AG82" s="74"/>
       <c r="AH82" s="75"/>
       <c r="AI82" s="75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AJ82" s="32"/>
@@ -29428,15 +28896,15 @@
       <c r="AN82" s="33"/>
       <c r="AO82" s="33"/>
       <c r="AP82" s="34">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ82" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AQ82" s="32">
+      <c r="AR82" s="32">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AR82" s="32">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS82" s="32"/>
@@ -29452,16 +28920,16 @@
         <v>3461.9999999999995</v>
       </c>
       <c r="BC82" s="45">
-        <f t="shared" si="42"/>
+        <f>+X82</f>
         <v>3199</v>
       </c>
       <c r="BD82" s="45"/>
       <c r="BE82" s="45">
-        <f t="shared" si="50"/>
+        <f t="shared" si="47"/>
         <v>262.99999999999955</v>
       </c>
       <c r="BF82" s="39">
-        <f t="shared" si="51"/>
+        <f t="shared" si="48"/>
         <v>7.5967648757943262E-2</v>
       </c>
     </row>
@@ -29517,7 +28985,7 @@
         <v>1233.6599999999999</v>
       </c>
       <c r="T83" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>4105.3</v>
       </c>
       <c r="U83" s="46">
@@ -29547,7 +29015,7 @@
       <c r="AG83" s="74"/>
       <c r="AH83" s="75"/>
       <c r="AI83" s="75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AJ83" s="32"/>
@@ -29557,15 +29025,15 @@
       <c r="AN83" s="33"/>
       <c r="AO83" s="33"/>
       <c r="AP83" s="34">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ83" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AQ83" s="32">
+      <c r="AR83" s="32">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AR83" s="32">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS83" s="32"/>
@@ -29581,16 +29049,16 @@
         <v>4105.25</v>
       </c>
       <c r="BC83" s="45">
-        <f t="shared" si="42"/>
+        <f>+X83</f>
         <v>3974.2</v>
       </c>
       <c r="BD83" s="45"/>
       <c r="BE83" s="45">
-        <f t="shared" si="50"/>
+        <f t="shared" si="47"/>
         <v>131.05000000000018</v>
       </c>
       <c r="BF83" s="39">
-        <f t="shared" si="51"/>
+        <f t="shared" si="48"/>
         <v>3.1922538213263546E-2</v>
       </c>
     </row>
@@ -29646,7 +29114,7 @@
         <v>1236.5100000000002</v>
       </c>
       <c r="T84" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>4131.3</v>
       </c>
       <c r="U84" s="46">
@@ -29676,7 +29144,7 @@
       <c r="AG84" s="74"/>
       <c r="AH84" s="75"/>
       <c r="AI84" s="75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AJ84" s="32"/>
@@ -29686,15 +29154,15 @@
       <c r="AN84" s="33"/>
       <c r="AO84" s="33"/>
       <c r="AP84" s="34">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ84" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AQ84" s="32">
+      <c r="AR84" s="32">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AR84" s="32">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS84" s="32"/>
@@ -29710,64 +29178,64 @@
         <v>4152.76</v>
       </c>
       <c r="BC84" s="45">
-        <f t="shared" si="42"/>
+        <f>+X84</f>
         <v>4199.6000000000004</v>
       </c>
       <c r="BD84" s="45"/>
       <c r="BE84" s="45">
-        <f t="shared" si="50"/>
+        <f t="shared" si="47"/>
         <v>-46.840000000000146</v>
       </c>
       <c r="BF84" s="39">
-        <f t="shared" si="51"/>
+        <f t="shared" si="48"/>
         <v>-1.1279245610148467E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:58" s="91" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A85" s="76">
+    <row r="85" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A85" s="21">
         <f>IF(ISBLANK(F85),"",COUNTA($F$6:F85))</f>
         <v>80</v>
       </c>
-      <c r="B85" s="77" t="s">
+      <c r="B85" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="C85" s="77" t="s">
+      <c r="C85" s="37" t="s">
         <v>61</v>
       </c>
-      <c r="D85" s="78"/>
-      <c r="E85" s="79" t="s">
+      <c r="D85" s="22"/>
+      <c r="E85" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="F85" s="80">
+      <c r="F85" s="36">
         <v>46252</v>
       </c>
-      <c r="G85" s="81" t="s">
+      <c r="G85" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="H85" s="81">
+      <c r="H85" s="24">
         <v>57</v>
       </c>
-      <c r="I85" s="81">
+      <c r="I85" s="24">
         <v>1</v>
       </c>
-      <c r="J85" s="81" t="s">
+      <c r="J85" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="K85" s="82">
+      <c r="K85" s="25">
         <v>162004407</v>
       </c>
-      <c r="L85" s="83">
+      <c r="L85" s="26">
         <v>46253</v>
       </c>
-      <c r="M85" s="84">
+      <c r="M85" s="38">
         <v>46254</v>
       </c>
-      <c r="N85" s="85">
+      <c r="N85" s="52">
         <v>16592</v>
       </c>
-      <c r="O85" s="86"/>
-      <c r="P85" s="86"/>
-      <c r="Q85" s="86"/>
+      <c r="O85" s="27"/>
+      <c r="P85" s="27"/>
+      <c r="Q85" s="27"/>
       <c r="R85" s="46">
         <v>5066.26</v>
       </c>
@@ -29775,7 +29243,7 @@
         <v>1171.8600000000001</v>
       </c>
       <c r="T85" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3894.4</v>
       </c>
       <c r="U85" s="46">
@@ -29805,98 +29273,98 @@
       <c r="AG85" s="74"/>
       <c r="AH85" s="75"/>
       <c r="AI85" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AJ85" s="32"/>
+      <c r="AK85" s="32"/>
+      <c r="AL85" s="32"/>
+      <c r="AM85" s="33"/>
+      <c r="AN85" s="33"/>
+      <c r="AO85" s="33"/>
+      <c r="AP85" s="34">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AJ85" s="87"/>
-      <c r="AK85" s="87"/>
-      <c r="AL85" s="87"/>
-      <c r="AM85" s="88"/>
-      <c r="AN85" s="88"/>
-      <c r="AO85" s="88"/>
-      <c r="AP85" s="89">
+      <c r="AQ85" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AQ85" s="87">
+      <c r="AR85" s="32">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AR85" s="87">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AS85" s="87"/>
-      <c r="AT85" s="87"/>
-      <c r="AU85" s="87"/>
-      <c r="AV85" s="87"/>
-      <c r="AW85" s="87"/>
-      <c r="AX85" s="87"/>
-      <c r="AY85" s="87"/>
-      <c r="AZ85" s="90"/>
-      <c r="BB85" s="92">
+      <c r="AS85" s="32"/>
+      <c r="AT85" s="32"/>
+      <c r="AU85" s="32"/>
+      <c r="AV85" s="32"/>
+      <c r="AW85" s="32"/>
+      <c r="AX85" s="32"/>
+      <c r="AY85" s="32"/>
+      <c r="AZ85" s="35"/>
+      <c r="BB85" s="45">
         <f>IF(AND(AB85="",AC85=""),T85,IF(AC85="",AB85,AC85))</f>
         <v>3894.35</v>
       </c>
-      <c r="BC85" s="92">
-        <f t="shared" si="42"/>
+      <c r="BC85" s="45">
+        <f>+X85</f>
         <v>3755.4</v>
       </c>
-      <c r="BD85" s="92"/>
-      <c r="BE85" s="92">
-        <f t="shared" si="50"/>
+      <c r="BD85" s="45"/>
+      <c r="BE85" s="45">
+        <f t="shared" si="47"/>
         <v>138.94999999999982</v>
       </c>
       <c r="BF85" s="39">
-        <f t="shared" si="51"/>
+        <f t="shared" si="48"/>
         <v>3.5679895232837266E-2</v>
       </c>
     </row>
-    <row r="86" spans="1:58" s="91" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A86" s="76">
+    <row r="86" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A86" s="21">
         <f>IF(ISBLANK(F86),"",COUNTA($F$6:F86))</f>
         <v>81</v>
       </c>
-      <c r="B86" s="77" t="s">
+      <c r="B86" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="C86" s="77" t="s">
+      <c r="C86" s="37" t="s">
         <v>61</v>
       </c>
-      <c r="D86" s="78"/>
-      <c r="E86" s="79" t="s">
+      <c r="D86" s="22"/>
+      <c r="E86" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="F86" s="80">
+      <c r="F86" s="36">
         <v>46253</v>
       </c>
-      <c r="G86" s="81" t="s">
+      <c r="G86" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="H86" s="81">
+      <c r="H86" s="24">
         <v>59</v>
       </c>
-      <c r="I86" s="81">
+      <c r="I86" s="24">
         <v>6</v>
       </c>
-      <c r="J86" s="81" t="s">
+      <c r="J86" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="K86" s="82">
+      <c r="K86" s="25">
         <v>162006452</v>
       </c>
-      <c r="L86" s="83">
+      <c r="L86" s="26">
         <v>46253</v>
       </c>
-      <c r="M86" s="84">
+      <c r="M86" s="38">
         <v>46254</v>
       </c>
-      <c r="N86" s="85">
+      <c r="N86" s="52">
         <v>16593</v>
       </c>
-      <c r="O86" s="86"/>
-      <c r="P86" s="86"/>
-      <c r="Q86" s="86"/>
+      <c r="O86" s="27"/>
+      <c r="P86" s="27"/>
+      <c r="Q86" s="27"/>
       <c r="R86" s="46">
         <v>4811.58</v>
       </c>
@@ -29904,7 +29372,7 @@
         <v>1109.98</v>
       </c>
       <c r="T86" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3701.6</v>
       </c>
       <c r="U86" s="46">
@@ -29913,16 +29381,16 @@
       <c r="V86" s="46"/>
       <c r="W86" s="46"/>
       <c r="X86" s="46">
-        <v>3701.6</v>
+        <v>3674.2</v>
       </c>
       <c r="Y86" s="46"/>
       <c r="Z86" s="46">
         <f>+T86-X86</f>
-        <v>0</v>
+        <v>27.400000000000091</v>
       </c>
       <c r="AA86" s="39">
         <f>Z86/T86</f>
-        <v>0</v>
+        <v>7.4022044521288343E-3</v>
       </c>
       <c r="AB86" s="73">
         <v>3701.55</v>
@@ -29934,98 +29402,98 @@
       <c r="AG86" s="74"/>
       <c r="AH86" s="75"/>
       <c r="AI86" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AJ86" s="32"/>
+      <c r="AK86" s="32"/>
+      <c r="AL86" s="32"/>
+      <c r="AM86" s="33"/>
+      <c r="AN86" s="33"/>
+      <c r="AO86" s="33"/>
+      <c r="AP86" s="34">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AJ86" s="87"/>
-      <c r="AK86" s="87"/>
-      <c r="AL86" s="87"/>
-      <c r="AM86" s="88"/>
-      <c r="AN86" s="88"/>
-      <c r="AO86" s="88"/>
-      <c r="AP86" s="89">
+      <c r="AQ86" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AQ86" s="87">
+      <c r="AR86" s="32">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AR86" s="87">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AS86" s="87"/>
-      <c r="AT86" s="87"/>
-      <c r="AU86" s="87"/>
-      <c r="AV86" s="87"/>
-      <c r="AW86" s="87"/>
-      <c r="AX86" s="87"/>
-      <c r="AY86" s="87"/>
-      <c r="AZ86" s="90"/>
-      <c r="BB86" s="92">
+      <c r="AS86" s="32"/>
+      <c r="AT86" s="32"/>
+      <c r="AU86" s="32"/>
+      <c r="AV86" s="32"/>
+      <c r="AW86" s="32"/>
+      <c r="AX86" s="32"/>
+      <c r="AY86" s="32"/>
+      <c r="AZ86" s="35"/>
+      <c r="BB86" s="45">
         <f>IF(AND(AB86="",AC86=""),T86,IF(AC86="",AB86,AC86))</f>
         <v>3701.55</v>
       </c>
-      <c r="BC86" s="92">
-        <f t="shared" si="42"/>
-        <v>3701.6</v>
-      </c>
-      <c r="BD86" s="92"/>
-      <c r="BE86" s="92">
-        <f t="shared" si="50"/>
-        <v>-4.9999999999727152E-2</v>
+      <c r="BC86" s="45">
+        <f>+X86</f>
+        <v>3674.2</v>
+      </c>
+      <c r="BD86" s="45"/>
+      <c r="BE86" s="45">
+        <f t="shared" si="47"/>
+        <v>27.350000000000364</v>
       </c>
       <c r="BF86" s="39">
-        <f t="shared" si="51"/>
-        <v>-1.3507854817502708E-5</v>
+        <f t="shared" si="48"/>
+        <v>7.3887965852143999E-3</v>
       </c>
     </row>
-    <row r="87" spans="1:58" s="91" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="76">
+    <row r="87" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A87" s="21">
         <f>IF(ISBLANK(F87),"",COUNTA($F$6:F87))</f>
         <v>82</v>
       </c>
-      <c r="B87" s="77" t="s">
+      <c r="B87" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="C87" s="77" t="s">
+      <c r="C87" s="37" t="s">
         <v>61</v>
       </c>
-      <c r="D87" s="78"/>
-      <c r="E87" s="79" t="s">
+      <c r="D87" s="22"/>
+      <c r="E87" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="F87" s="80">
+      <c r="F87" s="36">
         <v>46253</v>
       </c>
-      <c r="G87" s="81" t="s">
+      <c r="G87" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="H87" s="81">
+      <c r="H87" s="24">
         <v>58</v>
       </c>
-      <c r="I87" s="81">
+      <c r="I87" s="24">
         <v>2</v>
       </c>
-      <c r="J87" s="81" t="s">
+      <c r="J87" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="K87" s="82">
+      <c r="K87" s="25">
         <v>162006453</v>
       </c>
-      <c r="L87" s="83">
+      <c r="L87" s="26">
         <v>46254</v>
       </c>
-      <c r="M87" s="84">
+      <c r="M87" s="38">
         <v>46254</v>
       </c>
-      <c r="N87" s="85">
+      <c r="N87" s="52">
         <v>16594</v>
       </c>
-      <c r="O87" s="86"/>
-      <c r="P87" s="86"/>
-      <c r="Q87" s="86"/>
+      <c r="O87" s="27"/>
+      <c r="P87" s="27"/>
+      <c r="Q87" s="27"/>
       <c r="R87" s="46">
         <v>5082.71</v>
       </c>
@@ -30033,7 +29501,7 @@
         <v>1171.9099999999999</v>
       </c>
       <c r="T87" s="46">
-        <f t="shared" ref="T87" si="52">+R87-S87</f>
+        <f t="shared" ref="T87" si="49">+R87-S87</f>
         <v>3910.8</v>
       </c>
       <c r="U87" s="46">
@@ -30063,281 +29531,309 @@
       <c r="AG87" s="74"/>
       <c r="AH87" s="75"/>
       <c r="AI87" s="75">
-        <f t="shared" ref="AI87" si="53">+AG87+AH87</f>
-        <v>0</v>
-      </c>
-      <c r="AJ87" s="87"/>
-      <c r="AK87" s="87"/>
-      <c r="AL87" s="87"/>
-      <c r="AM87" s="88"/>
-      <c r="AN87" s="88"/>
-      <c r="AO87" s="88"/>
-      <c r="AP87" s="89">
-        <f t="shared" ref="AP87" si="54">ROUNDUP((AO87-AM87+(AO87&lt;AM87))*24,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AQ87" s="87">
-        <f t="shared" ref="AQ87" si="55">IF(AP87&gt;5,(AP87-5),0)</f>
-        <v>0</v>
-      </c>
-      <c r="AR87" s="87">
-        <f t="shared" ref="AR87" si="56">+AQ87*8850</f>
-        <v>0</v>
-      </c>
-      <c r="AS87" s="87"/>
-      <c r="AT87" s="87"/>
-      <c r="AU87" s="87"/>
-      <c r="AV87" s="87"/>
-      <c r="AW87" s="87"/>
-      <c r="AX87" s="87"/>
-      <c r="AY87" s="87"/>
-      <c r="AZ87" s="90"/>
-      <c r="BB87" s="92">
+        <f t="shared" ref="AI87" si="50">+AG87+AH87</f>
+        <v>0</v>
+      </c>
+      <c r="AJ87" s="32"/>
+      <c r="AK87" s="32"/>
+      <c r="AL87" s="32"/>
+      <c r="AM87" s="33"/>
+      <c r="AN87" s="33"/>
+      <c r="AO87" s="33"/>
+      <c r="AP87" s="34">
+        <f t="shared" ref="AP87" si="51">ROUNDUP((AO87-AM87+(AO87&lt;AM87))*24,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ87" s="32">
+        <f t="shared" ref="AQ87" si="52">IF(AP87&gt;5,(AP87-5),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AR87" s="32">
+        <f t="shared" ref="AR87" si="53">+AQ87*8850</f>
+        <v>0</v>
+      </c>
+      <c r="AS87" s="32"/>
+      <c r="AT87" s="32"/>
+      <c r="AU87" s="32"/>
+      <c r="AV87" s="32"/>
+      <c r="AW87" s="32"/>
+      <c r="AX87" s="32"/>
+      <c r="AY87" s="32"/>
+      <c r="AZ87" s="35"/>
+      <c r="BB87" s="45">
         <f>IF(AND(AB87="",AC87=""),T87,IF(AC87="",AB87,AC87))</f>
         <v>3910.8</v>
       </c>
-      <c r="BC87" s="92">
-        <f t="shared" si="42"/>
+      <c r="BC87" s="45">
+        <f>+X87</f>
         <v>3805.2</v>
       </c>
-      <c r="BD87" s="92"/>
-      <c r="BE87" s="92">
-        <f t="shared" si="50"/>
+      <c r="BD87" s="45"/>
+      <c r="BE87" s="45">
+        <f t="shared" si="47"/>
         <v>105.60000000000036</v>
       </c>
       <c r="BF87" s="39">
-        <f t="shared" si="51"/>
+        <f t="shared" si="48"/>
         <v>2.7002147898128354E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="53">
+    <row r="88" spans="1:58" s="91" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A88" s="76">
         <f>IF(ISBLANK(F88),"",COUNTA($F$6:F88))</f>
         <v>83</v>
       </c>
-      <c r="B88" s="54" t="s">
+      <c r="B88" s="77" t="s">
         <v>60</v>
       </c>
-      <c r="C88" s="54" t="s">
+      <c r="C88" s="77" t="s">
         <v>61</v>
       </c>
-      <c r="D88" s="55"/>
-      <c r="E88" s="56" t="s">
+      <c r="D88" s="78"/>
+      <c r="E88" s="79" t="s">
         <v>65</v>
       </c>
-      <c r="F88" s="57">
+      <c r="F88" s="80">
         <v>46254</v>
       </c>
-      <c r="G88" s="58" t="s">
+      <c r="G88" s="81" t="s">
         <v>59</v>
       </c>
-      <c r="H88" s="58">
+      <c r="H88" s="81">
         <v>59</v>
       </c>
-      <c r="I88" s="58">
-        <v>0</v>
-      </c>
-      <c r="J88" s="58" t="s">
+      <c r="I88" s="81">
+        <v>0</v>
+      </c>
+      <c r="J88" s="81" t="s">
         <v>67</v>
       </c>
-      <c r="K88" s="59">
+      <c r="K88" s="82">
         <v>162011721</v>
       </c>
-      <c r="L88" s="60">
+      <c r="L88" s="83">
         <v>46254</v>
       </c>
-      <c r="M88" s="61"/>
-      <c r="N88" s="62"/>
-      <c r="O88" s="63"/>
-      <c r="P88" s="63"/>
-      <c r="Q88" s="63"/>
-      <c r="R88" s="64"/>
-      <c r="S88" s="64"/>
-      <c r="T88" s="64">
+      <c r="M88" s="84">
+        <v>46256</v>
+      </c>
+      <c r="N88" s="85">
+        <v>16599</v>
+      </c>
+      <c r="O88" s="86"/>
+      <c r="P88" s="86"/>
+      <c r="Q88" s="86"/>
+      <c r="R88" s="46">
+        <v>5183.7299999999996</v>
+      </c>
+      <c r="S88" s="46">
+        <v>1199.2299999999996</v>
+      </c>
+      <c r="T88" s="46">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U88" s="64"/>
-      <c r="V88" s="64"/>
-      <c r="W88" s="64"/>
-      <c r="X88" s="64"/>
-      <c r="Y88" s="64"/>
-      <c r="Z88" s="64">
+        <v>3984.5</v>
+      </c>
+      <c r="U88" s="46">
+        <v>4010.2</v>
+      </c>
+      <c r="V88" s="46"/>
+      <c r="W88" s="46"/>
+      <c r="X88" s="46">
+        <v>4055.6</v>
+      </c>
+      <c r="Y88" s="46"/>
+      <c r="Z88" s="46">
         <f>+T88-X88</f>
-        <v>0</v>
-      </c>
-      <c r="AA88" s="65" t="e">
+        <v>-71.099999999999909</v>
+      </c>
+      <c r="AA88" s="39">
         <f>Z88/T88</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB88" s="66"/>
-      <c r="AC88" s="66"/>
-      <c r="AD88" s="66"/>
-      <c r="AE88" s="65"/>
-      <c r="AF88" s="67"/>
-      <c r="AG88" s="67"/>
-      <c r="AH88" s="68"/>
-      <c r="AI88" s="68">
+        <v>-1.7844146066005751E-2</v>
+      </c>
+      <c r="AB88" s="73">
+        <v>4007.28</v>
+      </c>
+      <c r="AC88" s="73"/>
+      <c r="AD88" s="73"/>
+      <c r="AE88" s="39"/>
+      <c r="AF88" s="74"/>
+      <c r="AG88" s="74"/>
+      <c r="AH88" s="75"/>
+      <c r="AI88" s="75">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AJ88" s="69"/>
-      <c r="AK88" s="69"/>
-      <c r="AL88" s="69"/>
-      <c r="AM88" s="70"/>
-      <c r="AN88" s="70"/>
-      <c r="AO88" s="70"/>
-      <c r="AP88" s="71">
+      <c r="AJ88" s="87"/>
+      <c r="AK88" s="87"/>
+      <c r="AL88" s="87"/>
+      <c r="AM88" s="88"/>
+      <c r="AN88" s="88"/>
+      <c r="AO88" s="88"/>
+      <c r="AP88" s="89">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AQ88" s="69">
+      <c r="AQ88" s="87">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AR88" s="69">
+      <c r="AR88" s="87">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AS88" s="69"/>
-      <c r="AT88" s="69"/>
-      <c r="AU88" s="69"/>
-      <c r="AV88" s="69"/>
-      <c r="AW88" s="69"/>
-      <c r="AX88" s="69"/>
-      <c r="AY88" s="69"/>
-      <c r="AZ88" s="72"/>
-      <c r="BB88" s="45">
+      <c r="AS88" s="87"/>
+      <c r="AT88" s="87"/>
+      <c r="AU88" s="87"/>
+      <c r="AV88" s="87"/>
+      <c r="AW88" s="87"/>
+      <c r="AX88" s="87"/>
+      <c r="AY88" s="87"/>
+      <c r="AZ88" s="90"/>
+      <c r="BB88" s="92">
         <f>IF(AND(AB88="",AC88=""),T88,IF(AC88="",AB88,AC88))</f>
-        <v>0</v>
-      </c>
-      <c r="BC88" s="45">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="BD88" s="45"/>
-      <c r="BE88" s="45">
-        <f t="shared" ref="BE88:BE96" si="57">+BB88-BC88</f>
-        <v>0</v>
-      </c>
-      <c r="BF88" s="39" t="e">
-        <f t="shared" ref="BF88:BF97" si="58">+BE88/BB88</f>
-        <v>#DIV/0!</v>
+        <v>4007.28</v>
+      </c>
+      <c r="BC88" s="92">
+        <f>+X88</f>
+        <v>4055.6</v>
+      </c>
+      <c r="BD88" s="92"/>
+      <c r="BE88" s="92">
+        <f t="shared" ref="BE88:BE106" si="54">+BB88-BC88</f>
+        <v>-48.319999999999709</v>
+      </c>
+      <c r="BF88" s="39">
+        <f t="shared" ref="BF88:BF107" si="55">+BE88/BB88</f>
+        <v>-1.2058054341099127E-2</v>
       </c>
     </row>
-    <row r="89" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A89" s="53">
+    <row r="89" spans="1:58" s="91" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A89" s="76">
         <f>IF(ISBLANK(F89),"",COUNTA($F$6:F89))</f>
         <v>84</v>
       </c>
-      <c r="B89" s="54" t="s">
+      <c r="B89" s="77" t="s">
         <v>60</v>
       </c>
-      <c r="C89" s="54" t="s">
+      <c r="C89" s="77" t="s">
         <v>61</v>
       </c>
-      <c r="D89" s="55"/>
-      <c r="E89" s="56" t="s">
+      <c r="D89" s="78"/>
+      <c r="E89" s="79" t="s">
         <v>65</v>
       </c>
-      <c r="F89" s="57">
+      <c r="F89" s="80">
         <v>46255</v>
       </c>
-      <c r="G89" s="58" t="s">
+      <c r="G89" s="81" t="s">
         <v>59</v>
       </c>
-      <c r="H89" s="58">
+      <c r="H89" s="81">
         <v>58</v>
       </c>
-      <c r="I89" s="58">
+      <c r="I89" s="81">
         <v>1</v>
       </c>
-      <c r="J89" s="58" t="s">
+      <c r="J89" s="81" t="s">
         <v>67</v>
       </c>
-      <c r="K89" s="59">
+      <c r="K89" s="82">
         <v>162011724</v>
       </c>
-      <c r="L89" s="60">
+      <c r="L89" s="83">
         <v>46256</v>
       </c>
-      <c r="M89" s="61"/>
-      <c r="N89" s="62"/>
-      <c r="O89" s="63"/>
-      <c r="P89" s="63"/>
-      <c r="Q89" s="63"/>
-      <c r="R89" s="64"/>
-      <c r="S89" s="64"/>
-      <c r="T89" s="64">
-        <f t="shared" ref="T89:T95" si="59">+R89-S89</f>
-        <v>0</v>
-      </c>
-      <c r="U89" s="64"/>
-      <c r="V89" s="64"/>
-      <c r="W89" s="64"/>
-      <c r="X89" s="64"/>
-      <c r="Y89" s="64"/>
-      <c r="Z89" s="64">
+      <c r="M89" s="84">
+        <v>46257</v>
+      </c>
+      <c r="N89" s="85">
+        <v>16606</v>
+      </c>
+      <c r="O89" s="86"/>
+      <c r="P89" s="86"/>
+      <c r="Q89" s="86"/>
+      <c r="R89" s="46">
+        <v>4996.3999999999996</v>
+      </c>
+      <c r="S89" s="46">
+        <v>1208.6999999999998</v>
+      </c>
+      <c r="T89" s="46">
+        <f t="shared" ref="T89:T105" si="56">+R89-S89</f>
+        <v>3787.7</v>
+      </c>
+      <c r="U89" s="46">
+        <v>3965.6</v>
+      </c>
+      <c r="V89" s="46"/>
+      <c r="W89" s="46"/>
+      <c r="X89" s="46">
+        <v>3917.2</v>
+      </c>
+      <c r="Y89" s="46"/>
+      <c r="Z89" s="46">
         <f>+T89-X89</f>
-        <v>0</v>
-      </c>
-      <c r="AA89" s="65" t="e">
+        <v>-129.5</v>
+      </c>
+      <c r="AA89" s="39">
         <f>Z89/T89</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB89" s="66"/>
-      <c r="AC89" s="66"/>
-      <c r="AD89" s="66"/>
-      <c r="AE89" s="65"/>
-      <c r="AF89" s="67"/>
-      <c r="AG89" s="67"/>
-      <c r="AH89" s="68"/>
-      <c r="AI89" s="68">
-        <f t="shared" ref="AI89:AI95" si="60">+AG89+AH89</f>
-        <v>0</v>
-      </c>
-      <c r="AJ89" s="69"/>
-      <c r="AK89" s="69"/>
-      <c r="AL89" s="69"/>
-      <c r="AM89" s="70"/>
-      <c r="AN89" s="70"/>
-      <c r="AO89" s="70"/>
-      <c r="AP89" s="71">
-        <f t="shared" ref="AP89:AP95" si="61">ROUNDUP((AO89-AM89+(AO89&lt;AM89))*24,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AQ89" s="69">
-        <f t="shared" ref="AQ89:AQ95" si="62">IF(AP89&gt;5,(AP89-5),0)</f>
-        <v>0</v>
-      </c>
-      <c r="AR89" s="69">
-        <f t="shared" ref="AR89:AR95" si="63">+AQ89*8850</f>
-        <v>0</v>
-      </c>
-      <c r="AS89" s="69"/>
-      <c r="AT89" s="69"/>
-      <c r="AU89" s="69"/>
-      <c r="AV89" s="69"/>
-      <c r="AW89" s="69"/>
-      <c r="AX89" s="69"/>
-      <c r="AY89" s="69"/>
-      <c r="AZ89" s="72"/>
-      <c r="BB89" s="45">
+        <v>-3.4189613749768991E-2</v>
+      </c>
+      <c r="AB89" s="73">
+        <v>3796.25</v>
+      </c>
+      <c r="AC89" s="73"/>
+      <c r="AD89" s="73"/>
+      <c r="AE89" s="39"/>
+      <c r="AF89" s="74"/>
+      <c r="AG89" s="74"/>
+      <c r="AH89" s="75"/>
+      <c r="AI89" s="75">
+        <f t="shared" ref="AI89:AI105" si="57">+AG89+AH89</f>
+        <v>0</v>
+      </c>
+      <c r="AJ89" s="87"/>
+      <c r="AK89" s="87"/>
+      <c r="AL89" s="87"/>
+      <c r="AM89" s="88"/>
+      <c r="AN89" s="88"/>
+      <c r="AO89" s="88"/>
+      <c r="AP89" s="89">
+        <f t="shared" ref="AP89:AP105" si="58">ROUNDUP((AO89-AM89+(AO89&lt;AM89))*24,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ89" s="87">
+        <f t="shared" ref="AQ89:AQ105" si="59">IF(AP89&gt;5,(AP89-5),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AR89" s="87">
+        <f t="shared" ref="AR89:AR105" si="60">+AQ89*8850</f>
+        <v>0</v>
+      </c>
+      <c r="AS89" s="87"/>
+      <c r="AT89" s="87"/>
+      <c r="AU89" s="87"/>
+      <c r="AV89" s="87"/>
+      <c r="AW89" s="87"/>
+      <c r="AX89" s="87"/>
+      <c r="AY89" s="87"/>
+      <c r="AZ89" s="90"/>
+      <c r="BB89" s="92">
         <f>IF(AND(AB89="",AC89=""),T89,IF(AC89="",AB89,AC89))</f>
-        <v>0</v>
-      </c>
-      <c r="BC89" s="45">
-        <f t="shared" ref="BC89:BC95" si="64">+X89</f>
-        <v>0</v>
-      </c>
-      <c r="BD89" s="45"/>
-      <c r="BE89" s="45">
-        <f t="shared" ref="BE89:BE95" si="65">+BB89-BC89</f>
-        <v>0</v>
-      </c>
-      <c r="BF89" s="39" t="e">
-        <f t="shared" ref="BF89:BF95" si="66">+BE89/BB89</f>
-        <v>#DIV/0!</v>
+        <v>3796.25</v>
+      </c>
+      <c r="BC89" s="92">
+        <f>+X89</f>
+        <v>3917.2</v>
+      </c>
+      <c r="BD89" s="92"/>
+      <c r="BE89" s="92">
+        <f t="shared" ref="BE89:BE105" si="61">+BB89-BC89</f>
+        <v>-120.94999999999982</v>
+      </c>
+      <c r="BF89" s="39">
+        <f t="shared" ref="BF89:BF105" si="62">+BE89/BB89</f>
+        <v>-3.1860388541323628E-2</v>
       </c>
     </row>
     <row r="90" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -30384,7 +29880,7 @@
       <c r="R90" s="64"/>
       <c r="S90" s="64"/>
       <c r="T90" s="64">
-        <f t="shared" si="59"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="U90" s="64"/>
@@ -30408,7 +29904,7 @@
       <c r="AG90" s="67"/>
       <c r="AH90" s="68"/>
       <c r="AI90" s="68">
-        <f t="shared" si="60"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="AJ90" s="69"/>
@@ -30418,15 +29914,15 @@
       <c r="AN90" s="70"/>
       <c r="AO90" s="70"/>
       <c r="AP90" s="71">
-        <f t="shared" si="61"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="AQ90" s="69">
-        <f t="shared" si="62"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="AR90" s="69">
-        <f t="shared" si="63"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="AS90" s="69"/>
@@ -30442,993 +29938,2257 @@
         <v>0</v>
       </c>
       <c r="BC90" s="45">
-        <f t="shared" si="64"/>
+        <f>+X90</f>
         <v>0</v>
       </c>
       <c r="BD90" s="45"/>
       <c r="BE90" s="45">
-        <f t="shared" si="65"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="BF90" s="39" t="e">
-        <f t="shared" si="66"/>
+        <f t="shared" si="62"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="91" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A91" s="53">
+    <row r="91" spans="1:58" s="91" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A91" s="76">
         <f>IF(ISBLANK(F91),"",COUNTA($F$6:F91))</f>
         <v>86</v>
       </c>
-      <c r="B91" s="54" t="s">
+      <c r="B91" s="77" t="s">
         <v>60</v>
       </c>
-      <c r="C91" s="54" t="s">
+      <c r="C91" s="77" t="s">
         <v>61</v>
       </c>
-      <c r="D91" s="55"/>
-      <c r="E91" s="56" t="s">
+      <c r="D91" s="78"/>
+      <c r="E91" s="79" t="s">
         <v>63</v>
       </c>
-      <c r="F91" s="57">
+      <c r="F91" s="80">
         <v>46256</v>
       </c>
-      <c r="G91" s="58" t="s">
+      <c r="G91" s="81" t="s">
         <v>59</v>
       </c>
-      <c r="H91" s="58">
+      <c r="H91" s="81">
         <v>58</v>
       </c>
-      <c r="I91" s="58">
-        <v>0</v>
-      </c>
-      <c r="J91" s="58" t="s">
+      <c r="I91" s="81">
+        <v>0</v>
+      </c>
+      <c r="J91" s="81" t="s">
         <v>63</v>
       </c>
-      <c r="K91" s="59">
+      <c r="K91" s="82">
         <v>162006457</v>
       </c>
-      <c r="L91" s="60">
+      <c r="L91" s="83">
         <v>46256</v>
       </c>
-      <c r="M91" s="61"/>
-      <c r="N91" s="62"/>
-      <c r="O91" s="63"/>
-      <c r="P91" s="63"/>
-      <c r="Q91" s="63"/>
-      <c r="R91" s="64"/>
-      <c r="S91" s="64"/>
-      <c r="T91" s="64">
+      <c r="M91" s="84">
+        <v>46258</v>
+      </c>
+      <c r="N91" s="85">
+        <v>16609</v>
+      </c>
+      <c r="O91" s="86"/>
+      <c r="P91" s="86"/>
+      <c r="Q91" s="86"/>
+      <c r="R91" s="46">
+        <v>5260.17</v>
+      </c>
+      <c r="S91" s="46">
+        <v>1212.27</v>
+      </c>
+      <c r="T91" s="46">
+        <f t="shared" si="56"/>
+        <v>4047.9</v>
+      </c>
+      <c r="U91" s="46">
+        <v>4051</v>
+      </c>
+      <c r="V91" s="46"/>
+      <c r="W91" s="46"/>
+      <c r="X91" s="46">
+        <v>4050.4</v>
+      </c>
+      <c r="Y91" s="46"/>
+      <c r="Z91" s="46">
+        <f>+T91-X91</f>
+        <v>-2.5</v>
+      </c>
+      <c r="AA91" s="39">
+        <f>Z91/T91</f>
+        <v>-6.1760418982682375E-4</v>
+      </c>
+      <c r="AB91" s="73">
+        <v>4047.85</v>
+      </c>
+      <c r="AC91" s="73"/>
+      <c r="AD91" s="73"/>
+      <c r="AE91" s="39"/>
+      <c r="AF91" s="74"/>
+      <c r="AG91" s="74"/>
+      <c r="AH91" s="75"/>
+      <c r="AI91" s="75">
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
+      <c r="AJ91" s="87"/>
+      <c r="AK91" s="87"/>
+      <c r="AL91" s="87"/>
+      <c r="AM91" s="88"/>
+      <c r="AN91" s="88"/>
+      <c r="AO91" s="88"/>
+      <c r="AP91" s="89">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="AQ91" s="87">
         <f t="shared" si="59"/>
         <v>0</v>
       </c>
-      <c r="U91" s="64"/>
-      <c r="V91" s="64"/>
-      <c r="W91" s="64"/>
-      <c r="X91" s="64"/>
-      <c r="Y91" s="64"/>
-      <c r="Z91" s="64">
-        <f>+T91-X91</f>
-        <v>0</v>
-      </c>
-      <c r="AA91" s="65" t="e">
-        <f>Z91/T91</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB91" s="66"/>
-      <c r="AC91" s="66"/>
-      <c r="AD91" s="66"/>
-      <c r="AE91" s="65"/>
-      <c r="AF91" s="67"/>
-      <c r="AG91" s="67"/>
-      <c r="AH91" s="68"/>
-      <c r="AI91" s="68">
+      <c r="AR91" s="87">
         <f t="shared" si="60"/>
         <v>0</v>
       </c>
-      <c r="AJ91" s="69"/>
-      <c r="AK91" s="69"/>
-      <c r="AL91" s="69"/>
-      <c r="AM91" s="70"/>
-      <c r="AN91" s="70"/>
-      <c r="AO91" s="70"/>
-      <c r="AP91" s="71">
+      <c r="AS91" s="87"/>
+      <c r="AT91" s="87"/>
+      <c r="AU91" s="87"/>
+      <c r="AV91" s="87"/>
+      <c r="AW91" s="87"/>
+      <c r="AX91" s="87"/>
+      <c r="AY91" s="87"/>
+      <c r="AZ91" s="90"/>
+      <c r="BB91" s="92">
+        <f>IF(AND(AB91="",AC91=""),T91,IF(AC91="",AB91,AC91))</f>
+        <v>4047.85</v>
+      </c>
+      <c r="BC91" s="92">
+        <f>+X91</f>
+        <v>4050.4</v>
+      </c>
+      <c r="BD91" s="92"/>
+      <c r="BE91" s="92">
         <f t="shared" si="61"/>
-        <v>0</v>
-      </c>
-      <c r="AQ91" s="69">
+        <v>-2.5500000000001819</v>
+      </c>
+      <c r="BF91" s="39">
         <f t="shared" si="62"/>
-        <v>0</v>
-      </c>
-      <c r="AR91" s="69">
-        <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="AS91" s="69"/>
-      <c r="AT91" s="69"/>
-      <c r="AU91" s="69"/>
-      <c r="AV91" s="69"/>
-      <c r="AW91" s="69"/>
-      <c r="AX91" s="69"/>
-      <c r="AY91" s="69"/>
-      <c r="AZ91" s="72"/>
-      <c r="BB91" s="45">
-        <f>IF(AND(AB91="",AC91=""),T91,IF(AC91="",AB91,AC91))</f>
-        <v>0</v>
-      </c>
-      <c r="BC91" s="45">
-        <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="BD91" s="45"/>
-      <c r="BE91" s="45">
-        <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="BF91" s="39" t="e">
-        <f t="shared" si="66"/>
-        <v>#DIV/0!</v>
+        <v>-6.2996405499220133E-4</v>
       </c>
     </row>
-    <row r="92" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A92" s="53">
+    <row r="92" spans="1:58" s="91" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A92" s="76">
         <f>IF(ISBLANK(F92),"",COUNTA($F$6:F92))</f>
         <v>87</v>
       </c>
-      <c r="B92" s="54" t="s">
+      <c r="B92" s="77" t="s">
         <v>60</v>
       </c>
-      <c r="C92" s="54" t="s">
+      <c r="C92" s="77" t="s">
         <v>61</v>
       </c>
-      <c r="D92" s="55"/>
-      <c r="E92" s="56" t="s">
+      <c r="D92" s="78"/>
+      <c r="E92" s="79" t="s">
         <v>65</v>
       </c>
-      <c r="F92" s="57">
+      <c r="F92" s="80">
         <v>46256</v>
       </c>
-      <c r="G92" s="58" t="s">
+      <c r="G92" s="81" t="s">
         <v>59</v>
       </c>
-      <c r="H92" s="58">
+      <c r="H92" s="81">
         <v>58</v>
       </c>
-      <c r="I92" s="58">
-        <v>0</v>
-      </c>
-      <c r="J92" s="58" t="s">
+      <c r="I92" s="81">
+        <v>0</v>
+      </c>
+      <c r="J92" s="81" t="s">
         <v>67</v>
       </c>
-      <c r="K92" s="59">
+      <c r="K92" s="82">
         <v>162011726</v>
       </c>
-      <c r="L92" s="60">
+      <c r="L92" s="83">
         <v>46256</v>
       </c>
-      <c r="M92" s="61"/>
-      <c r="N92" s="62"/>
-      <c r="O92" s="63"/>
-      <c r="P92" s="63"/>
-      <c r="Q92" s="63"/>
-      <c r="R92" s="64"/>
-      <c r="S92" s="64"/>
-      <c r="T92" s="64">
+      <c r="M92" s="84">
+        <v>46258</v>
+      </c>
+      <c r="N92" s="85">
+        <v>16610</v>
+      </c>
+      <c r="O92" s="86"/>
+      <c r="P92" s="86"/>
+      <c r="Q92" s="86"/>
+      <c r="R92" s="46">
+        <v>5261.8</v>
+      </c>
+      <c r="S92" s="46">
+        <v>1219.6000000000004</v>
+      </c>
+      <c r="T92" s="46">
+        <f t="shared" si="56"/>
+        <v>4042.2</v>
+      </c>
+      <c r="U92" s="46">
+        <v>4074.2</v>
+      </c>
+      <c r="V92" s="46"/>
+      <c r="W92" s="46"/>
+      <c r="X92" s="46">
+        <v>4037.2</v>
+      </c>
+      <c r="Y92" s="46"/>
+      <c r="Z92" s="46">
+        <f>+T92-X92</f>
+        <v>5</v>
+      </c>
+      <c r="AA92" s="39">
+        <f>Z92/T92</f>
+        <v>1.2369501756469251E-3</v>
+      </c>
+      <c r="AB92" s="73">
+        <v>4046.23</v>
+      </c>
+      <c r="AC92" s="73"/>
+      <c r="AD92" s="73"/>
+      <c r="AE92" s="39"/>
+      <c r="AF92" s="74"/>
+      <c r="AG92" s="74"/>
+      <c r="AH92" s="75"/>
+      <c r="AI92" s="75">
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
+      <c r="AJ92" s="87"/>
+      <c r="AK92" s="87"/>
+      <c r="AL92" s="87"/>
+      <c r="AM92" s="88"/>
+      <c r="AN92" s="88"/>
+      <c r="AO92" s="88"/>
+      <c r="AP92" s="89">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="AQ92" s="87">
         <f t="shared" si="59"/>
         <v>0</v>
       </c>
-      <c r="U92" s="64"/>
-      <c r="V92" s="64"/>
-      <c r="W92" s="64"/>
-      <c r="X92" s="64"/>
-      <c r="Y92" s="64"/>
-      <c r="Z92" s="64">
-        <f>+T92-X92</f>
-        <v>0</v>
-      </c>
-      <c r="AA92" s="65" t="e">
-        <f>Z92/T92</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB92" s="66"/>
-      <c r="AC92" s="66"/>
-      <c r="AD92" s="66"/>
-      <c r="AE92" s="65"/>
-      <c r="AF92" s="67"/>
-      <c r="AG92" s="67"/>
-      <c r="AH92" s="68"/>
-      <c r="AI92" s="68">
+      <c r="AR92" s="87">
         <f t="shared" si="60"/>
         <v>0</v>
       </c>
-      <c r="AJ92" s="69"/>
-      <c r="AK92" s="69"/>
-      <c r="AL92" s="69"/>
-      <c r="AM92" s="70"/>
-      <c r="AN92" s="70"/>
-      <c r="AO92" s="70"/>
-      <c r="AP92" s="71">
+      <c r="AS92" s="87"/>
+      <c r="AT92" s="87"/>
+      <c r="AU92" s="87"/>
+      <c r="AV92" s="87"/>
+      <c r="AW92" s="87"/>
+      <c r="AX92" s="87"/>
+      <c r="AY92" s="87"/>
+      <c r="AZ92" s="90"/>
+      <c r="BB92" s="92">
+        <f>IF(AND(AB92="",AC92=""),T92,IF(AC92="",AB92,AC92))</f>
+        <v>4046.23</v>
+      </c>
+      <c r="BC92" s="92">
+        <f>+X92</f>
+        <v>4037.2</v>
+      </c>
+      <c r="BD92" s="92"/>
+      <c r="BE92" s="92">
         <f t="shared" si="61"/>
-        <v>0</v>
-      </c>
-      <c r="AQ92" s="69">
+        <v>9.0300000000002001</v>
+      </c>
+      <c r="BF92" s="39">
         <f t="shared" si="62"/>
-        <v>0</v>
-      </c>
-      <c r="AR92" s="69">
-        <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="AS92" s="69"/>
-      <c r="AT92" s="69"/>
-      <c r="AU92" s="69"/>
-      <c r="AV92" s="69"/>
-      <c r="AW92" s="69"/>
-      <c r="AX92" s="69"/>
-      <c r="AY92" s="69"/>
-      <c r="AZ92" s="72"/>
-      <c r="BB92" s="45">
-        <f>IF(AND(AB92="",AC92=""),T92,IF(AC92="",AB92,AC92))</f>
-        <v>0</v>
-      </c>
-      <c r="BC92" s="45">
-        <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="BD92" s="45"/>
-      <c r="BE92" s="45">
-        <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="BF92" s="39" t="e">
-        <f t="shared" si="66"/>
-        <v>#DIV/0!</v>
+        <v>2.2317070458180086E-3</v>
       </c>
     </row>
-    <row r="93" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A93" s="53">
+    <row r="93" spans="1:58" s="91" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A93" s="76">
         <f>IF(ISBLANK(F93),"",COUNTA($F$6:F93))</f>
         <v>88</v>
       </c>
-      <c r="B93" s="54" t="s">
+      <c r="B93" s="77" t="s">
         <v>60</v>
       </c>
-      <c r="C93" s="54" t="s">
+      <c r="C93" s="77" t="s">
         <v>61</v>
       </c>
-      <c r="D93" s="55"/>
-      <c r="E93" s="56" t="s">
+      <c r="D93" s="78"/>
+      <c r="E93" s="79" t="s">
         <v>66</v>
       </c>
-      <c r="F93" s="57">
+      <c r="F93" s="80">
         <v>46256</v>
       </c>
-      <c r="G93" s="58" t="s">
+      <c r="G93" s="81" t="s">
         <v>59</v>
       </c>
-      <c r="H93" s="58">
+      <c r="H93" s="81">
         <v>59</v>
       </c>
-      <c r="I93" s="58">
-        <v>0</v>
-      </c>
-      <c r="J93" s="58" t="s">
+      <c r="I93" s="81">
+        <v>0</v>
+      </c>
+      <c r="J93" s="81" t="s">
         <v>66</v>
       </c>
-      <c r="K93" s="59">
+      <c r="K93" s="82">
         <v>162003211</v>
       </c>
-      <c r="L93" s="60">
+      <c r="L93" s="83">
         <v>46257</v>
       </c>
-      <c r="M93" s="61"/>
-      <c r="N93" s="62"/>
-      <c r="O93" s="63"/>
-      <c r="P93" s="63"/>
-      <c r="Q93" s="63"/>
-      <c r="R93" s="64"/>
-      <c r="S93" s="64"/>
-      <c r="T93" s="64">
+      <c r="M93" s="84">
+        <v>46258</v>
+      </c>
+      <c r="N93" s="85">
+        <v>16612</v>
+      </c>
+      <c r="O93" s="86"/>
+      <c r="P93" s="86"/>
+      <c r="Q93" s="86"/>
+      <c r="R93" s="46">
+        <v>5349.67</v>
+      </c>
+      <c r="S93" s="46">
+        <v>1232.4700000000003</v>
+      </c>
+      <c r="T93" s="46">
+        <f t="shared" si="56"/>
+        <v>4117.2</v>
+      </c>
+      <c r="U93" s="46">
+        <v>4117.3999999999996</v>
+      </c>
+      <c r="V93" s="46"/>
+      <c r="W93" s="46"/>
+      <c r="X93" s="46">
+        <v>4023.4</v>
+      </c>
+      <c r="Y93" s="46"/>
+      <c r="Z93" s="46">
+        <f>+T93-X93</f>
+        <v>93.799999999999727</v>
+      </c>
+      <c r="AA93" s="39">
+        <f>Z93/T93</f>
+        <v>2.2782473525697011E-2</v>
+      </c>
+      <c r="AB93" s="73">
+        <v>4117.16</v>
+      </c>
+      <c r="AC93" s="73"/>
+      <c r="AD93" s="73"/>
+      <c r="AE93" s="39"/>
+      <c r="AF93" s="74"/>
+      <c r="AG93" s="74"/>
+      <c r="AH93" s="75"/>
+      <c r="AI93" s="75">
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
+      <c r="AJ93" s="87"/>
+      <c r="AK93" s="87"/>
+      <c r="AL93" s="87"/>
+      <c r="AM93" s="88"/>
+      <c r="AN93" s="88"/>
+      <c r="AO93" s="88"/>
+      <c r="AP93" s="89">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="AQ93" s="87">
         <f t="shared" si="59"/>
         <v>0</v>
       </c>
-      <c r="U93" s="64"/>
-      <c r="V93" s="64"/>
-      <c r="W93" s="64"/>
-      <c r="X93" s="64"/>
-      <c r="Y93" s="64"/>
-      <c r="Z93" s="64">
-        <f>+T93-X93</f>
-        <v>0</v>
-      </c>
-      <c r="AA93" s="65" t="e">
-        <f>Z93/T93</f>
+      <c r="AR93" s="87">
+        <f t="shared" si="60"/>
+        <v>0</v>
+      </c>
+      <c r="AS93" s="87"/>
+      <c r="AT93" s="87"/>
+      <c r="AU93" s="87"/>
+      <c r="AV93" s="87"/>
+      <c r="AW93" s="87"/>
+      <c r="AX93" s="87"/>
+      <c r="AY93" s="87"/>
+      <c r="AZ93" s="90"/>
+      <c r="BB93" s="92">
+        <f>IF(AND(AB93="",AC93=""),T93,IF(AC93="",AB93,AC93))</f>
+        <v>4117.16</v>
+      </c>
+      <c r="BC93" s="92">
+        <f>+X93</f>
+        <v>4023.4</v>
+      </c>
+      <c r="BD93" s="92"/>
+      <c r="BE93" s="92">
+        <f t="shared" si="61"/>
+        <v>93.759999999999764</v>
+      </c>
+      <c r="BF93" s="39">
+        <f t="shared" si="62"/>
+        <v>2.2772979432424238E-2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:58" s="91" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A94" s="76">
+        <f>IF(ISBLANK(F94),"",COUNTA($F$6:F94))</f>
+        <v>89</v>
+      </c>
+      <c r="B94" s="77" t="s">
+        <v>60</v>
+      </c>
+      <c r="C94" s="77" t="s">
+        <v>61</v>
+      </c>
+      <c r="D94" s="78"/>
+      <c r="E94" s="79" t="s">
+        <v>64</v>
+      </c>
+      <c r="F94" s="80">
+        <v>46256</v>
+      </c>
+      <c r="G94" s="81" t="s">
+        <v>59</v>
+      </c>
+      <c r="H94" s="81">
+        <v>58</v>
+      </c>
+      <c r="I94" s="81">
+        <v>4</v>
+      </c>
+      <c r="J94" s="81" t="s">
+        <v>64</v>
+      </c>
+      <c r="K94" s="82">
+        <v>162004413</v>
+      </c>
+      <c r="L94" s="83">
+        <v>46257</v>
+      </c>
+      <c r="M94" s="84">
+        <v>46258</v>
+      </c>
+      <c r="N94" s="85">
+        <v>16613</v>
+      </c>
+      <c r="O94" s="86"/>
+      <c r="P94" s="86"/>
+      <c r="Q94" s="86"/>
+      <c r="R94" s="46">
+        <v>4882.43</v>
+      </c>
+      <c r="S94" s="46">
+        <v>1127.5300000000002</v>
+      </c>
+      <c r="T94" s="46">
+        <f t="shared" si="56"/>
+        <v>3754.9</v>
+      </c>
+      <c r="U94" s="46">
+        <v>3768.4</v>
+      </c>
+      <c r="V94" s="46"/>
+      <c r="W94" s="46"/>
+      <c r="X94" s="46">
+        <v>3746.2</v>
+      </c>
+      <c r="Y94" s="46"/>
+      <c r="Z94" s="46">
+        <f>+T94-X94</f>
+        <v>8.7000000000002728</v>
+      </c>
+      <c r="AA94" s="39">
+        <f>Z94/T94</f>
+        <v>2.3169724892807457E-3</v>
+      </c>
+      <c r="AB94" s="73">
+        <v>3754.85</v>
+      </c>
+      <c r="AC94" s="73"/>
+      <c r="AD94" s="73"/>
+      <c r="AE94" s="39"/>
+      <c r="AF94" s="74"/>
+      <c r="AG94" s="74"/>
+      <c r="AH94" s="75"/>
+      <c r="AI94" s="75">
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
+      <c r="AJ94" s="87"/>
+      <c r="AK94" s="87"/>
+      <c r="AL94" s="87"/>
+      <c r="AM94" s="88"/>
+      <c r="AN94" s="88"/>
+      <c r="AO94" s="88"/>
+      <c r="AP94" s="89">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="AQ94" s="87">
+        <f t="shared" si="59"/>
+        <v>0</v>
+      </c>
+      <c r="AR94" s="87">
+        <f t="shared" si="60"/>
+        <v>0</v>
+      </c>
+      <c r="AS94" s="87"/>
+      <c r="AT94" s="87"/>
+      <c r="AU94" s="87"/>
+      <c r="AV94" s="87"/>
+      <c r="AW94" s="87"/>
+      <c r="AX94" s="87"/>
+      <c r="AY94" s="87"/>
+      <c r="AZ94" s="90"/>
+      <c r="BB94" s="92">
+        <f>IF(AND(AB94="",AC94=""),T94,IF(AC94="",AB94,AC94))</f>
+        <v>3754.85</v>
+      </c>
+      <c r="BC94" s="92">
+        <f>+X94</f>
+        <v>3746.2</v>
+      </c>
+      <c r="BD94" s="92"/>
+      <c r="BE94" s="92">
+        <f t="shared" si="61"/>
+        <v>8.6500000000000909</v>
+      </c>
+      <c r="BF94" s="39">
+        <f t="shared" si="62"/>
+        <v>2.3036872311810301E-3</v>
+      </c>
+    </row>
+    <row r="95" spans="1:58" s="91" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A95" s="76">
+        <f>IF(ISBLANK(F95),"",COUNTA($F$6:F95))</f>
+        <v>90</v>
+      </c>
+      <c r="B95" s="77" t="s">
+        <v>60</v>
+      </c>
+      <c r="C95" s="77" t="s">
+        <v>61</v>
+      </c>
+      <c r="D95" s="78"/>
+      <c r="E95" s="79" t="s">
+        <v>64</v>
+      </c>
+      <c r="F95" s="80">
+        <v>46257</v>
+      </c>
+      <c r="G95" s="81" t="s">
+        <v>59</v>
+      </c>
+      <c r="H95" s="81">
+        <v>59</v>
+      </c>
+      <c r="I95" s="81">
+        <v>0</v>
+      </c>
+      <c r="J95" s="81" t="s">
+        <v>64</v>
+      </c>
+      <c r="K95" s="82">
+        <v>162004415</v>
+      </c>
+      <c r="L95" s="83">
+        <v>46258</v>
+      </c>
+      <c r="M95" s="84">
+        <v>46259</v>
+      </c>
+      <c r="N95" s="85">
+        <v>16615</v>
+      </c>
+      <c r="O95" s="86"/>
+      <c r="P95" s="86"/>
+      <c r="Q95" s="86"/>
+      <c r="R95" s="46">
+        <v>5334.45</v>
+      </c>
+      <c r="S95" s="46">
+        <v>1233.6499999999996</v>
+      </c>
+      <c r="T95" s="46">
+        <f t="shared" ref="T95:T104" si="63">+R95-S95</f>
+        <v>4100.8</v>
+      </c>
+      <c r="U95" s="46">
+        <v>4117.3999999999996</v>
+      </c>
+      <c r="V95" s="46"/>
+      <c r="W95" s="46"/>
+      <c r="X95" s="46">
+        <v>4060.8</v>
+      </c>
+      <c r="Y95" s="46"/>
+      <c r="Z95" s="46">
+        <f>+T95-X95</f>
+        <v>40</v>
+      </c>
+      <c r="AA95" s="39">
+        <f>Z95/T95</f>
+        <v>9.7541943035505257E-3</v>
+      </c>
+      <c r="AB95" s="73">
+        <v>4100.8</v>
+      </c>
+      <c r="AC95" s="73"/>
+      <c r="AD95" s="73"/>
+      <c r="AE95" s="39"/>
+      <c r="AF95" s="74"/>
+      <c r="AG95" s="74"/>
+      <c r="AH95" s="75"/>
+      <c r="AI95" s="75">
+        <f t="shared" ref="AI95:AI104" si="64">+AG95+AH95</f>
+        <v>0</v>
+      </c>
+      <c r="AJ95" s="87"/>
+      <c r="AK95" s="87"/>
+      <c r="AL95" s="87"/>
+      <c r="AM95" s="88"/>
+      <c r="AN95" s="88"/>
+      <c r="AO95" s="88"/>
+      <c r="AP95" s="89">
+        <f t="shared" ref="AP95:AP104" si="65">ROUNDUP((AO95-AM95+(AO95&lt;AM95))*24,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ95" s="87">
+        <f t="shared" ref="AQ95:AQ104" si="66">IF(AP95&gt;5,(AP95-5),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AR95" s="87">
+        <f t="shared" ref="AR95:AR104" si="67">+AQ95*8850</f>
+        <v>0</v>
+      </c>
+      <c r="AS95" s="87"/>
+      <c r="AT95" s="87"/>
+      <c r="AU95" s="87"/>
+      <c r="AV95" s="87"/>
+      <c r="AW95" s="87"/>
+      <c r="AX95" s="87"/>
+      <c r="AY95" s="87"/>
+      <c r="AZ95" s="90"/>
+      <c r="BB95" s="92">
+        <f>IF(AND(AB95="",AC95=""),T95,IF(AC95="",AB95,AC95))</f>
+        <v>4100.8</v>
+      </c>
+      <c r="BC95" s="92">
+        <f>+X95</f>
+        <v>4060.8</v>
+      </c>
+      <c r="BD95" s="92"/>
+      <c r="BE95" s="92">
+        <f t="shared" ref="BE95:BE104" si="68">+BB95-BC95</f>
+        <v>40</v>
+      </c>
+      <c r="BF95" s="39">
+        <f t="shared" ref="BF95:BF104" si="69">+BE95/BB95</f>
+        <v>9.7541943035505257E-3</v>
+      </c>
+    </row>
+    <row r="96" spans="1:58" s="91" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A96" s="76">
+        <f>IF(ISBLANK(F96),"",COUNTA($F$6:F96))</f>
+        <v>91</v>
+      </c>
+      <c r="B96" s="77" t="s">
+        <v>60</v>
+      </c>
+      <c r="C96" s="77" t="s">
+        <v>61</v>
+      </c>
+      <c r="D96" s="78"/>
+      <c r="E96" s="79" t="s">
+        <v>66</v>
+      </c>
+      <c r="F96" s="80">
+        <v>46257</v>
+      </c>
+      <c r="G96" s="81" t="s">
+        <v>59</v>
+      </c>
+      <c r="H96" s="81">
+        <v>58</v>
+      </c>
+      <c r="I96" s="81">
+        <v>7</v>
+      </c>
+      <c r="J96" s="81" t="s">
+        <v>66</v>
+      </c>
+      <c r="K96" s="82">
+        <v>162003213</v>
+      </c>
+      <c r="L96" s="83">
+        <v>46257</v>
+      </c>
+      <c r="M96" s="84">
+        <v>46259</v>
+      </c>
+      <c r="N96" s="85">
+        <v>16619</v>
+      </c>
+      <c r="O96" s="86"/>
+      <c r="P96" s="86"/>
+      <c r="Q96" s="86"/>
+      <c r="R96" s="46">
+        <v>4625.7</v>
+      </c>
+      <c r="S96" s="46">
+        <v>1069.5</v>
+      </c>
+      <c r="T96" s="46">
+        <f t="shared" si="63"/>
+        <v>3556.2</v>
+      </c>
+      <c r="U96" s="46">
+        <v>3556.4</v>
+      </c>
+      <c r="V96" s="46"/>
+      <c r="W96" s="46"/>
+      <c r="X96" s="46">
+        <v>3579.4</v>
+      </c>
+      <c r="Y96" s="46"/>
+      <c r="Z96" s="46">
+        <f>+T96-X96</f>
+        <v>-23.200000000000273</v>
+      </c>
+      <c r="AA96" s="39">
+        <f>Z96/T96</f>
+        <v>-6.5238175580676775E-3</v>
+      </c>
+      <c r="AB96" s="73">
+        <v>3656.72</v>
+      </c>
+      <c r="AC96" s="73"/>
+      <c r="AD96" s="73"/>
+      <c r="AE96" s="39"/>
+      <c r="AF96" s="74"/>
+      <c r="AG96" s="74"/>
+      <c r="AH96" s="75"/>
+      <c r="AI96" s="75">
+        <f t="shared" si="64"/>
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="87"/>
+      <c r="AK96" s="87"/>
+      <c r="AL96" s="87"/>
+      <c r="AM96" s="88"/>
+      <c r="AN96" s="88"/>
+      <c r="AO96" s="88"/>
+      <c r="AP96" s="89">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="AQ96" s="87">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
+      <c r="AR96" s="87">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="AS96" s="87"/>
+      <c r="AT96" s="87"/>
+      <c r="AU96" s="87"/>
+      <c r="AV96" s="87"/>
+      <c r="AW96" s="87"/>
+      <c r="AX96" s="87"/>
+      <c r="AY96" s="87"/>
+      <c r="AZ96" s="90"/>
+      <c r="BB96" s="92">
+        <f>IF(AND(AB96="",AC96=""),T96,IF(AC96="",AB96,AC96))</f>
+        <v>3656.72</v>
+      </c>
+      <c r="BC96" s="92">
+        <f>+X96</f>
+        <v>3579.4</v>
+      </c>
+      <c r="BD96" s="92"/>
+      <c r="BE96" s="92">
+        <f t="shared" si="68"/>
+        <v>77.319999999999709</v>
+      </c>
+      <c r="BF96" s="39">
+        <f t="shared" si="69"/>
+        <v>2.1144632348115172E-2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A97" s="53">
+        <f>IF(ISBLANK(F97),"",COUNTA($F$6:F97))</f>
+        <v>92</v>
+      </c>
+      <c r="B97" s="54" t="s">
+        <v>60</v>
+      </c>
+      <c r="C97" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="D97" s="55"/>
+      <c r="E97" s="56" t="s">
+        <v>63</v>
+      </c>
+      <c r="F97" s="57">
+        <v>46257</v>
+      </c>
+      <c r="G97" s="58" t="s">
+        <v>59</v>
+      </c>
+      <c r="H97" s="58">
+        <v>59</v>
+      </c>
+      <c r="I97" s="58">
+        <v>3</v>
+      </c>
+      <c r="J97" s="58" t="s">
+        <v>63</v>
+      </c>
+      <c r="K97" s="59">
+        <v>162006463</v>
+      </c>
+      <c r="L97" s="60">
+        <v>46258</v>
+      </c>
+      <c r="M97" s="61"/>
+      <c r="N97" s="62"/>
+      <c r="O97" s="63"/>
+      <c r="P97" s="63"/>
+      <c r="Q97" s="63"/>
+      <c r="R97" s="64"/>
+      <c r="S97" s="64"/>
+      <c r="T97" s="64">
+        <f t="shared" si="63"/>
+        <v>0</v>
+      </c>
+      <c r="U97" s="64"/>
+      <c r="V97" s="64"/>
+      <c r="W97" s="64"/>
+      <c r="X97" s="64"/>
+      <c r="Y97" s="64"/>
+      <c r="Z97" s="64">
+        <f>+T97-X97</f>
+        <v>0</v>
+      </c>
+      <c r="AA97" s="65" t="e">
+        <f>Z97/T97</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB93" s="66"/>
-      <c r="AC93" s="66"/>
-      <c r="AD93" s="66"/>
-      <c r="AE93" s="65"/>
-      <c r="AF93" s="67"/>
-      <c r="AG93" s="67"/>
-      <c r="AH93" s="68"/>
-      <c r="AI93" s="68">
+      <c r="AB97" s="66"/>
+      <c r="AC97" s="66"/>
+      <c r="AD97" s="66"/>
+      <c r="AE97" s="65"/>
+      <c r="AF97" s="67"/>
+      <c r="AG97" s="67"/>
+      <c r="AH97" s="68"/>
+      <c r="AI97" s="68">
+        <f t="shared" si="64"/>
+        <v>0</v>
+      </c>
+      <c r="AJ97" s="69"/>
+      <c r="AK97" s="69"/>
+      <c r="AL97" s="69"/>
+      <c r="AM97" s="70"/>
+      <c r="AN97" s="70"/>
+      <c r="AO97" s="70"/>
+      <c r="AP97" s="71">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="AQ97" s="69">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
+      <c r="AR97" s="69">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="AS97" s="69"/>
+      <c r="AT97" s="69"/>
+      <c r="AU97" s="69"/>
+      <c r="AV97" s="69"/>
+      <c r="AW97" s="69"/>
+      <c r="AX97" s="69"/>
+      <c r="AY97" s="69"/>
+      <c r="AZ97" s="72"/>
+      <c r="BB97" s="45">
+        <f>IF(AND(AB97="",AC97=""),T97,IF(AC97="",AB97,AC97))</f>
+        <v>0</v>
+      </c>
+      <c r="BC97" s="45">
+        <f>+X97</f>
+        <v>0</v>
+      </c>
+      <c r="BD97" s="45"/>
+      <c r="BE97" s="45">
+        <f t="shared" si="68"/>
+        <v>0</v>
+      </c>
+      <c r="BF97" s="39" t="e">
+        <f t="shared" si="69"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="98" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A98" s="53">
+        <f>IF(ISBLANK(F98),"",COUNTA($F$6:F98))</f>
+        <v>93</v>
+      </c>
+      <c r="B98" s="54" t="s">
+        <v>60</v>
+      </c>
+      <c r="C98" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="D98" s="55"/>
+      <c r="E98" s="56" t="s">
+        <v>65</v>
+      </c>
+      <c r="F98" s="57">
+        <v>46259</v>
+      </c>
+      <c r="G98" s="58" t="s">
+        <v>59</v>
+      </c>
+      <c r="H98" s="58">
+        <v>58</v>
+      </c>
+      <c r="I98" s="58">
+        <v>3</v>
+      </c>
+      <c r="J98" s="58" t="s">
+        <v>67</v>
+      </c>
+      <c r="K98" s="59">
+        <v>162011729</v>
+      </c>
+      <c r="L98" s="60">
+        <v>46259</v>
+      </c>
+      <c r="M98" s="61"/>
+      <c r="N98" s="62"/>
+      <c r="O98" s="63"/>
+      <c r="P98" s="63"/>
+      <c r="Q98" s="63"/>
+      <c r="R98" s="64"/>
+      <c r="S98" s="64"/>
+      <c r="T98" s="64">
+        <f t="shared" si="63"/>
+        <v>0</v>
+      </c>
+      <c r="U98" s="64"/>
+      <c r="V98" s="64"/>
+      <c r="W98" s="64"/>
+      <c r="X98" s="64"/>
+      <c r="Y98" s="64"/>
+      <c r="Z98" s="64">
+        <f>+T98-X98</f>
+        <v>0</v>
+      </c>
+      <c r="AA98" s="65" t="e">
+        <f>Z98/T98</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB98" s="66"/>
+      <c r="AC98" s="66"/>
+      <c r="AD98" s="66"/>
+      <c r="AE98" s="65"/>
+      <c r="AF98" s="67"/>
+      <c r="AG98" s="67"/>
+      <c r="AH98" s="68"/>
+      <c r="AI98" s="68">
+        <f t="shared" si="64"/>
+        <v>0</v>
+      </c>
+      <c r="AJ98" s="69"/>
+      <c r="AK98" s="69"/>
+      <c r="AL98" s="69"/>
+      <c r="AM98" s="70"/>
+      <c r="AN98" s="70"/>
+      <c r="AO98" s="70"/>
+      <c r="AP98" s="71">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="AQ98" s="69">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
+      <c r="AR98" s="69">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="AS98" s="69"/>
+      <c r="AT98" s="69"/>
+      <c r="AU98" s="69"/>
+      <c r="AV98" s="69"/>
+      <c r="AW98" s="69"/>
+      <c r="AX98" s="69"/>
+      <c r="AY98" s="69"/>
+      <c r="AZ98" s="72"/>
+      <c r="BB98" s="45">
+        <f>IF(AND(AB98="",AC98=""),T98,IF(AC98="",AB98,AC98))</f>
+        <v>0</v>
+      </c>
+      <c r="BC98" s="45">
+        <f>+X98</f>
+        <v>0</v>
+      </c>
+      <c r="BD98" s="45"/>
+      <c r="BE98" s="45">
+        <f t="shared" si="68"/>
+        <v>0</v>
+      </c>
+      <c r="BF98" s="39" t="e">
+        <f t="shared" si="69"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="99" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A99" s="53">
+        <f>IF(ISBLANK(F99),"",COUNTA($F$6:F99))</f>
+        <v>94</v>
+      </c>
+      <c r="B99" s="54" t="s">
+        <v>60</v>
+      </c>
+      <c r="C99" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="D99" s="55"/>
+      <c r="E99" s="56" t="s">
+        <v>66</v>
+      </c>
+      <c r="F99" s="57">
+        <v>46259</v>
+      </c>
+      <c r="G99" s="58" t="s">
+        <v>59</v>
+      </c>
+      <c r="H99" s="58">
+        <v>59</v>
+      </c>
+      <c r="I99" s="58">
+        <v>0</v>
+      </c>
+      <c r="J99" s="58" t="s">
+        <v>66</v>
+      </c>
+      <c r="K99" s="59">
+        <v>162003217</v>
+      </c>
+      <c r="L99" s="60">
+        <v>46259</v>
+      </c>
+      <c r="M99" s="61"/>
+      <c r="N99" s="62"/>
+      <c r="O99" s="63"/>
+      <c r="P99" s="63"/>
+      <c r="Q99" s="63"/>
+      <c r="R99" s="64"/>
+      <c r="S99" s="64"/>
+      <c r="T99" s="64">
+        <f t="shared" si="63"/>
+        <v>0</v>
+      </c>
+      <c r="U99" s="64"/>
+      <c r="V99" s="64"/>
+      <c r="W99" s="64"/>
+      <c r="X99" s="64"/>
+      <c r="Y99" s="64"/>
+      <c r="Z99" s="64">
+        <f>+T99-X99</f>
+        <v>0</v>
+      </c>
+      <c r="AA99" s="65" t="e">
+        <f>Z99/T99</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB99" s="66"/>
+      <c r="AC99" s="66"/>
+      <c r="AD99" s="66"/>
+      <c r="AE99" s="65"/>
+      <c r="AF99" s="67"/>
+      <c r="AG99" s="67"/>
+      <c r="AH99" s="68"/>
+      <c r="AI99" s="68">
+        <f t="shared" si="64"/>
+        <v>0</v>
+      </c>
+      <c r="AJ99" s="69"/>
+      <c r="AK99" s="69"/>
+      <c r="AL99" s="69"/>
+      <c r="AM99" s="70"/>
+      <c r="AN99" s="70"/>
+      <c r="AO99" s="70"/>
+      <c r="AP99" s="71">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="AQ99" s="69">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
+      <c r="AR99" s="69">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="AS99" s="69"/>
+      <c r="AT99" s="69"/>
+      <c r="AU99" s="69"/>
+      <c r="AV99" s="69"/>
+      <c r="AW99" s="69"/>
+      <c r="AX99" s="69"/>
+      <c r="AY99" s="69"/>
+      <c r="AZ99" s="72"/>
+      <c r="BB99" s="45">
+        <f>IF(AND(AB99="",AC99=""),T99,IF(AC99="",AB99,AC99))</f>
+        <v>0</v>
+      </c>
+      <c r="BC99" s="45">
+        <f>+X99</f>
+        <v>0</v>
+      </c>
+      <c r="BD99" s="45"/>
+      <c r="BE99" s="45">
+        <f t="shared" si="68"/>
+        <v>0</v>
+      </c>
+      <c r="BF99" s="39" t="e">
+        <f t="shared" si="69"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="100" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A100" s="53">
+        <f>IF(ISBLANK(F100),"",COUNTA($F$6:F100))</f>
+        <v>95</v>
+      </c>
+      <c r="B100" s="54" t="s">
+        <v>60</v>
+      </c>
+      <c r="C100" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="D100" s="55"/>
+      <c r="E100" s="56" t="s">
+        <v>63</v>
+      </c>
+      <c r="F100" s="57">
+        <v>46260</v>
+      </c>
+      <c r="G100" s="58" t="s">
+        <v>59</v>
+      </c>
+      <c r="H100" s="58">
+        <v>58</v>
+      </c>
+      <c r="I100" s="58">
+        <v>1</v>
+      </c>
+      <c r="J100" s="58" t="s">
+        <v>63</v>
+      </c>
+      <c r="K100" s="59">
+        <v>162006472</v>
+      </c>
+      <c r="L100" s="60">
+        <v>46260</v>
+      </c>
+      <c r="M100" s="61"/>
+      <c r="N100" s="62"/>
+      <c r="O100" s="63"/>
+      <c r="P100" s="63"/>
+      <c r="Q100" s="63"/>
+      <c r="R100" s="64"/>
+      <c r="S100" s="64"/>
+      <c r="T100" s="64">
+        <f t="shared" si="63"/>
+        <v>0</v>
+      </c>
+      <c r="U100" s="64"/>
+      <c r="V100" s="64"/>
+      <c r="W100" s="64"/>
+      <c r="X100" s="64"/>
+      <c r="Y100" s="64"/>
+      <c r="Z100" s="64">
+        <f>+T100-X100</f>
+        <v>0</v>
+      </c>
+      <c r="AA100" s="65" t="e">
+        <f>Z100/T100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB100" s="66"/>
+      <c r="AC100" s="66"/>
+      <c r="AD100" s="66"/>
+      <c r="AE100" s="65"/>
+      <c r="AF100" s="67"/>
+      <c r="AG100" s="67"/>
+      <c r="AH100" s="68"/>
+      <c r="AI100" s="68">
+        <f t="shared" si="64"/>
+        <v>0</v>
+      </c>
+      <c r="AJ100" s="69"/>
+      <c r="AK100" s="69"/>
+      <c r="AL100" s="69"/>
+      <c r="AM100" s="70"/>
+      <c r="AN100" s="70"/>
+      <c r="AO100" s="70"/>
+      <c r="AP100" s="71">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="AQ100" s="69">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
+      <c r="AR100" s="69">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="AS100" s="69"/>
+      <c r="AT100" s="69"/>
+      <c r="AU100" s="69"/>
+      <c r="AV100" s="69"/>
+      <c r="AW100" s="69"/>
+      <c r="AX100" s="69"/>
+      <c r="AY100" s="69"/>
+      <c r="AZ100" s="72"/>
+      <c r="BB100" s="45">
+        <f>IF(AND(AB100="",AC100=""),T100,IF(AC100="",AB100,AC100))</f>
+        <v>0</v>
+      </c>
+      <c r="BC100" s="45">
+        <f>+X100</f>
+        <v>0</v>
+      </c>
+      <c r="BD100" s="45"/>
+      <c r="BE100" s="45">
+        <f t="shared" si="68"/>
+        <v>0</v>
+      </c>
+      <c r="BF100" s="39" t="e">
+        <f t="shared" si="69"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="101" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A101" s="53">
+        <f>IF(ISBLANK(F101),"",COUNTA($F$6:F101))</f>
+        <v>96</v>
+      </c>
+      <c r="B101" s="54" t="s">
+        <v>60</v>
+      </c>
+      <c r="C101" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="D101" s="55"/>
+      <c r="E101" s="56" t="s">
+        <v>66</v>
+      </c>
+      <c r="F101" s="57">
+        <v>46260</v>
+      </c>
+      <c r="G101" s="58" t="s">
+        <v>59</v>
+      </c>
+      <c r="H101" s="58">
+        <v>58</v>
+      </c>
+      <c r="I101" s="58">
+        <v>1</v>
+      </c>
+      <c r="J101" s="58" t="s">
+        <v>66</v>
+      </c>
+      <c r="K101" s="59">
+        <v>162003219</v>
+      </c>
+      <c r="L101" s="60">
+        <v>46260</v>
+      </c>
+      <c r="M101" s="61"/>
+      <c r="N101" s="62"/>
+      <c r="O101" s="63"/>
+      <c r="P101" s="63"/>
+      <c r="Q101" s="63"/>
+      <c r="R101" s="64"/>
+      <c r="S101" s="64"/>
+      <c r="T101" s="64">
+        <f t="shared" si="63"/>
+        <v>0</v>
+      </c>
+      <c r="U101" s="64"/>
+      <c r="V101" s="64"/>
+      <c r="W101" s="64"/>
+      <c r="X101" s="64"/>
+      <c r="Y101" s="64"/>
+      <c r="Z101" s="64">
+        <f>+T101-X101</f>
+        <v>0</v>
+      </c>
+      <c r="AA101" s="65" t="e">
+        <f>Z101/T101</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB101" s="66"/>
+      <c r="AC101" s="66"/>
+      <c r="AD101" s="66"/>
+      <c r="AE101" s="65"/>
+      <c r="AF101" s="67"/>
+      <c r="AG101" s="67"/>
+      <c r="AH101" s="68"/>
+      <c r="AI101" s="68">
+        <f t="shared" si="64"/>
+        <v>0</v>
+      </c>
+      <c r="AJ101" s="69"/>
+      <c r="AK101" s="69"/>
+      <c r="AL101" s="69"/>
+      <c r="AM101" s="70"/>
+      <c r="AN101" s="70"/>
+      <c r="AO101" s="70"/>
+      <c r="AP101" s="71">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="AQ101" s="69">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
+      <c r="AR101" s="69">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="AS101" s="69"/>
+      <c r="AT101" s="69"/>
+      <c r="AU101" s="69"/>
+      <c r="AV101" s="69"/>
+      <c r="AW101" s="69"/>
+      <c r="AX101" s="69"/>
+      <c r="AY101" s="69"/>
+      <c r="AZ101" s="72"/>
+      <c r="BB101" s="45">
+        <f>IF(AND(AB101="",AC101=""),T101,IF(AC101="",AB101,AC101))</f>
+        <v>0</v>
+      </c>
+      <c r="BC101" s="45">
+        <f>+X101</f>
+        <v>0</v>
+      </c>
+      <c r="BD101" s="45"/>
+      <c r="BE101" s="45">
+        <f t="shared" si="68"/>
+        <v>0</v>
+      </c>
+      <c r="BF101" s="39" t="e">
+        <f t="shared" si="69"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="102" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A102" s="53">
+        <f>IF(ISBLANK(F102),"",COUNTA($F$6:F102))</f>
+        <v>97</v>
+      </c>
+      <c r="B102" s="54" t="s">
+        <v>60</v>
+      </c>
+      <c r="C102" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="D102" s="55"/>
+      <c r="E102" s="56" t="s">
+        <v>65</v>
+      </c>
+      <c r="F102" s="57">
+        <v>46260</v>
+      </c>
+      <c r="G102" s="58" t="s">
+        <v>59</v>
+      </c>
+      <c r="H102" s="58">
+        <v>58</v>
+      </c>
+      <c r="I102" s="58">
+        <v>2</v>
+      </c>
+      <c r="J102" s="58" t="s">
+        <v>67</v>
+      </c>
+      <c r="K102" s="59">
+        <v>162011731</v>
+      </c>
+      <c r="L102" s="60">
+        <v>46260</v>
+      </c>
+      <c r="M102" s="61"/>
+      <c r="N102" s="62"/>
+      <c r="O102" s="63"/>
+      <c r="P102" s="63"/>
+      <c r="Q102" s="63"/>
+      <c r="R102" s="64"/>
+      <c r="S102" s="64"/>
+      <c r="T102" s="64">
+        <f t="shared" si="63"/>
+        <v>0</v>
+      </c>
+      <c r="U102" s="64"/>
+      <c r="V102" s="64"/>
+      <c r="W102" s="64"/>
+      <c r="X102" s="64"/>
+      <c r="Y102" s="64"/>
+      <c r="Z102" s="64">
+        <f>+T102-X102</f>
+        <v>0</v>
+      </c>
+      <c r="AA102" s="65" t="e">
+        <f>Z102/T102</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB102" s="66"/>
+      <c r="AC102" s="66"/>
+      <c r="AD102" s="66"/>
+      <c r="AE102" s="65"/>
+      <c r="AF102" s="67"/>
+      <c r="AG102" s="67"/>
+      <c r="AH102" s="68"/>
+      <c r="AI102" s="68">
+        <f t="shared" si="64"/>
+        <v>0</v>
+      </c>
+      <c r="AJ102" s="69"/>
+      <c r="AK102" s="69"/>
+      <c r="AL102" s="69"/>
+      <c r="AM102" s="70"/>
+      <c r="AN102" s="70"/>
+      <c r="AO102" s="70"/>
+      <c r="AP102" s="71">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="AQ102" s="69">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
+      <c r="AR102" s="69">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="AS102" s="69"/>
+      <c r="AT102" s="69"/>
+      <c r="AU102" s="69"/>
+      <c r="AV102" s="69"/>
+      <c r="AW102" s="69"/>
+      <c r="AX102" s="69"/>
+      <c r="AY102" s="69"/>
+      <c r="AZ102" s="72"/>
+      <c r="BB102" s="45">
+        <f>IF(AND(AB102="",AC102=""),T102,IF(AC102="",AB102,AC102))</f>
+        <v>0</v>
+      </c>
+      <c r="BC102" s="45">
+        <f>+X102</f>
+        <v>0</v>
+      </c>
+      <c r="BD102" s="45"/>
+      <c r="BE102" s="45">
+        <f t="shared" si="68"/>
+        <v>0</v>
+      </c>
+      <c r="BF102" s="39" t="e">
+        <f t="shared" si="69"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="103" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A103" s="21" t="str">
+        <f>IF(ISBLANK(F103),"",COUNTA($F$6:F103))</f>
+        <v/>
+      </c>
+      <c r="B103" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="C103" s="37" t="s">
+        <v>61</v>
+      </c>
+      <c r="D103" s="22"/>
+      <c r="E103" s="23"/>
+      <c r="F103" s="36"/>
+      <c r="G103" s="24"/>
+      <c r="H103" s="24"/>
+      <c r="I103" s="24"/>
+      <c r="J103" s="24"/>
+      <c r="K103" s="25"/>
+      <c r="L103" s="26"/>
+      <c r="M103" s="38"/>
+      <c r="N103" s="52"/>
+      <c r="O103" s="27"/>
+      <c r="P103" s="27"/>
+      <c r="Q103" s="27"/>
+      <c r="R103" s="28"/>
+      <c r="S103" s="28"/>
+      <c r="T103" s="46">
+        <f t="shared" si="63"/>
+        <v>0</v>
+      </c>
+      <c r="U103" s="28"/>
+      <c r="V103" s="28"/>
+      <c r="W103" s="28"/>
+      <c r="X103" s="28"/>
+      <c r="Y103" s="28"/>
+      <c r="Z103" s="28">
+        <f>+T103-X103</f>
+        <v>0</v>
+      </c>
+      <c r="AA103" s="29" t="e">
+        <f>Z103/T103</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB103" s="40"/>
+      <c r="AC103" s="40"/>
+      <c r="AD103" s="40"/>
+      <c r="AE103" s="29"/>
+      <c r="AF103" s="30"/>
+      <c r="AG103" s="30"/>
+      <c r="AH103" s="31"/>
+      <c r="AI103" s="31">
+        <f t="shared" si="64"/>
+        <v>0</v>
+      </c>
+      <c r="AJ103" s="32"/>
+      <c r="AK103" s="32"/>
+      <c r="AL103" s="32"/>
+      <c r="AM103" s="33"/>
+      <c r="AN103" s="33"/>
+      <c r="AO103" s="33"/>
+      <c r="AP103" s="34">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="AQ103" s="32">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
+      <c r="AR103" s="32">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="AS103" s="32"/>
+      <c r="AT103" s="32"/>
+      <c r="AU103" s="32"/>
+      <c r="AV103" s="32"/>
+      <c r="AW103" s="32"/>
+      <c r="AX103" s="32"/>
+      <c r="AY103" s="32"/>
+      <c r="AZ103" s="35"/>
+      <c r="BB103" s="45">
+        <f>IF(AND(AB103="",AC103=""),T103,IF(AC103="",AB103,AC103))</f>
+        <v>0</v>
+      </c>
+      <c r="BC103" s="45">
+        <f>+X103</f>
+        <v>0</v>
+      </c>
+      <c r="BD103" s="45"/>
+      <c r="BE103" s="45">
+        <f t="shared" si="68"/>
+        <v>0</v>
+      </c>
+      <c r="BF103" s="39" t="e">
+        <f t="shared" si="69"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="104" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A104" s="21" t="str">
+        <f>IF(ISBLANK(F104),"",COUNTA($F$6:F104))</f>
+        <v/>
+      </c>
+      <c r="B104" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="C104" s="37" t="s">
+        <v>61</v>
+      </c>
+      <c r="D104" s="22"/>
+      <c r="E104" s="23"/>
+      <c r="F104" s="36"/>
+      <c r="G104" s="24"/>
+      <c r="H104" s="24"/>
+      <c r="I104" s="24"/>
+      <c r="J104" s="24"/>
+      <c r="K104" s="25"/>
+      <c r="L104" s="26"/>
+      <c r="M104" s="38"/>
+      <c r="N104" s="52"/>
+      <c r="O104" s="27"/>
+      <c r="P104" s="27"/>
+      <c r="Q104" s="27"/>
+      <c r="R104" s="28"/>
+      <c r="S104" s="28"/>
+      <c r="T104" s="46">
+        <f t="shared" si="63"/>
+        <v>0</v>
+      </c>
+      <c r="U104" s="28"/>
+      <c r="V104" s="28"/>
+      <c r="W104" s="28"/>
+      <c r="X104" s="28"/>
+      <c r="Y104" s="28"/>
+      <c r="Z104" s="28">
+        <f>+T104-X104</f>
+        <v>0</v>
+      </c>
+      <c r="AA104" s="29" t="e">
+        <f>Z104/T104</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB104" s="40"/>
+      <c r="AC104" s="40"/>
+      <c r="AD104" s="40"/>
+      <c r="AE104" s="29"/>
+      <c r="AF104" s="30"/>
+      <c r="AG104" s="30"/>
+      <c r="AH104" s="31"/>
+      <c r="AI104" s="31">
+        <f t="shared" si="64"/>
+        <v>0</v>
+      </c>
+      <c r="AJ104" s="32"/>
+      <c r="AK104" s="32"/>
+      <c r="AL104" s="32"/>
+      <c r="AM104" s="33"/>
+      <c r="AN104" s="33"/>
+      <c r="AO104" s="33"/>
+      <c r="AP104" s="34">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="AQ104" s="32">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
+      <c r="AR104" s="32">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="AS104" s="32"/>
+      <c r="AT104" s="32"/>
+      <c r="AU104" s="32"/>
+      <c r="AV104" s="32"/>
+      <c r="AW104" s="32"/>
+      <c r="AX104" s="32"/>
+      <c r="AY104" s="32"/>
+      <c r="AZ104" s="35"/>
+      <c r="BB104" s="45">
+        <f>IF(AND(AB104="",AC104=""),T104,IF(AC104="",AB104,AC104))</f>
+        <v>0</v>
+      </c>
+      <c r="BC104" s="45">
+        <f>+X104</f>
+        <v>0</v>
+      </c>
+      <c r="BD104" s="45"/>
+      <c r="BE104" s="45">
+        <f t="shared" si="68"/>
+        <v>0</v>
+      </c>
+      <c r="BF104" s="39" t="e">
+        <f t="shared" si="69"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="105" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A105" s="21" t="str">
+        <f>IF(ISBLANK(F105),"",COUNTA($F$6:F105))</f>
+        <v/>
+      </c>
+      <c r="B105" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="C105" s="37" t="s">
+        <v>61</v>
+      </c>
+      <c r="D105" s="22"/>
+      <c r="E105" s="23"/>
+      <c r="F105" s="36"/>
+      <c r="G105" s="24"/>
+      <c r="H105" s="24"/>
+      <c r="I105" s="24"/>
+      <c r="J105" s="24"/>
+      <c r="K105" s="25"/>
+      <c r="L105" s="26"/>
+      <c r="M105" s="38"/>
+      <c r="N105" s="52"/>
+      <c r="O105" s="27"/>
+      <c r="P105" s="27"/>
+      <c r="Q105" s="27"/>
+      <c r="R105" s="28"/>
+      <c r="S105" s="28"/>
+      <c r="T105" s="46">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
+      <c r="U105" s="28"/>
+      <c r="V105" s="28"/>
+      <c r="W105" s="28"/>
+      <c r="X105" s="28"/>
+      <c r="Y105" s="28"/>
+      <c r="Z105" s="28">
+        <f>+T105-X105</f>
+        <v>0</v>
+      </c>
+      <c r="AA105" s="29" t="e">
+        <f>Z105/T105</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB105" s="40"/>
+      <c r="AC105" s="40"/>
+      <c r="AD105" s="40"/>
+      <c r="AE105" s="29"/>
+      <c r="AF105" s="30"/>
+      <c r="AG105" s="30"/>
+      <c r="AH105" s="31"/>
+      <c r="AI105" s="31">
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
+      <c r="AJ105" s="32"/>
+      <c r="AK105" s="32"/>
+      <c r="AL105" s="32"/>
+      <c r="AM105" s="33"/>
+      <c r="AN105" s="33"/>
+      <c r="AO105" s="33"/>
+      <c r="AP105" s="34">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="AQ105" s="32">
+        <f t="shared" si="59"/>
+        <v>0</v>
+      </c>
+      <c r="AR105" s="32">
         <f t="shared" si="60"/>
         <v>0</v>
       </c>
-      <c r="AJ93" s="69"/>
-      <c r="AK93" s="69"/>
-      <c r="AL93" s="69"/>
-      <c r="AM93" s="70"/>
-      <c r="AN93" s="70"/>
-      <c r="AO93" s="70"/>
-      <c r="AP93" s="71">
+      <c r="AS105" s="32"/>
+      <c r="AT105" s="32"/>
+      <c r="AU105" s="32"/>
+      <c r="AV105" s="32"/>
+      <c r="AW105" s="32"/>
+      <c r="AX105" s="32"/>
+      <c r="AY105" s="32"/>
+      <c r="AZ105" s="35"/>
+      <c r="BB105" s="45">
+        <f>IF(AND(AB105="",AC105=""),T105,IF(AC105="",AB105,AC105))</f>
+        <v>0</v>
+      </c>
+      <c r="BC105" s="45">
+        <f>+X105</f>
+        <v>0</v>
+      </c>
+      <c r="BD105" s="45"/>
+      <c r="BE105" s="45">
         <f t="shared" si="61"/>
         <v>0</v>
       </c>
-      <c r="AQ93" s="69">
+      <c r="BF105" s="39" t="e">
         <f t="shared" si="62"/>
-        <v>0</v>
-      </c>
-      <c r="AR93" s="69">
-        <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="AS93" s="69"/>
-      <c r="AT93" s="69"/>
-      <c r="AU93" s="69"/>
-      <c r="AV93" s="69"/>
-      <c r="AW93" s="69"/>
-      <c r="AX93" s="69"/>
-      <c r="AY93" s="69"/>
-      <c r="AZ93" s="72"/>
-      <c r="BB93" s="45">
-        <f>IF(AND(AB93="",AC93=""),T93,IF(AC93="",AB93,AC93))</f>
-        <v>0</v>
-      </c>
-      <c r="BC93" s="45">
-        <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="BD93" s="45"/>
-      <c r="BE93" s="45">
-        <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="BF93" s="39" t="e">
-        <f t="shared" si="66"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="94" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A94" s="21" t="str">
-        <f>IF(ISBLANK(F94),"",COUNTA($F$6:F94))</f>
+    <row r="106" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A106" s="21" t="str">
+        <f>IF(ISBLANK(F106),"",COUNTA($F$6:F106))</f>
         <v/>
       </c>
-      <c r="B94" s="37" t="s">
+      <c r="B106" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="C94" s="37" t="s">
+      <c r="C106" s="37" t="s">
         <v>61</v>
       </c>
-      <c r="D94" s="22"/>
-      <c r="E94" s="23"/>
-      <c r="F94" s="36"/>
-      <c r="G94" s="24"/>
-      <c r="H94" s="24"/>
-      <c r="I94" s="24"/>
-      <c r="J94" s="24"/>
-      <c r="K94" s="25"/>
-      <c r="L94" s="26"/>
-      <c r="M94" s="38"/>
-      <c r="N94" s="52"/>
-      <c r="O94" s="27"/>
-      <c r="P94" s="27"/>
-      <c r="Q94" s="27"/>
-      <c r="R94" s="28"/>
-      <c r="S94" s="28"/>
-      <c r="T94" s="46">
-        <f t="shared" si="59"/>
-        <v>0</v>
-      </c>
-      <c r="U94" s="28"/>
-      <c r="V94" s="28"/>
-      <c r="W94" s="28"/>
-      <c r="X94" s="28"/>
-      <c r="Y94" s="28"/>
-      <c r="Z94" s="28">
-        <f>+T94-X94</f>
-        <v>0</v>
-      </c>
-      <c r="AA94" s="29" t="e">
-        <f>Z94/T94</f>
+      <c r="D106" s="22"/>
+      <c r="E106" s="23"/>
+      <c r="F106" s="36"/>
+      <c r="G106" s="24"/>
+      <c r="H106" s="24"/>
+      <c r="I106" s="24"/>
+      <c r="J106" s="24"/>
+      <c r="K106" s="25"/>
+      <c r="L106" s="26"/>
+      <c r="M106" s="38"/>
+      <c r="N106" s="52"/>
+      <c r="O106" s="27"/>
+      <c r="P106" s="27"/>
+      <c r="Q106" s="27"/>
+      <c r="R106" s="28"/>
+      <c r="S106" s="28"/>
+      <c r="T106" s="46">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U106" s="28"/>
+      <c r="V106" s="28"/>
+      <c r="W106" s="28"/>
+      <c r="X106" s="28"/>
+      <c r="Y106" s="28"/>
+      <c r="Z106" s="28">
+        <f>+T106-X106</f>
+        <v>0</v>
+      </c>
+      <c r="AA106" s="29" t="e">
+        <f>Z106/T106</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB94" s="40"/>
-      <c r="AC94" s="40"/>
-      <c r="AD94" s="40"/>
-      <c r="AE94" s="29"/>
-      <c r="AF94" s="30"/>
-      <c r="AG94" s="30"/>
-      <c r="AH94" s="31"/>
-      <c r="AI94" s="31">
-        <f t="shared" si="60"/>
-        <v>0</v>
-      </c>
-      <c r="AJ94" s="32"/>
-      <c r="AK94" s="32"/>
-      <c r="AL94" s="32"/>
-      <c r="AM94" s="33"/>
-      <c r="AN94" s="33"/>
-      <c r="AO94" s="33"/>
-      <c r="AP94" s="34">
-        <f t="shared" si="61"/>
-        <v>0</v>
-      </c>
-      <c r="AQ94" s="32">
-        <f t="shared" si="62"/>
-        <v>0</v>
-      </c>
-      <c r="AR94" s="32">
-        <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="AS94" s="32"/>
-      <c r="AT94" s="32"/>
-      <c r="AU94" s="32"/>
-      <c r="AV94" s="32"/>
-      <c r="AW94" s="32"/>
-      <c r="AX94" s="32"/>
-      <c r="AY94" s="32"/>
-      <c r="AZ94" s="35"/>
-      <c r="BB94" s="45">
-        <f>IF(AND(AB94="",AC94=""),T94,IF(AC94="",AB94,AC94))</f>
-        <v>0</v>
-      </c>
-      <c r="BC94" s="45">
-        <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="BD94" s="45"/>
-      <c r="BE94" s="45">
-        <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="BF94" s="39" t="e">
-        <f t="shared" si="66"/>
+      <c r="AB106" s="40"/>
+      <c r="AC106" s="40"/>
+      <c r="AD106" s="40"/>
+      <c r="AE106" s="29"/>
+      <c r="AF106" s="30"/>
+      <c r="AG106" s="30"/>
+      <c r="AH106" s="31"/>
+      <c r="AI106" s="31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ106" s="32"/>
+      <c r="AK106" s="32"/>
+      <c r="AL106" s="32"/>
+      <c r="AM106" s="33"/>
+      <c r="AN106" s="33"/>
+      <c r="AO106" s="33"/>
+      <c r="AP106" s="34">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AQ106" s="32">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AR106" s="32">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AS106" s="32"/>
+      <c r="AT106" s="32"/>
+      <c r="AU106" s="32"/>
+      <c r="AV106" s="32"/>
+      <c r="AW106" s="32"/>
+      <c r="AX106" s="32"/>
+      <c r="AY106" s="32"/>
+      <c r="AZ106" s="35"/>
+      <c r="BB106" s="45">
+        <f>IF(AND(AB106="",AC106=""),T106,IF(AC106="",AB106,AC106))</f>
+        <v>0</v>
+      </c>
+      <c r="BC106" s="45">
+        <f>+X106</f>
+        <v>0</v>
+      </c>
+      <c r="BD106" s="45"/>
+      <c r="BE106" s="45">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="BF106" s="39" t="e">
+        <f t="shared" si="55"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="95" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A95" s="21" t="str">
-        <f>IF(ISBLANK(F95),"",COUNTA($F$6:F95))</f>
-        <v/>
-      </c>
-      <c r="B95" s="37" t="s">
-        <v>60</v>
-      </c>
-      <c r="C95" s="37" t="s">
-        <v>61</v>
-      </c>
-      <c r="D95" s="22"/>
-      <c r="E95" s="23"/>
-      <c r="F95" s="36"/>
-      <c r="G95" s="24"/>
-      <c r="H95" s="24"/>
-      <c r="I95" s="24"/>
-      <c r="J95" s="24"/>
-      <c r="K95" s="25"/>
-      <c r="L95" s="26"/>
-      <c r="M95" s="38"/>
-      <c r="N95" s="52"/>
-      <c r="O95" s="27"/>
-      <c r="P95" s="27"/>
-      <c r="Q95" s="27"/>
-      <c r="R95" s="28"/>
-      <c r="S95" s="28"/>
-      <c r="T95" s="46">
-        <f t="shared" si="59"/>
-        <v>0</v>
-      </c>
-      <c r="U95" s="28"/>
-      <c r="V95" s="28"/>
-      <c r="W95" s="28"/>
-      <c r="X95" s="28"/>
-      <c r="Y95" s="28"/>
-      <c r="Z95" s="28">
-        <f>+T95-X95</f>
-        <v>0</v>
-      </c>
-      <c r="AA95" s="29" t="e">
-        <f>Z95/T95</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB95" s="40"/>
-      <c r="AC95" s="40"/>
-      <c r="AD95" s="40"/>
-      <c r="AE95" s="29"/>
-      <c r="AF95" s="30"/>
-      <c r="AG95" s="30"/>
-      <c r="AH95" s="31"/>
-      <c r="AI95" s="31">
-        <f t="shared" si="60"/>
-        <v>0</v>
-      </c>
-      <c r="AJ95" s="32"/>
-      <c r="AK95" s="32"/>
-      <c r="AL95" s="32"/>
-      <c r="AM95" s="33"/>
-      <c r="AN95" s="33"/>
-      <c r="AO95" s="33"/>
-      <c r="AP95" s="34">
-        <f t="shared" si="61"/>
-        <v>0</v>
-      </c>
-      <c r="AQ95" s="32">
-        <f t="shared" si="62"/>
-        <v>0</v>
-      </c>
-      <c r="AR95" s="32">
-        <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="AS95" s="32"/>
-      <c r="AT95" s="32"/>
-      <c r="AU95" s="32"/>
-      <c r="AV95" s="32"/>
-      <c r="AW95" s="32"/>
-      <c r="AX95" s="32"/>
-      <c r="AY95" s="32"/>
-      <c r="AZ95" s="35"/>
-      <c r="BB95" s="45">
-        <f>IF(AND(AB95="",AC95=""),T95,IF(AC95="",AB95,AC95))</f>
-        <v>0</v>
-      </c>
-      <c r="BC95" s="45">
-        <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="BD95" s="45"/>
-      <c r="BE95" s="45">
-        <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="BF95" s="39" t="e">
-        <f t="shared" si="66"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="96" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A96" s="21" t="str">
-        <f>IF(ISBLANK(F96),"",COUNTA($F$6:F96))</f>
-        <v/>
-      </c>
-      <c r="B96" s="37" t="s">
-        <v>60</v>
-      </c>
-      <c r="C96" s="37" t="s">
-        <v>61</v>
-      </c>
-      <c r="D96" s="22"/>
-      <c r="E96" s="23"/>
-      <c r="F96" s="36"/>
-      <c r="G96" s="24"/>
-      <c r="H96" s="24"/>
-      <c r="I96" s="24"/>
-      <c r="J96" s="24"/>
-      <c r="K96" s="25"/>
-      <c r="L96" s="26"/>
-      <c r="M96" s="38"/>
-      <c r="N96" s="52"/>
-      <c r="O96" s="27"/>
-      <c r="P96" s="27"/>
-      <c r="Q96" s="27"/>
-      <c r="R96" s="28"/>
-      <c r="S96" s="28"/>
-      <c r="T96" s="46">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U96" s="28"/>
-      <c r="V96" s="28"/>
-      <c r="W96" s="28"/>
-      <c r="X96" s="28"/>
-      <c r="Y96" s="28"/>
-      <c r="Z96" s="28">
-        <f>+T96-X96</f>
-        <v>0</v>
-      </c>
-      <c r="AA96" s="29" t="e">
-        <f>Z96/T96</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB96" s="40"/>
-      <c r="AC96" s="40"/>
-      <c r="AD96" s="40"/>
-      <c r="AE96" s="29"/>
-      <c r="AF96" s="30"/>
-      <c r="AG96" s="30"/>
-      <c r="AH96" s="31"/>
-      <c r="AI96" s="31">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AJ96" s="32"/>
-      <c r="AK96" s="32"/>
-      <c r="AL96" s="32"/>
-      <c r="AM96" s="33"/>
-      <c r="AN96" s="33"/>
-      <c r="AO96" s="33"/>
-      <c r="AP96" s="34">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AQ96" s="32">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AR96" s="32">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AS96" s="32"/>
-      <c r="AT96" s="32"/>
-      <c r="AU96" s="32"/>
-      <c r="AV96" s="32"/>
-      <c r="AW96" s="32"/>
-      <c r="AX96" s="32"/>
-      <c r="AY96" s="32"/>
-      <c r="AZ96" s="35"/>
-      <c r="BB96" s="45">
-        <f>IF(AND(AB96="",AC96=""),T96,IF(AC96="",AB96,AC96))</f>
-        <v>0</v>
-      </c>
-      <c r="BC96" s="45">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="BD96" s="45"/>
-      <c r="BE96" s="45">
-        <f t="shared" si="57"/>
-        <v>0</v>
-      </c>
-      <c r="BF96" s="39" t="e">
-        <f t="shared" si="58"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="97" spans="1:58" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="9">
-        <f>+COUNT(A6:A96)</f>
-        <v>88</v>
-      </c>
-      <c r="B97" s="10">
-        <f>+COUNTIF(X6:X96,"&gt;0")</f>
-        <v>82</v>
-      </c>
-      <c r="C97" s="10"/>
-      <c r="D97" s="10"/>
-      <c r="E97" s="10"/>
-      <c r="F97" s="10"/>
-      <c r="G97" s="10"/>
-      <c r="H97" s="10"/>
-      <c r="I97" s="10"/>
-      <c r="J97" s="10"/>
-      <c r="K97" s="10"/>
-      <c r="L97" s="11"/>
-      <c r="M97" s="10"/>
-      <c r="N97" s="10"/>
-      <c r="O97" s="10"/>
-      <c r="P97" s="10"/>
-      <c r="Q97" s="10"/>
-      <c r="R97" s="12">
-        <f t="shared" ref="R97:Y97" si="67">SUM(R6:R96)</f>
-        <v>411199.76999999996</v>
-      </c>
-      <c r="S97" s="12">
-        <f t="shared" si="67"/>
-        <v>95997.169999999984</v>
-      </c>
-      <c r="T97" s="12">
-        <f t="shared" si="67"/>
-        <v>315202.59999999998</v>
-      </c>
-      <c r="U97" s="12">
-        <f t="shared" si="67"/>
-        <v>316848.10000000003</v>
-      </c>
-      <c r="V97" s="12">
-        <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="W97" s="12">
-        <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="X97" s="12">
-        <f t="shared" si="67"/>
-        <v>313263.89999999997</v>
-      </c>
-      <c r="Y97" s="12">
-        <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="Z97" s="12">
-        <f>T97-X97</f>
-        <v>1938.7000000000116</v>
-      </c>
-      <c r="AA97" s="13">
-        <f>Z97/T97</f>
-        <v>6.1506472345088901E-3</v>
-      </c>
-      <c r="AB97" s="41"/>
-      <c r="AC97" s="41"/>
-      <c r="AD97" s="41"/>
-      <c r="AE97" s="13"/>
-      <c r="AF97" s="12">
-        <f>SUM(AF6:AF96)</f>
-        <v>0</v>
-      </c>
-      <c r="AG97" s="12">
-        <f>SUM(AG6:AG96)</f>
-        <v>0</v>
-      </c>
-      <c r="AH97" s="12">
-        <f>SUM(AH6:AH96)</f>
-        <v>0</v>
-      </c>
-      <c r="AI97" s="12">
-        <f>SUM(AI6:AI96)</f>
-        <v>0</v>
-      </c>
-      <c r="AJ97" s="14"/>
-      <c r="AK97" s="14"/>
-      <c r="AL97" s="12"/>
-      <c r="AM97" s="15"/>
-      <c r="AN97" s="16"/>
-      <c r="AO97" s="16"/>
-      <c r="AP97" s="17"/>
-      <c r="AQ97" s="10">
-        <f>SUM(AQ6:AQ96)</f>
-        <v>0</v>
-      </c>
-      <c r="AR97" s="18">
-        <f>SUM(AR6:AR96)</f>
-        <v>0</v>
-      </c>
-      <c r="AS97" s="10">
-        <f>SUM(AS6:AS96)</f>
-        <v>0</v>
-      </c>
-      <c r="AT97" s="10">
-        <f>SUM(AT6:AT96)</f>
-        <v>0</v>
-      </c>
-      <c r="AU97" s="10">
-        <f>SUM(AU6:AU96)</f>
-        <v>0</v>
-      </c>
-      <c r="AV97" s="10">
-        <f>+SUM(AV6:AV96)</f>
-        <v>0</v>
-      </c>
-      <c r="AW97" s="10">
-        <f>SUM(AW6:AW96)</f>
-        <v>0</v>
-      </c>
-      <c r="AX97" s="10">
-        <f>SUM(AX6:AX96)</f>
-        <v>0</v>
-      </c>
-      <c r="AY97" s="10">
-        <f>SUM(AY6:AY96)</f>
-        <v>0</v>
-      </c>
-      <c r="AZ97" s="19"/>
-      <c r="BB97" s="42">
-        <f>SUM(BB6:BB96)</f>
-        <v>316704.51999999996</v>
-      </c>
-      <c r="BC97" s="42">
-        <f>SUM(BC6:BC96)</f>
-        <v>313263.89999999997</v>
-      </c>
-      <c r="BD97" s="42">
-        <f>SUM(BD6:BD96)</f>
-        <v>0</v>
-      </c>
-      <c r="BE97" s="42">
-        <f>SUM(BE6:BE96)</f>
-        <v>3440.6199999999972</v>
-      </c>
-      <c r="BF97" s="43">
-        <f t="shared" si="58"/>
-        <v>1.0863817163076793E-2</v>
+    <row r="107" spans="1:58" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="9">
+        <f>+COUNT(A6:A106)</f>
+        <v>97</v>
+      </c>
+      <c r="B107" s="10">
+        <f>+COUNTIF(X6:X106,"&gt;0")</f>
+        <v>90</v>
+      </c>
+      <c r="C107" s="10"/>
+      <c r="D107" s="10"/>
+      <c r="E107" s="10"/>
+      <c r="F107" s="10"/>
+      <c r="G107" s="10"/>
+      <c r="H107" s="10"/>
+      <c r="I107" s="10"/>
+      <c r="J107" s="10"/>
+      <c r="K107" s="10"/>
+      <c r="L107" s="11"/>
+      <c r="M107" s="10"/>
+      <c r="N107" s="10"/>
+      <c r="O107" s="10"/>
+      <c r="P107" s="10"/>
+      <c r="Q107" s="10"/>
+      <c r="R107" s="12">
+        <f t="shared" ref="R107:Y107" si="70">SUM(R6:R106)</f>
+        <v>452094.11999999994</v>
+      </c>
+      <c r="S107" s="12">
+        <f t="shared" si="70"/>
+        <v>105500.11999999998</v>
+      </c>
+      <c r="T107" s="12">
+        <f t="shared" si="70"/>
+        <v>346594.00000000006</v>
+      </c>
+      <c r="U107" s="12">
+        <f t="shared" si="70"/>
+        <v>348508.70000000013</v>
+      </c>
+      <c r="V107" s="12">
+        <f t="shared" si="70"/>
+        <v>0</v>
+      </c>
+      <c r="W107" s="12">
+        <f t="shared" si="70"/>
+        <v>0</v>
+      </c>
+      <c r="X107" s="12">
+        <f t="shared" si="70"/>
+        <v>344720.86000000004</v>
+      </c>
+      <c r="Y107" s="12">
+        <f t="shared" si="70"/>
+        <v>0</v>
+      </c>
+      <c r="Z107" s="12">
+        <f>T107-X107</f>
+        <v>1873.140000000014</v>
+      </c>
+      <c r="AA107" s="13">
+        <f>Z107/T107</f>
+        <v>5.4044213113903115E-3</v>
+      </c>
+      <c r="AB107" s="41"/>
+      <c r="AC107" s="41"/>
+      <c r="AD107" s="41"/>
+      <c r="AE107" s="13"/>
+      <c r="AF107" s="12">
+        <f>SUM(AF6:AF106)</f>
+        <v>0</v>
+      </c>
+      <c r="AG107" s="12">
+        <f>SUM(AG6:AG106)</f>
+        <v>0</v>
+      </c>
+      <c r="AH107" s="12">
+        <f>SUM(AH6:AH106)</f>
+        <v>0</v>
+      </c>
+      <c r="AI107" s="12">
+        <f>SUM(AI6:AI106)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ107" s="14"/>
+      <c r="AK107" s="14"/>
+      <c r="AL107" s="12"/>
+      <c r="AM107" s="15"/>
+      <c r="AN107" s="16"/>
+      <c r="AO107" s="16"/>
+      <c r="AP107" s="17"/>
+      <c r="AQ107" s="10">
+        <f>SUM(AQ6:AQ106)</f>
+        <v>0</v>
+      </c>
+      <c r="AR107" s="18">
+        <f>SUM(AR6:AR106)</f>
+        <v>0</v>
+      </c>
+      <c r="AS107" s="10">
+        <f>SUM(AS6:AS106)</f>
+        <v>0</v>
+      </c>
+      <c r="AT107" s="10">
+        <f>SUM(AT6:AT106)</f>
+        <v>0</v>
+      </c>
+      <c r="AU107" s="10">
+        <f>SUM(AU6:AU106)</f>
+        <v>0</v>
+      </c>
+      <c r="AV107" s="10">
+        <f>+SUM(AV6:AV106)</f>
+        <v>0</v>
+      </c>
+      <c r="AW107" s="10">
+        <f>SUM(AW6:AW106)</f>
+        <v>0</v>
+      </c>
+      <c r="AX107" s="10">
+        <f>SUM(AX6:AX106)</f>
+        <v>0</v>
+      </c>
+      <c r="AY107" s="10">
+        <f>SUM(AY6:AY106)</f>
+        <v>0</v>
+      </c>
+      <c r="AZ107" s="19"/>
+      <c r="BB107" s="42">
+        <f>SUM(BB6:BB106)</f>
+        <v>348231.65999999986</v>
+      </c>
+      <c r="BC107" s="42">
+        <f>SUM(BC6:BC106)</f>
+        <v>344720.86000000004</v>
+      </c>
+      <c r="BD107" s="42">
+        <f>SUM(BD6:BD106)</f>
+        <v>0</v>
+      </c>
+      <c r="BE107" s="42">
+        <f>SUM(BE6:BE106)</f>
+        <v>3510.7999999999975</v>
+      </c>
+      <c r="BF107" s="43">
+        <f t="shared" si="55"/>
+        <v>1.0081794400888187E-2</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="K6:K12">
-    <cfRule type="duplicateValues" dxfId="70" priority="1031"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="1052"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K6:K12">
-    <cfRule type="duplicateValues" dxfId="69" priority="1032"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="1033"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="1053"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="1054"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K96">
-    <cfRule type="duplicateValues" dxfId="67" priority="1034"/>
+  <conditionalFormatting sqref="K106">
+    <cfRule type="duplicateValues" dxfId="85" priority="1055"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K96">
-    <cfRule type="duplicateValues" dxfId="66" priority="1035"/>
-    <cfRule type="duplicateValues" dxfId="65" priority="1036"/>
+  <conditionalFormatting sqref="K106">
+    <cfRule type="duplicateValues" dxfId="84" priority="1056"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="1057"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K96 K5">
-    <cfRule type="duplicateValues" dxfId="64" priority="1037"/>
+  <conditionalFormatting sqref="K106 K5">
+    <cfRule type="duplicateValues" dxfId="82" priority="1058"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K96:K97 K5">
-    <cfRule type="duplicateValues" dxfId="63" priority="1039"/>
+  <conditionalFormatting sqref="K106:K107 K5">
+    <cfRule type="duplicateValues" dxfId="81" priority="1060"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K96:K97">
-    <cfRule type="duplicateValues" dxfId="62" priority="1041"/>
+  <conditionalFormatting sqref="K106:K107">
+    <cfRule type="duplicateValues" dxfId="80" priority="1062"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13:K14 K88">
-    <cfRule type="duplicateValues" dxfId="61" priority="1042"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="1063"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13:K14 K88">
-    <cfRule type="duplicateValues" dxfId="60" priority="1044"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="1045"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="1065"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="1066"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K13:K14 K5 K88 K96:K97">
-    <cfRule type="duplicateValues" dxfId="58" priority="1048"/>
+  <conditionalFormatting sqref="K13:K14 K5 K88 K106:K107">
+    <cfRule type="duplicateValues" dxfId="76" priority="1069"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K88 K5:K14 K96:K97">
-    <cfRule type="duplicateValues" dxfId="57" priority="1051"/>
+  <conditionalFormatting sqref="K88 K5:K14 K106:K107">
+    <cfRule type="duplicateValues" dxfId="75" priority="1072"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K36 K15:K26">
-    <cfRule type="duplicateValues" dxfId="56" priority="1053"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="1074"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K36 K15:K26">
-    <cfRule type="duplicateValues" dxfId="55" priority="1055"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="1056"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="1076"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="1077"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K15:K26">
-    <cfRule type="duplicateValues" dxfId="53" priority="1059"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="1080"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27:K35">
-    <cfRule type="duplicateValues" dxfId="52" priority="1060"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="1081"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27:K35">
-    <cfRule type="duplicateValues" dxfId="51" priority="1061"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="1062"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="1082"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="1083"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K5:K36 K88 K96:K97">
-    <cfRule type="duplicateValues" dxfId="49" priority="1063"/>
+  <conditionalFormatting sqref="K5:K36 K88 K106:K107">
+    <cfRule type="duplicateValues" dxfId="67" priority="1084"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K37:K54 K61:K64">
+    <cfRule type="duplicateValues" dxfId="66" priority="74"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K37:K54 K61:K64">
+    <cfRule type="duplicateValues" dxfId="65" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="76"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K37:K54">
+    <cfRule type="duplicateValues" dxfId="63" priority="77"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K37:K54">
+    <cfRule type="duplicateValues" dxfId="62" priority="78"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K37:K54">
+    <cfRule type="duplicateValues" dxfId="61" priority="79"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K6:K54 K61:K64 K88 K106:K107">
+    <cfRule type="duplicateValues" dxfId="60" priority="70"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K55:K60">
+    <cfRule type="duplicateValues" dxfId="59" priority="61"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K55:K60">
+    <cfRule type="duplicateValues" dxfId="58" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="63"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K55:K60">
+    <cfRule type="duplicateValues" dxfId="56" priority="64"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K55:K60">
+    <cfRule type="duplicateValues" dxfId="55" priority="65"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K55:K60">
+    <cfRule type="duplicateValues" dxfId="54" priority="66"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K55:K60">
+    <cfRule type="duplicateValues" dxfId="53" priority="60"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K6:K64 K88 K106:K107">
+    <cfRule type="duplicateValues" dxfId="52" priority="59"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K65:K87">
+    <cfRule type="duplicateValues" dxfId="51" priority="50"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K65:K87">
+    <cfRule type="duplicateValues" dxfId="50" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="52"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K65:K87">
     <cfRule type="duplicateValues" dxfId="48" priority="53"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K37:K54 K61:K64">
+  <conditionalFormatting sqref="K65:K87">
     <cfRule type="duplicateValues" dxfId="47" priority="54"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K65:K87">
     <cfRule type="duplicateValues" dxfId="46" priority="55"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K37:K54">
-    <cfRule type="duplicateValues" dxfId="45" priority="56"/>
+  <conditionalFormatting sqref="K65:K87">
+    <cfRule type="duplicateValues" dxfId="45" priority="49"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K37:K54">
-    <cfRule type="duplicateValues" dxfId="44" priority="57"/>
+  <conditionalFormatting sqref="K65:K87">
+    <cfRule type="duplicateValues" dxfId="44" priority="48"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K37:K54">
-    <cfRule type="duplicateValues" dxfId="43" priority="58"/>
+  <conditionalFormatting sqref="K6:K88 K106:K107">
+    <cfRule type="duplicateValues" dxfId="43" priority="47"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6:K54 K61:K64 K88 K96:K97">
-    <cfRule type="duplicateValues" dxfId="42" priority="49"/>
+  <conditionalFormatting sqref="K5:K88 K106:K107">
+    <cfRule type="duplicateValues" dxfId="42" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="46"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K55:K60">
-    <cfRule type="duplicateValues" dxfId="41" priority="40"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K55:K60">
-    <cfRule type="duplicateValues" dxfId="40" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="42"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K55:K60">
+  <conditionalFormatting sqref="K5:K88">
     <cfRule type="duplicateValues" dxfId="38" priority="43"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K55:K60">
-    <cfRule type="duplicateValues" dxfId="37" priority="44"/>
+  <conditionalFormatting sqref="K89:K94 K105">
+    <cfRule type="duplicateValues" dxfId="37" priority="30"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K55:K60">
-    <cfRule type="duplicateValues" dxfId="36" priority="45"/>
+  <conditionalFormatting sqref="K89:K94 K105">
+    <cfRule type="duplicateValues" dxfId="36" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="32"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K55:K60">
-    <cfRule type="duplicateValues" dxfId="35" priority="39"/>
+  <conditionalFormatting sqref="K89:K94 K105">
+    <cfRule type="duplicateValues" dxfId="34" priority="33"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6:K64 K88 K96:K97">
-    <cfRule type="duplicateValues" dxfId="34" priority="38"/>
+  <conditionalFormatting sqref="K89:K94 K105">
+    <cfRule type="duplicateValues" dxfId="33" priority="34"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K65:K87">
-    <cfRule type="duplicateValues" dxfId="33" priority="29"/>
+  <conditionalFormatting sqref="K89:K94 K105">
+    <cfRule type="duplicateValues" dxfId="32" priority="35"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K65:K87">
-    <cfRule type="duplicateValues" dxfId="32" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="31"/>
+  <conditionalFormatting sqref="K89:K94 K105">
+    <cfRule type="duplicateValues" dxfId="31" priority="36"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K65:K87">
-    <cfRule type="duplicateValues" dxfId="30" priority="32"/>
+  <conditionalFormatting sqref="K89:K94 K105">
+    <cfRule type="duplicateValues" dxfId="30" priority="37"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K65:K87">
-    <cfRule type="duplicateValues" dxfId="29" priority="33"/>
+  <conditionalFormatting sqref="K89:K94 K105">
+    <cfRule type="duplicateValues" dxfId="29" priority="38"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K65:K87">
-    <cfRule type="duplicateValues" dxfId="28" priority="34"/>
+  <conditionalFormatting sqref="K89:K94 K105">
+    <cfRule type="duplicateValues" dxfId="28" priority="29"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K65:K87">
+  <conditionalFormatting sqref="K89:K94 K105">
     <cfRule type="duplicateValues" dxfId="27" priority="28"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K65:K87">
+  <conditionalFormatting sqref="K89:K94 K105">
     <cfRule type="duplicateValues" dxfId="26" priority="27"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6:K88 K96:K97">
-    <cfRule type="duplicateValues" dxfId="25" priority="26"/>
+  <conditionalFormatting sqref="K89:K94 K105">
+    <cfRule type="duplicateValues" dxfId="25" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="26"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K5:K88 K96:K97">
-    <cfRule type="duplicateValues" dxfId="24" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="25"/>
+  <conditionalFormatting sqref="K5:K94 K105:K107">
+    <cfRule type="duplicateValues" dxfId="21" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K5:K88">
-    <cfRule type="duplicateValues" dxfId="20" priority="22"/>
+  <conditionalFormatting sqref="K95:K104">
+    <cfRule type="duplicateValues" dxfId="20" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K89:K95">
-    <cfRule type="duplicateValues" dxfId="19" priority="9"/>
+  <conditionalFormatting sqref="K95:K104">
+    <cfRule type="duplicateValues" dxfId="19" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K89:K95">
-    <cfRule type="duplicateValues" dxfId="18" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="11"/>
+  <conditionalFormatting sqref="K95:K104">
+    <cfRule type="duplicateValues" dxfId="17" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K89:K95">
-    <cfRule type="duplicateValues" dxfId="16" priority="12"/>
+  <conditionalFormatting sqref="K95:K104">
+    <cfRule type="duplicateValues" dxfId="16" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K89:K95">
-    <cfRule type="duplicateValues" dxfId="15" priority="13"/>
+  <conditionalFormatting sqref="K95:K104">
+    <cfRule type="duplicateValues" dxfId="15" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K89:K95">
-    <cfRule type="duplicateValues" dxfId="14" priority="14"/>
+  <conditionalFormatting sqref="K95:K104">
+    <cfRule type="duplicateValues" dxfId="14" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K89:K95">
-    <cfRule type="duplicateValues" dxfId="13" priority="15"/>
+  <conditionalFormatting sqref="K95:K104">
+    <cfRule type="duplicateValues" dxfId="13" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K89:K95">
-    <cfRule type="duplicateValues" dxfId="12" priority="16"/>
+  <conditionalFormatting sqref="K95:K104">
+    <cfRule type="duplicateValues" dxfId="12" priority="18"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K89:K95">
-    <cfRule type="duplicateValues" dxfId="11" priority="17"/>
+  <conditionalFormatting sqref="K95:K104">
+    <cfRule type="duplicateValues" dxfId="11" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K89:K95">
+  <conditionalFormatting sqref="K95:K104">
     <cfRule type="duplicateValues" dxfId="10" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K89:K95">
+  <conditionalFormatting sqref="K95:K104">
     <cfRule type="duplicateValues" dxfId="9" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K89:K95">
-    <cfRule type="duplicateValues" dxfId="8" priority="6"/>
+  <conditionalFormatting sqref="K95:K104">
+    <cfRule type="duplicateValues" dxfId="8" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K89:K95">
-    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+  <conditionalFormatting sqref="K95:K104">
+    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K5:K97">
+  <conditionalFormatting sqref="K5:K107">
     <cfRule type="duplicateValues" dxfId="3" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BB6:BB96">
-    <cfRule type="expression" dxfId="2" priority="1120">
+  <conditionalFormatting sqref="BB6:BB106">
+    <cfRule type="expression" dxfId="2" priority="1153">
       <formula>$AC6&lt;&gt;""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="1121">
+    <cfRule type="expression" dxfId="1" priority="1154">
       <formula>$AB6&lt;&gt;""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="1122">
+    <cfRule type="expression" dxfId="0" priority="1155">
       <formula>$T6&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Shortage.xlsx
+++ b/Shortage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\MR1\PPGS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{793559C1-1146-4580-A59E-409CECD92D55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DF34319-8654-4182-8C8C-594444F2AC91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Aug-26" sheetId="5" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Aug-26'!$A$5:$BH$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Aug-26'!$A$5:$BF$117</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jul-26'!$A$5:$BG$127</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1223" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1279" uniqueCount="75">
   <si>
     <t>sl.no.</t>
   </si>
@@ -755,7 +755,15 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="141">
+  <dxfs count="271">
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -774,6 +782,196 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2148,6 +2346,1088 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -18616,134 +19896,134 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="K126">
-    <cfRule type="duplicateValues" dxfId="140" priority="748"/>
+    <cfRule type="duplicateValues" dxfId="160" priority="748"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K6 K24">
-    <cfRule type="duplicateValues" dxfId="139" priority="749"/>
+    <cfRule type="duplicateValues" dxfId="159" priority="749"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7:K23">
-    <cfRule type="duplicateValues" dxfId="138" priority="751"/>
+    <cfRule type="duplicateValues" dxfId="158" priority="751"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K126 K6:K24">
-    <cfRule type="duplicateValues" dxfId="137" priority="752"/>
-    <cfRule type="duplicateValues" dxfId="136" priority="753"/>
+    <cfRule type="duplicateValues" dxfId="157" priority="752"/>
+    <cfRule type="duplicateValues" dxfId="156" priority="753"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25:K31 K54:K57">
-    <cfRule type="duplicateValues" dxfId="135" priority="756"/>
+    <cfRule type="duplicateValues" dxfId="155" priority="756"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25:K31 K54:K57">
-    <cfRule type="duplicateValues" dxfId="134" priority="758"/>
-    <cfRule type="duplicateValues" dxfId="133" priority="759"/>
+    <cfRule type="duplicateValues" dxfId="154" priority="758"/>
+    <cfRule type="duplicateValues" dxfId="153" priority="759"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27:K53">
-    <cfRule type="duplicateValues" dxfId="132" priority="762"/>
+    <cfRule type="duplicateValues" dxfId="152" priority="762"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27:K53">
-    <cfRule type="duplicateValues" dxfId="131" priority="763"/>
-    <cfRule type="duplicateValues" dxfId="130" priority="764"/>
+    <cfRule type="duplicateValues" dxfId="151" priority="763"/>
+    <cfRule type="duplicateValues" dxfId="150" priority="764"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K126 K6:K57">
-    <cfRule type="duplicateValues" dxfId="129" priority="765"/>
+    <cfRule type="duplicateValues" dxfId="149" priority="765"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K58:K62 K72:K75">
-    <cfRule type="duplicateValues" dxfId="128" priority="767"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="767"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K58:K62 K72:K75">
-    <cfRule type="duplicateValues" dxfId="127" priority="769"/>
-    <cfRule type="duplicateValues" dxfId="126" priority="770"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="769"/>
+    <cfRule type="duplicateValues" dxfId="146" priority="770"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K58:K62">
-    <cfRule type="duplicateValues" dxfId="125" priority="773"/>
+    <cfRule type="duplicateValues" dxfId="145" priority="773"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K126 K5:K62 K72:K75">
-    <cfRule type="duplicateValues" dxfId="124" priority="774"/>
+    <cfRule type="duplicateValues" dxfId="144" priority="774"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K63:K71">
-    <cfRule type="duplicateValues" dxfId="123" priority="777"/>
+    <cfRule type="duplicateValues" dxfId="143" priority="777"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K63:K71">
-    <cfRule type="duplicateValues" dxfId="122" priority="778"/>
-    <cfRule type="duplicateValues" dxfId="121" priority="779"/>
+    <cfRule type="duplicateValues" dxfId="142" priority="778"/>
+    <cfRule type="duplicateValues" dxfId="141" priority="779"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K126 K5:K75">
-    <cfRule type="duplicateValues" dxfId="120" priority="780"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="780"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K76:K79 K90:K92 K116">
-    <cfRule type="duplicateValues" dxfId="119" priority="782"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="782"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K76:K79 K90:K92 K116">
-    <cfRule type="duplicateValues" dxfId="118" priority="785"/>
-    <cfRule type="duplicateValues" dxfId="117" priority="786"/>
+    <cfRule type="duplicateValues" dxfId="138" priority="785"/>
+    <cfRule type="duplicateValues" dxfId="137" priority="786"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K76:K79">
-    <cfRule type="duplicateValues" dxfId="116" priority="791"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="791"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K80:K89">
-    <cfRule type="duplicateValues" dxfId="115" priority="792"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="792"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K80:K89">
-    <cfRule type="duplicateValues" dxfId="114" priority="793"/>
-    <cfRule type="duplicateValues" dxfId="113" priority="794"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="793"/>
+    <cfRule type="duplicateValues" dxfId="133" priority="794"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K126:K127 K5:K92 K116">
-    <cfRule type="duplicateValues" dxfId="112" priority="795"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="795"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K99:K113 K115">
-    <cfRule type="duplicateValues" dxfId="111" priority="798"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="798"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K99:K113 K115">
-    <cfRule type="duplicateValues" dxfId="110" priority="800"/>
-    <cfRule type="duplicateValues" dxfId="109" priority="801"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="800"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="801"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K93:K98">
-    <cfRule type="duplicateValues" dxfId="108" priority="804"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="804"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K93:K98">
-    <cfRule type="duplicateValues" dxfId="107" priority="805"/>
-    <cfRule type="duplicateValues" dxfId="106" priority="806"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="805"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="806"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K126:K127 K5:K113 K115:K116">
-    <cfRule type="duplicateValues" dxfId="105" priority="807"/>
+    <cfRule type="duplicateValues" dxfId="125" priority="807"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K114">
-    <cfRule type="duplicateValues" dxfId="104" priority="810"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="810"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K114">
-    <cfRule type="duplicateValues" dxfId="103" priority="811"/>
-    <cfRule type="duplicateValues" dxfId="102" priority="812"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="811"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="812"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K126:K127 K5:K116">
-    <cfRule type="duplicateValues" dxfId="101" priority="813"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="813"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K117:K123 K125">
-    <cfRule type="duplicateValues" dxfId="100" priority="844"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="844"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K117:K123 K125">
-    <cfRule type="duplicateValues" dxfId="99" priority="846"/>
-    <cfRule type="duplicateValues" dxfId="98" priority="847"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="846"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="847"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5:K123 K125:K127">
-    <cfRule type="duplicateValues" dxfId="97" priority="850"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="850"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K124">
-    <cfRule type="duplicateValues" dxfId="96" priority="852"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="852"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K124">
-    <cfRule type="duplicateValues" dxfId="95" priority="853"/>
-    <cfRule type="duplicateValues" dxfId="94" priority="854"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="853"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="854"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5:K127">
-    <cfRule type="duplicateValues" dxfId="93" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="92" priority="855"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="855"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB6:BB126">
-    <cfRule type="expression" dxfId="91" priority="1019">
+    <cfRule type="expression" dxfId="111" priority="1019">
       <formula>$AC6&lt;&gt;""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="90" priority="1020">
+    <cfRule type="expression" dxfId="110" priority="1020">
       <formula>$AB6&lt;&gt;""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="89" priority="1021">
+    <cfRule type="expression" dxfId="109" priority="1021">
       <formula>$T6&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18754,7 +20034,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{499C2CF5-E587-4B95-9659-4BA38F5371D8}">
-  <dimension ref="A1:BF107"/>
+  <dimension ref="A1:BF117"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.42578125" bestFit="1" customWidth="1"/>
@@ -19052,7 +20332,7 @@
         <v>1195.7700000000004</v>
       </c>
       <c r="T6" s="46">
-        <f t="shared" ref="T6:T106" si="0">+R6-S6</f>
+        <f t="shared" ref="T6:T116" si="0">+R6-S6</f>
         <v>3897.2</v>
       </c>
       <c r="U6" s="46">
@@ -19075,14 +20355,16 @@
       <c r="AB6" s="73">
         <v>3897.2</v>
       </c>
-      <c r="AC6" s="73"/>
+      <c r="AC6" s="73">
+        <v>3897.2</v>
+      </c>
       <c r="AD6" s="73"/>
       <c r="AE6" s="39"/>
       <c r="AF6" s="74"/>
       <c r="AG6" s="74"/>
       <c r="AH6" s="75"/>
       <c r="AI6" s="75">
-        <f t="shared" ref="AI6:AI106" si="1">+AG6+AH6</f>
+        <f t="shared" ref="AI6:AI116" si="1">+AG6+AH6</f>
         <v>0</v>
       </c>
       <c r="AJ6" s="32"/>
@@ -19092,15 +20374,15 @@
       <c r="AN6" s="33"/>
       <c r="AO6" s="33"/>
       <c r="AP6" s="34">
-        <f t="shared" ref="AP6:AP106" si="2">ROUNDUP((AO6-AM6+(AO6&lt;AM6))*24,0)</f>
+        <f t="shared" ref="AP6:AP116" si="2">ROUNDUP((AO6-AM6+(AO6&lt;AM6))*24,0)</f>
         <v>0</v>
       </c>
       <c r="AQ6" s="32">
-        <f t="shared" ref="AQ6:AQ106" si="3">IF(AP6&gt;5,(AP6-5),0)</f>
+        <f t="shared" ref="AQ6:AQ116" si="3">IF(AP6&gt;5,(AP6-5),0)</f>
         <v>0</v>
       </c>
       <c r="AR6" s="32">
-        <f t="shared" ref="AR6:AR106" si="4">+AQ6*8850</f>
+        <f t="shared" ref="AR6:AR116" si="4">+AQ6*8850</f>
         <v>0</v>
       </c>
       <c r="AS6" s="32"/>
@@ -19204,7 +20486,9 @@
       <c r="AB7" s="73">
         <v>3906.7</v>
       </c>
-      <c r="AC7" s="73"/>
+      <c r="AC7" s="73">
+        <v>3906.7</v>
+      </c>
       <c r="AD7" s="73"/>
       <c r="AE7" s="39"/>
       <c r="AF7" s="74"/>
@@ -19333,7 +20617,9 @@
       <c r="AB8" s="73">
         <v>3568.7</v>
       </c>
-      <c r="AC8" s="73"/>
+      <c r="AC8" s="73">
+        <v>3568.7</v>
+      </c>
       <c r="AD8" s="73"/>
       <c r="AE8" s="39"/>
       <c r="AF8" s="74"/>
@@ -19462,7 +20748,9 @@
       <c r="AB9" s="73">
         <v>4135.0600000000004</v>
       </c>
-      <c r="AC9" s="73"/>
+      <c r="AC9" s="73">
+        <v>4129.5600000000004</v>
+      </c>
       <c r="AD9" s="73"/>
       <c r="AE9" s="39"/>
       <c r="AF9" s="74"/>
@@ -19500,7 +20788,7 @@
       <c r="AZ9" s="35"/>
       <c r="BB9" s="45">
         <f>IF(AND(AB9="",AC9=""),T9,IF(AC9="",AB9,AC9))</f>
-        <v>4135.0600000000004</v>
+        <v>4129.5600000000004</v>
       </c>
       <c r="BC9" s="45">
         <f>+X9</f>
@@ -19509,11 +20797,11 @@
       <c r="BD9" s="45"/>
       <c r="BE9" s="45">
         <f t="shared" si="5"/>
-        <v>-13.139999999999418</v>
+        <v>-18.639999999999418</v>
       </c>
       <c r="BF9" s="39">
         <f t="shared" si="6"/>
-        <v>-3.177704797511866E-3</v>
+        <v>-4.5137980801827349E-3</v>
       </c>
     </row>
     <row r="10" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -19591,7 +20879,9 @@
       <c r="AB10" s="73">
         <v>3969.81</v>
       </c>
-      <c r="AC10" s="73"/>
+      <c r="AC10" s="73">
+        <v>3963.91</v>
+      </c>
       <c r="AD10" s="73"/>
       <c r="AE10" s="39"/>
       <c r="AF10" s="74"/>
@@ -19629,7 +20919,7 @@
       <c r="AZ10" s="35"/>
       <c r="BB10" s="45">
         <f>IF(AND(AB10="",AC10=""),T10,IF(AC10="",AB10,AC10))</f>
-        <v>3969.81</v>
+        <v>3963.91</v>
       </c>
       <c r="BC10" s="45">
         <f>+X10</f>
@@ -19638,11 +20928,11 @@
       <c r="BD10" s="45"/>
       <c r="BE10" s="45">
         <f t="shared" si="5"/>
-        <v>-56.389999999999873</v>
+        <v>-62.289999999999964</v>
       </c>
       <c r="BF10" s="39">
         <f t="shared" si="6"/>
-        <v>-1.4204710049095516E-2</v>
+        <v>-1.5714282110340538E-2</v>
       </c>
     </row>
     <row r="11" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -19720,7 +21010,9 @@
       <c r="AB11" s="73">
         <v>3830.4</v>
       </c>
-      <c r="AC11" s="73"/>
+      <c r="AC11" s="73">
+        <v>3830.4</v>
+      </c>
       <c r="AD11" s="73"/>
       <c r="AE11" s="39"/>
       <c r="AF11" s="74"/>
@@ -19849,7 +21141,9 @@
       <c r="AB12" s="73">
         <v>3426.75</v>
       </c>
-      <c r="AC12" s="73"/>
+      <c r="AC12" s="73">
+        <v>3426.75</v>
+      </c>
       <c r="AD12" s="73"/>
       <c r="AE12" s="39"/>
       <c r="AF12" s="74"/>
@@ -19978,7 +21272,9 @@
       <c r="AB13" s="73">
         <v>3937.35</v>
       </c>
-      <c r="AC13" s="73"/>
+      <c r="AC13" s="73">
+        <v>3937.35</v>
+      </c>
       <c r="AD13" s="73"/>
       <c r="AE13" s="39"/>
       <c r="AF13" s="74"/>
@@ -22286,16 +23582,16 @@
       <c r="V31" s="46"/>
       <c r="W31" s="46"/>
       <c r="X31" s="46">
-        <v>3884.2</v>
+        <v>3884.21</v>
       </c>
       <c r="Y31" s="46"/>
       <c r="Z31" s="46">
         <f>+T31-X31</f>
-        <v>23</v>
+        <v>22.989999999999782</v>
       </c>
       <c r="AA31" s="39">
         <f>Z31/T31</f>
-        <v>5.8865683865683867E-3</v>
+        <v>5.8840090090089532E-3</v>
       </c>
       <c r="AB31" s="73">
         <v>3907.2</v>
@@ -22342,16 +23638,16 @@
       </c>
       <c r="BC31" s="45">
         <f>+X31</f>
-        <v>3884.2</v>
+        <v>3884.21</v>
       </c>
       <c r="BD31" s="45"/>
       <c r="BE31" s="45">
         <f t="shared" si="24"/>
-        <v>23</v>
+        <v>22.989999999999782</v>
       </c>
       <c r="BF31" s="39">
         <f t="shared" si="25"/>
-        <v>5.8865683865683867E-3</v>
+        <v>5.8840090090089532E-3</v>
       </c>
     </row>
     <row r="32" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -29578,51 +30874,51 @@
         <v>2.7002147898128354E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:58" s="91" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="76">
+    <row r="88" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A88" s="21">
         <f>IF(ISBLANK(F88),"",COUNTA($F$6:F88))</f>
         <v>83</v>
       </c>
-      <c r="B88" s="77" t="s">
+      <c r="B88" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="C88" s="77" t="s">
+      <c r="C88" s="37" t="s">
         <v>61</v>
       </c>
-      <c r="D88" s="78"/>
-      <c r="E88" s="79" t="s">
+      <c r="D88" s="22"/>
+      <c r="E88" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="F88" s="80">
+      <c r="F88" s="36">
         <v>46254</v>
       </c>
-      <c r="G88" s="81" t="s">
+      <c r="G88" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="H88" s="81">
+      <c r="H88" s="24">
         <v>59</v>
       </c>
-      <c r="I88" s="81">
-        <v>0</v>
-      </c>
-      <c r="J88" s="81" t="s">
+      <c r="I88" s="24">
+        <v>0</v>
+      </c>
+      <c r="J88" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="K88" s="82">
+      <c r="K88" s="25">
         <v>162011721</v>
       </c>
-      <c r="L88" s="83">
+      <c r="L88" s="26">
         <v>46254</v>
       </c>
-      <c r="M88" s="84">
+      <c r="M88" s="38">
         <v>46256</v>
       </c>
-      <c r="N88" s="85">
+      <c r="N88" s="52">
         <v>16599</v>
       </c>
-      <c r="O88" s="86"/>
-      <c r="P88" s="86"/>
-      <c r="Q88" s="86"/>
+      <c r="O88" s="27"/>
+      <c r="P88" s="27"/>
+      <c r="Q88" s="27"/>
       <c r="R88" s="46">
         <v>5183.7299999999996</v>
       </c>
@@ -29663,95 +30959,95 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AJ88" s="87"/>
-      <c r="AK88" s="87"/>
-      <c r="AL88" s="87"/>
-      <c r="AM88" s="88"/>
-      <c r="AN88" s="88"/>
-      <c r="AO88" s="88"/>
-      <c r="AP88" s="89">
+      <c r="AJ88" s="32"/>
+      <c r="AK88" s="32"/>
+      <c r="AL88" s="32"/>
+      <c r="AM88" s="33"/>
+      <c r="AN88" s="33"/>
+      <c r="AO88" s="33"/>
+      <c r="AP88" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AQ88" s="87">
+      <c r="AQ88" s="32">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AR88" s="87">
+      <c r="AR88" s="32">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AS88" s="87"/>
-      <c r="AT88" s="87"/>
-      <c r="AU88" s="87"/>
-      <c r="AV88" s="87"/>
-      <c r="AW88" s="87"/>
-      <c r="AX88" s="87"/>
-      <c r="AY88" s="87"/>
-      <c r="AZ88" s="90"/>
-      <c r="BB88" s="92">
+      <c r="AS88" s="32"/>
+      <c r="AT88" s="32"/>
+      <c r="AU88" s="32"/>
+      <c r="AV88" s="32"/>
+      <c r="AW88" s="32"/>
+      <c r="AX88" s="32"/>
+      <c r="AY88" s="32"/>
+      <c r="AZ88" s="35"/>
+      <c r="BB88" s="45">
         <f>IF(AND(AB88="",AC88=""),T88,IF(AC88="",AB88,AC88))</f>
         <v>4007.28</v>
       </c>
-      <c r="BC88" s="92">
+      <c r="BC88" s="45">
         <f>+X88</f>
         <v>4055.6</v>
       </c>
-      <c r="BD88" s="92"/>
-      <c r="BE88" s="92">
-        <f t="shared" ref="BE88:BE106" si="54">+BB88-BC88</f>
+      <c r="BD88" s="45"/>
+      <c r="BE88" s="45">
+        <f t="shared" ref="BE88:BE116" si="54">+BB88-BC88</f>
         <v>-48.319999999999709</v>
       </c>
       <c r="BF88" s="39">
-        <f t="shared" ref="BF88:BF107" si="55">+BE88/BB88</f>
+        <f t="shared" ref="BF88:BF117" si="55">+BE88/BB88</f>
         <v>-1.2058054341099127E-2</v>
       </c>
     </row>
-    <row r="89" spans="1:58" s="91" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A89" s="76">
+    <row r="89" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A89" s="21">
         <f>IF(ISBLANK(F89),"",COUNTA($F$6:F89))</f>
         <v>84</v>
       </c>
-      <c r="B89" s="77" t="s">
+      <c r="B89" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="C89" s="77" t="s">
+      <c r="C89" s="37" t="s">
         <v>61</v>
       </c>
-      <c r="D89" s="78"/>
-      <c r="E89" s="79" t="s">
+      <c r="D89" s="22"/>
+      <c r="E89" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="F89" s="80">
+      <c r="F89" s="36">
         <v>46255</v>
       </c>
-      <c r="G89" s="81" t="s">
+      <c r="G89" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="H89" s="81">
+      <c r="H89" s="24">
         <v>58</v>
       </c>
-      <c r="I89" s="81">
+      <c r="I89" s="24">
         <v>1</v>
       </c>
-      <c r="J89" s="81" t="s">
+      <c r="J89" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="K89" s="82">
+      <c r="K89" s="25">
         <v>162011724</v>
       </c>
-      <c r="L89" s="83">
+      <c r="L89" s="26">
         <v>46256</v>
       </c>
-      <c r="M89" s="84">
+      <c r="M89" s="38">
         <v>46257</v>
       </c>
-      <c r="N89" s="85">
+      <c r="N89" s="52">
         <v>16606</v>
       </c>
-      <c r="O89" s="86"/>
-      <c r="P89" s="86"/>
-      <c r="Q89" s="86"/>
+      <c r="O89" s="27"/>
+      <c r="P89" s="27"/>
+      <c r="Q89" s="27"/>
       <c r="R89" s="46">
         <v>4996.3999999999996</v>
       </c>
@@ -29759,7 +31055,7 @@
         <v>1208.6999999999998</v>
       </c>
       <c r="T89" s="46">
-        <f t="shared" ref="T89:T105" si="56">+R89-S89</f>
+        <f t="shared" ref="T89:T115" si="56">+R89-S89</f>
         <v>3787.7</v>
       </c>
       <c r="U89" s="46">
@@ -29789,50 +31085,50 @@
       <c r="AG89" s="74"/>
       <c r="AH89" s="75"/>
       <c r="AI89" s="75">
-        <f t="shared" ref="AI89:AI105" si="57">+AG89+AH89</f>
-        <v>0</v>
-      </c>
-      <c r="AJ89" s="87"/>
-      <c r="AK89" s="87"/>
-      <c r="AL89" s="87"/>
-      <c r="AM89" s="88"/>
-      <c r="AN89" s="88"/>
-      <c r="AO89" s="88"/>
-      <c r="AP89" s="89">
-        <f t="shared" ref="AP89:AP105" si="58">ROUNDUP((AO89-AM89+(AO89&lt;AM89))*24,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AQ89" s="87">
-        <f t="shared" ref="AQ89:AQ105" si="59">IF(AP89&gt;5,(AP89-5),0)</f>
-        <v>0</v>
-      </c>
-      <c r="AR89" s="87">
-        <f t="shared" ref="AR89:AR105" si="60">+AQ89*8850</f>
-        <v>0</v>
-      </c>
-      <c r="AS89" s="87"/>
-      <c r="AT89" s="87"/>
-      <c r="AU89" s="87"/>
-      <c r="AV89" s="87"/>
-      <c r="AW89" s="87"/>
-      <c r="AX89" s="87"/>
-      <c r="AY89" s="87"/>
-      <c r="AZ89" s="90"/>
-      <c r="BB89" s="92">
+        <f t="shared" ref="AI89:AI115" si="57">+AG89+AH89</f>
+        <v>0</v>
+      </c>
+      <c r="AJ89" s="32"/>
+      <c r="AK89" s="32"/>
+      <c r="AL89" s="32"/>
+      <c r="AM89" s="33"/>
+      <c r="AN89" s="33"/>
+      <c r="AO89" s="33"/>
+      <c r="AP89" s="34">
+        <f t="shared" ref="AP89:AP115" si="58">ROUNDUP((AO89-AM89+(AO89&lt;AM89))*24,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ89" s="32">
+        <f t="shared" ref="AQ89:AQ115" si="59">IF(AP89&gt;5,(AP89-5),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AR89" s="32">
+        <f t="shared" ref="AR89:AR115" si="60">+AQ89*8850</f>
+        <v>0</v>
+      </c>
+      <c r="AS89" s="32"/>
+      <c r="AT89" s="32"/>
+      <c r="AU89" s="32"/>
+      <c r="AV89" s="32"/>
+      <c r="AW89" s="32"/>
+      <c r="AX89" s="32"/>
+      <c r="AY89" s="32"/>
+      <c r="AZ89" s="35"/>
+      <c r="BB89" s="45">
         <f>IF(AND(AB89="",AC89=""),T89,IF(AC89="",AB89,AC89))</f>
         <v>3796.25</v>
       </c>
-      <c r="BC89" s="92">
+      <c r="BC89" s="45">
         <f>+X89</f>
         <v>3917.2</v>
       </c>
-      <c r="BD89" s="92"/>
-      <c r="BE89" s="92">
-        <f t="shared" ref="BE89:BE105" si="61">+BB89-BC89</f>
+      <c r="BD89" s="45"/>
+      <c r="BE89" s="45">
+        <f t="shared" ref="BE89:BE115" si="61">+BB89-BC89</f>
         <v>-120.94999999999982</v>
       </c>
       <c r="BF89" s="39">
-        <f t="shared" ref="BF89:BF105" si="62">+BE89/BB89</f>
+        <f t="shared" ref="BF89:BF115" si="62">+BE89/BB89</f>
         <v>-3.1860388541323628E-2</v>
       </c>
     </row>
@@ -29951,51 +31247,51 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="91" spans="1:58" s="91" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A91" s="76">
+    <row r="91" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A91" s="21">
         <f>IF(ISBLANK(F91),"",COUNTA($F$6:F91))</f>
         <v>86</v>
       </c>
-      <c r="B91" s="77" t="s">
+      <c r="B91" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="C91" s="77" t="s">
+      <c r="C91" s="37" t="s">
         <v>61</v>
       </c>
-      <c r="D91" s="78"/>
-      <c r="E91" s="79" t="s">
+      <c r="D91" s="22"/>
+      <c r="E91" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="F91" s="80">
+      <c r="F91" s="36">
         <v>46256</v>
       </c>
-      <c r="G91" s="81" t="s">
+      <c r="G91" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="H91" s="81">
+      <c r="H91" s="24">
         <v>58</v>
       </c>
-      <c r="I91" s="81">
-        <v>0</v>
-      </c>
-      <c r="J91" s="81" t="s">
+      <c r="I91" s="24">
+        <v>0</v>
+      </c>
+      <c r="J91" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="K91" s="82">
+      <c r="K91" s="25">
         <v>162006457</v>
       </c>
-      <c r="L91" s="83">
+      <c r="L91" s="26">
         <v>46256</v>
       </c>
-      <c r="M91" s="84">
+      <c r="M91" s="38">
         <v>46258</v>
       </c>
-      <c r="N91" s="85">
+      <c r="N91" s="52">
         <v>16609</v>
       </c>
-      <c r="O91" s="86"/>
-      <c r="P91" s="86"/>
-      <c r="Q91" s="86"/>
+      <c r="O91" s="27"/>
+      <c r="P91" s="27"/>
+      <c r="Q91" s="27"/>
       <c r="R91" s="46">
         <v>5260.17</v>
       </c>
@@ -30036,42 +31332,42 @@
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="AJ91" s="87"/>
-      <c r="AK91" s="87"/>
-      <c r="AL91" s="87"/>
-      <c r="AM91" s="88"/>
-      <c r="AN91" s="88"/>
-      <c r="AO91" s="88"/>
-      <c r="AP91" s="89">
+      <c r="AJ91" s="32"/>
+      <c r="AK91" s="32"/>
+      <c r="AL91" s="32"/>
+      <c r="AM91" s="33"/>
+      <c r="AN91" s="33"/>
+      <c r="AO91" s="33"/>
+      <c r="AP91" s="34">
         <f t="shared" si="58"/>
         <v>0</v>
       </c>
-      <c r="AQ91" s="87">
+      <c r="AQ91" s="32">
         <f t="shared" si="59"/>
         <v>0</v>
       </c>
-      <c r="AR91" s="87">
+      <c r="AR91" s="32">
         <f t="shared" si="60"/>
         <v>0</v>
       </c>
-      <c r="AS91" s="87"/>
-      <c r="AT91" s="87"/>
-      <c r="AU91" s="87"/>
-      <c r="AV91" s="87"/>
-      <c r="AW91" s="87"/>
-      <c r="AX91" s="87"/>
-      <c r="AY91" s="87"/>
-      <c r="AZ91" s="90"/>
-      <c r="BB91" s="92">
+      <c r="AS91" s="32"/>
+      <c r="AT91" s="32"/>
+      <c r="AU91" s="32"/>
+      <c r="AV91" s="32"/>
+      <c r="AW91" s="32"/>
+      <c r="AX91" s="32"/>
+      <c r="AY91" s="32"/>
+      <c r="AZ91" s="35"/>
+      <c r="BB91" s="45">
         <f>IF(AND(AB91="",AC91=""),T91,IF(AC91="",AB91,AC91))</f>
         <v>4047.85</v>
       </c>
-      <c r="BC91" s="92">
+      <c r="BC91" s="45">
         <f>+X91</f>
         <v>4050.4</v>
       </c>
-      <c r="BD91" s="92"/>
-      <c r="BE91" s="92">
+      <c r="BD91" s="45"/>
+      <c r="BE91" s="45">
         <f t="shared" si="61"/>
         <v>-2.5500000000001819</v>
       </c>
@@ -30080,51 +31376,51 @@
         <v>-6.2996405499220133E-4</v>
       </c>
     </row>
-    <row r="92" spans="1:58" s="91" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A92" s="76">
+    <row r="92" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A92" s="21">
         <f>IF(ISBLANK(F92),"",COUNTA($F$6:F92))</f>
         <v>87</v>
       </c>
-      <c r="B92" s="77" t="s">
+      <c r="B92" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="C92" s="77" t="s">
+      <c r="C92" s="37" t="s">
         <v>61</v>
       </c>
-      <c r="D92" s="78"/>
-      <c r="E92" s="79" t="s">
+      <c r="D92" s="22"/>
+      <c r="E92" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="F92" s="80">
+      <c r="F92" s="36">
         <v>46256</v>
       </c>
-      <c r="G92" s="81" t="s">
+      <c r="G92" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="H92" s="81">
+      <c r="H92" s="24">
         <v>58</v>
       </c>
-      <c r="I92" s="81">
-        <v>0</v>
-      </c>
-      <c r="J92" s="81" t="s">
+      <c r="I92" s="24">
+        <v>0</v>
+      </c>
+      <c r="J92" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="K92" s="82">
+      <c r="K92" s="25">
         <v>162011726</v>
       </c>
-      <c r="L92" s="83">
+      <c r="L92" s="26">
         <v>46256</v>
       </c>
-      <c r="M92" s="84">
+      <c r="M92" s="38">
         <v>46258</v>
       </c>
-      <c r="N92" s="85">
+      <c r="N92" s="52">
         <v>16610</v>
       </c>
-      <c r="O92" s="86"/>
-      <c r="P92" s="86"/>
-      <c r="Q92" s="86"/>
+      <c r="O92" s="27"/>
+      <c r="P92" s="27"/>
+      <c r="Q92" s="27"/>
       <c r="R92" s="46">
         <v>5261.8</v>
       </c>
@@ -30165,42 +31461,42 @@
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="AJ92" s="87"/>
-      <c r="AK92" s="87"/>
-      <c r="AL92" s="87"/>
-      <c r="AM92" s="88"/>
-      <c r="AN92" s="88"/>
-      <c r="AO92" s="88"/>
-      <c r="AP92" s="89">
+      <c r="AJ92" s="32"/>
+      <c r="AK92" s="32"/>
+      <c r="AL92" s="32"/>
+      <c r="AM92" s="33"/>
+      <c r="AN92" s="33"/>
+      <c r="AO92" s="33"/>
+      <c r="AP92" s="34">
         <f t="shared" si="58"/>
         <v>0</v>
       </c>
-      <c r="AQ92" s="87">
+      <c r="AQ92" s="32">
         <f t="shared" si="59"/>
         <v>0</v>
       </c>
-      <c r="AR92" s="87">
+      <c r="AR92" s="32">
         <f t="shared" si="60"/>
         <v>0</v>
       </c>
-      <c r="AS92" s="87"/>
-      <c r="AT92" s="87"/>
-      <c r="AU92" s="87"/>
-      <c r="AV92" s="87"/>
-      <c r="AW92" s="87"/>
-      <c r="AX92" s="87"/>
-      <c r="AY92" s="87"/>
-      <c r="AZ92" s="90"/>
-      <c r="BB92" s="92">
+      <c r="AS92" s="32"/>
+      <c r="AT92" s="32"/>
+      <c r="AU92" s="32"/>
+      <c r="AV92" s="32"/>
+      <c r="AW92" s="32"/>
+      <c r="AX92" s="32"/>
+      <c r="AY92" s="32"/>
+      <c r="AZ92" s="35"/>
+      <c r="BB92" s="45">
         <f>IF(AND(AB92="",AC92=""),T92,IF(AC92="",AB92,AC92))</f>
         <v>4046.23</v>
       </c>
-      <c r="BC92" s="92">
+      <c r="BC92" s="45">
         <f>+X92</f>
         <v>4037.2</v>
       </c>
-      <c r="BD92" s="92"/>
-      <c r="BE92" s="92">
+      <c r="BD92" s="45"/>
+      <c r="BE92" s="45">
         <f t="shared" si="61"/>
         <v>9.0300000000002001</v>
       </c>
@@ -30209,51 +31505,51 @@
         <v>2.2317070458180086E-3</v>
       </c>
     </row>
-    <row r="93" spans="1:58" s="91" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A93" s="76">
+    <row r="93" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A93" s="21">
         <f>IF(ISBLANK(F93),"",COUNTA($F$6:F93))</f>
         <v>88</v>
       </c>
-      <c r="B93" s="77" t="s">
+      <c r="B93" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="C93" s="77" t="s">
+      <c r="C93" s="37" t="s">
         <v>61</v>
       </c>
-      <c r="D93" s="78"/>
-      <c r="E93" s="79" t="s">
+      <c r="D93" s="22"/>
+      <c r="E93" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="F93" s="80">
+      <c r="F93" s="36">
         <v>46256</v>
       </c>
-      <c r="G93" s="81" t="s">
+      <c r="G93" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="H93" s="81">
+      <c r="H93" s="24">
         <v>59</v>
       </c>
-      <c r="I93" s="81">
-        <v>0</v>
-      </c>
-      <c r="J93" s="81" t="s">
+      <c r="I93" s="24">
+        <v>0</v>
+      </c>
+      <c r="J93" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="K93" s="82">
+      <c r="K93" s="25">
         <v>162003211</v>
       </c>
-      <c r="L93" s="83">
+      <c r="L93" s="26">
         <v>46257</v>
       </c>
-      <c r="M93" s="84">
+      <c r="M93" s="38">
         <v>46258</v>
       </c>
-      <c r="N93" s="85">
+      <c r="N93" s="52">
         <v>16612</v>
       </c>
-      <c r="O93" s="86"/>
-      <c r="P93" s="86"/>
-      <c r="Q93" s="86"/>
+      <c r="O93" s="27"/>
+      <c r="P93" s="27"/>
+      <c r="Q93" s="27"/>
       <c r="R93" s="46">
         <v>5349.67</v>
       </c>
@@ -30294,42 +31590,42 @@
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="AJ93" s="87"/>
-      <c r="AK93" s="87"/>
-      <c r="AL93" s="87"/>
-      <c r="AM93" s="88"/>
-      <c r="AN93" s="88"/>
-      <c r="AO93" s="88"/>
-      <c r="AP93" s="89">
+      <c r="AJ93" s="32"/>
+      <c r="AK93" s="32"/>
+      <c r="AL93" s="32"/>
+      <c r="AM93" s="33"/>
+      <c r="AN93" s="33"/>
+      <c r="AO93" s="33"/>
+      <c r="AP93" s="34">
         <f t="shared" si="58"/>
         <v>0</v>
       </c>
-      <c r="AQ93" s="87">
+      <c r="AQ93" s="32">
         <f t="shared" si="59"/>
         <v>0</v>
       </c>
-      <c r="AR93" s="87">
+      <c r="AR93" s="32">
         <f t="shared" si="60"/>
         <v>0</v>
       </c>
-      <c r="AS93" s="87"/>
-      <c r="AT93" s="87"/>
-      <c r="AU93" s="87"/>
-      <c r="AV93" s="87"/>
-      <c r="AW93" s="87"/>
-      <c r="AX93" s="87"/>
-      <c r="AY93" s="87"/>
-      <c r="AZ93" s="90"/>
-      <c r="BB93" s="92">
+      <c r="AS93" s="32"/>
+      <c r="AT93" s="32"/>
+      <c r="AU93" s="32"/>
+      <c r="AV93" s="32"/>
+      <c r="AW93" s="32"/>
+      <c r="AX93" s="32"/>
+      <c r="AY93" s="32"/>
+      <c r="AZ93" s="35"/>
+      <c r="BB93" s="45">
         <f>IF(AND(AB93="",AC93=""),T93,IF(AC93="",AB93,AC93))</f>
         <v>4117.16</v>
       </c>
-      <c r="BC93" s="92">
+      <c r="BC93" s="45">
         <f>+X93</f>
         <v>4023.4</v>
       </c>
-      <c r="BD93" s="92"/>
-      <c r="BE93" s="92">
+      <c r="BD93" s="45"/>
+      <c r="BE93" s="45">
         <f t="shared" si="61"/>
         <v>93.759999999999764</v>
       </c>
@@ -30338,51 +31634,51 @@
         <v>2.2772979432424238E-2</v>
       </c>
     </row>
-    <row r="94" spans="1:58" s="91" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A94" s="76">
+    <row r="94" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A94" s="21">
         <f>IF(ISBLANK(F94),"",COUNTA($F$6:F94))</f>
         <v>89</v>
       </c>
-      <c r="B94" s="77" t="s">
+      <c r="B94" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="C94" s="77" t="s">
+      <c r="C94" s="37" t="s">
         <v>61</v>
       </c>
-      <c r="D94" s="78"/>
-      <c r="E94" s="79" t="s">
+      <c r="D94" s="22"/>
+      <c r="E94" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="F94" s="80">
+      <c r="F94" s="36">
         <v>46256</v>
       </c>
-      <c r="G94" s="81" t="s">
+      <c r="G94" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="H94" s="81">
+      <c r="H94" s="24">
         <v>58</v>
       </c>
-      <c r="I94" s="81">
+      <c r="I94" s="24">
         <v>4</v>
       </c>
-      <c r="J94" s="81" t="s">
+      <c r="J94" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="K94" s="82">
+      <c r="K94" s="25">
         <v>162004413</v>
       </c>
-      <c r="L94" s="83">
+      <c r="L94" s="26">
         <v>46257</v>
       </c>
-      <c r="M94" s="84">
+      <c r="M94" s="38">
         <v>46258</v>
       </c>
-      <c r="N94" s="85">
+      <c r="N94" s="52">
         <v>16613</v>
       </c>
-      <c r="O94" s="86"/>
-      <c r="P94" s="86"/>
-      <c r="Q94" s="86"/>
+      <c r="O94" s="27"/>
+      <c r="P94" s="27"/>
+      <c r="Q94" s="27"/>
       <c r="R94" s="46">
         <v>4882.43</v>
       </c>
@@ -30423,42 +31719,42 @@
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="AJ94" s="87"/>
-      <c r="AK94" s="87"/>
-      <c r="AL94" s="87"/>
-      <c r="AM94" s="88"/>
-      <c r="AN94" s="88"/>
-      <c r="AO94" s="88"/>
-      <c r="AP94" s="89">
+      <c r="AJ94" s="32"/>
+      <c r="AK94" s="32"/>
+      <c r="AL94" s="32"/>
+      <c r="AM94" s="33"/>
+      <c r="AN94" s="33"/>
+      <c r="AO94" s="33"/>
+      <c r="AP94" s="34">
         <f t="shared" si="58"/>
         <v>0</v>
       </c>
-      <c r="AQ94" s="87">
+      <c r="AQ94" s="32">
         <f t="shared" si="59"/>
         <v>0</v>
       </c>
-      <c r="AR94" s="87">
+      <c r="AR94" s="32">
         <f t="shared" si="60"/>
         <v>0</v>
       </c>
-      <c r="AS94" s="87"/>
-      <c r="AT94" s="87"/>
-      <c r="AU94" s="87"/>
-      <c r="AV94" s="87"/>
-      <c r="AW94" s="87"/>
-      <c r="AX94" s="87"/>
-      <c r="AY94" s="87"/>
-      <c r="AZ94" s="90"/>
-      <c r="BB94" s="92">
+      <c r="AS94" s="32"/>
+      <c r="AT94" s="32"/>
+      <c r="AU94" s="32"/>
+      <c r="AV94" s="32"/>
+      <c r="AW94" s="32"/>
+      <c r="AX94" s="32"/>
+      <c r="AY94" s="32"/>
+      <c r="AZ94" s="35"/>
+      <c r="BB94" s="45">
         <f>IF(AND(AB94="",AC94=""),T94,IF(AC94="",AB94,AC94))</f>
         <v>3754.85</v>
       </c>
-      <c r="BC94" s="92">
+      <c r="BC94" s="45">
         <f>+X94</f>
         <v>3746.2</v>
       </c>
-      <c r="BD94" s="92"/>
-      <c r="BE94" s="92">
+      <c r="BD94" s="45"/>
+      <c r="BE94" s="45">
         <f t="shared" si="61"/>
         <v>8.6500000000000909</v>
       </c>
@@ -30467,51 +31763,51 @@
         <v>2.3036872311810301E-3</v>
       </c>
     </row>
-    <row r="95" spans="1:58" s="91" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A95" s="76">
+    <row r="95" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A95" s="21">
         <f>IF(ISBLANK(F95),"",COUNTA($F$6:F95))</f>
         <v>90</v>
       </c>
-      <c r="B95" s="77" t="s">
+      <c r="B95" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="C95" s="77" t="s">
+      <c r="C95" s="37" t="s">
         <v>61</v>
       </c>
-      <c r="D95" s="78"/>
-      <c r="E95" s="79" t="s">
+      <c r="D95" s="22"/>
+      <c r="E95" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="F95" s="80">
+      <c r="F95" s="36">
         <v>46257</v>
       </c>
-      <c r="G95" s="81" t="s">
+      <c r="G95" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="H95" s="81">
+      <c r="H95" s="24">
         <v>59</v>
       </c>
-      <c r="I95" s="81">
-        <v>0</v>
-      </c>
-      <c r="J95" s="81" t="s">
+      <c r="I95" s="24">
+        <v>0</v>
+      </c>
+      <c r="J95" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="K95" s="82">
+      <c r="K95" s="25">
         <v>162004415</v>
       </c>
-      <c r="L95" s="83">
+      <c r="L95" s="26">
         <v>46258</v>
       </c>
-      <c r="M95" s="84">
+      <c r="M95" s="38">
         <v>46259</v>
       </c>
-      <c r="N95" s="85">
+      <c r="N95" s="52">
         <v>16615</v>
       </c>
-      <c r="O95" s="86"/>
-      <c r="P95" s="86"/>
-      <c r="Q95" s="86"/>
+      <c r="O95" s="27"/>
+      <c r="P95" s="27"/>
+      <c r="Q95" s="27"/>
       <c r="R95" s="46">
         <v>5334.45</v>
       </c>
@@ -30519,7 +31815,7 @@
         <v>1233.6499999999996</v>
       </c>
       <c r="T95" s="46">
-        <f t="shared" ref="T95:T104" si="63">+R95-S95</f>
+        <f t="shared" ref="T95:T114" si="63">+R95-S95</f>
         <v>4100.8</v>
       </c>
       <c r="U95" s="46">
@@ -30549,98 +31845,98 @@
       <c r="AG95" s="74"/>
       <c r="AH95" s="75"/>
       <c r="AI95" s="75">
-        <f t="shared" ref="AI95:AI104" si="64">+AG95+AH95</f>
-        <v>0</v>
-      </c>
-      <c r="AJ95" s="87"/>
-      <c r="AK95" s="87"/>
-      <c r="AL95" s="87"/>
-      <c r="AM95" s="88"/>
-      <c r="AN95" s="88"/>
-      <c r="AO95" s="88"/>
-      <c r="AP95" s="89">
-        <f t="shared" ref="AP95:AP104" si="65">ROUNDUP((AO95-AM95+(AO95&lt;AM95))*24,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AQ95" s="87">
-        <f t="shared" ref="AQ95:AQ104" si="66">IF(AP95&gt;5,(AP95-5),0)</f>
-        <v>0</v>
-      </c>
-      <c r="AR95" s="87">
-        <f t="shared" ref="AR95:AR104" si="67">+AQ95*8850</f>
-        <v>0</v>
-      </c>
-      <c r="AS95" s="87"/>
-      <c r="AT95" s="87"/>
-      <c r="AU95" s="87"/>
-      <c r="AV95" s="87"/>
-      <c r="AW95" s="87"/>
-      <c r="AX95" s="87"/>
-      <c r="AY95" s="87"/>
-      <c r="AZ95" s="90"/>
-      <c r="BB95" s="92">
+        <f t="shared" ref="AI95:AI114" si="64">+AG95+AH95</f>
+        <v>0</v>
+      </c>
+      <c r="AJ95" s="32"/>
+      <c r="AK95" s="32"/>
+      <c r="AL95" s="32"/>
+      <c r="AM95" s="33"/>
+      <c r="AN95" s="33"/>
+      <c r="AO95" s="33"/>
+      <c r="AP95" s="34">
+        <f t="shared" ref="AP95:AP114" si="65">ROUNDUP((AO95-AM95+(AO95&lt;AM95))*24,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ95" s="32">
+        <f t="shared" ref="AQ95:AQ114" si="66">IF(AP95&gt;5,(AP95-5),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AR95" s="32">
+        <f t="shared" ref="AR95:AR114" si="67">+AQ95*8850</f>
+        <v>0</v>
+      </c>
+      <c r="AS95" s="32"/>
+      <c r="AT95" s="32"/>
+      <c r="AU95" s="32"/>
+      <c r="AV95" s="32"/>
+      <c r="AW95" s="32"/>
+      <c r="AX95" s="32"/>
+      <c r="AY95" s="32"/>
+      <c r="AZ95" s="35"/>
+      <c r="BB95" s="45">
         <f>IF(AND(AB95="",AC95=""),T95,IF(AC95="",AB95,AC95))</f>
         <v>4100.8</v>
       </c>
-      <c r="BC95" s="92">
+      <c r="BC95" s="45">
         <f>+X95</f>
         <v>4060.8</v>
       </c>
-      <c r="BD95" s="92"/>
-      <c r="BE95" s="92">
-        <f t="shared" ref="BE95:BE104" si="68">+BB95-BC95</f>
+      <c r="BD95" s="45"/>
+      <c r="BE95" s="45">
+        <f t="shared" ref="BE95:BE114" si="68">+BB95-BC95</f>
         <v>40</v>
       </c>
       <c r="BF95" s="39">
-        <f t="shared" ref="BF95:BF104" si="69">+BE95/BB95</f>
+        <f t="shared" ref="BF95:BF114" si="69">+BE95/BB95</f>
         <v>9.7541943035505257E-3</v>
       </c>
     </row>
-    <row r="96" spans="1:58" s="91" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A96" s="76">
+    <row r="96" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A96" s="21">
         <f>IF(ISBLANK(F96),"",COUNTA($F$6:F96))</f>
         <v>91</v>
       </c>
-      <c r="B96" s="77" t="s">
+      <c r="B96" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="C96" s="77" t="s">
+      <c r="C96" s="37" t="s">
         <v>61</v>
       </c>
-      <c r="D96" s="78"/>
-      <c r="E96" s="79" t="s">
+      <c r="D96" s="22"/>
+      <c r="E96" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="F96" s="80">
+      <c r="F96" s="36">
         <v>46257</v>
       </c>
-      <c r="G96" s="81" t="s">
+      <c r="G96" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="H96" s="81">
+      <c r="H96" s="24">
         <v>58</v>
       </c>
-      <c r="I96" s="81">
+      <c r="I96" s="24">
         <v>7</v>
       </c>
-      <c r="J96" s="81" t="s">
+      <c r="J96" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="K96" s="82">
+      <c r="K96" s="25">
         <v>162003213</v>
       </c>
-      <c r="L96" s="83">
+      <c r="L96" s="26">
         <v>46257</v>
       </c>
-      <c r="M96" s="84">
+      <c r="M96" s="38">
         <v>46259</v>
       </c>
-      <c r="N96" s="85">
+      <c r="N96" s="52">
         <v>16619</v>
       </c>
-      <c r="O96" s="86"/>
-      <c r="P96" s="86"/>
-      <c r="Q96" s="86"/>
+      <c r="O96" s="27"/>
+      <c r="P96" s="27"/>
+      <c r="Q96" s="27"/>
       <c r="R96" s="46">
         <v>4625.7</v>
       </c>
@@ -30681,42 +31977,42 @@
         <f t="shared" si="64"/>
         <v>0</v>
       </c>
-      <c r="AJ96" s="87"/>
-      <c r="AK96" s="87"/>
-      <c r="AL96" s="87"/>
-      <c r="AM96" s="88"/>
-      <c r="AN96" s="88"/>
-      <c r="AO96" s="88"/>
-      <c r="AP96" s="89">
+      <c r="AJ96" s="32"/>
+      <c r="AK96" s="32"/>
+      <c r="AL96" s="32"/>
+      <c r="AM96" s="33"/>
+      <c r="AN96" s="33"/>
+      <c r="AO96" s="33"/>
+      <c r="AP96" s="34">
         <f t="shared" si="65"/>
         <v>0</v>
       </c>
-      <c r="AQ96" s="87">
+      <c r="AQ96" s="32">
         <f t="shared" si="66"/>
         <v>0</v>
       </c>
-      <c r="AR96" s="87">
+      <c r="AR96" s="32">
         <f t="shared" si="67"/>
         <v>0</v>
       </c>
-      <c r="AS96" s="87"/>
-      <c r="AT96" s="87"/>
-      <c r="AU96" s="87"/>
-      <c r="AV96" s="87"/>
-      <c r="AW96" s="87"/>
-      <c r="AX96" s="87"/>
-      <c r="AY96" s="87"/>
-      <c r="AZ96" s="90"/>
-      <c r="BB96" s="92">
+      <c r="AS96" s="32"/>
+      <c r="AT96" s="32"/>
+      <c r="AU96" s="32"/>
+      <c r="AV96" s="32"/>
+      <c r="AW96" s="32"/>
+      <c r="AX96" s="32"/>
+      <c r="AY96" s="32"/>
+      <c r="AZ96" s="35"/>
+      <c r="BB96" s="45">
         <f>IF(AND(AB96="",AC96=""),T96,IF(AC96="",AB96,AC96))</f>
         <v>3656.72</v>
       </c>
-      <c r="BC96" s="92">
+      <c r="BC96" s="45">
         <f>+X96</f>
         <v>3579.4</v>
       </c>
-      <c r="BD96" s="92"/>
-      <c r="BE96" s="92">
+      <c r="BD96" s="45"/>
+      <c r="BE96" s="45">
         <f t="shared" si="68"/>
         <v>77.319999999999709</v>
       </c>
@@ -30725,1470 +32021,2867 @@
         <v>2.1144632348115172E-2</v>
       </c>
     </row>
-    <row r="97" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A97" s="53">
+    <row r="97" spans="1:58" s="91" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A97" s="76">
         <f>IF(ISBLANK(F97),"",COUNTA($F$6:F97))</f>
         <v>92</v>
       </c>
-      <c r="B97" s="54" t="s">
+      <c r="B97" s="77" t="s">
         <v>60</v>
       </c>
-      <c r="C97" s="54" t="s">
+      <c r="C97" s="77" t="s">
         <v>61</v>
       </c>
-      <c r="D97" s="55"/>
-      <c r="E97" s="56" t="s">
+      <c r="D97" s="78"/>
+      <c r="E97" s="79" t="s">
         <v>63</v>
       </c>
-      <c r="F97" s="57">
+      <c r="F97" s="80">
         <v>46257</v>
       </c>
-      <c r="G97" s="58" t="s">
+      <c r="G97" s="81" t="s">
         <v>59</v>
       </c>
-      <c r="H97" s="58">
+      <c r="H97" s="81">
         <v>59</v>
       </c>
-      <c r="I97" s="58">
+      <c r="I97" s="81">
         <v>3</v>
       </c>
-      <c r="J97" s="58" t="s">
+      <c r="J97" s="81" t="s">
         <v>63</v>
       </c>
-      <c r="K97" s="59">
+      <c r="K97" s="82">
         <v>162006463</v>
       </c>
-      <c r="L97" s="60">
+      <c r="L97" s="83">
         <v>46258</v>
       </c>
-      <c r="M97" s="61"/>
-      <c r="N97" s="62"/>
-      <c r="O97" s="63"/>
-      <c r="P97" s="63"/>
-      <c r="Q97" s="63"/>
-      <c r="R97" s="64"/>
-      <c r="S97" s="64"/>
-      <c r="T97" s="64">
+      <c r="M97" s="84">
+        <v>46260</v>
+      </c>
+      <c r="N97" s="85">
+        <v>16620</v>
+      </c>
+      <c r="O97" s="86"/>
+      <c r="P97" s="86"/>
+      <c r="Q97" s="86"/>
+      <c r="R97" s="46">
+        <v>5067.75</v>
+      </c>
+      <c r="S97" s="46">
+        <v>1175.8499999999999</v>
+      </c>
+      <c r="T97" s="46">
         <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="U97" s="64"/>
-      <c r="V97" s="64"/>
-      <c r="W97" s="64"/>
-      <c r="X97" s="64"/>
-      <c r="Y97" s="64"/>
-      <c r="Z97" s="64">
+        <v>3891.9</v>
+      </c>
+      <c r="U97" s="46">
+        <v>3905.2</v>
+      </c>
+      <c r="V97" s="46"/>
+      <c r="W97" s="46"/>
+      <c r="X97" s="46">
+        <v>4017</v>
+      </c>
+      <c r="Y97" s="46"/>
+      <c r="Z97" s="46">
         <f>+T97-X97</f>
-        <v>0</v>
-      </c>
-      <c r="AA97" s="65" t="e">
+        <v>-125.09999999999991</v>
+      </c>
+      <c r="AA97" s="39">
         <f>Z97/T97</f>
+        <v>-3.2143683033993654E-2</v>
+      </c>
+      <c r="AB97" s="73">
+        <v>3891.25</v>
+      </c>
+      <c r="AC97" s="73"/>
+      <c r="AD97" s="73"/>
+      <c r="AE97" s="39"/>
+      <c r="AF97" s="74"/>
+      <c r="AG97" s="74"/>
+      <c r="AH97" s="75"/>
+      <c r="AI97" s="75">
+        <f t="shared" si="64"/>
+        <v>0</v>
+      </c>
+      <c r="AJ97" s="87"/>
+      <c r="AK97" s="87"/>
+      <c r="AL97" s="87"/>
+      <c r="AM97" s="88"/>
+      <c r="AN97" s="88"/>
+      <c r="AO97" s="88"/>
+      <c r="AP97" s="89">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="AQ97" s="87">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
+      <c r="AR97" s="87">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="AS97" s="87"/>
+      <c r="AT97" s="87"/>
+      <c r="AU97" s="87"/>
+      <c r="AV97" s="87"/>
+      <c r="AW97" s="87"/>
+      <c r="AX97" s="87"/>
+      <c r="AY97" s="87"/>
+      <c r="AZ97" s="90"/>
+      <c r="BB97" s="92">
+        <f>IF(AND(AB97="",AC97=""),T97,IF(AC97="",AB97,AC97))</f>
+        <v>3891.25</v>
+      </c>
+      <c r="BC97" s="92">
+        <f>+X97</f>
+        <v>4017</v>
+      </c>
+      <c r="BD97" s="92"/>
+      <c r="BE97" s="92">
+        <f t="shared" si="68"/>
+        <v>-125.75</v>
+      </c>
+      <c r="BF97" s="39">
+        <f t="shared" si="69"/>
+        <v>-3.2316093800192743E-2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:58" s="91" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A98" s="76">
+        <f>IF(ISBLANK(F98),"",COUNTA($F$6:F98))</f>
+        <v>93</v>
+      </c>
+      <c r="B98" s="77" t="s">
+        <v>60</v>
+      </c>
+      <c r="C98" s="77" t="s">
+        <v>61</v>
+      </c>
+      <c r="D98" s="78"/>
+      <c r="E98" s="79" t="s">
+        <v>65</v>
+      </c>
+      <c r="F98" s="80">
+        <v>46259</v>
+      </c>
+      <c r="G98" s="81" t="s">
+        <v>59</v>
+      </c>
+      <c r="H98" s="81">
+        <v>58</v>
+      </c>
+      <c r="I98" s="81">
+        <v>3</v>
+      </c>
+      <c r="J98" s="81" t="s">
+        <v>67</v>
+      </c>
+      <c r="K98" s="82">
+        <v>162011729</v>
+      </c>
+      <c r="L98" s="83">
+        <v>46259</v>
+      </c>
+      <c r="M98" s="84">
+        <v>46261</v>
+      </c>
+      <c r="N98" s="85">
+        <v>16626</v>
+      </c>
+      <c r="O98" s="86"/>
+      <c r="P98" s="86"/>
+      <c r="Q98" s="86"/>
+      <c r="R98" s="46">
+        <v>4989.3999999999996</v>
+      </c>
+      <c r="S98" s="46">
+        <v>1154.0999999999995</v>
+      </c>
+      <c r="T98" s="46">
+        <f t="shared" si="63"/>
+        <v>3835.3</v>
+      </c>
+      <c r="U98" s="46">
+        <v>3870.4</v>
+      </c>
+      <c r="V98" s="46"/>
+      <c r="W98" s="46"/>
+      <c r="X98" s="46">
+        <v>3890.3</v>
+      </c>
+      <c r="Y98" s="46"/>
+      <c r="Z98" s="46">
+        <f>+T98-X98</f>
+        <v>-55</v>
+      </c>
+      <c r="AA98" s="39">
+        <f>Z98/T98</f>
+        <v>-1.4340468802961958E-2</v>
+      </c>
+      <c r="AB98" s="73">
+        <v>3847.16</v>
+      </c>
+      <c r="AC98" s="73"/>
+      <c r="AD98" s="73"/>
+      <c r="AE98" s="39"/>
+      <c r="AF98" s="74"/>
+      <c r="AG98" s="74"/>
+      <c r="AH98" s="75"/>
+      <c r="AI98" s="75">
+        <f t="shared" si="64"/>
+        <v>0</v>
+      </c>
+      <c r="AJ98" s="87"/>
+      <c r="AK98" s="87"/>
+      <c r="AL98" s="87"/>
+      <c r="AM98" s="88"/>
+      <c r="AN98" s="88"/>
+      <c r="AO98" s="88"/>
+      <c r="AP98" s="89">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="AQ98" s="87">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
+      <c r="AR98" s="87">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="AS98" s="87"/>
+      <c r="AT98" s="87"/>
+      <c r="AU98" s="87"/>
+      <c r="AV98" s="87"/>
+      <c r="AW98" s="87"/>
+      <c r="AX98" s="87"/>
+      <c r="AY98" s="87"/>
+      <c r="AZ98" s="90"/>
+      <c r="BB98" s="92">
+        <f>IF(AND(AB98="",AC98=""),T98,IF(AC98="",AB98,AC98))</f>
+        <v>3847.16</v>
+      </c>
+      <c r="BC98" s="92">
+        <f>+X98</f>
+        <v>3890.3</v>
+      </c>
+      <c r="BD98" s="92"/>
+      <c r="BE98" s="92">
+        <f t="shared" si="68"/>
+        <v>-43.140000000000327</v>
+      </c>
+      <c r="BF98" s="39">
+        <f t="shared" si="69"/>
+        <v>-1.1213466557148735E-2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:58" s="91" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A99" s="76">
+        <f>IF(ISBLANK(F99),"",COUNTA($F$6:F99))</f>
+        <v>94</v>
+      </c>
+      <c r="B99" s="77" t="s">
+        <v>60</v>
+      </c>
+      <c r="C99" s="77" t="s">
+        <v>61</v>
+      </c>
+      <c r="D99" s="78"/>
+      <c r="E99" s="79" t="s">
+        <v>66</v>
+      </c>
+      <c r="F99" s="80">
+        <v>46259</v>
+      </c>
+      <c r="G99" s="81" t="s">
+        <v>59</v>
+      </c>
+      <c r="H99" s="81">
+        <v>59</v>
+      </c>
+      <c r="I99" s="81">
+        <v>0</v>
+      </c>
+      <c r="J99" s="81" t="s">
+        <v>66</v>
+      </c>
+      <c r="K99" s="82">
+        <v>162003217</v>
+      </c>
+      <c r="L99" s="83">
+        <v>46259</v>
+      </c>
+      <c r="M99" s="84">
+        <v>46261</v>
+      </c>
+      <c r="N99" s="85">
+        <v>16627</v>
+      </c>
+      <c r="O99" s="86"/>
+      <c r="P99" s="86"/>
+      <c r="Q99" s="86"/>
+      <c r="R99" s="46">
+        <v>5350.5</v>
+      </c>
+      <c r="S99" s="46">
+        <v>1233.5</v>
+      </c>
+      <c r="T99" s="46">
+        <f t="shared" si="63"/>
+        <v>4117</v>
+      </c>
+      <c r="U99" s="46">
+        <v>4117.2</v>
+      </c>
+      <c r="V99" s="46"/>
+      <c r="W99" s="46"/>
+      <c r="X99" s="46">
+        <v>4223.2</v>
+      </c>
+      <c r="Y99" s="46"/>
+      <c r="Z99" s="46">
+        <f>+T99-X99</f>
+        <v>-106.19999999999982</v>
+      </c>
+      <c r="AA99" s="39">
+        <f>Z99/T99</f>
+        <v>-2.5795482147194515E-2</v>
+      </c>
+      <c r="AB99" s="73">
+        <v>4117.07</v>
+      </c>
+      <c r="AC99" s="73"/>
+      <c r="AD99" s="73"/>
+      <c r="AE99" s="39"/>
+      <c r="AF99" s="74"/>
+      <c r="AG99" s="74"/>
+      <c r="AH99" s="75"/>
+      <c r="AI99" s="75">
+        <f t="shared" si="64"/>
+        <v>0</v>
+      </c>
+      <c r="AJ99" s="87"/>
+      <c r="AK99" s="87"/>
+      <c r="AL99" s="87"/>
+      <c r="AM99" s="88"/>
+      <c r="AN99" s="88"/>
+      <c r="AO99" s="88"/>
+      <c r="AP99" s="89">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="AQ99" s="87">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
+      <c r="AR99" s="87">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="AS99" s="87"/>
+      <c r="AT99" s="87"/>
+      <c r="AU99" s="87"/>
+      <c r="AV99" s="87"/>
+      <c r="AW99" s="87"/>
+      <c r="AX99" s="87"/>
+      <c r="AY99" s="87"/>
+      <c r="AZ99" s="90"/>
+      <c r="BB99" s="92">
+        <f>IF(AND(AB99="",AC99=""),T99,IF(AC99="",AB99,AC99))</f>
+        <v>4117.07</v>
+      </c>
+      <c r="BC99" s="92">
+        <f>+X99</f>
+        <v>4223.2</v>
+      </c>
+      <c r="BD99" s="92"/>
+      <c r="BE99" s="92">
+        <f t="shared" si="68"/>
+        <v>-106.13000000000011</v>
+      </c>
+      <c r="BF99" s="39">
+        <f t="shared" si="69"/>
+        <v>-2.5778041179771078E-2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:58" s="91" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A100" s="76">
+        <f>IF(ISBLANK(F100),"",COUNTA($F$6:F100))</f>
+        <v>95</v>
+      </c>
+      <c r="B100" s="77" t="s">
+        <v>60</v>
+      </c>
+      <c r="C100" s="77" t="s">
+        <v>61</v>
+      </c>
+      <c r="D100" s="78"/>
+      <c r="E100" s="79" t="s">
+        <v>63</v>
+      </c>
+      <c r="F100" s="80">
+        <v>46260</v>
+      </c>
+      <c r="G100" s="81" t="s">
+        <v>59</v>
+      </c>
+      <c r="H100" s="81">
+        <v>58</v>
+      </c>
+      <c r="I100" s="81">
+        <v>1</v>
+      </c>
+      <c r="J100" s="81" t="s">
+        <v>63</v>
+      </c>
+      <c r="K100" s="82">
+        <v>162006472</v>
+      </c>
+      <c r="L100" s="83">
+        <v>46260</v>
+      </c>
+      <c r="M100" s="84">
+        <v>46262</v>
+      </c>
+      <c r="N100" s="85">
+        <v>16631</v>
+      </c>
+      <c r="O100" s="86"/>
+      <c r="P100" s="86"/>
+      <c r="Q100" s="86"/>
+      <c r="R100" s="46">
+        <v>5174.1499999999996</v>
+      </c>
+      <c r="S100" s="46">
+        <v>1218.5499999999997</v>
+      </c>
+      <c r="T100" s="46">
+        <f t="shared" si="63"/>
+        <v>3955.6</v>
+      </c>
+      <c r="U100" s="46">
+        <v>3962.8</v>
+      </c>
+      <c r="V100" s="46"/>
+      <c r="W100" s="46"/>
+      <c r="X100" s="46">
+        <v>4007.4</v>
+      </c>
+      <c r="Y100" s="46"/>
+      <c r="Z100" s="46">
+        <f>+T100-X100</f>
+        <v>-51.800000000000182</v>
+      </c>
+      <c r="AA100" s="39">
+        <f>Z100/T100</f>
+        <v>-1.3095358479118259E-2</v>
+      </c>
+      <c r="AB100" s="73">
+        <v>3955.55</v>
+      </c>
+      <c r="AC100" s="73"/>
+      <c r="AD100" s="73"/>
+      <c r="AE100" s="39"/>
+      <c r="AF100" s="74"/>
+      <c r="AG100" s="74"/>
+      <c r="AH100" s="75"/>
+      <c r="AI100" s="75">
+        <f t="shared" si="64"/>
+        <v>0</v>
+      </c>
+      <c r="AJ100" s="87"/>
+      <c r="AK100" s="87"/>
+      <c r="AL100" s="87"/>
+      <c r="AM100" s="88"/>
+      <c r="AN100" s="88"/>
+      <c r="AO100" s="88"/>
+      <c r="AP100" s="89">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="AQ100" s="87">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
+      <c r="AR100" s="87">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="AS100" s="87"/>
+      <c r="AT100" s="87"/>
+      <c r="AU100" s="87"/>
+      <c r="AV100" s="87"/>
+      <c r="AW100" s="87"/>
+      <c r="AX100" s="87"/>
+      <c r="AY100" s="87"/>
+      <c r="AZ100" s="90"/>
+      <c r="BB100" s="92">
+        <f>IF(AND(AB100="",AC100=""),T100,IF(AC100="",AB100,AC100))</f>
+        <v>3955.55</v>
+      </c>
+      <c r="BC100" s="92">
+        <f>+X100</f>
+        <v>4007.4</v>
+      </c>
+      <c r="BD100" s="92"/>
+      <c r="BE100" s="92">
+        <f t="shared" si="68"/>
+        <v>-51.849999999999909</v>
+      </c>
+      <c r="BF100" s="39">
+        <f t="shared" si="69"/>
+        <v>-1.3108164477759074E-2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:58" s="91" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A101" s="76">
+        <f>IF(ISBLANK(F101),"",COUNTA($F$6:F101))</f>
+        <v>96</v>
+      </c>
+      <c r="B101" s="77" t="s">
+        <v>60</v>
+      </c>
+      <c r="C101" s="77" t="s">
+        <v>61</v>
+      </c>
+      <c r="D101" s="78"/>
+      <c r="E101" s="79" t="s">
+        <v>66</v>
+      </c>
+      <c r="F101" s="80">
+        <v>46260</v>
+      </c>
+      <c r="G101" s="81" t="s">
+        <v>59</v>
+      </c>
+      <c r="H101" s="81">
+        <v>58</v>
+      </c>
+      <c r="I101" s="81">
+        <v>1</v>
+      </c>
+      <c r="J101" s="81" t="s">
+        <v>66</v>
+      </c>
+      <c r="K101" s="82">
+        <v>162003219</v>
+      </c>
+      <c r="L101" s="83">
+        <v>46260</v>
+      </c>
+      <c r="M101" s="84">
+        <v>46262</v>
+      </c>
+      <c r="N101" s="85">
+        <v>16629</v>
+      </c>
+      <c r="O101" s="86"/>
+      <c r="P101" s="86"/>
+      <c r="Q101" s="86"/>
+      <c r="R101" s="46">
+        <v>5168.46</v>
+      </c>
+      <c r="S101" s="46">
+        <v>1195.2600000000002</v>
+      </c>
+      <c r="T101" s="46">
+        <f t="shared" si="63"/>
+        <v>3973.2</v>
+      </c>
+      <c r="U101" s="46">
+        <v>3973.2</v>
+      </c>
+      <c r="V101" s="46"/>
+      <c r="W101" s="46"/>
+      <c r="X101" s="46">
+        <v>3911.6</v>
+      </c>
+      <c r="Y101" s="46"/>
+      <c r="Z101" s="46">
+        <f>+T101-X101</f>
+        <v>61.599999999999909</v>
+      </c>
+      <c r="AA101" s="39">
+        <f>Z101/T101</f>
+        <v>1.5503875968992225E-2</v>
+      </c>
+      <c r="AB101" s="73">
+        <v>3973.16</v>
+      </c>
+      <c r="AC101" s="73"/>
+      <c r="AD101" s="73"/>
+      <c r="AE101" s="39"/>
+      <c r="AF101" s="74"/>
+      <c r="AG101" s="74"/>
+      <c r="AH101" s="75"/>
+      <c r="AI101" s="75">
+        <f t="shared" si="64"/>
+        <v>0</v>
+      </c>
+      <c r="AJ101" s="87"/>
+      <c r="AK101" s="87"/>
+      <c r="AL101" s="87"/>
+      <c r="AM101" s="88"/>
+      <c r="AN101" s="88"/>
+      <c r="AO101" s="88"/>
+      <c r="AP101" s="89">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="AQ101" s="87">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
+      <c r="AR101" s="87">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="AS101" s="87"/>
+      <c r="AT101" s="87"/>
+      <c r="AU101" s="87"/>
+      <c r="AV101" s="87"/>
+      <c r="AW101" s="87"/>
+      <c r="AX101" s="87"/>
+      <c r="AY101" s="87"/>
+      <c r="AZ101" s="90"/>
+      <c r="BB101" s="92">
+        <f>IF(AND(AB101="",AC101=""),T101,IF(AC101="",AB101,AC101))</f>
+        <v>3973.16</v>
+      </c>
+      <c r="BC101" s="92">
+        <f>+X101</f>
+        <v>3911.6</v>
+      </c>
+      <c r="BD101" s="92"/>
+      <c r="BE101" s="92">
+        <f t="shared" si="68"/>
+        <v>61.559999999999945</v>
+      </c>
+      <c r="BF101" s="39">
+        <f t="shared" si="69"/>
+        <v>1.5493964501807112E-2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:58" s="91" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A102" s="76">
+        <f>IF(ISBLANK(F102),"",COUNTA($F$6:F102))</f>
+        <v>97</v>
+      </c>
+      <c r="B102" s="77" t="s">
+        <v>60</v>
+      </c>
+      <c r="C102" s="77" t="s">
+        <v>61</v>
+      </c>
+      <c r="D102" s="78"/>
+      <c r="E102" s="79" t="s">
+        <v>65</v>
+      </c>
+      <c r="F102" s="80">
+        <v>46260</v>
+      </c>
+      <c r="G102" s="81" t="s">
+        <v>59</v>
+      </c>
+      <c r="H102" s="81">
+        <v>58</v>
+      </c>
+      <c r="I102" s="81">
+        <v>2</v>
+      </c>
+      <c r="J102" s="81" t="s">
+        <v>67</v>
+      </c>
+      <c r="K102" s="82">
+        <v>162011731</v>
+      </c>
+      <c r="L102" s="83">
+        <v>46260</v>
+      </c>
+      <c r="M102" s="84">
+        <v>46263</v>
+      </c>
+      <c r="N102" s="85">
+        <v>16634</v>
+      </c>
+      <c r="O102" s="86"/>
+      <c r="P102" s="86"/>
+      <c r="Q102" s="86"/>
+      <c r="R102" s="46">
+        <v>4900.8</v>
+      </c>
+      <c r="S102" s="46">
+        <v>1179.4000000000001</v>
+      </c>
+      <c r="T102" s="46">
+        <f t="shared" si="63"/>
+        <v>3721.4</v>
+      </c>
+      <c r="U102" s="46">
+        <v>3915</v>
+      </c>
+      <c r="V102" s="46"/>
+      <c r="W102" s="46"/>
+      <c r="X102" s="46">
+        <v>3693.2</v>
+      </c>
+      <c r="Y102" s="46"/>
+      <c r="Z102" s="46">
+        <f>+T102-X102</f>
+        <v>28.200000000000273</v>
+      </c>
+      <c r="AA102" s="39">
+        <f>Z102/T102</f>
+        <v>7.5777933035954944E-3</v>
+      </c>
+      <c r="AB102" s="73">
+        <v>3736.33</v>
+      </c>
+      <c r="AC102" s="73"/>
+      <c r="AD102" s="73"/>
+      <c r="AE102" s="39"/>
+      <c r="AF102" s="74"/>
+      <c r="AG102" s="74"/>
+      <c r="AH102" s="75"/>
+      <c r="AI102" s="75">
+        <f t="shared" si="64"/>
+        <v>0</v>
+      </c>
+      <c r="AJ102" s="87"/>
+      <c r="AK102" s="87"/>
+      <c r="AL102" s="87"/>
+      <c r="AM102" s="88"/>
+      <c r="AN102" s="88"/>
+      <c r="AO102" s="88"/>
+      <c r="AP102" s="89">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="AQ102" s="87">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
+      <c r="AR102" s="87">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="AS102" s="87"/>
+      <c r="AT102" s="87"/>
+      <c r="AU102" s="87"/>
+      <c r="AV102" s="87"/>
+      <c r="AW102" s="87"/>
+      <c r="AX102" s="87"/>
+      <c r="AY102" s="87"/>
+      <c r="AZ102" s="90"/>
+      <c r="BB102" s="92">
+        <f>IF(AND(AB102="",AC102=""),T102,IF(AC102="",AB102,AC102))</f>
+        <v>3736.33</v>
+      </c>
+      <c r="BC102" s="92">
+        <f>+X102</f>
+        <v>3693.2</v>
+      </c>
+      <c r="BD102" s="92"/>
+      <c r="BE102" s="92">
+        <f t="shared" si="68"/>
+        <v>43.130000000000109</v>
+      </c>
+      <c r="BF102" s="39">
+        <f t="shared" si="69"/>
+        <v>1.1543412921235573E-2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:58" s="91" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A103" s="76">
+        <f>IF(ISBLANK(F103),"",COUNTA($F$6:F103))</f>
+        <v>98</v>
+      </c>
+      <c r="B103" s="77" t="s">
+        <v>60</v>
+      </c>
+      <c r="C103" s="77" t="s">
+        <v>61</v>
+      </c>
+      <c r="D103" s="78"/>
+      <c r="E103" s="79" t="s">
+        <v>63</v>
+      </c>
+      <c r="F103" s="80">
+        <v>46261</v>
+      </c>
+      <c r="G103" s="81" t="s">
+        <v>59</v>
+      </c>
+      <c r="H103" s="81">
+        <v>59</v>
+      </c>
+      <c r="I103" s="81">
+        <v>12</v>
+      </c>
+      <c r="J103" s="81" t="s">
+        <v>63</v>
+      </c>
+      <c r="K103" s="82">
+        <v>162006475</v>
+      </c>
+      <c r="L103" s="83">
+        <v>46261</v>
+      </c>
+      <c r="M103" s="84">
+        <v>46262</v>
+      </c>
+      <c r="N103" s="85">
+        <v>16633</v>
+      </c>
+      <c r="O103" s="86"/>
+      <c r="P103" s="86"/>
+      <c r="Q103" s="86"/>
+      <c r="R103" s="46">
+        <v>4262.7700000000004</v>
+      </c>
+      <c r="S103" s="46">
+        <v>977.67000000000053</v>
+      </c>
+      <c r="T103" s="46">
+        <f t="shared" ref="T103:T112" si="70">+R103-S103</f>
+        <v>3285.1</v>
+      </c>
+      <c r="U103" s="46">
+        <v>3289</v>
+      </c>
+      <c r="V103" s="46"/>
+      <c r="W103" s="46"/>
+      <c r="X103" s="46">
+        <v>3300.2</v>
+      </c>
+      <c r="Y103" s="46"/>
+      <c r="Z103" s="46">
+        <f>+T103-X103</f>
+        <v>-15.099999999999909</v>
+      </c>
+      <c r="AA103" s="39">
+        <f>Z103/T103</f>
+        <v>-4.5965115217192504E-3</v>
+      </c>
+      <c r="AB103" s="73"/>
+      <c r="AC103" s="73"/>
+      <c r="AD103" s="73"/>
+      <c r="AE103" s="39"/>
+      <c r="AF103" s="74"/>
+      <c r="AG103" s="74"/>
+      <c r="AH103" s="75"/>
+      <c r="AI103" s="75">
+        <f t="shared" ref="AI103:AI112" si="71">+AG103+AH103</f>
+        <v>0</v>
+      </c>
+      <c r="AJ103" s="87"/>
+      <c r="AK103" s="87"/>
+      <c r="AL103" s="87"/>
+      <c r="AM103" s="88"/>
+      <c r="AN103" s="88"/>
+      <c r="AO103" s="88"/>
+      <c r="AP103" s="89">
+        <f t="shared" ref="AP103:AP112" si="72">ROUNDUP((AO103-AM103+(AO103&lt;AM103))*24,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ103" s="87">
+        <f t="shared" ref="AQ103:AQ112" si="73">IF(AP103&gt;5,(AP103-5),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AR103" s="87">
+        <f t="shared" ref="AR103:AR112" si="74">+AQ103*8850</f>
+        <v>0</v>
+      </c>
+      <c r="AS103" s="87"/>
+      <c r="AT103" s="87"/>
+      <c r="AU103" s="87"/>
+      <c r="AV103" s="87"/>
+      <c r="AW103" s="87"/>
+      <c r="AX103" s="87"/>
+      <c r="AY103" s="87"/>
+      <c r="AZ103" s="90"/>
+      <c r="BB103" s="92">
+        <f>IF(AND(AB103="",AC103=""),T103,IF(AC103="",AB103,AC103))</f>
+        <v>3285.1</v>
+      </c>
+      <c r="BC103" s="92">
+        <f>+X103</f>
+        <v>3300.2</v>
+      </c>
+      <c r="BD103" s="92"/>
+      <c r="BE103" s="92">
+        <f t="shared" ref="BE103:BE112" si="75">+BB103-BC103</f>
+        <v>-15.099999999999909</v>
+      </c>
+      <c r="BF103" s="39">
+        <f t="shared" ref="BF103:BF112" si="76">+BE103/BB103</f>
+        <v>-4.5965115217192504E-3</v>
+      </c>
+    </row>
+    <row r="104" spans="1:58" s="91" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A104" s="76">
+        <f>IF(ISBLANK(F104),"",COUNTA($F$6:F104))</f>
+        <v>99</v>
+      </c>
+      <c r="B104" s="77" t="s">
+        <v>60</v>
+      </c>
+      <c r="C104" s="77" t="s">
+        <v>61</v>
+      </c>
+      <c r="D104" s="78"/>
+      <c r="E104" s="79" t="s">
+        <v>65</v>
+      </c>
+      <c r="F104" s="80">
+        <v>46261</v>
+      </c>
+      <c r="G104" s="81" t="s">
+        <v>59</v>
+      </c>
+      <c r="H104" s="81">
+        <v>58</v>
+      </c>
+      <c r="I104" s="81">
+        <v>2</v>
+      </c>
+      <c r="J104" s="81" t="s">
+        <v>67</v>
+      </c>
+      <c r="K104" s="82">
+        <v>162011733</v>
+      </c>
+      <c r="L104" s="83">
+        <v>46261</v>
+      </c>
+      <c r="M104" s="84">
+        <v>46263</v>
+      </c>
+      <c r="N104" s="85">
+        <v>16636</v>
+      </c>
+      <c r="O104" s="86"/>
+      <c r="P104" s="86"/>
+      <c r="Q104" s="86"/>
+      <c r="R104" s="46">
+        <v>4922.2</v>
+      </c>
+      <c r="S104" s="46">
+        <v>1153.5999999999999</v>
+      </c>
+      <c r="T104" s="46">
+        <f t="shared" si="70"/>
+        <v>3768.6</v>
+      </c>
+      <c r="U104" s="46">
+        <v>3932.6</v>
+      </c>
+      <c r="V104" s="46"/>
+      <c r="W104" s="46"/>
+      <c r="X104" s="46">
+        <v>3810.8</v>
+      </c>
+      <c r="Y104" s="46"/>
+      <c r="Z104" s="46">
+        <f>+T104-X104</f>
+        <v>-42.200000000000273</v>
+      </c>
+      <c r="AA104" s="39">
+        <f>Z104/T104</f>
+        <v>-1.1197792283606718E-2</v>
+      </c>
+      <c r="AB104" s="73">
+        <v>3788.6</v>
+      </c>
+      <c r="AC104" s="73"/>
+      <c r="AD104" s="73"/>
+      <c r="AE104" s="39"/>
+      <c r="AF104" s="74"/>
+      <c r="AG104" s="74"/>
+      <c r="AH104" s="75"/>
+      <c r="AI104" s="75">
+        <f t="shared" si="71"/>
+        <v>0</v>
+      </c>
+      <c r="AJ104" s="87"/>
+      <c r="AK104" s="87"/>
+      <c r="AL104" s="87"/>
+      <c r="AM104" s="88"/>
+      <c r="AN104" s="88"/>
+      <c r="AO104" s="88"/>
+      <c r="AP104" s="89">
+        <f t="shared" si="72"/>
+        <v>0</v>
+      </c>
+      <c r="AQ104" s="87">
+        <f t="shared" si="73"/>
+        <v>0</v>
+      </c>
+      <c r="AR104" s="87">
+        <f t="shared" si="74"/>
+        <v>0</v>
+      </c>
+      <c r="AS104" s="87"/>
+      <c r="AT104" s="87"/>
+      <c r="AU104" s="87"/>
+      <c r="AV104" s="87"/>
+      <c r="AW104" s="87"/>
+      <c r="AX104" s="87"/>
+      <c r="AY104" s="87"/>
+      <c r="AZ104" s="90"/>
+      <c r="BB104" s="92">
+        <f>IF(AND(AB104="",AC104=""),T104,IF(AC104="",AB104,AC104))</f>
+        <v>3788.6</v>
+      </c>
+      <c r="BC104" s="92">
+        <f>+X104</f>
+        <v>3810.8</v>
+      </c>
+      <c r="BD104" s="92"/>
+      <c r="BE104" s="92">
+        <f t="shared" si="75"/>
+        <v>-22.200000000000273</v>
+      </c>
+      <c r="BF104" s="39">
+        <f t="shared" si="76"/>
+        <v>-5.8596843161062857E-3</v>
+      </c>
+    </row>
+    <row r="105" spans="1:58" s="91" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A105" s="76">
+        <f>IF(ISBLANK(F105),"",COUNTA($F$6:F105))</f>
+        <v>100</v>
+      </c>
+      <c r="B105" s="77" t="s">
+        <v>60</v>
+      </c>
+      <c r="C105" s="77" t="s">
+        <v>61</v>
+      </c>
+      <c r="D105" s="78"/>
+      <c r="E105" s="79" t="s">
+        <v>66</v>
+      </c>
+      <c r="F105" s="80">
+        <v>46261</v>
+      </c>
+      <c r="G105" s="81" t="s">
+        <v>59</v>
+      </c>
+      <c r="H105" s="81">
+        <v>58</v>
+      </c>
+      <c r="I105" s="81">
+        <v>1</v>
+      </c>
+      <c r="J105" s="81" t="s">
+        <v>66</v>
+      </c>
+      <c r="K105" s="82">
+        <v>162003223</v>
+      </c>
+      <c r="L105" s="83">
+        <v>46261</v>
+      </c>
+      <c r="M105" s="84">
+        <v>46264</v>
+      </c>
+      <c r="N105" s="85">
+        <v>16637</v>
+      </c>
+      <c r="O105" s="86"/>
+      <c r="P105" s="86"/>
+      <c r="Q105" s="86"/>
+      <c r="R105" s="46">
+        <v>5170.7</v>
+      </c>
+      <c r="S105" s="46">
+        <v>1196.6999999999998</v>
+      </c>
+      <c r="T105" s="46">
+        <f t="shared" si="70"/>
+        <v>3974</v>
+      </c>
+      <c r="U105" s="46">
+        <v>3974</v>
+      </c>
+      <c r="V105" s="46"/>
+      <c r="W105" s="46"/>
+      <c r="X105" s="46">
+        <v>4100.08</v>
+      </c>
+      <c r="Y105" s="46"/>
+      <c r="Z105" s="46">
+        <f>+T105-X105</f>
+        <v>-126.07999999999993</v>
+      </c>
+      <c r="AA105" s="39">
+        <f>Z105/T105</f>
+        <v>-3.1726220432813271E-2</v>
+      </c>
+      <c r="AB105" s="73">
+        <v>3973.98</v>
+      </c>
+      <c r="AC105" s="73"/>
+      <c r="AD105" s="73"/>
+      <c r="AE105" s="39"/>
+      <c r="AF105" s="74"/>
+      <c r="AG105" s="74"/>
+      <c r="AH105" s="75"/>
+      <c r="AI105" s="75">
+        <f t="shared" si="71"/>
+        <v>0</v>
+      </c>
+      <c r="AJ105" s="87"/>
+      <c r="AK105" s="87"/>
+      <c r="AL105" s="87"/>
+      <c r="AM105" s="88"/>
+      <c r="AN105" s="88"/>
+      <c r="AO105" s="88"/>
+      <c r="AP105" s="89">
+        <f t="shared" si="72"/>
+        <v>0</v>
+      </c>
+      <c r="AQ105" s="87">
+        <f t="shared" si="73"/>
+        <v>0</v>
+      </c>
+      <c r="AR105" s="87">
+        <f t="shared" si="74"/>
+        <v>0</v>
+      </c>
+      <c r="AS105" s="87"/>
+      <c r="AT105" s="87"/>
+      <c r="AU105" s="87"/>
+      <c r="AV105" s="87"/>
+      <c r="AW105" s="87"/>
+      <c r="AX105" s="87"/>
+      <c r="AY105" s="87"/>
+      <c r="AZ105" s="90"/>
+      <c r="BB105" s="92">
+        <f>IF(AND(AB105="",AC105=""),T105,IF(AC105="",AB105,AC105))</f>
+        <v>3973.98</v>
+      </c>
+      <c r="BC105" s="92">
+        <f>+X105</f>
+        <v>4100.08</v>
+      </c>
+      <c r="BD105" s="92"/>
+      <c r="BE105" s="92">
+        <f t="shared" si="75"/>
+        <v>-126.09999999999991</v>
+      </c>
+      <c r="BF105" s="39">
+        <f t="shared" si="76"/>
+        <v>-3.1731412840527606E-2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:58" s="91" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A106" s="76">
+        <f>IF(ISBLANK(F106),"",COUNTA($F$6:F106))</f>
+        <v>101</v>
+      </c>
+      <c r="B106" s="77" t="s">
+        <v>60</v>
+      </c>
+      <c r="C106" s="77" t="s">
+        <v>61</v>
+      </c>
+      <c r="D106" s="78"/>
+      <c r="E106" s="79" t="s">
+        <v>66</v>
+      </c>
+      <c r="F106" s="80">
+        <v>46262</v>
+      </c>
+      <c r="G106" s="81" t="s">
+        <v>59</v>
+      </c>
+      <c r="H106" s="81">
+        <v>57</v>
+      </c>
+      <c r="I106" s="81">
+        <v>2</v>
+      </c>
+      <c r="J106" s="81" t="s">
+        <v>66</v>
+      </c>
+      <c r="K106" s="82">
+        <v>162003225</v>
+      </c>
+      <c r="L106" s="83">
+        <v>46262</v>
+      </c>
+      <c r="M106" s="84">
+        <v>46265</v>
+      </c>
+      <c r="N106" s="85">
+        <v>16641</v>
+      </c>
+      <c r="O106" s="86"/>
+      <c r="P106" s="86"/>
+      <c r="Q106" s="86"/>
+      <c r="R106" s="46">
+        <v>4989.8</v>
+      </c>
+      <c r="S106" s="46">
+        <v>1147.5</v>
+      </c>
+      <c r="T106" s="46">
+        <f t="shared" si="70"/>
+        <v>3842.3</v>
+      </c>
+      <c r="U106" s="46">
+        <v>3842.4</v>
+      </c>
+      <c r="V106" s="46"/>
+      <c r="W106" s="46"/>
+      <c r="X106" s="46">
+        <v>3848.2</v>
+      </c>
+      <c r="Y106" s="46"/>
+      <c r="Z106" s="46">
+        <f>+T106-X106</f>
+        <v>-5.8999999999996362</v>
+      </c>
+      <c r="AA106" s="39">
+        <f>Z106/T106</f>
+        <v>-1.5355386096868116E-3</v>
+      </c>
+      <c r="AB106" s="73">
+        <v>3842.28</v>
+      </c>
+      <c r="AC106" s="73"/>
+      <c r="AD106" s="73"/>
+      <c r="AE106" s="39"/>
+      <c r="AF106" s="74"/>
+      <c r="AG106" s="74"/>
+      <c r="AH106" s="75"/>
+      <c r="AI106" s="75">
+        <f t="shared" si="71"/>
+        <v>0</v>
+      </c>
+      <c r="AJ106" s="87"/>
+      <c r="AK106" s="87"/>
+      <c r="AL106" s="87"/>
+      <c r="AM106" s="88"/>
+      <c r="AN106" s="88"/>
+      <c r="AO106" s="88"/>
+      <c r="AP106" s="89">
+        <f t="shared" si="72"/>
+        <v>0</v>
+      </c>
+      <c r="AQ106" s="87">
+        <f t="shared" si="73"/>
+        <v>0</v>
+      </c>
+      <c r="AR106" s="87">
+        <f t="shared" si="74"/>
+        <v>0</v>
+      </c>
+      <c r="AS106" s="87"/>
+      <c r="AT106" s="87"/>
+      <c r="AU106" s="87"/>
+      <c r="AV106" s="87"/>
+      <c r="AW106" s="87"/>
+      <c r="AX106" s="87"/>
+      <c r="AY106" s="87"/>
+      <c r="AZ106" s="90"/>
+      <c r="BB106" s="92">
+        <f>IF(AND(AB106="",AC106=""),T106,IF(AC106="",AB106,AC106))</f>
+        <v>3842.28</v>
+      </c>
+      <c r="BC106" s="92">
+        <f>+X106</f>
+        <v>3848.2</v>
+      </c>
+      <c r="BD106" s="92"/>
+      <c r="BE106" s="92">
+        <f t="shared" si="75"/>
+        <v>-5.919999999999618</v>
+      </c>
+      <c r="BF106" s="39">
+        <f t="shared" si="76"/>
+        <v>-1.540751845258445E-3</v>
+      </c>
+    </row>
+    <row r="107" spans="1:58" s="91" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A107" s="76">
+        <f>IF(ISBLANK(F107),"",COUNTA($F$6:F107))</f>
+        <v>102</v>
+      </c>
+      <c r="B107" s="77" t="s">
+        <v>60</v>
+      </c>
+      <c r="C107" s="77" t="s">
+        <v>61</v>
+      </c>
+      <c r="D107" s="78"/>
+      <c r="E107" s="79" t="s">
+        <v>65</v>
+      </c>
+      <c r="F107" s="80">
+        <v>46262</v>
+      </c>
+      <c r="G107" s="81" t="s">
+        <v>59</v>
+      </c>
+      <c r="H107" s="81">
+        <v>58</v>
+      </c>
+      <c r="I107" s="81">
+        <v>4</v>
+      </c>
+      <c r="J107" s="81" t="s">
+        <v>67</v>
+      </c>
+      <c r="K107" s="82">
+        <v>162011736</v>
+      </c>
+      <c r="L107" s="83">
+        <v>46263</v>
+      </c>
+      <c r="M107" s="84">
+        <v>46265</v>
+      </c>
+      <c r="N107" s="85">
+        <v>16642</v>
+      </c>
+      <c r="O107" s="86"/>
+      <c r="P107" s="86"/>
+      <c r="Q107" s="86"/>
+      <c r="R107" s="46">
+        <v>4842</v>
+      </c>
+      <c r="S107" s="46">
+        <v>1125.5</v>
+      </c>
+      <c r="T107" s="46">
+        <f t="shared" si="70"/>
+        <v>3716.5</v>
+      </c>
+      <c r="U107" s="46">
+        <v>3801.8</v>
+      </c>
+      <c r="V107" s="46"/>
+      <c r="W107" s="46"/>
+      <c r="X107" s="46">
+        <v>3856.4</v>
+      </c>
+      <c r="Y107" s="46"/>
+      <c r="Z107" s="46">
+        <f>+T107-X107</f>
+        <v>-139.90000000000009</v>
+      </c>
+      <c r="AA107" s="39">
+        <f>Z107/T107</f>
+        <v>-3.7642943629759208E-2</v>
+      </c>
+      <c r="AB107" s="73">
+        <v>3738.64</v>
+      </c>
+      <c r="AC107" s="73"/>
+      <c r="AD107" s="73"/>
+      <c r="AE107" s="39"/>
+      <c r="AF107" s="74"/>
+      <c r="AG107" s="74"/>
+      <c r="AH107" s="75"/>
+      <c r="AI107" s="75">
+        <f t="shared" si="71"/>
+        <v>0</v>
+      </c>
+      <c r="AJ107" s="87"/>
+      <c r="AK107" s="87"/>
+      <c r="AL107" s="87"/>
+      <c r="AM107" s="88"/>
+      <c r="AN107" s="88"/>
+      <c r="AO107" s="88"/>
+      <c r="AP107" s="89">
+        <f t="shared" si="72"/>
+        <v>0</v>
+      </c>
+      <c r="AQ107" s="87">
+        <f t="shared" si="73"/>
+        <v>0</v>
+      </c>
+      <c r="AR107" s="87">
+        <f t="shared" si="74"/>
+        <v>0</v>
+      </c>
+      <c r="AS107" s="87"/>
+      <c r="AT107" s="87"/>
+      <c r="AU107" s="87"/>
+      <c r="AV107" s="87"/>
+      <c r="AW107" s="87"/>
+      <c r="AX107" s="87"/>
+      <c r="AY107" s="87"/>
+      <c r="AZ107" s="90"/>
+      <c r="BB107" s="92">
+        <f>IF(AND(AB107="",AC107=""),T107,IF(AC107="",AB107,AC107))</f>
+        <v>3738.64</v>
+      </c>
+      <c r="BC107" s="92">
+        <f>+X107</f>
+        <v>3856.4</v>
+      </c>
+      <c r="BD107" s="92"/>
+      <c r="BE107" s="92">
+        <f t="shared" si="75"/>
+        <v>-117.76000000000022</v>
+      </c>
+      <c r="BF107" s="39">
+        <f t="shared" si="76"/>
+        <v>-3.1498084865084687E-2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:58" s="91" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A108" s="76">
+        <f>IF(ISBLANK(F108),"",COUNTA($F$6:F108))</f>
+        <v>103</v>
+      </c>
+      <c r="B108" s="77" t="s">
+        <v>60</v>
+      </c>
+      <c r="C108" s="77" t="s">
+        <v>61</v>
+      </c>
+      <c r="D108" s="78"/>
+      <c r="E108" s="79" t="s">
+        <v>66</v>
+      </c>
+      <c r="F108" s="80">
+        <v>46262</v>
+      </c>
+      <c r="G108" s="81" t="s">
+        <v>59</v>
+      </c>
+      <c r="H108" s="81">
+        <v>59</v>
+      </c>
+      <c r="I108" s="81">
+        <v>2</v>
+      </c>
+      <c r="J108" s="81" t="s">
+        <v>66</v>
+      </c>
+      <c r="K108" s="82">
+        <v>162003226</v>
+      </c>
+      <c r="L108" s="83">
+        <v>46263</v>
+      </c>
+      <c r="M108" s="84">
+        <v>46264</v>
+      </c>
+      <c r="N108" s="85">
+        <v>16638</v>
+      </c>
+      <c r="O108" s="86"/>
+      <c r="P108" s="86"/>
+      <c r="Q108" s="86"/>
+      <c r="R108" s="46">
+        <v>5168.9399999999996</v>
+      </c>
+      <c r="S108" s="46">
+        <v>1193.2399999999998</v>
+      </c>
+      <c r="T108" s="46">
+        <f t="shared" si="70"/>
+        <v>3975.7</v>
+      </c>
+      <c r="U108" s="46">
+        <v>3975.8</v>
+      </c>
+      <c r="V108" s="46"/>
+      <c r="W108" s="46"/>
+      <c r="X108" s="46">
+        <v>3912.4</v>
+      </c>
+      <c r="Y108" s="46"/>
+      <c r="Z108" s="46">
+        <f>+T108-X108</f>
+        <v>63.299999999999727</v>
+      </c>
+      <c r="AA108" s="39">
+        <f>Z108/T108</f>
+        <v>1.5921724476192802E-2</v>
+      </c>
+      <c r="AB108" s="73">
+        <v>3975.7</v>
+      </c>
+      <c r="AC108" s="73"/>
+      <c r="AD108" s="73"/>
+      <c r="AE108" s="39"/>
+      <c r="AF108" s="74"/>
+      <c r="AG108" s="74"/>
+      <c r="AH108" s="75"/>
+      <c r="AI108" s="75">
+        <f t="shared" si="71"/>
+        <v>0</v>
+      </c>
+      <c r="AJ108" s="87"/>
+      <c r="AK108" s="87"/>
+      <c r="AL108" s="87"/>
+      <c r="AM108" s="88"/>
+      <c r="AN108" s="88"/>
+      <c r="AO108" s="88"/>
+      <c r="AP108" s="89">
+        <f t="shared" si="72"/>
+        <v>0</v>
+      </c>
+      <c r="AQ108" s="87">
+        <f t="shared" si="73"/>
+        <v>0</v>
+      </c>
+      <c r="AR108" s="87">
+        <f t="shared" si="74"/>
+        <v>0</v>
+      </c>
+      <c r="AS108" s="87"/>
+      <c r="AT108" s="87"/>
+      <c r="AU108" s="87"/>
+      <c r="AV108" s="87"/>
+      <c r="AW108" s="87"/>
+      <c r="AX108" s="87"/>
+      <c r="AY108" s="87"/>
+      <c r="AZ108" s="90"/>
+      <c r="BB108" s="92">
+        <f>IF(AND(AB108="",AC108=""),T108,IF(AC108="",AB108,AC108))</f>
+        <v>3975.7</v>
+      </c>
+      <c r="BC108" s="92">
+        <f>+X108</f>
+        <v>3912.4</v>
+      </c>
+      <c r="BD108" s="92"/>
+      <c r="BE108" s="92">
+        <f t="shared" si="75"/>
+        <v>63.299999999999727</v>
+      </c>
+      <c r="BF108" s="39">
+        <f t="shared" si="76"/>
+        <v>1.5921724476192802E-2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A109" s="53">
+        <f>IF(ISBLANK(F109),"",COUNTA($F$6:F109))</f>
+        <v>104</v>
+      </c>
+      <c r="B109" s="54" t="s">
+        <v>60</v>
+      </c>
+      <c r="C109" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="D109" s="55"/>
+      <c r="E109" s="56" t="s">
+        <v>65</v>
+      </c>
+      <c r="F109" s="57">
+        <v>46263</v>
+      </c>
+      <c r="G109" s="58" t="s">
+        <v>59</v>
+      </c>
+      <c r="H109" s="58">
+        <v>58</v>
+      </c>
+      <c r="I109" s="58">
+        <v>3</v>
+      </c>
+      <c r="J109" s="58" t="s">
+        <v>67</v>
+      </c>
+      <c r="K109" s="59">
+        <v>162011737</v>
+      </c>
+      <c r="L109" s="60">
+        <v>46263</v>
+      </c>
+      <c r="M109" s="61"/>
+      <c r="N109" s="62"/>
+      <c r="O109" s="63"/>
+      <c r="P109" s="63"/>
+      <c r="Q109" s="63"/>
+      <c r="R109" s="64"/>
+      <c r="S109" s="64"/>
+      <c r="T109" s="64">
+        <f t="shared" si="70"/>
+        <v>0</v>
+      </c>
+      <c r="U109" s="64"/>
+      <c r="V109" s="64"/>
+      <c r="W109" s="64"/>
+      <c r="X109" s="64"/>
+      <c r="Y109" s="64"/>
+      <c r="Z109" s="64">
+        <f>+T109-X109</f>
+        <v>0</v>
+      </c>
+      <c r="AA109" s="65" t="e">
+        <f>Z109/T109</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB97" s="66"/>
-      <c r="AC97" s="66"/>
-      <c r="AD97" s="66"/>
-      <c r="AE97" s="65"/>
-      <c r="AF97" s="67"/>
-      <c r="AG97" s="67"/>
-      <c r="AH97" s="68"/>
-      <c r="AI97" s="68">
+      <c r="AB109" s="66"/>
+      <c r="AC109" s="66"/>
+      <c r="AD109" s="66"/>
+      <c r="AE109" s="65"/>
+      <c r="AF109" s="67"/>
+      <c r="AG109" s="67"/>
+      <c r="AH109" s="68"/>
+      <c r="AI109" s="68">
+        <f t="shared" si="71"/>
+        <v>0</v>
+      </c>
+      <c r="AJ109" s="69"/>
+      <c r="AK109" s="69"/>
+      <c r="AL109" s="69"/>
+      <c r="AM109" s="70"/>
+      <c r="AN109" s="70"/>
+      <c r="AO109" s="70"/>
+      <c r="AP109" s="71">
+        <f t="shared" si="72"/>
+        <v>0</v>
+      </c>
+      <c r="AQ109" s="69">
+        <f t="shared" si="73"/>
+        <v>0</v>
+      </c>
+      <c r="AR109" s="69">
+        <f t="shared" si="74"/>
+        <v>0</v>
+      </c>
+      <c r="AS109" s="69"/>
+      <c r="AT109" s="69"/>
+      <c r="AU109" s="69"/>
+      <c r="AV109" s="69"/>
+      <c r="AW109" s="69"/>
+      <c r="AX109" s="69"/>
+      <c r="AY109" s="69"/>
+      <c r="AZ109" s="72"/>
+      <c r="BB109" s="45">
+        <f>IF(AND(AB109="",AC109=""),T109,IF(AC109="",AB109,AC109))</f>
+        <v>0</v>
+      </c>
+      <c r="BC109" s="45">
+        <f>+X109</f>
+        <v>0</v>
+      </c>
+      <c r="BD109" s="45"/>
+      <c r="BE109" s="45">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="BF109" s="39" t="e">
+        <f t="shared" si="76"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="110" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A110" s="53">
+        <f>IF(ISBLANK(F110),"",COUNTA($F$6:F110))</f>
+        <v>105</v>
+      </c>
+      <c r="B110" s="54" t="s">
+        <v>60</v>
+      </c>
+      <c r="C110" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="D110" s="55"/>
+      <c r="E110" s="56" t="s">
+        <v>66</v>
+      </c>
+      <c r="F110" s="57">
+        <v>46263</v>
+      </c>
+      <c r="G110" s="58" t="s">
+        <v>59</v>
+      </c>
+      <c r="H110" s="58">
+        <v>59</v>
+      </c>
+      <c r="I110" s="58">
+        <v>8</v>
+      </c>
+      <c r="J110" s="58" t="s">
+        <v>66</v>
+      </c>
+      <c r="K110" s="59">
+        <v>162003229</v>
+      </c>
+      <c r="L110" s="60">
+        <v>46263</v>
+      </c>
+      <c r="M110" s="61"/>
+      <c r="N110" s="62"/>
+      <c r="O110" s="63"/>
+      <c r="P110" s="63"/>
+      <c r="Q110" s="63"/>
+      <c r="R110" s="64"/>
+      <c r="S110" s="64"/>
+      <c r="T110" s="64">
+        <f t="shared" si="70"/>
+        <v>0</v>
+      </c>
+      <c r="U110" s="64"/>
+      <c r="V110" s="64"/>
+      <c r="W110" s="64"/>
+      <c r="X110" s="64"/>
+      <c r="Y110" s="64"/>
+      <c r="Z110" s="64">
+        <f>+T110-X110</f>
+        <v>0</v>
+      </c>
+      <c r="AA110" s="65" t="e">
+        <f>Z110/T110</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB110" s="66"/>
+      <c r="AC110" s="66"/>
+      <c r="AD110" s="66"/>
+      <c r="AE110" s="65"/>
+      <c r="AF110" s="67"/>
+      <c r="AG110" s="67"/>
+      <c r="AH110" s="68"/>
+      <c r="AI110" s="68">
+        <f t="shared" si="71"/>
+        <v>0</v>
+      </c>
+      <c r="AJ110" s="69"/>
+      <c r="AK110" s="69"/>
+      <c r="AL110" s="69"/>
+      <c r="AM110" s="70"/>
+      <c r="AN110" s="70"/>
+      <c r="AO110" s="70"/>
+      <c r="AP110" s="71">
+        <f t="shared" si="72"/>
+        <v>0</v>
+      </c>
+      <c r="AQ110" s="69">
+        <f t="shared" si="73"/>
+        <v>0</v>
+      </c>
+      <c r="AR110" s="69">
+        <f t="shared" si="74"/>
+        <v>0</v>
+      </c>
+      <c r="AS110" s="69"/>
+      <c r="AT110" s="69"/>
+      <c r="AU110" s="69"/>
+      <c r="AV110" s="69"/>
+      <c r="AW110" s="69"/>
+      <c r="AX110" s="69"/>
+      <c r="AY110" s="69"/>
+      <c r="AZ110" s="72"/>
+      <c r="BB110" s="45">
+        <f>IF(AND(AB110="",AC110=""),T110,IF(AC110="",AB110,AC110))</f>
+        <v>0</v>
+      </c>
+      <c r="BC110" s="45">
+        <f>+X110</f>
+        <v>0</v>
+      </c>
+      <c r="BD110" s="45"/>
+      <c r="BE110" s="45">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="BF110" s="39" t="e">
+        <f t="shared" si="76"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="111" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A111" s="53">
+        <f>IF(ISBLANK(F111),"",COUNTA($F$6:F111))</f>
+        <v>106</v>
+      </c>
+      <c r="B111" s="54" t="s">
+        <v>60</v>
+      </c>
+      <c r="C111" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="D111" s="55"/>
+      <c r="E111" s="56" t="s">
+        <v>65</v>
+      </c>
+      <c r="F111" s="57">
+        <v>46264</v>
+      </c>
+      <c r="G111" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="H111" s="58">
+        <v>59</v>
+      </c>
+      <c r="I111" s="58">
+        <v>1</v>
+      </c>
+      <c r="J111" s="58" t="s">
+        <v>67</v>
+      </c>
+      <c r="K111" s="59">
+        <v>162011739</v>
+      </c>
+      <c r="L111" s="60">
+        <v>46264</v>
+      </c>
+      <c r="M111" s="61"/>
+      <c r="N111" s="62"/>
+      <c r="O111" s="63"/>
+      <c r="P111" s="63"/>
+      <c r="Q111" s="63"/>
+      <c r="R111" s="64"/>
+      <c r="S111" s="64"/>
+      <c r="T111" s="64">
+        <f t="shared" si="70"/>
+        <v>0</v>
+      </c>
+      <c r="U111" s="64"/>
+      <c r="V111" s="64"/>
+      <c r="W111" s="64"/>
+      <c r="X111" s="64"/>
+      <c r="Y111" s="64"/>
+      <c r="Z111" s="64">
+        <f>+T111-X111</f>
+        <v>0</v>
+      </c>
+      <c r="AA111" s="65" t="e">
+        <f>Z111/T111</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB111" s="66"/>
+      <c r="AC111" s="66"/>
+      <c r="AD111" s="66"/>
+      <c r="AE111" s="65"/>
+      <c r="AF111" s="67"/>
+      <c r="AG111" s="67"/>
+      <c r="AH111" s="68"/>
+      <c r="AI111" s="68">
+        <f t="shared" si="71"/>
+        <v>0</v>
+      </c>
+      <c r="AJ111" s="69"/>
+      <c r="AK111" s="69"/>
+      <c r="AL111" s="69"/>
+      <c r="AM111" s="70"/>
+      <c r="AN111" s="70"/>
+      <c r="AO111" s="70"/>
+      <c r="AP111" s="71">
+        <f t="shared" si="72"/>
+        <v>0</v>
+      </c>
+      <c r="AQ111" s="69">
+        <f t="shared" si="73"/>
+        <v>0</v>
+      </c>
+      <c r="AR111" s="69">
+        <f t="shared" si="74"/>
+        <v>0</v>
+      </c>
+      <c r="AS111" s="69"/>
+      <c r="AT111" s="69"/>
+      <c r="AU111" s="69"/>
+      <c r="AV111" s="69"/>
+      <c r="AW111" s="69"/>
+      <c r="AX111" s="69"/>
+      <c r="AY111" s="69"/>
+      <c r="AZ111" s="72"/>
+      <c r="BB111" s="45">
+        <f>IF(AND(AB111="",AC111=""),T111,IF(AC111="",AB111,AC111))</f>
+        <v>0</v>
+      </c>
+      <c r="BC111" s="45">
+        <f>+X111</f>
+        <v>0</v>
+      </c>
+      <c r="BD111" s="45"/>
+      <c r="BE111" s="45">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="BF111" s="39" t="e">
+        <f t="shared" si="76"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="112" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A112" s="53">
+        <f>IF(ISBLANK(F112),"",COUNTA($F$6:F112))</f>
+        <v>107</v>
+      </c>
+      <c r="B112" s="54" t="s">
+        <v>60</v>
+      </c>
+      <c r="C112" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="D112" s="55"/>
+      <c r="E112" s="56" t="s">
+        <v>65</v>
+      </c>
+      <c r="F112" s="57">
+        <v>46264</v>
+      </c>
+      <c r="G112" s="58" t="s">
+        <v>59</v>
+      </c>
+      <c r="H112" s="58">
+        <v>59</v>
+      </c>
+      <c r="I112" s="58">
+        <v>3</v>
+      </c>
+      <c r="J112" s="58" t="s">
+        <v>67</v>
+      </c>
+      <c r="K112" s="59">
+        <v>162011741</v>
+      </c>
+      <c r="L112" s="60">
+        <v>46265</v>
+      </c>
+      <c r="M112" s="61"/>
+      <c r="N112" s="62"/>
+      <c r="O112" s="63"/>
+      <c r="P112" s="63"/>
+      <c r="Q112" s="63"/>
+      <c r="R112" s="64"/>
+      <c r="S112" s="64"/>
+      <c r="T112" s="64">
+        <f t="shared" si="70"/>
+        <v>0</v>
+      </c>
+      <c r="U112" s="64"/>
+      <c r="V112" s="64"/>
+      <c r="W112" s="64"/>
+      <c r="X112" s="64"/>
+      <c r="Y112" s="64"/>
+      <c r="Z112" s="64">
+        <f>+T112-X112</f>
+        <v>0</v>
+      </c>
+      <c r="AA112" s="65" t="e">
+        <f>Z112/T112</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB112" s="66"/>
+      <c r="AC112" s="66"/>
+      <c r="AD112" s="66"/>
+      <c r="AE112" s="65"/>
+      <c r="AF112" s="67"/>
+      <c r="AG112" s="67"/>
+      <c r="AH112" s="68"/>
+      <c r="AI112" s="68">
+        <f t="shared" si="71"/>
+        <v>0</v>
+      </c>
+      <c r="AJ112" s="69"/>
+      <c r="AK112" s="69"/>
+      <c r="AL112" s="69"/>
+      <c r="AM112" s="70"/>
+      <c r="AN112" s="70"/>
+      <c r="AO112" s="70"/>
+      <c r="AP112" s="71">
+        <f t="shared" si="72"/>
+        <v>0</v>
+      </c>
+      <c r="AQ112" s="69">
+        <f t="shared" si="73"/>
+        <v>0</v>
+      </c>
+      <c r="AR112" s="69">
+        <f t="shared" si="74"/>
+        <v>0</v>
+      </c>
+      <c r="AS112" s="69"/>
+      <c r="AT112" s="69"/>
+      <c r="AU112" s="69"/>
+      <c r="AV112" s="69"/>
+      <c r="AW112" s="69"/>
+      <c r="AX112" s="69"/>
+      <c r="AY112" s="69"/>
+      <c r="AZ112" s="72"/>
+      <c r="BB112" s="45">
+        <f>IF(AND(AB112="",AC112=""),T112,IF(AC112="",AB112,AC112))</f>
+        <v>0</v>
+      </c>
+      <c r="BC112" s="45">
+        <f>+X112</f>
+        <v>0</v>
+      </c>
+      <c r="BD112" s="45"/>
+      <c r="BE112" s="45">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="BF112" s="39" t="e">
+        <f t="shared" si="76"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="113" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A113" s="53">
+        <f>IF(ISBLANK(F113),"",COUNTA($F$6:F113))</f>
+        <v>108</v>
+      </c>
+      <c r="B113" s="54" t="s">
+        <v>60</v>
+      </c>
+      <c r="C113" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="D113" s="55"/>
+      <c r="E113" s="56" t="s">
+        <v>65</v>
+      </c>
+      <c r="F113" s="57">
+        <v>46265</v>
+      </c>
+      <c r="G113" s="58" t="s">
+        <v>59</v>
+      </c>
+      <c r="H113" s="58">
+        <v>58</v>
+      </c>
+      <c r="I113" s="58">
+        <v>1</v>
+      </c>
+      <c r="J113" s="58" t="s">
+        <v>67</v>
+      </c>
+      <c r="K113" s="59">
+        <v>162011743</v>
+      </c>
+      <c r="L113" s="60">
+        <v>46265</v>
+      </c>
+      <c r="M113" s="61"/>
+      <c r="N113" s="62"/>
+      <c r="O113" s="63"/>
+      <c r="P113" s="63"/>
+      <c r="Q113" s="63"/>
+      <c r="R113" s="64"/>
+      <c r="S113" s="64"/>
+      <c r="T113" s="64">
+        <f t="shared" si="63"/>
+        <v>0</v>
+      </c>
+      <c r="U113" s="64"/>
+      <c r="V113" s="64"/>
+      <c r="W113" s="64"/>
+      <c r="X113" s="64"/>
+      <c r="Y113" s="64"/>
+      <c r="Z113" s="64">
+        <f>+T113-X113</f>
+        <v>0</v>
+      </c>
+      <c r="AA113" s="65" t="e">
+        <f>Z113/T113</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB113" s="66"/>
+      <c r="AC113" s="66"/>
+      <c r="AD113" s="66"/>
+      <c r="AE113" s="65"/>
+      <c r="AF113" s="67"/>
+      <c r="AG113" s="67"/>
+      <c r="AH113" s="68"/>
+      <c r="AI113" s="68">
         <f t="shared" si="64"/>
         <v>0</v>
       </c>
-      <c r="AJ97" s="69"/>
-      <c r="AK97" s="69"/>
-      <c r="AL97" s="69"/>
-      <c r="AM97" s="70"/>
-      <c r="AN97" s="70"/>
-      <c r="AO97" s="70"/>
-      <c r="AP97" s="71">
+      <c r="AJ113" s="69"/>
+      <c r="AK113" s="69"/>
+      <c r="AL113" s="69"/>
+      <c r="AM113" s="70"/>
+      <c r="AN113" s="70"/>
+      <c r="AO113" s="70"/>
+      <c r="AP113" s="71">
         <f t="shared" si="65"/>
         <v>0</v>
       </c>
-      <c r="AQ97" s="69">
+      <c r="AQ113" s="69">
         <f t="shared" si="66"/>
         <v>0</v>
       </c>
-      <c r="AR97" s="69">
+      <c r="AR113" s="69">
         <f t="shared" si="67"/>
         <v>0</v>
       </c>
-      <c r="AS97" s="69"/>
-      <c r="AT97" s="69"/>
-      <c r="AU97" s="69"/>
-      <c r="AV97" s="69"/>
-      <c r="AW97" s="69"/>
-      <c r="AX97" s="69"/>
-      <c r="AY97" s="69"/>
-      <c r="AZ97" s="72"/>
-      <c r="BB97" s="45">
-        <f>IF(AND(AB97="",AC97=""),T97,IF(AC97="",AB97,AC97))</f>
-        <v>0</v>
-      </c>
-      <c r="BC97" s="45">
-        <f>+X97</f>
-        <v>0</v>
-      </c>
-      <c r="BD97" s="45"/>
-      <c r="BE97" s="45">
+      <c r="AS113" s="69"/>
+      <c r="AT113" s="69"/>
+      <c r="AU113" s="69"/>
+      <c r="AV113" s="69"/>
+      <c r="AW113" s="69"/>
+      <c r="AX113" s="69"/>
+      <c r="AY113" s="69"/>
+      <c r="AZ113" s="72"/>
+      <c r="BB113" s="45">
+        <f>IF(AND(AB113="",AC113=""),T113,IF(AC113="",AB113,AC113))</f>
+        <v>0</v>
+      </c>
+      <c r="BC113" s="45">
+        <f>+X113</f>
+        <v>0</v>
+      </c>
+      <c r="BD113" s="45"/>
+      <c r="BE113" s="45">
         <f t="shared" si="68"/>
         <v>0</v>
       </c>
-      <c r="BF97" s="39" t="e">
+      <c r="BF113" s="39" t="e">
         <f t="shared" si="69"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="98" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A98" s="53">
-        <f>IF(ISBLANK(F98),"",COUNTA($F$6:F98))</f>
-        <v>93</v>
-      </c>
-      <c r="B98" s="54" t="s">
+    <row r="114" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A114" s="53">
+        <f>IF(ISBLANK(F114),"",COUNTA($F$6:F114))</f>
+        <v>109</v>
+      </c>
+      <c r="B114" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="C98" s="54" t="s">
+      <c r="C114" s="54" t="s">
         <v>61</v>
       </c>
-      <c r="D98" s="55"/>
-      <c r="E98" s="56" t="s">
+      <c r="D114" s="55"/>
+      <c r="E114" s="56" t="s">
         <v>65</v>
       </c>
-      <c r="F98" s="57">
-        <v>46259</v>
-      </c>
-      <c r="G98" s="58" t="s">
+      <c r="F114" s="57">
+        <v>46265</v>
+      </c>
+      <c r="G114" s="58" t="s">
         <v>59</v>
       </c>
-      <c r="H98" s="58">
+      <c r="H114" s="58">
         <v>58</v>
       </c>
-      <c r="I98" s="58">
-        <v>3</v>
-      </c>
-      <c r="J98" s="58" t="s">
+      <c r="I114" s="58">
+        <v>2</v>
+      </c>
+      <c r="J114" s="58" t="s">
         <v>67</v>
       </c>
-      <c r="K98" s="59">
-        <v>162011729</v>
-      </c>
-      <c r="L98" s="60">
-        <v>46259</v>
-      </c>
-      <c r="M98" s="61"/>
-      <c r="N98" s="62"/>
-      <c r="O98" s="63"/>
-      <c r="P98" s="63"/>
-      <c r="Q98" s="63"/>
-      <c r="R98" s="64"/>
-      <c r="S98" s="64"/>
-      <c r="T98" s="64">
+      <c r="K114" s="59">
+        <v>162011744</v>
+      </c>
+      <c r="L114" s="60">
+        <v>46266</v>
+      </c>
+      <c r="M114" s="61"/>
+      <c r="N114" s="62"/>
+      <c r="O114" s="63"/>
+      <c r="P114" s="63"/>
+      <c r="Q114" s="63"/>
+      <c r="R114" s="64"/>
+      <c r="S114" s="64"/>
+      <c r="T114" s="64">
         <f t="shared" si="63"/>
         <v>0</v>
       </c>
-      <c r="U98" s="64"/>
-      <c r="V98" s="64"/>
-      <c r="W98" s="64"/>
-      <c r="X98" s="64"/>
-      <c r="Y98" s="64"/>
-      <c r="Z98" s="64">
-        <f>+T98-X98</f>
-        <v>0</v>
-      </c>
-      <c r="AA98" s="65" t="e">
-        <f>Z98/T98</f>
+      <c r="U114" s="64"/>
+      <c r="V114" s="64"/>
+      <c r="W114" s="64"/>
+      <c r="X114" s="64"/>
+      <c r="Y114" s="64"/>
+      <c r="Z114" s="64">
+        <f>+T114-X114</f>
+        <v>0</v>
+      </c>
+      <c r="AA114" s="65" t="e">
+        <f>Z114/T114</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB98" s="66"/>
-      <c r="AC98" s="66"/>
-      <c r="AD98" s="66"/>
-      <c r="AE98" s="65"/>
-      <c r="AF98" s="67"/>
-      <c r="AG98" s="67"/>
-      <c r="AH98" s="68"/>
-      <c r="AI98" s="68">
+      <c r="AB114" s="66"/>
+      <c r="AC114" s="66"/>
+      <c r="AD114" s="66"/>
+      <c r="AE114" s="65"/>
+      <c r="AF114" s="67"/>
+      <c r="AG114" s="67"/>
+      <c r="AH114" s="68"/>
+      <c r="AI114" s="68">
         <f t="shared" si="64"/>
         <v>0</v>
       </c>
-      <c r="AJ98" s="69"/>
-      <c r="AK98" s="69"/>
-      <c r="AL98" s="69"/>
-      <c r="AM98" s="70"/>
-      <c r="AN98" s="70"/>
-      <c r="AO98" s="70"/>
-      <c r="AP98" s="71">
+      <c r="AJ114" s="69"/>
+      <c r="AK114" s="69"/>
+      <c r="AL114" s="69"/>
+      <c r="AM114" s="70"/>
+      <c r="AN114" s="70"/>
+      <c r="AO114" s="70"/>
+      <c r="AP114" s="71">
         <f t="shared" si="65"/>
         <v>0</v>
       </c>
-      <c r="AQ98" s="69">
+      <c r="AQ114" s="69">
         <f t="shared" si="66"/>
         <v>0</v>
       </c>
-      <c r="AR98" s="69">
+      <c r="AR114" s="69">
         <f t="shared" si="67"/>
         <v>0</v>
       </c>
-      <c r="AS98" s="69"/>
-      <c r="AT98" s="69"/>
-      <c r="AU98" s="69"/>
-      <c r="AV98" s="69"/>
-      <c r="AW98" s="69"/>
-      <c r="AX98" s="69"/>
-      <c r="AY98" s="69"/>
-      <c r="AZ98" s="72"/>
-      <c r="BB98" s="45">
-        <f>IF(AND(AB98="",AC98=""),T98,IF(AC98="",AB98,AC98))</f>
-        <v>0</v>
-      </c>
-      <c r="BC98" s="45">
-        <f>+X98</f>
-        <v>0</v>
-      </c>
-      <c r="BD98" s="45"/>
-      <c r="BE98" s="45">
+      <c r="AS114" s="69"/>
+      <c r="AT114" s="69"/>
+      <c r="AU114" s="69"/>
+      <c r="AV114" s="69"/>
+      <c r="AW114" s="69"/>
+      <c r="AX114" s="69"/>
+      <c r="AY114" s="69"/>
+      <c r="AZ114" s="72"/>
+      <c r="BB114" s="45">
+        <f>IF(AND(AB114="",AC114=""),T114,IF(AC114="",AB114,AC114))</f>
+        <v>0</v>
+      </c>
+      <c r="BC114" s="45">
+        <f>+X114</f>
+        <v>0</v>
+      </c>
+      <c r="BD114" s="45"/>
+      <c r="BE114" s="45">
         <f t="shared" si="68"/>
         <v>0</v>
       </c>
-      <c r="BF98" s="39" t="e">
+      <c r="BF114" s="39" t="e">
         <f t="shared" si="69"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="99" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A99" s="53">
-        <f>IF(ISBLANK(F99),"",COUNTA($F$6:F99))</f>
-        <v>94</v>
-      </c>
-      <c r="B99" s="54" t="s">
+    <row r="115" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A115" s="21" t="str">
+        <f>IF(ISBLANK(F115),"",COUNTA($F$6:F115))</f>
+        <v/>
+      </c>
+      <c r="B115" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="C99" s="54" t="s">
+      <c r="C115" s="37" t="s">
         <v>61</v>
       </c>
-      <c r="D99" s="55"/>
-      <c r="E99" s="56" t="s">
-        <v>66</v>
-      </c>
-      <c r="F99" s="57">
-        <v>46259</v>
-      </c>
-      <c r="G99" s="58" t="s">
-        <v>59</v>
-      </c>
-      <c r="H99" s="58">
-        <v>59</v>
-      </c>
-      <c r="I99" s="58">
-        <v>0</v>
-      </c>
-      <c r="J99" s="58" t="s">
-        <v>66</v>
-      </c>
-      <c r="K99" s="59">
-        <v>162003217</v>
-      </c>
-      <c r="L99" s="60">
-        <v>46259</v>
-      </c>
-      <c r="M99" s="61"/>
-      <c r="N99" s="62"/>
-      <c r="O99" s="63"/>
-      <c r="P99" s="63"/>
-      <c r="Q99" s="63"/>
-      <c r="R99" s="64"/>
-      <c r="S99" s="64"/>
-      <c r="T99" s="64">
-        <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="U99" s="64"/>
-      <c r="V99" s="64"/>
-      <c r="W99" s="64"/>
-      <c r="X99" s="64"/>
-      <c r="Y99" s="64"/>
-      <c r="Z99" s="64">
-        <f>+T99-X99</f>
-        <v>0</v>
-      </c>
-      <c r="AA99" s="65" t="e">
-        <f>Z99/T99</f>
+      <c r="D115" s="22"/>
+      <c r="E115" s="23"/>
+      <c r="F115" s="36"/>
+      <c r="G115" s="24"/>
+      <c r="H115" s="24"/>
+      <c r="I115" s="24"/>
+      <c r="J115" s="24"/>
+      <c r="K115" s="25"/>
+      <c r="L115" s="26"/>
+      <c r="M115" s="38"/>
+      <c r="N115" s="52"/>
+      <c r="O115" s="27"/>
+      <c r="P115" s="27"/>
+      <c r="Q115" s="27"/>
+      <c r="R115" s="28"/>
+      <c r="S115" s="28"/>
+      <c r="T115" s="46">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
+      <c r="U115" s="28"/>
+      <c r="V115" s="28"/>
+      <c r="W115" s="28"/>
+      <c r="X115" s="28"/>
+      <c r="Y115" s="28"/>
+      <c r="Z115" s="28">
+        <f>+T115-X115</f>
+        <v>0</v>
+      </c>
+      <c r="AA115" s="29" t="e">
+        <f>Z115/T115</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB99" s="66"/>
-      <c r="AC99" s="66"/>
-      <c r="AD99" s="66"/>
-      <c r="AE99" s="65"/>
-      <c r="AF99" s="67"/>
-      <c r="AG99" s="67"/>
-      <c r="AH99" s="68"/>
-      <c r="AI99" s="68">
-        <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="AJ99" s="69"/>
-      <c r="AK99" s="69"/>
-      <c r="AL99" s="69"/>
-      <c r="AM99" s="70"/>
-      <c r="AN99" s="70"/>
-      <c r="AO99" s="70"/>
-      <c r="AP99" s="71">
-        <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AQ99" s="69">
-        <f t="shared" si="66"/>
-        <v>0</v>
-      </c>
-      <c r="AR99" s="69">
-        <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AS99" s="69"/>
-      <c r="AT99" s="69"/>
-      <c r="AU99" s="69"/>
-      <c r="AV99" s="69"/>
-      <c r="AW99" s="69"/>
-      <c r="AX99" s="69"/>
-      <c r="AY99" s="69"/>
-      <c r="AZ99" s="72"/>
-      <c r="BB99" s="45">
-        <f>IF(AND(AB99="",AC99=""),T99,IF(AC99="",AB99,AC99))</f>
-        <v>0</v>
-      </c>
-      <c r="BC99" s="45">
-        <f>+X99</f>
-        <v>0</v>
-      </c>
-      <c r="BD99" s="45"/>
-      <c r="BE99" s="45">
-        <f t="shared" si="68"/>
-        <v>0</v>
-      </c>
-      <c r="BF99" s="39" t="e">
-        <f t="shared" si="69"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="100" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="53">
-        <f>IF(ISBLANK(F100),"",COUNTA($F$6:F100))</f>
-        <v>95</v>
-      </c>
-      <c r="B100" s="54" t="s">
-        <v>60</v>
-      </c>
-      <c r="C100" s="54" t="s">
-        <v>61</v>
-      </c>
-      <c r="D100" s="55"/>
-      <c r="E100" s="56" t="s">
-        <v>63</v>
-      </c>
-      <c r="F100" s="57">
-        <v>46260</v>
-      </c>
-      <c r="G100" s="58" t="s">
-        <v>59</v>
-      </c>
-      <c r="H100" s="58">
-        <v>58</v>
-      </c>
-      <c r="I100" s="58">
-        <v>1</v>
-      </c>
-      <c r="J100" s="58" t="s">
-        <v>63</v>
-      </c>
-      <c r="K100" s="59">
-        <v>162006472</v>
-      </c>
-      <c r="L100" s="60">
-        <v>46260</v>
-      </c>
-      <c r="M100" s="61"/>
-      <c r="N100" s="62"/>
-      <c r="O100" s="63"/>
-      <c r="P100" s="63"/>
-      <c r="Q100" s="63"/>
-      <c r="R100" s="64"/>
-      <c r="S100" s="64"/>
-      <c r="T100" s="64">
-        <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="U100" s="64"/>
-      <c r="V100" s="64"/>
-      <c r="W100" s="64"/>
-      <c r="X100" s="64"/>
-      <c r="Y100" s="64"/>
-      <c r="Z100" s="64">
-        <f>+T100-X100</f>
-        <v>0</v>
-      </c>
-      <c r="AA100" s="65" t="e">
-        <f>Z100/T100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB100" s="66"/>
-      <c r="AC100" s="66"/>
-      <c r="AD100" s="66"/>
-      <c r="AE100" s="65"/>
-      <c r="AF100" s="67"/>
-      <c r="AG100" s="67"/>
-      <c r="AH100" s="68"/>
-      <c r="AI100" s="68">
-        <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="AJ100" s="69"/>
-      <c r="AK100" s="69"/>
-      <c r="AL100" s="69"/>
-      <c r="AM100" s="70"/>
-      <c r="AN100" s="70"/>
-      <c r="AO100" s="70"/>
-      <c r="AP100" s="71">
-        <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AQ100" s="69">
-        <f t="shared" si="66"/>
-        <v>0</v>
-      </c>
-      <c r="AR100" s="69">
-        <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AS100" s="69"/>
-      <c r="AT100" s="69"/>
-      <c r="AU100" s="69"/>
-      <c r="AV100" s="69"/>
-      <c r="AW100" s="69"/>
-      <c r="AX100" s="69"/>
-      <c r="AY100" s="69"/>
-      <c r="AZ100" s="72"/>
-      <c r="BB100" s="45">
-        <f>IF(AND(AB100="",AC100=""),T100,IF(AC100="",AB100,AC100))</f>
-        <v>0</v>
-      </c>
-      <c r="BC100" s="45">
-        <f>+X100</f>
-        <v>0</v>
-      </c>
-      <c r="BD100" s="45"/>
-      <c r="BE100" s="45">
-        <f t="shared" si="68"/>
-        <v>0</v>
-      </c>
-      <c r="BF100" s="39" t="e">
-        <f t="shared" si="69"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="101" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="53">
-        <f>IF(ISBLANK(F101),"",COUNTA($F$6:F101))</f>
-        <v>96</v>
-      </c>
-      <c r="B101" s="54" t="s">
-        <v>60</v>
-      </c>
-      <c r="C101" s="54" t="s">
-        <v>61</v>
-      </c>
-      <c r="D101" s="55"/>
-      <c r="E101" s="56" t="s">
-        <v>66</v>
-      </c>
-      <c r="F101" s="57">
-        <v>46260</v>
-      </c>
-      <c r="G101" s="58" t="s">
-        <v>59</v>
-      </c>
-      <c r="H101" s="58">
-        <v>58</v>
-      </c>
-      <c r="I101" s="58">
-        <v>1</v>
-      </c>
-      <c r="J101" s="58" t="s">
-        <v>66</v>
-      </c>
-      <c r="K101" s="59">
-        <v>162003219</v>
-      </c>
-      <c r="L101" s="60">
-        <v>46260</v>
-      </c>
-      <c r="M101" s="61"/>
-      <c r="N101" s="62"/>
-      <c r="O101" s="63"/>
-      <c r="P101" s="63"/>
-      <c r="Q101" s="63"/>
-      <c r="R101" s="64"/>
-      <c r="S101" s="64"/>
-      <c r="T101" s="64">
-        <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="U101" s="64"/>
-      <c r="V101" s="64"/>
-      <c r="W101" s="64"/>
-      <c r="X101" s="64"/>
-      <c r="Y101" s="64"/>
-      <c r="Z101" s="64">
-        <f>+T101-X101</f>
-        <v>0</v>
-      </c>
-      <c r="AA101" s="65" t="e">
-        <f>Z101/T101</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB101" s="66"/>
-      <c r="AC101" s="66"/>
-      <c r="AD101" s="66"/>
-      <c r="AE101" s="65"/>
-      <c r="AF101" s="67"/>
-      <c r="AG101" s="67"/>
-      <c r="AH101" s="68"/>
-      <c r="AI101" s="68">
-        <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="AJ101" s="69"/>
-      <c r="AK101" s="69"/>
-      <c r="AL101" s="69"/>
-      <c r="AM101" s="70"/>
-      <c r="AN101" s="70"/>
-      <c r="AO101" s="70"/>
-      <c r="AP101" s="71">
-        <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AQ101" s="69">
-        <f t="shared" si="66"/>
-        <v>0</v>
-      </c>
-      <c r="AR101" s="69">
-        <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AS101" s="69"/>
-      <c r="AT101" s="69"/>
-      <c r="AU101" s="69"/>
-      <c r="AV101" s="69"/>
-      <c r="AW101" s="69"/>
-      <c r="AX101" s="69"/>
-      <c r="AY101" s="69"/>
-      <c r="AZ101" s="72"/>
-      <c r="BB101" s="45">
-        <f>IF(AND(AB101="",AC101=""),T101,IF(AC101="",AB101,AC101))</f>
-        <v>0</v>
-      </c>
-      <c r="BC101" s="45">
-        <f>+X101</f>
-        <v>0</v>
-      </c>
-      <c r="BD101" s="45"/>
-      <c r="BE101" s="45">
-        <f t="shared" si="68"/>
-        <v>0</v>
-      </c>
-      <c r="BF101" s="39" t="e">
-        <f t="shared" si="69"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="102" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A102" s="53">
-        <f>IF(ISBLANK(F102),"",COUNTA($F$6:F102))</f>
-        <v>97</v>
-      </c>
-      <c r="B102" s="54" t="s">
-        <v>60</v>
-      </c>
-      <c r="C102" s="54" t="s">
-        <v>61</v>
-      </c>
-      <c r="D102" s="55"/>
-      <c r="E102" s="56" t="s">
-        <v>65</v>
-      </c>
-      <c r="F102" s="57">
-        <v>46260</v>
-      </c>
-      <c r="G102" s="58" t="s">
-        <v>59</v>
-      </c>
-      <c r="H102" s="58">
-        <v>58</v>
-      </c>
-      <c r="I102" s="58">
-        <v>2</v>
-      </c>
-      <c r="J102" s="58" t="s">
-        <v>67</v>
-      </c>
-      <c r="K102" s="59">
-        <v>162011731</v>
-      </c>
-      <c r="L102" s="60">
-        <v>46260</v>
-      </c>
-      <c r="M102" s="61"/>
-      <c r="N102" s="62"/>
-      <c r="O102" s="63"/>
-      <c r="P102" s="63"/>
-      <c r="Q102" s="63"/>
-      <c r="R102" s="64"/>
-      <c r="S102" s="64"/>
-      <c r="T102" s="64">
-        <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="U102" s="64"/>
-      <c r="V102" s="64"/>
-      <c r="W102" s="64"/>
-      <c r="X102" s="64"/>
-      <c r="Y102" s="64"/>
-      <c r="Z102" s="64">
-        <f>+T102-X102</f>
-        <v>0</v>
-      </c>
-      <c r="AA102" s="65" t="e">
-        <f>Z102/T102</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB102" s="66"/>
-      <c r="AC102" s="66"/>
-      <c r="AD102" s="66"/>
-      <c r="AE102" s="65"/>
-      <c r="AF102" s="67"/>
-      <c r="AG102" s="67"/>
-      <c r="AH102" s="68"/>
-      <c r="AI102" s="68">
-        <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="AJ102" s="69"/>
-      <c r="AK102" s="69"/>
-      <c r="AL102" s="69"/>
-      <c r="AM102" s="70"/>
-      <c r="AN102" s="70"/>
-      <c r="AO102" s="70"/>
-      <c r="AP102" s="71">
-        <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AQ102" s="69">
-        <f t="shared" si="66"/>
-        <v>0</v>
-      </c>
-      <c r="AR102" s="69">
-        <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AS102" s="69"/>
-      <c r="AT102" s="69"/>
-      <c r="AU102" s="69"/>
-      <c r="AV102" s="69"/>
-      <c r="AW102" s="69"/>
-      <c r="AX102" s="69"/>
-      <c r="AY102" s="69"/>
-      <c r="AZ102" s="72"/>
-      <c r="BB102" s="45">
-        <f>IF(AND(AB102="",AC102=""),T102,IF(AC102="",AB102,AC102))</f>
-        <v>0</v>
-      </c>
-      <c r="BC102" s="45">
-        <f>+X102</f>
-        <v>0</v>
-      </c>
-      <c r="BD102" s="45"/>
-      <c r="BE102" s="45">
-        <f t="shared" si="68"/>
-        <v>0</v>
-      </c>
-      <c r="BF102" s="39" t="e">
-        <f t="shared" si="69"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="103" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A103" s="21" t="str">
-        <f>IF(ISBLANK(F103),"",COUNTA($F$6:F103))</f>
-        <v/>
-      </c>
-      <c r="B103" s="37" t="s">
-        <v>60</v>
-      </c>
-      <c r="C103" s="37" t="s">
-        <v>61</v>
-      </c>
-      <c r="D103" s="22"/>
-      <c r="E103" s="23"/>
-      <c r="F103" s="36"/>
-      <c r="G103" s="24"/>
-      <c r="H103" s="24"/>
-      <c r="I103" s="24"/>
-      <c r="J103" s="24"/>
-      <c r="K103" s="25"/>
-      <c r="L103" s="26"/>
-      <c r="M103" s="38"/>
-      <c r="N103" s="52"/>
-      <c r="O103" s="27"/>
-      <c r="P103" s="27"/>
-      <c r="Q103" s="27"/>
-      <c r="R103" s="28"/>
-      <c r="S103" s="28"/>
-      <c r="T103" s="46">
-        <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="U103" s="28"/>
-      <c r="V103" s="28"/>
-      <c r="W103" s="28"/>
-      <c r="X103" s="28"/>
-      <c r="Y103" s="28"/>
-      <c r="Z103" s="28">
-        <f>+T103-X103</f>
-        <v>0</v>
-      </c>
-      <c r="AA103" s="29" t="e">
-        <f>Z103/T103</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB103" s="40"/>
-      <c r="AC103" s="40"/>
-      <c r="AD103" s="40"/>
-      <c r="AE103" s="29"/>
-      <c r="AF103" s="30"/>
-      <c r="AG103" s="30"/>
-      <c r="AH103" s="31"/>
-      <c r="AI103" s="31">
-        <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="AJ103" s="32"/>
-      <c r="AK103" s="32"/>
-      <c r="AL103" s="32"/>
-      <c r="AM103" s="33"/>
-      <c r="AN103" s="33"/>
-      <c r="AO103" s="33"/>
-      <c r="AP103" s="34">
-        <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AQ103" s="32">
-        <f t="shared" si="66"/>
-        <v>0</v>
-      </c>
-      <c r="AR103" s="32">
-        <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AS103" s="32"/>
-      <c r="AT103" s="32"/>
-      <c r="AU103" s="32"/>
-      <c r="AV103" s="32"/>
-      <c r="AW103" s="32"/>
-      <c r="AX103" s="32"/>
-      <c r="AY103" s="32"/>
-      <c r="AZ103" s="35"/>
-      <c r="BB103" s="45">
-        <f>IF(AND(AB103="",AC103=""),T103,IF(AC103="",AB103,AC103))</f>
-        <v>0</v>
-      </c>
-      <c r="BC103" s="45">
-        <f>+X103</f>
-        <v>0</v>
-      </c>
-      <c r="BD103" s="45"/>
-      <c r="BE103" s="45">
-        <f t="shared" si="68"/>
-        <v>0</v>
-      </c>
-      <c r="BF103" s="39" t="e">
-        <f t="shared" si="69"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="104" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A104" s="21" t="str">
-        <f>IF(ISBLANK(F104),"",COUNTA($F$6:F104))</f>
-        <v/>
-      </c>
-      <c r="B104" s="37" t="s">
-        <v>60</v>
-      </c>
-      <c r="C104" s="37" t="s">
-        <v>61</v>
-      </c>
-      <c r="D104" s="22"/>
-      <c r="E104" s="23"/>
-      <c r="F104" s="36"/>
-      <c r="G104" s="24"/>
-      <c r="H104" s="24"/>
-      <c r="I104" s="24"/>
-      <c r="J104" s="24"/>
-      <c r="K104" s="25"/>
-      <c r="L104" s="26"/>
-      <c r="M104" s="38"/>
-      <c r="N104" s="52"/>
-      <c r="O104" s="27"/>
-      <c r="P104" s="27"/>
-      <c r="Q104" s="27"/>
-      <c r="R104" s="28"/>
-      <c r="S104" s="28"/>
-      <c r="T104" s="46">
-        <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="U104" s="28"/>
-      <c r="V104" s="28"/>
-      <c r="W104" s="28"/>
-      <c r="X104" s="28"/>
-      <c r="Y104" s="28"/>
-      <c r="Z104" s="28">
-        <f>+T104-X104</f>
-        <v>0</v>
-      </c>
-      <c r="AA104" s="29" t="e">
-        <f>Z104/T104</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB104" s="40"/>
-      <c r="AC104" s="40"/>
-      <c r="AD104" s="40"/>
-      <c r="AE104" s="29"/>
-      <c r="AF104" s="30"/>
-      <c r="AG104" s="30"/>
-      <c r="AH104" s="31"/>
-      <c r="AI104" s="31">
-        <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="AJ104" s="32"/>
-      <c r="AK104" s="32"/>
-      <c r="AL104" s="32"/>
-      <c r="AM104" s="33"/>
-      <c r="AN104" s="33"/>
-      <c r="AO104" s="33"/>
-      <c r="AP104" s="34">
-        <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AQ104" s="32">
-        <f t="shared" si="66"/>
-        <v>0</v>
-      </c>
-      <c r="AR104" s="32">
-        <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AS104" s="32"/>
-      <c r="AT104" s="32"/>
-      <c r="AU104" s="32"/>
-      <c r="AV104" s="32"/>
-      <c r="AW104" s="32"/>
-      <c r="AX104" s="32"/>
-      <c r="AY104" s="32"/>
-      <c r="AZ104" s="35"/>
-      <c r="BB104" s="45">
-        <f>IF(AND(AB104="",AC104=""),T104,IF(AC104="",AB104,AC104))</f>
-        <v>0</v>
-      </c>
-      <c r="BC104" s="45">
-        <f>+X104</f>
-        <v>0</v>
-      </c>
-      <c r="BD104" s="45"/>
-      <c r="BE104" s="45">
-        <f t="shared" si="68"/>
-        <v>0</v>
-      </c>
-      <c r="BF104" s="39" t="e">
-        <f t="shared" si="69"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="105" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A105" s="21" t="str">
-        <f>IF(ISBLANK(F105),"",COUNTA($F$6:F105))</f>
-        <v/>
-      </c>
-      <c r="B105" s="37" t="s">
-        <v>60</v>
-      </c>
-      <c r="C105" s="37" t="s">
-        <v>61</v>
-      </c>
-      <c r="D105" s="22"/>
-      <c r="E105" s="23"/>
-      <c r="F105" s="36"/>
-      <c r="G105" s="24"/>
-      <c r="H105" s="24"/>
-      <c r="I105" s="24"/>
-      <c r="J105" s="24"/>
-      <c r="K105" s="25"/>
-      <c r="L105" s="26"/>
-      <c r="M105" s="38"/>
-      <c r="N105" s="52"/>
-      <c r="O105" s="27"/>
-      <c r="P105" s="27"/>
-      <c r="Q105" s="27"/>
-      <c r="R105" s="28"/>
-      <c r="S105" s="28"/>
-      <c r="T105" s="46">
-        <f t="shared" si="56"/>
-        <v>0</v>
-      </c>
-      <c r="U105" s="28"/>
-      <c r="V105" s="28"/>
-      <c r="W105" s="28"/>
-      <c r="X105" s="28"/>
-      <c r="Y105" s="28"/>
-      <c r="Z105" s="28">
-        <f>+T105-X105</f>
-        <v>0</v>
-      </c>
-      <c r="AA105" s="29" t="e">
-        <f>Z105/T105</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB105" s="40"/>
-      <c r="AC105" s="40"/>
-      <c r="AD105" s="40"/>
-      <c r="AE105" s="29"/>
-      <c r="AF105" s="30"/>
-      <c r="AG105" s="30"/>
-      <c r="AH105" s="31"/>
-      <c r="AI105" s="31">
+      <c r="AB115" s="40"/>
+      <c r="AC115" s="40"/>
+      <c r="AD115" s="40"/>
+      <c r="AE115" s="29"/>
+      <c r="AF115" s="30"/>
+      <c r="AG115" s="30"/>
+      <c r="AH115" s="31"/>
+      <c r="AI115" s="31">
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="AJ105" s="32"/>
-      <c r="AK105" s="32"/>
-      <c r="AL105" s="32"/>
-      <c r="AM105" s="33"/>
-      <c r="AN105" s="33"/>
-      <c r="AO105" s="33"/>
-      <c r="AP105" s="34">
+      <c r="AJ115" s="32"/>
+      <c r="AK115" s="32"/>
+      <c r="AL115" s="32"/>
+      <c r="AM115" s="33"/>
+      <c r="AN115" s="33"/>
+      <c r="AO115" s="33"/>
+      <c r="AP115" s="34">
         <f t="shared" si="58"/>
         <v>0</v>
       </c>
-      <c r="AQ105" s="32">
+      <c r="AQ115" s="32">
         <f t="shared" si="59"/>
         <v>0</v>
       </c>
-      <c r="AR105" s="32">
+      <c r="AR115" s="32">
         <f t="shared" si="60"/>
         <v>0</v>
       </c>
-      <c r="AS105" s="32"/>
-      <c r="AT105" s="32"/>
-      <c r="AU105" s="32"/>
-      <c r="AV105" s="32"/>
-      <c r="AW105" s="32"/>
-      <c r="AX105" s="32"/>
-      <c r="AY105" s="32"/>
-      <c r="AZ105" s="35"/>
-      <c r="BB105" s="45">
-        <f>IF(AND(AB105="",AC105=""),T105,IF(AC105="",AB105,AC105))</f>
-        <v>0</v>
-      </c>
-      <c r="BC105" s="45">
-        <f>+X105</f>
-        <v>0</v>
-      </c>
-      <c r="BD105" s="45"/>
-      <c r="BE105" s="45">
+      <c r="AS115" s="32"/>
+      <c r="AT115" s="32"/>
+      <c r="AU115" s="32"/>
+      <c r="AV115" s="32"/>
+      <c r="AW115" s="32"/>
+      <c r="AX115" s="32"/>
+      <c r="AY115" s="32"/>
+      <c r="AZ115" s="35"/>
+      <c r="BB115" s="45">
+        <f>IF(AND(AB115="",AC115=""),T115,IF(AC115="",AB115,AC115))</f>
+        <v>0</v>
+      </c>
+      <c r="BC115" s="45">
+        <f>+X115</f>
+        <v>0</v>
+      </c>
+      <c r="BD115" s="45"/>
+      <c r="BE115" s="45">
         <f t="shared" si="61"/>
         <v>0</v>
       </c>
-      <c r="BF105" s="39" t="e">
+      <c r="BF115" s="39" t="e">
         <f t="shared" si="62"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="106" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A106" s="21" t="str">
-        <f>IF(ISBLANK(F106),"",COUNTA($F$6:F106))</f>
+    <row r="116" spans="1:58" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A116" s="21" t="str">
+        <f>IF(ISBLANK(F116),"",COUNTA($F$6:F116))</f>
         <v/>
       </c>
-      <c r="B106" s="37" t="s">
+      <c r="B116" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="C106" s="37" t="s">
+      <c r="C116" s="37" t="s">
         <v>61</v>
       </c>
-      <c r="D106" s="22"/>
-      <c r="E106" s="23"/>
-      <c r="F106" s="36"/>
-      <c r="G106" s="24"/>
-      <c r="H106" s="24"/>
-      <c r="I106" s="24"/>
-      <c r="J106" s="24"/>
-      <c r="K106" s="25"/>
-      <c r="L106" s="26"/>
-      <c r="M106" s="38"/>
-      <c r="N106" s="52"/>
-      <c r="O106" s="27"/>
-      <c r="P106" s="27"/>
-      <c r="Q106" s="27"/>
-      <c r="R106" s="28"/>
-      <c r="S106" s="28"/>
-      <c r="T106" s="46">
+      <c r="D116" s="22"/>
+      <c r="E116" s="23"/>
+      <c r="F116" s="36"/>
+      <c r="G116" s="24"/>
+      <c r="H116" s="24"/>
+      <c r="I116" s="24"/>
+      <c r="J116" s="24"/>
+      <c r="K116" s="25"/>
+      <c r="L116" s="26"/>
+      <c r="M116" s="38"/>
+      <c r="N116" s="52"/>
+      <c r="O116" s="27"/>
+      <c r="P116" s="27"/>
+      <c r="Q116" s="27"/>
+      <c r="R116" s="28"/>
+      <c r="S116" s="28"/>
+      <c r="T116" s="46">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U106" s="28"/>
-      <c r="V106" s="28"/>
-      <c r="W106" s="28"/>
-      <c r="X106" s="28"/>
-      <c r="Y106" s="28"/>
-      <c r="Z106" s="28">
-        <f>+T106-X106</f>
-        <v>0</v>
-      </c>
-      <c r="AA106" s="29" t="e">
-        <f>Z106/T106</f>
+      <c r="U116" s="28"/>
+      <c r="V116" s="28"/>
+      <c r="W116" s="28"/>
+      <c r="X116" s="28"/>
+      <c r="Y116" s="28"/>
+      <c r="Z116" s="28">
+        <f>+T116-X116</f>
+        <v>0</v>
+      </c>
+      <c r="AA116" s="29" t="e">
+        <f>Z116/T116</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB106" s="40"/>
-      <c r="AC106" s="40"/>
-      <c r="AD106" s="40"/>
-      <c r="AE106" s="29"/>
-      <c r="AF106" s="30"/>
-      <c r="AG106" s="30"/>
-      <c r="AH106" s="31"/>
-      <c r="AI106" s="31">
+      <c r="AB116" s="40"/>
+      <c r="AC116" s="40"/>
+      <c r="AD116" s="40"/>
+      <c r="AE116" s="29"/>
+      <c r="AF116" s="30"/>
+      <c r="AG116" s="30"/>
+      <c r="AH116" s="31"/>
+      <c r="AI116" s="31">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AJ106" s="32"/>
-      <c r="AK106" s="32"/>
-      <c r="AL106" s="32"/>
-      <c r="AM106" s="33"/>
-      <c r="AN106" s="33"/>
-      <c r="AO106" s="33"/>
-      <c r="AP106" s="34">
+      <c r="AJ116" s="32"/>
+      <c r="AK116" s="32"/>
+      <c r="AL116" s="32"/>
+      <c r="AM116" s="33"/>
+      <c r="AN116" s="33"/>
+      <c r="AO116" s="33"/>
+      <c r="AP116" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AQ106" s="32">
+      <c r="AQ116" s="32">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AR106" s="32">
+      <c r="AR116" s="32">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AS106" s="32"/>
-      <c r="AT106" s="32"/>
-      <c r="AU106" s="32"/>
-      <c r="AV106" s="32"/>
-      <c r="AW106" s="32"/>
-      <c r="AX106" s="32"/>
-      <c r="AY106" s="32"/>
-      <c r="AZ106" s="35"/>
-      <c r="BB106" s="45">
-        <f>IF(AND(AB106="",AC106=""),T106,IF(AC106="",AB106,AC106))</f>
-        <v>0</v>
-      </c>
-      <c r="BC106" s="45">
-        <f>+X106</f>
-        <v>0</v>
-      </c>
-      <c r="BD106" s="45"/>
-      <c r="BE106" s="45">
+      <c r="AS116" s="32"/>
+      <c r="AT116" s="32"/>
+      <c r="AU116" s="32"/>
+      <c r="AV116" s="32"/>
+      <c r="AW116" s="32"/>
+      <c r="AX116" s="32"/>
+      <c r="AY116" s="32"/>
+      <c r="AZ116" s="35"/>
+      <c r="BB116" s="45">
+        <f>IF(AND(AB116="",AC116=""),T116,IF(AC116="",AB116,AC116))</f>
+        <v>0</v>
+      </c>
+      <c r="BC116" s="45">
+        <f>+X116</f>
+        <v>0</v>
+      </c>
+      <c r="BD116" s="45"/>
+      <c r="BE116" s="45">
         <f t="shared" si="54"/>
         <v>0</v>
       </c>
-      <c r="BF106" s="39" t="e">
+      <c r="BF116" s="39" t="e">
         <f t="shared" si="55"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="107" spans="1:58" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="9">
-        <f>+COUNT(A6:A106)</f>
-        <v>97</v>
-      </c>
-      <c r="B107" s="10">
-        <f>+COUNTIF(X6:X106,"&gt;0")</f>
-        <v>90</v>
-      </c>
-      <c r="C107" s="10"/>
-      <c r="D107" s="10"/>
-      <c r="E107" s="10"/>
-      <c r="F107" s="10"/>
-      <c r="G107" s="10"/>
-      <c r="H107" s="10"/>
-      <c r="I107" s="10"/>
-      <c r="J107" s="10"/>
-      <c r="K107" s="10"/>
-      <c r="L107" s="11"/>
-      <c r="M107" s="10"/>
-      <c r="N107" s="10"/>
-      <c r="O107" s="10"/>
-      <c r="P107" s="10"/>
-      <c r="Q107" s="10"/>
-      <c r="R107" s="12">
-        <f t="shared" ref="R107:Y107" si="70">SUM(R6:R106)</f>
-        <v>452094.11999999994</v>
-      </c>
-      <c r="S107" s="12">
-        <f t="shared" si="70"/>
-        <v>105500.11999999998</v>
-      </c>
-      <c r="T107" s="12">
-        <f t="shared" si="70"/>
-        <v>346594.00000000006</v>
-      </c>
-      <c r="U107" s="12">
-        <f t="shared" si="70"/>
-        <v>348508.70000000013</v>
-      </c>
-      <c r="V107" s="12">
-        <f t="shared" si="70"/>
-        <v>0</v>
-      </c>
-      <c r="W107" s="12">
-        <f t="shared" si="70"/>
-        <v>0</v>
-      </c>
-      <c r="X107" s="12">
-        <f t="shared" si="70"/>
-        <v>344720.86000000004</v>
-      </c>
-      <c r="Y107" s="12">
-        <f t="shared" si="70"/>
-        <v>0</v>
-      </c>
-      <c r="Z107" s="12">
-        <f>T107-X107</f>
-        <v>1873.140000000014</v>
-      </c>
-      <c r="AA107" s="13">
-        <f>Z107/T107</f>
-        <v>5.4044213113903115E-3</v>
-      </c>
-      <c r="AB107" s="41"/>
-      <c r="AC107" s="41"/>
-      <c r="AD107" s="41"/>
-      <c r="AE107" s="13"/>
-      <c r="AF107" s="12">
-        <f>SUM(AF6:AF106)</f>
-        <v>0</v>
-      </c>
-      <c r="AG107" s="12">
-        <f>SUM(AG6:AG106)</f>
-        <v>0</v>
-      </c>
-      <c r="AH107" s="12">
-        <f>SUM(AH6:AH106)</f>
-        <v>0</v>
-      </c>
-      <c r="AI107" s="12">
-        <f>SUM(AI6:AI106)</f>
-        <v>0</v>
-      </c>
-      <c r="AJ107" s="14"/>
-      <c r="AK107" s="14"/>
-      <c r="AL107" s="12"/>
-      <c r="AM107" s="15"/>
-      <c r="AN107" s="16"/>
-      <c r="AO107" s="16"/>
-      <c r="AP107" s="17"/>
-      <c r="AQ107" s="10">
-        <f>SUM(AQ6:AQ106)</f>
-        <v>0</v>
-      </c>
-      <c r="AR107" s="18">
-        <f>SUM(AR6:AR106)</f>
-        <v>0</v>
-      </c>
-      <c r="AS107" s="10">
-        <f>SUM(AS6:AS106)</f>
-        <v>0</v>
-      </c>
-      <c r="AT107" s="10">
-        <f>SUM(AT6:AT106)</f>
-        <v>0</v>
-      </c>
-      <c r="AU107" s="10">
-        <f>SUM(AU6:AU106)</f>
-        <v>0</v>
-      </c>
-      <c r="AV107" s="10">
-        <f>+SUM(AV6:AV106)</f>
-        <v>0</v>
-      </c>
-      <c r="AW107" s="10">
-        <f>SUM(AW6:AW106)</f>
-        <v>0</v>
-      </c>
-      <c r="AX107" s="10">
-        <f>SUM(AX6:AX106)</f>
-        <v>0</v>
-      </c>
-      <c r="AY107" s="10">
-        <f>SUM(AY6:AY106)</f>
-        <v>0</v>
-      </c>
-      <c r="AZ107" s="19"/>
-      <c r="BB107" s="42">
-        <f>SUM(BB6:BB106)</f>
-        <v>348231.65999999986</v>
-      </c>
-      <c r="BC107" s="42">
-        <f>SUM(BC6:BC106)</f>
-        <v>344720.86000000004</v>
-      </c>
-      <c r="BD107" s="42">
-        <f>SUM(BD6:BD106)</f>
-        <v>0</v>
-      </c>
-      <c r="BE107" s="42">
-        <f>SUM(BE6:BE106)</f>
-        <v>3510.7999999999975</v>
-      </c>
-      <c r="BF107" s="43">
+    <row r="117" spans="1:58" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="9">
+        <f>+COUNT(A6:A116)</f>
+        <v>109</v>
+      </c>
+      <c r="B117" s="10">
+        <f>+COUNTIF(X6:X116,"&gt;0")</f>
+        <v>102</v>
+      </c>
+      <c r="C117" s="10"/>
+      <c r="D117" s="10"/>
+      <c r="E117" s="10"/>
+      <c r="F117" s="10"/>
+      <c r="G117" s="10"/>
+      <c r="H117" s="10"/>
+      <c r="I117" s="10"/>
+      <c r="J117" s="10"/>
+      <c r="K117" s="10"/>
+      <c r="L117" s="11"/>
+      <c r="M117" s="10"/>
+      <c r="N117" s="10"/>
+      <c r="O117" s="10"/>
+      <c r="P117" s="10"/>
+      <c r="Q117" s="10"/>
+      <c r="R117" s="12">
+        <f t="shared" ref="R117:Y117" si="77">SUM(R6:R116)</f>
+        <v>512101.59</v>
+      </c>
+      <c r="S117" s="12">
+        <f t="shared" si="77"/>
+        <v>119450.98999999999</v>
+      </c>
+      <c r="T117" s="12">
+        <f t="shared" si="77"/>
+        <v>392650.60000000003</v>
+      </c>
+      <c r="U117" s="12">
+        <f t="shared" si="77"/>
+        <v>395068.10000000015</v>
+      </c>
+      <c r="V117" s="12">
+        <f t="shared" si="77"/>
+        <v>0</v>
+      </c>
+      <c r="W117" s="12">
+        <f t="shared" si="77"/>
+        <v>0</v>
+      </c>
+      <c r="X117" s="12">
+        <f t="shared" si="77"/>
+        <v>391291.65000000014</v>
+      </c>
+      <c r="Y117" s="12">
+        <f t="shared" si="77"/>
+        <v>0</v>
+      </c>
+      <c r="Z117" s="12">
+        <f>T117-X117</f>
+        <v>1358.9499999998952</v>
+      </c>
+      <c r="AA117" s="13">
+        <f>Z117/T117</f>
+        <v>3.4609650411839307E-3</v>
+      </c>
+      <c r="AB117" s="41"/>
+      <c r="AC117" s="41"/>
+      <c r="AD117" s="41"/>
+      <c r="AE117" s="13"/>
+      <c r="AF117" s="12">
+        <f>SUM(AF6:AF116)</f>
+        <v>0</v>
+      </c>
+      <c r="AG117" s="12">
+        <f>SUM(AG6:AG116)</f>
+        <v>0</v>
+      </c>
+      <c r="AH117" s="12">
+        <f>SUM(AH6:AH116)</f>
+        <v>0</v>
+      </c>
+      <c r="AI117" s="12">
+        <f>SUM(AI6:AI116)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ117" s="14"/>
+      <c r="AK117" s="14"/>
+      <c r="AL117" s="12"/>
+      <c r="AM117" s="15"/>
+      <c r="AN117" s="16"/>
+      <c r="AO117" s="16"/>
+      <c r="AP117" s="17"/>
+      <c r="AQ117" s="10">
+        <f>SUM(AQ6:AQ116)</f>
+        <v>0</v>
+      </c>
+      <c r="AR117" s="18">
+        <f>SUM(AR6:AR116)</f>
+        <v>0</v>
+      </c>
+      <c r="AS117" s="10">
+        <f>SUM(AS6:AS116)</f>
+        <v>0</v>
+      </c>
+      <c r="AT117" s="10">
+        <f>SUM(AT6:AT116)</f>
+        <v>0</v>
+      </c>
+      <c r="AU117" s="10">
+        <f>SUM(AU6:AU116)</f>
+        <v>0</v>
+      </c>
+      <c r="AV117" s="10">
+        <f>+SUM(AV6:AV116)</f>
+        <v>0</v>
+      </c>
+      <c r="AW117" s="10">
+        <f>SUM(AW6:AW116)</f>
+        <v>0</v>
+      </c>
+      <c r="AX117" s="10">
+        <f>SUM(AX6:AX116)</f>
+        <v>0</v>
+      </c>
+      <c r="AY117" s="10">
+        <f>SUM(AY6:AY116)</f>
+        <v>0</v>
+      </c>
+      <c r="AZ117" s="19"/>
+      <c r="BB117" s="42">
+        <f>SUM(BB6:BB116)</f>
+        <v>394345.07999999984</v>
+      </c>
+      <c r="BC117" s="42">
+        <f>SUM(BC6:BC116)</f>
+        <v>391291.65000000014</v>
+      </c>
+      <c r="BD117" s="42">
+        <f>SUM(BD6:BD116)</f>
+        <v>0</v>
+      </c>
+      <c r="BE117" s="42">
+        <f>SUM(BE6:BE116)</f>
+        <v>3053.4299999999967</v>
+      </c>
+      <c r="BF117" s="43">
         <f t="shared" si="55"/>
-        <v>1.0081794400888187E-2</v>
+        <v>7.7430406891344956E-3</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="K6:K12">
-    <cfRule type="duplicateValues" dxfId="88" priority="1052"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="1074"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K6:K12">
-    <cfRule type="duplicateValues" dxfId="87" priority="1053"/>
-    <cfRule type="duplicateValues" dxfId="86" priority="1054"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="1075"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="1076"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K106">
-    <cfRule type="duplicateValues" dxfId="85" priority="1055"/>
+  <conditionalFormatting sqref="K116">
+    <cfRule type="duplicateValues" dxfId="105" priority="1077"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K106">
-    <cfRule type="duplicateValues" dxfId="84" priority="1056"/>
-    <cfRule type="duplicateValues" dxfId="83" priority="1057"/>
+  <conditionalFormatting sqref="K116">
+    <cfRule type="duplicateValues" dxfId="104" priority="1078"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="1079"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K106 K5">
-    <cfRule type="duplicateValues" dxfId="82" priority="1058"/>
+  <conditionalFormatting sqref="K116 K5">
+    <cfRule type="duplicateValues" dxfId="102" priority="1080"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K106:K107 K5">
-    <cfRule type="duplicateValues" dxfId="81" priority="1060"/>
+  <conditionalFormatting sqref="K116:K117 K5">
+    <cfRule type="duplicateValues" dxfId="101" priority="1082"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K106:K107">
-    <cfRule type="duplicateValues" dxfId="80" priority="1062"/>
+  <conditionalFormatting sqref="K116:K117">
+    <cfRule type="duplicateValues" dxfId="100" priority="1084"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13:K14 K88">
-    <cfRule type="duplicateValues" dxfId="79" priority="1063"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="1085"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13:K14 K88">
-    <cfRule type="duplicateValues" dxfId="78" priority="1065"/>
-    <cfRule type="duplicateValues" dxfId="77" priority="1066"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="1087"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="1088"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K13:K14 K5 K88 K106:K107">
-    <cfRule type="duplicateValues" dxfId="76" priority="1069"/>
+  <conditionalFormatting sqref="K13:K14 K5 K88 K116:K117">
+    <cfRule type="duplicateValues" dxfId="96" priority="1091"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K88 K5:K14 K106:K107">
-    <cfRule type="duplicateValues" dxfId="75" priority="1072"/>
+  <conditionalFormatting sqref="K88 K5:K14 K116:K117">
+    <cfRule type="duplicateValues" dxfId="95" priority="1094"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K36 K15:K26">
-    <cfRule type="duplicateValues" dxfId="74" priority="1074"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="1096"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K36 K15:K26">
-    <cfRule type="duplicateValues" dxfId="73" priority="1076"/>
-    <cfRule type="duplicateValues" dxfId="72" priority="1077"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="1098"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="1099"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K15:K26">
-    <cfRule type="duplicateValues" dxfId="71" priority="1080"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="1102"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27:K35">
-    <cfRule type="duplicateValues" dxfId="70" priority="1081"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="1103"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27:K35">
-    <cfRule type="duplicateValues" dxfId="69" priority="1082"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="1083"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="1104"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="1105"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K5:K36 K88 K106:K107">
-    <cfRule type="duplicateValues" dxfId="67" priority="1084"/>
+  <conditionalFormatting sqref="K5:K36 K88 K116:K117">
+    <cfRule type="duplicateValues" dxfId="87" priority="1106"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K37:K54 K61:K64">
-    <cfRule type="duplicateValues" dxfId="66" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="96"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K37:K54 K61:K64">
-    <cfRule type="duplicateValues" dxfId="65" priority="75"/>
-    <cfRule type="duplicateValues" dxfId="64" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="97"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="98"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K37:K54">
-    <cfRule type="duplicateValues" dxfId="63" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="99"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K37:K54">
-    <cfRule type="duplicateValues" dxfId="62" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="100"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K37:K54">
-    <cfRule type="duplicateValues" dxfId="61" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="101"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6:K54 K61:K64 K88 K106:K107">
-    <cfRule type="duplicateValues" dxfId="60" priority="70"/>
+  <conditionalFormatting sqref="K6:K54 K61:K64 K88 K116:K117">
+    <cfRule type="duplicateValues" dxfId="80" priority="92"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K55:K60">
-    <cfRule type="duplicateValues" dxfId="59" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="83"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K55:K60">
-    <cfRule type="duplicateValues" dxfId="58" priority="62"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K55:K60">
-    <cfRule type="duplicateValues" dxfId="56" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="86"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K55:K60">
-    <cfRule type="duplicateValues" dxfId="55" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="87"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K55:K60">
-    <cfRule type="duplicateValues" dxfId="54" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="88"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K55:K60">
-    <cfRule type="duplicateValues" dxfId="53" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="82"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6:K64 K88 K106:K107">
-    <cfRule type="duplicateValues" dxfId="52" priority="59"/>
+  <conditionalFormatting sqref="K6:K64 K88 K116:K117">
+    <cfRule type="duplicateValues" dxfId="72" priority="81"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K65:K87">
-    <cfRule type="duplicateValues" dxfId="51" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K65:K87">
-    <cfRule type="duplicateValues" dxfId="50" priority="51"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="74"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K65:K87">
-    <cfRule type="duplicateValues" dxfId="48" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="75"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K65:K87">
-    <cfRule type="duplicateValues" dxfId="47" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K65:K87">
-    <cfRule type="duplicateValues" dxfId="46" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="77"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K65:K87">
-    <cfRule type="duplicateValues" dxfId="45" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K65:K87">
-    <cfRule type="duplicateValues" dxfId="44" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="70"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6:K88 K106:K107">
-    <cfRule type="duplicateValues" dxfId="43" priority="47"/>
+  <conditionalFormatting sqref="K6:K88 K116:K117">
+    <cfRule type="duplicateValues" dxfId="63" priority="69"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K5:K88 K106:K107">
-    <cfRule type="duplicateValues" dxfId="42" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="44"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="46"/>
+  <conditionalFormatting sqref="K5:K88 K116:K117">
+    <cfRule type="duplicateValues" dxfId="62" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5:K88">
-    <cfRule type="duplicateValues" dxfId="38" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="65"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K89:K94 K105">
-    <cfRule type="duplicateValues" dxfId="37" priority="30"/>
+  <conditionalFormatting sqref="K89:K94 K115">
+    <cfRule type="duplicateValues" dxfId="57" priority="52"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K89:K94 K105">
-    <cfRule type="duplicateValues" dxfId="36" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="32"/>
+  <conditionalFormatting sqref="K89:K94 K115">
+    <cfRule type="duplicateValues" dxfId="56" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="54"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K89:K94 K105">
-    <cfRule type="duplicateValues" dxfId="34" priority="33"/>
+  <conditionalFormatting sqref="K89:K94">
+    <cfRule type="duplicateValues" dxfId="54" priority="55"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K89:K94 K105">
-    <cfRule type="duplicateValues" dxfId="33" priority="34"/>
+  <conditionalFormatting sqref="K89:K94">
+    <cfRule type="duplicateValues" dxfId="53" priority="56"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K89:K94 K105">
-    <cfRule type="duplicateValues" dxfId="32" priority="35"/>
+  <conditionalFormatting sqref="K89:K94">
+    <cfRule type="duplicateValues" dxfId="52" priority="57"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K89:K94 K105">
-    <cfRule type="duplicateValues" dxfId="31" priority="36"/>
+  <conditionalFormatting sqref="K89:K94">
+    <cfRule type="duplicateValues" dxfId="51" priority="58"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K89:K94 K105">
-    <cfRule type="duplicateValues" dxfId="30" priority="37"/>
+  <conditionalFormatting sqref="K89:K94">
+    <cfRule type="duplicateValues" dxfId="50" priority="59"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K89:K94 K105">
-    <cfRule type="duplicateValues" dxfId="29" priority="38"/>
+  <conditionalFormatting sqref="K89:K94">
+    <cfRule type="duplicateValues" dxfId="49" priority="60"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K89:K94 K105">
-    <cfRule type="duplicateValues" dxfId="28" priority="29"/>
+  <conditionalFormatting sqref="K89:K94">
+    <cfRule type="duplicateValues" dxfId="48" priority="51"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K89:K94 K105">
-    <cfRule type="duplicateValues" dxfId="27" priority="28"/>
+  <conditionalFormatting sqref="K89:K94">
+    <cfRule type="duplicateValues" dxfId="47" priority="50"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K89:K94 K105">
+  <conditionalFormatting sqref="K89:K94">
+    <cfRule type="duplicateValues" dxfId="46" priority="49"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K89:K94 K115">
+    <cfRule type="duplicateValues" dxfId="45" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="48"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K5:K94 K115:K117">
+    <cfRule type="duplicateValues" dxfId="41" priority="44"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K95:K102 K113:K114">
+    <cfRule type="duplicateValues" dxfId="40" priority="32"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K95:K102 K113:K114">
+    <cfRule type="duplicateValues" dxfId="39" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K95:K102 K113:K114">
+    <cfRule type="duplicateValues" dxfId="37" priority="35"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K95:K102 K113:K114">
+    <cfRule type="duplicateValues" dxfId="36" priority="36"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K95:K102 K113:K114">
+    <cfRule type="duplicateValues" dxfId="35" priority="37"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K95:K102 K113:K114">
+    <cfRule type="duplicateValues" dxfId="34" priority="38"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K95:K102 K113:K114">
+    <cfRule type="duplicateValues" dxfId="33" priority="39"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K95:K102 K113:K114">
+    <cfRule type="duplicateValues" dxfId="32" priority="40"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K95:K102 K113:K114">
+    <cfRule type="duplicateValues" dxfId="31" priority="31"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K95:K102 K113:K114">
+    <cfRule type="duplicateValues" dxfId="30" priority="30"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K95:K102 K113:K114">
+    <cfRule type="duplicateValues" dxfId="29" priority="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K95:K102 K113:K114">
+    <cfRule type="duplicateValues" dxfId="28" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="26"/>
     <cfRule type="duplicateValues" dxfId="26" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="28"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K89:K94 K105">
-    <cfRule type="duplicateValues" dxfId="25" priority="23"/>
+  <conditionalFormatting sqref="K95:K102 K113:K114">
     <cfRule type="duplicateValues" dxfId="24" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="26"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K5:K94 K105:K107">
-    <cfRule type="duplicateValues" dxfId="21" priority="22"/>
+  <conditionalFormatting sqref="K5:K102 K113:K117">
+    <cfRule type="duplicateValues" dxfId="23" priority="23"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K95:K104">
-    <cfRule type="duplicateValues" dxfId="20" priority="10"/>
+  <conditionalFormatting sqref="K103:K112">
+    <cfRule type="duplicateValues" dxfId="22" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K95:K104">
-    <cfRule type="duplicateValues" dxfId="19" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="12"/>
+  <conditionalFormatting sqref="K103:K112">
+    <cfRule type="duplicateValues" dxfId="21" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K95:K104">
-    <cfRule type="duplicateValues" dxfId="17" priority="13"/>
+  <conditionalFormatting sqref="K103:K112">
+    <cfRule type="duplicateValues" dxfId="19" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K95:K104">
-    <cfRule type="duplicateValues" dxfId="16" priority="14"/>
+  <conditionalFormatting sqref="K103:K112">
+    <cfRule type="duplicateValues" dxfId="18" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K95:K104">
-    <cfRule type="duplicateValues" dxfId="15" priority="15"/>
+  <conditionalFormatting sqref="K103:K112">
+    <cfRule type="duplicateValues" dxfId="17" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K95:K104">
-    <cfRule type="duplicateValues" dxfId="14" priority="16"/>
+  <conditionalFormatting sqref="K103:K112">
+    <cfRule type="duplicateValues" dxfId="16" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K95:K104">
-    <cfRule type="duplicateValues" dxfId="13" priority="17"/>
+  <conditionalFormatting sqref="K103:K112">
+    <cfRule type="duplicateValues" dxfId="15" priority="18"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K95:K104">
-    <cfRule type="duplicateValues" dxfId="12" priority="18"/>
+  <conditionalFormatting sqref="K103:K112">
+    <cfRule type="duplicateValues" dxfId="14" priority="19"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K95:K104">
-    <cfRule type="duplicateValues" dxfId="11" priority="9"/>
+  <conditionalFormatting sqref="K103:K112">
+    <cfRule type="duplicateValues" dxfId="13" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K95:K104">
-    <cfRule type="duplicateValues" dxfId="10" priority="8"/>
+  <conditionalFormatting sqref="K103:K112">
+    <cfRule type="duplicateValues" dxfId="12" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K95:K104">
-    <cfRule type="duplicateValues" dxfId="9" priority="7"/>
+  <conditionalFormatting sqref="K103:K112">
+    <cfRule type="duplicateValues" dxfId="11" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K95:K104">
-    <cfRule type="duplicateValues" dxfId="8" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+  <conditionalFormatting sqref="K103:K112">
+    <cfRule type="duplicateValues" dxfId="10" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K95:K104">
-    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
+  <conditionalFormatting sqref="K103:K112">
+    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K5:K107">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+  <conditionalFormatting sqref="K103:K112">
+    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BB6:BB106">
-    <cfRule type="expression" dxfId="2" priority="1153">
+  <conditionalFormatting sqref="K5:K117">
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BB6:BB116">
+    <cfRule type="expression" dxfId="3" priority="1181">
       <formula>$AC6&lt;&gt;""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="1154">
+    <cfRule type="expression" dxfId="2" priority="1182">
       <formula>$AB6&lt;&gt;""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="1155">
+    <cfRule type="expression" dxfId="1" priority="1183">
       <formula>$T6&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
